--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -2822,10 +2822,10 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Omar Escamilla / omare815</t>
+          <t>Omar Escamilla / omare815 — ¿mismo lead que WhatsApp +52 1 81 3408 2672? (verificar con Joel)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>México (Monterrey, 2h de la frontera con Texas)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Gemelos — lateral y mediapunta</t>
+          <t>Gemelos Gabriel (lateral izquierdo, 1.82m) y Rafael (medio, 1.82m) — Club Dallas FC filial México, titulares, buen nivel según el padre</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -2850,27 +2850,27 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Tiene, falta pedirlo</t>
+          <t>Tienen vídeo del año pasado + uno actualizado en camino (semanas)</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí — edad, nivel y plazo (agosto 2027) confirmados por el padre</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Pedir el vídeo (de mayo 2026, ya lo tienen listo)</t>
+          <t>Enviar la respuesta preparada 2026-09-11 (honestidad sobre ubicación de Joel + cifra de colocados + pedir el vídeo que ya tienen + Calendly)</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09-10 (WhatsApp)</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Datos completos, solo falta el vídeo</t>
+          <t>Preguntó dónde está Joel y por universidades/contactos de coaches/ejemplos de colocados — señal de compra fuerte, no objeción. Ver embudo-ventas.md 'Caso real: ya cualificado, pero pregunta por prueba social'</t>
         </is>
       </c>
     </row>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -2825,7 +2825,7 @@
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Omar Escamilla / omare815 — ¿mismo lead que WhatsApp +52 1 81 3408 2672? (verificar con Joel)</t>
+          <t>Omar Escamilla / omare815 — CONFIRMADO mismo lead que WhatsApp +52 1 81 3408 2672 (Gabriel y Rafael)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Cualificado</t>
+          <t>Llamada agendada</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2860,17 +2860,17 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Enviar la respuesta preparada 2026-09-11 (honestidad sobre ubicación de Joel + cifra de colocados + pedir el vídeo que ya tienen + Calendly)</t>
+          <t>Llamada el 15/09/2026 a las 12:00 — preparar guion específico antes, y pedir el vídeo si no ha llegado</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10 (WhatsApp)</t>
+          <t>2026-09-14 (WhatsApp)</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Preguntó dónde está Joel y por universidades/contactos de coaches/ejemplos de colocados — señal de compra fuerte, no objeción. Ver embudo-ventas.md 'Caso real: ya cualificado, pero pregunta por prueba social'</t>
+          <t>Confirmó que le gustó la web. Preguntó país de origen de Joel (respondido: España). Llamada agendada vía Calendly para el 15/09 12:00. Pendiente: vídeo actualizado</t>
         </is>
       </c>
     </row>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +166,9 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1893,10 +1896,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="90" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Contacto de Brasil</t>
+          <t>Leonardo Uren / equipo (Brasil) — posible partner, no solo cliente</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1906,37 +1909,62 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Sin evaluar</t>
+          <t>N/A — colaboración institucional, no un grupo de jugadores</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Contacto personal de Joel, sin explorar todavía</t>
+          <t>Conversación real ya avanzada abril-julio 2026: exploraron modelo de colaboración Brasil-España (jugadores/equipos en ambas direcciones), con el padre de Joel involucrado. Se enfrió tras propuesta de llamada el 03/07/2026 sin respuesta</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Joel</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
+          <t>Contacto personal de Joel</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Leonardo Uren</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Sin email — conversación por WhatsApp</t>
+        </is>
+      </c>
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Sin evaluar</t>
+          <t>Listo para enviar (reactivación)</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>Joel decide si vale la pena explorarlo</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr"/>
+          <t>Enviar el mensaje de reactivación de la columna Cuerpo — pendiente de que Joel lo mande</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>N/A — mensaje de WhatsApp, no email</t>
+        </is>
+      </c>
+      <c r="L17" s="14" t="inlineStr">
+        <is>
+          <t>Hi Leonardo! Hope you and the team are doing well.
+It's been a while since we talked - a lot has happened on our side too. We've been growing our international side, and with Spain now World Cup champions there's a lot more interest from clubs/academies wanting to connect with Spanish football, so it feels like a good moment to pick this back up.
+I still think there's real potential in a Brazil-Spain connection - players/teams coming to train in Spain, and maybe the other way around too. Would you be up for reopening that conversation? My dad would join again as well. No need to tie it to a specific trip this time - happy to find 20-30 minutes whenever works for you guys.
+Let me know!</t>
+        </is>
+      </c>
       <c r="M17" s="13" t="inlineStr"/>
-      <c r="N17" s="13" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr"/>
+      <c r="N17" s="13" t="n">
+        <v>46206</v>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:O17"/>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -2873,7 +2873,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Llamada agendada</t>
+          <t>Llamada realizada</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2888,17 +2888,17 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Llamada el 15/09/2026 a las 12:00 — preparar guion específico antes, y pedir el vídeo si no ha llegado</t>
+          <t>Esperando 'okay' de la familia para mandar evaluación/propuesta. Seguimiento suave si no hay respuesta antes del viernes 19/09/2026 (fin de semana según Joel). Confirmar con Joel si ya tiene el vídeo para tenerlo listo antes de que llegue el okay</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14 (WhatsApp)</t>
+          <t>2026-09-15 (llamada)</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Confirmó que le gustó la web. Preguntó país de origen de Joel (respondido: España). Llamada agendada vía Calendly para el 15/09 12:00. Pendiente: vídeo actualizado</t>
+          <t>Llamada realizada 15/09/2026. Resultado: la familia lo va a valorar 'en los próximos días', Joel manda evaluación/propuesta cuando den el okay. Joel ya envió foto de precios por WhatsApp + mensaje de cierre de llamada. Pendiente: confirmar si ya tienen el vídeo en mano, y si se aclaró en la llamada si buscan la misma universidad para los dos gemelos o están abiertos a separarse.</t>
         </is>
       </c>
     </row>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -2493,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3221,6 +3221,58 @@
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Daniel (apellido/@ de Instagram pendiente de confirmar)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>17 (nacido sept. 2009)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>España (recién mudado desde EEUU, ciudad por confirmar)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Jugó MLS NEXT U17 el año pasado en EEUU (nivel alto) — posición por confirmar</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Cualificado</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>No pedido todavía</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Sí — nivel MLS NEXT es señal fuerte, falta confirmar posición y club actual</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Esperar respuesta a las 3 preguntas (posición / ubicación en España / club actual) — probablemente avanza rápido a Calendly, es un lead fuerte</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Pregunta genuina sobre 1º vs 2º de Bachillerato y elegibilidad NCAA — no se improvisó respuesta, se remitió a la evaluación completa con el equipo especializado. Edad+plazo+nivel ya fuertes antes incluso de pedir vídeo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:J19"/>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -3319,7 +3319,7 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Pestaña plantilla — se activa cuando el perfil de LinkedIn esté pulido (roadmap-maestro.md tarea #8, sesión conjunta pendiente con Claude in Chrome). Reglas de mensaje: ver plan-ventas-maestro.md sección 4 — siempre a una persona con cargo concreto, con una señal real (post/torneo/resultado), nunca plantilla fría.</t>
+          <t>ACTIVA desde el 28/09/2026 — perfil de LinkedIn terminado (titular, experiencia, foto). Semana 1 (28/09-04/10): 5-10 conexiones/día con gente conocida (Mercy, Mount Aloysius, fútbol en España), sin vender nada, para construir base real antes de contactar decisores. Semana 2 en adelante: 5 conexiones/día a decisores reales de Segmento A/B (crm-ventas.xlsx), nota corta con señal real, ver plan-ventas-maestro.md sección 4.</t>
         </is>
       </c>
     </row>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Segmento A - Clubes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Segmento B - America" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Segmento C - Becas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="LinkedIn - Plan diario" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Oportunidades y notas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento A - Clubes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento B - America" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento C - Becas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn - Plan diario" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Segmento A - Clubes'!$A$5:$O$17</definedName>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>Enviar el email de la columna siguiente hoy</t>
+          <t>Enviar el email de la columna siguiente hoy — SIN adjuntos en este primer email, solo texto</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Enviar el email de la columna siguiente esta semana</t>
+          <t>Enviar el email de la columna siguiente esta semana — SIN adjuntos en este primer email, solo texto</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Enviar el email de la columna siguiente esta semana</t>
+          <t>Enviar el email de la columna siguiente esta semana — SIN adjuntos en este primer email, solo texto</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -16,9 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Segmento A - Clubes'!$A$5:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Segmento B - America'!$A$5:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Segmento C - Becas'!$A$5:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Segmento A - Clubes'!$A$5:$P$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Segmento B - America'!$A$5:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Segmento C - Becas'!$A$5:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Oportunidades y notas'!$A$4:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +169,9 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1139,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1157,6 +1160,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1255,6 +1259,11 @@
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Notas</t>
+        </is>
+      </c>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>Qué adjuntar (por etapa)</t>
         </is>
       </c>
     </row>
@@ -1333,6 +1342,11 @@
           <t>Email ya preparado y revisado 2026-08-29 — solo falta que Joel lo envíe</t>
         </is>
       </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -1404,6 +1418,11 @@
           <t>También: fotball@soreideil.no (contacto general del club)</t>
         </is>
       </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -1465,6 +1484,11 @@
           <t>Llamar o contactar vía redes sociales del club para conseguir email directo</t>
         </is>
       </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -1522,6 +1546,11 @@
           <t>Investigado 2026-08-29: club real con categorías U13-U15 chicas, pero sin decisor nombrado todavía — no está al nivel de Home Farm/Hastings todavía</t>
         </is>
       </c>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -1571,6 +1600,11 @@
           <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original</t>
         </is>
       </c>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -1630,6 +1664,11 @@
       <c r="O11" s="12" t="inlineStr">
         <is>
           <t>Investigado 2026-08-29: contacto general real, falta nombre de decisor</t>
+        </is>
+      </c>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
         </is>
       </c>
     </row>
@@ -1703,6 +1742,11 @@
           <t>Investigado 2026-08-29: el mejor de los 4 investigados hoy — decisor nombrado y academia real</t>
         </is>
       </c>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -1756,6 +1800,11 @@
           <t>Investigado 2026-08-29: discrepancia entre el research original y lo encontrado hoy — no mandar nada hasta confirmar</t>
         </is>
       </c>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -1801,6 +1850,11 @@
       <c r="M14" s="13" t="inlineStr"/>
       <c r="N14" s="13" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr"/>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -1846,6 +1900,11 @@
       <c r="M15" s="13" t="inlineStr"/>
       <c r="N15" s="13" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr"/>
+      <c r="P15" s="12" t="inlineStr">
+        <is>
+          <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -1895,6 +1954,11 @@
           <t>Ver 01-clients/pipeline.md — no duplicar seguimiento aquí, solo referencia</t>
         </is>
       </c>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>Seguimiento ya en marcha fuera del flujo de outreach: sin adjuntos nuevos.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -1965,9 +2029,14 @@
           <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa.</t>
         </is>
       </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>Es un posible partner, no una venta estándar: sin adjuntos. Mensaje de WhatsApp y proponer llamada; llevar a la llamada ficha Team Experience + Campus Internacional (pendiente) si derivan a servicios.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:O17"/>
+  <autoFilter ref="A5:P17"/>
   <mergeCells count="3">
     <mergeCell ref="A3:O4"/>
     <mergeCell ref="A1:O1"/>
@@ -1983,7 +2052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2069,7 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2093,6 +2163,11 @@
       <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Notas</t>
+        </is>
+      </c>
+      <c r="O5" s="15" t="inlineStr">
+        <is>
+          <t>Qué adjuntar (por etapa)</t>
         </is>
       </c>
     </row>
@@ -2139,6 +2214,11 @@
       <c r="L6" s="13" t="inlineStr"/>
       <c r="M6" s="13" t="inlineStr"/>
       <c r="N6" s="12" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>1er email/LinkedIn: NADA adjunto. Si responde: ficha Team Experience (equipos) o Campus Internacional (academias, ficha pendiente). Segmento secundario: no invertir en materiales a medida hasta tener conversaciones reales.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -2187,6 +2267,11 @@
           <t>Aviso: categoría IberCup es U11/U12 7v7 — confirmar que tienen categorías mayores antes de contactar</t>
         </is>
       </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>1er email/LinkedIn: NADA adjunto. Si responde: ficha Team Experience (equipos) o Campus Internacional (academias, ficha pendiente). Segmento secundario: no invertir en materiales a medida hasta tener conversaciones reales.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2235,6 +2320,11 @@
           <t>Mismo aviso de edad que arriba</t>
         </is>
       </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>1er email/LinkedIn: NADA adjunto. Si responde: ficha Team Experience (equipos) o Campus Internacional (academias, ficha pendiente). Segmento secundario: no invertir en materiales a medida hasta tener conversaciones reales.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2283,6 +2373,11 @@
           <t>Mismo aviso de edad que arriba</t>
         </is>
       </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>1er email/LinkedIn: NADA adjunto. Si responde: ficha Team Experience (equipos) o Campus Internacional (academias, ficha pendiente). Segmento secundario: no invertir en materiales a medida hasta tener conversaciones reales.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2331,6 +2426,11 @@
           <t>Mismo aviso de edad que arriba</t>
         </is>
       </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>1er email/LinkedIn: NADA adjunto. Si responde: ficha Team Experience (equipos) o Campus Internacional (academias, ficha pendiente). Segmento secundario: no invertir en materiales a medida hasta tener conversaciones reales.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2379,6 +2479,11 @@
           <t>Mismo aviso de edad que arriba</t>
         </is>
       </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>1er email/LinkedIn: NADA adjunto. Si responde: ficha Team Experience (equipos) o Campus Internacional (academias, ficha pendiente). Segmento secundario: no invertir en materiales a medida hasta tener conversaciones reales.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2427,6 +2532,11 @@
           <t>Programa grande con relaciones ya asentadas, mal candidato para primer contacto. Dejar como caso de estudio del mercado</t>
         </is>
       </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>1er email/LinkedIn: NADA adjunto. Si responde: ficha Team Experience (equipos) o Campus Internacional (academias, ficha pendiente). Segmento secundario: no invertir en materiales a medida hasta tener conversaciones reales.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2475,9 +2585,14 @@
           <t>Búsqueda rápida (2026-08-29) no encontró candidatos concretos — requiere sesión de investigación dedicada, no una búsqueda genérica</t>
         </is>
       </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>1er email/LinkedIn: NADA adjunto. Si responde: ficha Team Experience (equipos) o Campus Internacional (academias, ficha pendiente). Segmento secundario: no invertir en materiales a medida hasta tener conversaciones reales.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N13"/>
+  <autoFilter ref="A5:O13"/>
   <mergeCells count="3">
     <mergeCell ref="A3:N4"/>
     <mergeCell ref="A2:N2"/>
@@ -2493,7 +2608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2506,6 +2621,7 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2581,6 +2697,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>Qué adjuntar (por etapa)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2631,6 +2752,11 @@
       <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Dilema real: ir a EEUU 2027 vs. quedarse en Portugal a estudiar</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -2673,6 +2799,11 @@
           <t>Preguntó directamente por el sistema de becas</t>
         </is>
       </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2723,6 +2854,11 @@
       <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Lead fuerte — ya en EEUU, quiere seguir compitiendo y sacar diploma</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -2761,6 +2897,11 @@
           <t>Lead muy caliente, solo falta confirmar</t>
         </is>
       </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2797,6 +2938,11 @@
           <t>Intentaba cerrar día ('hoy o mañana'), se quedó sin respuesta</t>
         </is>
       </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2849,6 +2995,11 @@
           <t>Originalmente pedía Inglaterra, aceptó explorar vía EEUU</t>
         </is>
       </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -2901,6 +3052,11 @@
           <t>Llamada realizada 15/09/2026. Resultado: la familia lo va a valorar 'en los próximos días', Joel manda evaluación/propuesta cuando den el okay. Joel ya envió foto de precios por WhatsApp + mensaje de cierre de llamada. Pendiente: confirmar si ya tienen el vídeo en mano, y si se aclaró en la llamada si buscan la misma universidad para los dos gemelos o están abiertos a separarse.</t>
         </is>
       </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2947,6 +3103,11 @@
       <c r="J13" s="12" t="inlineStr">
         <is>
           <t>Pidió la guía explícitamente</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -2993,6 +3154,11 @@
           <t>Conversación avanzada que se enfrió</t>
         </is>
       </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3041,6 +3207,11 @@
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr"/>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3085,6 +3256,11 @@
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -3133,6 +3309,11 @@
           <t>Confirmado: Always Up sí trabaja otros deportes, no solo fútbol</t>
         </is>
       </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -3183,6 +3364,11 @@
       <c r="J18" s="12" t="inlineStr">
         <is>
           <t>Cuenta confirmada por Joel — verificar en próximo barrido</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3221,6 +3407,11 @@
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -3273,9 +3464,14 @@
           <t>Pregunta genuina sobre 1º vs 2º de Bachillerato y elegibilidad NCAA — no se improvisó respuesta, se remitió a la evaluación completa con el equipo especializado. Edad+plazo+nivel ya fuertes antes incluso de pedir vídeo.</t>
         </is>
       </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J19"/>
+  <autoFilter ref="A5:K20"/>
   <mergeCells count="3">
     <mergeCell ref="A3:J4"/>
     <mergeCell ref="A1:J1"/>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -2756,7 +2756,7 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       <c r="J15" s="12" t="inlineStr"/>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       <c r="J16" s="12" t="inlineStr"/>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       <c r="J19" s="12" t="inlineStr"/>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): guía de becas con marca Always Up (pendiente de crear; hasta entonces guia-becas.md, NUNCA el deck de University Soccer). Mensajes cortos, pensados para móvil. Llamada: Calendly.</t>
+          <t>1er DM: sin adjuntos. Tras cualificar (nivel + vídeo): ficha Always-Up-Becas-EEUU.pdf (2 págs, en español, pensada para móvil, sin precio). NUNCA el deck de University Soccer. Llamada: Calendly.</t>
         </is>
       </c>
     </row>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -1142,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Listo para enviar</t>
+          <t>Enviado</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>Enviar el email de la columna siguiente hoy — SIN adjuntos en este primer email, solo texto</t>
+          <t>Follow-up 1 el 27/10/2026 si no responde (mensaje corto que aporte algo, sin adjuntos). Si responde con interés: ficha Team Experience</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
@@ -1335,11 +1335,15 @@
 Joel</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr"/>
-      <c r="N6" s="13" t="inlineStr"/>
+      <c r="M6" s="13" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>46308</v>
+      </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>Email ya preparado y revisado 2026-08-29 — solo falta que Joel lo envíe</t>
+          <t>Email ya preparado y revisado 2026-08-29 — solo falta que Joel lo envíe | Enviado 13/10/2026 a las 15:23 (hora de Nueva York) desde joel.martinez@alwaysup.es, solo texto, sin firma ni adjuntos</t>
         </is>
       </c>
       <c r="P6" s="12" t="inlineStr">
@@ -1387,12 +1391,12 @@
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Listo para enviar</t>
+          <t>Enviado</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Enviar el email de la columna siguiente esta semana — SIN adjuntos en este primer email, solo texto</t>
+          <t>Follow-up 1 el 27/10/2026 si no responde (mensaje corto que aporte algo, sin adjuntos). Si responde con interés: ficha Team Experience</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
@@ -1411,11 +1415,15 @@
 Joel</t>
         </is>
       </c>
-      <c r="M7" s="13" t="inlineStr"/>
-      <c r="N7" s="13" t="inlineStr"/>
+      <c r="M7" s="13" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>46308</v>
+      </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>También: fotball@soreideil.no (contacto general del club)</t>
+          <t>También: fotball@soreideil.no (contacto general del club) | Enviado 13/10/2026 a las 15:31 (hora de Nueva York) desde joel.martinez@alwaysup.es, solo texto, sin firma ni adjuntos</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
@@ -1711,12 +1719,12 @@
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Listo para enviar</t>
+          <t>Enviado</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Enviar el email de la columna siguiente esta semana — SIN adjuntos en este primer email, solo texto</t>
+          <t>Follow-up 1 el 27/10/2026 si no responde (mensaje corto que aporte algo, sin adjuntos). Si responde con interés: ficha Team Experience</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1735,11 +1743,15 @@
 Joel</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr"/>
-      <c r="N12" s="13" t="inlineStr"/>
+      <c r="M12" s="13" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>46308</v>
+      </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: el mejor de los 4 investigados hoy — decisor nombrado y academia real</t>
+          <t>Investigado 2026-08-29: el mejor de los 4 investigados hoy — decisor nombrado y academia real | Enviado 13/10/2026 a las 15:33 (hora de Nueva York) desde joel.martinez@alwaysup.es, solo texto, sin firma ni adjuntos</t>
         </is>
       </c>
       <c r="P12" s="12" t="inlineStr">
@@ -2035,6 +2047,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <autoFilter ref="A5:P17"/>
   <mergeCells count="3">
@@ -2608,7 +2622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3039,17 +3053,17 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Esperando 'okay' de la familia para mandar evaluación/propuesta. Seguimiento suave si no hay respuesta antes del viernes 19/09/2026 (fin de semana según Joel). Confirmar con Joel si ya tiene el vídeo para tenerlo listo antes de que llegue el okay</t>
+          <t>Follow-up 13/10: lleva 14 días sin responder desde el 29/09; prometió vídeo y datos 'la próxima semana' (5/10) y no ha llegado. Pedir lo que tenga YA (aunque sea el del año pasado + notas) y empezar la primera lectura. NO ofrecer más descuento.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15 (llamada)</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Llamada realizada 15/09/2026. Resultado: la familia lo va a valorar 'en los próximos días', Joel manda evaluación/propuesta cuando den el okay. Joel ya envió foto de precios por WhatsApp + mensaje de cierre de llamada. Pendiente: confirmar si ya tienen el vídeo en mano, y si se aclaró en la llamada si buscan la misma universidad para los dos gemelos o están abiertos a separarse.</t>
+          <t>Llamada realizada 15/09/2026. Resultado: la familia lo va a valorar 'en los próximos días', Joel manda evaluación/propuesta cuando den el okay. Joel ya envió foto de precios por WhatsApp + mensaje de cierre de llamada. Pendiente: confirmar si ya tienen el vídeo en mano, y si se aclaró en la llamada si buscan la misma universidad para los dos gemelos o están abiertos a separarse. | 17/09 objeción: precio alto 'x2', quiere evaluación antes de decidir (qué beca y qué división). 18/09 oferta de Joel por niño: pago único $2.000 (en vez de $2.500) o 2 plazos $250 + $2.500 (en vez de $3.500). 27/09 Omar: 'la próxima semana te envío vídeo y datos'. Sin datos desde entonces.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -3470,6 +3484,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
   </sheetData>
   <autoFilter ref="A5:K20"/>
   <mergeCells count="3">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento A - Clubes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento B - America" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento C - Becas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn - Plan diario" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outreach - Copiar y pegar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento A - Clubes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento B - America" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmento C - Becas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn - Plan diario" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Segmento A - Clubes'!$A$5:$P$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Segmento B - America'!$A$5:$O$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Segmento C - Becas'!$A$5:$K$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Oportunidades y notas'!$A$4:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Segmento A - Clubes'!$A$5:$P$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Segmento B - America'!$A$5:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Segmento C - Becas'!$A$5:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Oportunidades y notas'!$A$4:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +96,17 @@
       <color rgb="001F4E78"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +121,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B1F3A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +207,40 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -913,6 +982,2176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Outreach: copiar y pegar (ordenado por fecha)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Cada fila es un envío listo. Fecha = día de envío. Hora = 09:30 locales del destinatario (la columna de Nueva York ya la convierte). Tras enviar: marca 'Hecho' y escribe la fecha real. Si el club contesta, deja de enviar el resto de sus filas y sigue el guion de respuestas en 02-sales/plan-outreach-30-dias.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Hora local (09:30)</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Hora Nueva York</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Para</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Asunto</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Texto para pegar</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>Cómo enviarlo</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>Hecho (fecha real)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="255" customHeight="1">
+      <c r="A5" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Holbeach United</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>Email 1</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>callum@holbeachunitedacademy.com</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>Training week in Spain for Holbeach United's academy</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+I'm Joel, founder of Always Up. We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams and a stadium tour, with accommodation and meals included.
+I saw Holbeach United was listed for the Costa Daurada Cup in Salou this year, and your Football &amp; Education Academy stood out, so I thought a week in Spain could be a good fit for your older squads.
+A longtime partner club of ours won its first-ever league title after training with us, and its coaches credit part of it to the experience.
+Would you be open to a short call next week, or would you prefer I send a one-page overview first?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>Outlook &gt; Nuevo correo. Para / Asunto / Cuerpo tal cual (incluye la firma). Sin adjuntos. Usa 'Programar envío' para la hora indicada. A los 5 min de enviar, mira la bandeja por si hay rebote.</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="n"/>
+    </row>
+    <row r="6" ht="255" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Søreide IL</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Email 1</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>fotball@soreideil.no</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>Training week in Spain for Søreide IL's youth teams</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>Hi Marius and Gunn,
+I'm Joel, founder of Always Up. My first email bounced from your youth committee address, so I'm writing to you directly.
+We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams, and accommodation and meals included.
+I saw Søreide IL was listed for the Costa Daurada Cup in Salou this summer, so Spain may already be on your radar. A longtime partner club of ours won its first-ever league title after training with us.
+Would you be open to a short call next week, or would you prefer a one-page overview first?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>Outlook &gt; Nuevo correo. Para / Asunto / Cuerpo tal cual (incluye la firma). Sin adjuntos. Usa 'Programar envío' para la hora indicada. A los 5 min de enviar, mira la bandeja por si hay rebote.</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="21" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Hastings United (Girls Academy)</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn: conectar</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Georgia Townsend (Head of Girls Academy, Hastings United)</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>(nota de conexión)</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Hi Georgia, I'm Joel, founder of Always Up. We help youth clubs train in Spain with Atlético de Madrid and Real Sociedad. I emailed you recently and wanted to connect here too. Best, Joel</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>A mano en LinkedIn (no automatizar): perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar. Máx. 300 caracteres. Si no aparece 'Añadir nota', conecta sin nota y manda este texto al aceptar. ATENCIÓN: Joel lo hace a mano.</t>
+        </is>
+      </c>
+      <c r="K7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="225" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>Email 1</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>kfia@ia.is</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>Question about youth trips to Spain</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Hi ÍA team,
+I'm Joel, founder of Always Up. We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams and a stadium tour, with accommodation and meals included.
+I saw ÍA Akranes was listed for the Costa Daurada Cup in Salou this year. Could you point me to the person who organises trips abroad for your youth teams (yngri flokkar)?
+A longtime partner club of ours won its first-ever league title after training with us, and its coaches credit part of it to the experience, so I'd be glad to share how it worked for them.
+Thanks a lot,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>Outlook &gt; Nuevo correo. Para / Asunto / Cuerpo tal cual (incluye la firma). Sin adjuntos. Usa 'Programar envío' para la hora indicada. A los 5 min de enviar, mira la bandeja por si hay rebote.</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="n"/>
+    </row>
+    <row r="9" ht="225" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Maidstone United (Girls Development Centre)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Email 1</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>info@maidstoneunited.co.uk</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>Question about the Girls Development Centre</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Hi team,
+I'm Joel, founder of Always Up. We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams and a stadium tour, with accommodation and meals included.
+I saw Maidstone United was in the Costa Daurada Cup line-up in Salou this summer and thought your Girls Development Centre could be a great fit. Could you point me to the right person to speak with about trips for the girls' teams?
+A longtime partner club of ours won its first-ever league title after training with us, so I'd be glad to share how it worked for them.
+Thanks a lot,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>Outlook &gt; Nuevo correo. Para / Asunto / Cuerpo tal cual (incluye la firma). Sin adjuntos. Usa 'Programar envío' para la hora indicada. A los 5 min de enviar, mira la bandeja por si hay rebote.</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="n"/>
+    </row>
+    <row r="10" ht="225" customHeight="1">
+      <c r="A10" s="19" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Whitehaven AFC (Juniors Girls U13-U15)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>Email 1</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>Luke.johnston@whitehavenafc.com</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>Training week in Spain for Whitehaven's girls teams</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>Hi Luke,
+I'm Joel, founder of Always Up. We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams and a stadium tour, with accommodation and meals included.
+I saw Whitehaven AFC was listed for the Costa Daurada Cup in Salou this summer, and the girls pathway (U13-U15) caught my eye. A longtime partner club of ours won its first-ever league title after training with us.
+Would a short call next week work, or would you prefer a one-page overview first? And if you're not the right person, could you point me to whoever organises trips for the girls' section?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>Outlook &gt; Nuevo correo. Para / Asunto / Cuerpo tal cual (incluye la firma). Sin adjuntos. Usa 'Programar envío' para la hora indicada. A los 5 min de enviar, mira la bandeja por si hay rebote. ATENCIÓN: Email obtenido de un buscador: comprobarlo en whitehavenafc.com/contact antes de enviar. Si es otro, usar el de la web.</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="n"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="21" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>vie</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Holbeach United</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn: conectar</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Callum Lawe (Holbeach United Football &amp; Education Academy)</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>(nota de conexión)</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Hi Callum, I'm Joel, founder of Always Up. We help youth clubs train in Spain with Atlético de Madrid and Real Sociedad. I emailed you recently and wanted to connect here too. Best, Joel</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>A mano en LinkedIn (no automatizar): perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar. Máx. 300 caracteres. Si no aparece 'Añadir nota', conecta sin nota y manda este texto al aceptar. ATENCIÓN: Joel lo hace a mano.</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="21" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>vie</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>Søreide IL</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn: conectar</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>Marius Engen (Sportslig leder, Søreide IL fotball)</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>(nota de conexión)</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Hi Marius, I'm Joel, founder of Always Up. We help youth clubs train in Spain with Atlético de Madrid and Real Sociedad. I emailed you recently and wanted to connect here too. Best, Joel</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>A mano en LinkedIn (no automatizar): perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar. Máx. 300 caracteres. Si no aparece 'Añadir nota', conecta sin nota y manda este texto al aceptar. ATENCIÓN: Joel lo hace a mano.</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="21" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>lun</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>Whitehaven AFC (Juniors Girls U13-U15)</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>LinkedIn: conectar</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>Luke Johnston (Chairman, Whitehaven AFC)</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>(nota de conexión)</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>Hi Luke, I'm Joel, founder of Always Up. We help youth clubs train in Spain with Atlético de Madrid and Real Sociedad. I emailed you recently and wanted to connect here too. Best, Joel</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t>A mano en LinkedIn (no automatizar): perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar. Máx. 300 caracteres. Si no aparece 'Añadir nota', conecta sin nota y manda este texto al aceptar. ATENCIÓN: Joel lo hace a mano.</t>
+        </is>
+      </c>
+      <c r="K13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="255" customHeight="1">
+      <c r="A14" s="22" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Hastings United (Girls Academy)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Follow-up 1</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>georgia.townsend@hastingsunited.com</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>Re: Bringing Hastings United's Girls Academy to train with LaLiga clubs in Spain</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>Hi Georgia,
+Following up on my note from last week, in case it got buried.
+To make it concrete: a typical week with us is 5 days in Madrid, with training sessions, matches against local academy teams, a tour of the Metropolitano stadium and museum, and full accommodation and meals, all organised by us.
+If you're considering Easter or summer 2027, it's a good moment to look at dates while there is flexibility.
+Would a short call work, or shall I send a one-page overview?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="n"/>
+    </row>
+    <row r="15" ht="255" customHeight="1">
+      <c r="A15" s="22" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>Home Farm FC (chicas U13-U15)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Follow-up 1</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>homefarmfc@gmail.com</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>Re: Bringing Home Farm FC to train with Atlético de Madrid &amp; Real Sociedad in Spain</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Hi all,
+Following up on my note from last week, in case it got buried.
+To make it concrete: a typical week with us is 5 days in Madrid, with training sessions, matches against local academy teams, a tour of the Metropolitano stadium and museum, and full accommodation and meals, all organised by us.
+If you're considering Easter or summer 2027, it's a good moment to look at dates while there is flexibility.
+Would a short call work, or shall I send a one-page overview?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="n"/>
+    </row>
+    <row r="16" ht="255" customHeight="1">
+      <c r="A16" s="22" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>Holbeach United</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Follow-up 1</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>callum@holbeachunitedacademy.com</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Holbeach United's academy</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+Following up on my note from last week, in case it got buried.
+To make it concrete: a typical week with us is 5 days in Madrid, with training sessions, matches against local academy teams, a tour of the Metropolitano stadium and museum, and full accommodation and meals, all organised by us.
+If you're considering Easter or summer 2027, it's a good moment to look at dates while there is flexibility.
+Would a short call work, or shall I send a one-page overview?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="n"/>
+    </row>
+    <row r="17" ht="255" customHeight="1">
+      <c r="A17" s="22" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>Søreide IL</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Follow-up 1</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>fotball@soreideil.no</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Søreide IL's youth teams</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Hi Marius and Gunn,
+Following up on my note from last week, in case it got buried.
+To make it concrete: a typical week with us is 5 days in Madrid, with training sessions, matches against local academy teams, a tour of the Metropolitano stadium and museum, and full accommodation and meals, all organised by us.
+If you're considering Easter or summer 2027, it's a good moment to look at dates while there is flexibility.
+Would a short call work, or shall I send a one-page overview?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="n"/>
+    </row>
+    <row r="18" ht="225" customHeight="1">
+      <c r="A18" s="22" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Follow-up 1</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>kfia@ia.is</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>Re: Question about youth trips to Spain</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>Hi ÍA team,
+Following up on my note from last week, in case it got buried.
+I'm trying to reach whoever organises trips and tours for the youth teams. If that's not you, a name or a forward would be very much appreciated.
+In short: a 5-day week in Madrid with training sessions, matches against local academy teams, a tour of the Metropolitano stadium and museum, and full accommodation and meals, all organised by us.
+Thanks a lot,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="n"/>
+    </row>
+    <row r="19" ht="225" customHeight="1">
+      <c r="A19" s="22" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>Maidstone United (Girls Development Centre)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>Follow-up 1</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>info@maidstoneunited.co.uk</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>Re: Question about the Girls Development Centre</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>Hi team,
+Following up on my note from last week, in case it got buried.
+I'm trying to reach whoever organises trips and tours for the youth teams. If that's not you, a name or a forward would be very much appreciated.
+In short: a 5-day week in Madrid with training sessions, matches against local academy teams, a tour of the Metropolitano stadium and museum, and full accommodation and meals, all organised by us.
+Thanks a lot,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="255" customHeight="1">
+      <c r="A20" s="22" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>Whitehaven AFC (Juniors Girls U13-U15)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>Follow-up 1</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>Luke.johnston@whitehavenafc.com</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Whitehaven's girls teams</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>Hi Luke,
+Following up on my note from last week, in case it got buried.
+To make it concrete: a typical week with us is 5 days in Madrid, with training sessions, matches against local academy teams, a tour of the Metropolitano stadium and museum, and full accommodation and meals, all organised by us.
+If you're considering Easter or summer 2027, it's a good moment to look at dates while there is flexibility.
+Would a short call work, or shall I send a one-page overview?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="195" customHeight="1">
+      <c r="A21" s="24" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>Hastings United (Girls Academy)</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>Follow-up 2</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>georgia.townsend@hastingsunited.com</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>Re: Bringing Hastings United's Girls Academy to train with LaLiga clubs in Spain</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="inlineStr">
+        <is>
+          <t>Hi Georgia,
+I'll keep this short. Most clubs aren't sure at first whether a trip like this is realistic for their families and calendar, and that's fair.
+A 15-minute call is enough to tell you whether it fits, with no commitment. If it's not the right time, just let me know and I'll check back in the new year.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K21" s="25" t="n"/>
+    </row>
+    <row r="22" ht="195" customHeight="1">
+      <c r="A22" s="24" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Home Farm FC (chicas U13-U15)</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>Follow-up 2</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>homefarmfc@gmail.com</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>Re: Bringing Home Farm FC to train with Atlético de Madrid &amp; Real Sociedad in Spain</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="inlineStr">
+        <is>
+          <t>Hi all,
+I'll keep this short. Most clubs aren't sure at first whether a trip like this is realistic for their families and calendar, and that's fair.
+A 15-minute call is enough to tell you whether it fits, with no commitment. If it's not the right time, just let me know and I'll check back in the new year.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K22" s="25" t="n"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
+      <c r="A23" s="21" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>Hastings United (Girls Academy)</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>DM en redes (opcional)</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>Instagram de Hastings United</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>(mensaje directo)</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>Hi! I'm Joel from Always Up. We organise training weeks in Spain for youth clubs (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who is the best person to talk to about trips for the youth teams?</t>
+        </is>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>A mano, desde la cuenta del club en la red social indicada. Solo si NO ha contestado al email 2. Mensaje corto, sin enlaces. ATENCIÓN: Solo si no hay respuesta al follow-up 2.</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n"/>
+    </row>
+    <row r="24" ht="195" customHeight="1">
+      <c r="A24" s="24" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>Holbeach United</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>Follow-up 2</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>callum@holbeachunitedacademy.com</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Holbeach United's academy</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+I'll keep this short. Most clubs aren't sure at first whether a trip like this is realistic for their families and calendar, and that's fair.
+A 15-minute call is enough to tell you whether it fits, with no commitment. If it's not the right time, just let me know and I'll check back in the new year.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K24" s="25" t="n"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="21" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Home Farm FC (chicas U13-U15)</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>DM en redes (opcional)</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram de Home Farm FC</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>(mensaje directo)</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>Hi! I'm Joel from Always Up. We organise training weeks in Spain for youth clubs (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who is the best person to talk to about trips for the youth teams?</t>
+        </is>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>A mano, desde la cuenta del club en la red social indicada. Solo si NO ha contestado al email 2. Mensaje corto, sin enlaces. ATENCIÓN: Solo si no hay respuesta al follow-up 2.</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n"/>
+    </row>
+    <row r="26" ht="195" customHeight="1">
+      <c r="A26" s="24" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Søreide IL</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>Follow-up 2</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>fotball@soreideil.no</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Søreide IL's youth teams</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="inlineStr">
+        <is>
+          <t>Hi Marius and Gunn,
+I'll keep this short. Most clubs aren't sure at first whether a trip like this is realistic for their families and calendar, and that's fair.
+A 15-minute call is enough to tell you whether it fits, with no commitment. If it's not the right time, just let me know and I'll check back in the new year.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K26" s="25" t="n"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="21" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Holbeach United</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>DM en redes (opcional)</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>Instagram @holbeachunitedcsa</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>(mensaje directo)</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>Hi! I'm Joel from Always Up. We organise training weeks in Spain for youth clubs (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who is the best person to talk to about trips for the youth teams?</t>
+        </is>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>A mano, desde la cuenta del club en la red social indicada. Solo si NO ha contestado al email 2. Mensaje corto, sin enlaces. ATENCIÓN: Solo si no hay respuesta al follow-up 2.</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n"/>
+    </row>
+    <row r="28" ht="195" customHeight="1">
+      <c r="A28" s="24" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>Follow-up 2</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>kfia@ia.is</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>Re: Question about youth trips to Spain</t>
+        </is>
+      </c>
+      <c r="I28" s="25" t="inlineStr">
+        <is>
+          <t>Hi ÍA team,
+I'll keep this short. Most clubs aren't sure at first whether a trip like this is realistic for their families and calendar, and that's fair.
+A 15-minute call is enough to tell you whether it fits, with no commitment. If it's not the right time, just let me know and I'll check back in the new year.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="195" customHeight="1">
+      <c r="A29" s="24" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>Maidstone United (Girls Development Centre)</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>Follow-up 2</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>info@maidstoneunited.co.uk</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>Re: Question about the Girls Development Centre</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="inlineStr">
+        <is>
+          <t>Hi team,
+I'll keep this short. Most clubs aren't sure at first whether a trip like this is realistic for their families and calendar, and that's fair.
+A 15-minute call is enough to tell you whether it fits, with no commitment. If it's not the right time, just let me know and I'll check back in the new year.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K29" s="25" t="n"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="21" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>Søreide IL</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>DM en redes (opcional)</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram de Søreide IL</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>(mensaje directo)</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>Hi! I'm Joel from Always Up. We organise training weeks in Spain for youth clubs (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who is the best person to talk to about trips for the youth teams?</t>
+        </is>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>A mano, desde la cuenta del club en la red social indicada. Solo si NO ha contestado al email 2. Mensaje corto, sin enlaces. ATENCIÓN: Solo si no hay respuesta al follow-up 2.</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="195" customHeight="1">
+      <c r="A31" s="24" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>Whitehaven AFC (Juniors Girls U13-U15)</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>Follow-up 2</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>Luke.johnston@whitehavenafc.com</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Whitehaven's girls teams</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="inlineStr">
+        <is>
+          <t>Hi Luke,
+I'll keep this short. Most clubs aren't sure at first whether a trip like this is realistic for their families and calendar, and that's fair.
+A 15-minute call is enough to tell you whether it fits, with no commitment. If it's not the right time, just let me know and I'll check back in the new year.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal.</t>
+        </is>
+      </c>
+      <c r="K31" s="25" t="n"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="21" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>vie</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>DM en redes (opcional)</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram de ÍA Akranes</t>
+        </is>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t>(mensaje directo)</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>Hi! I'm Joel from Always Up. We organise training weeks in Spain for youth clubs (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who is the best person to talk to about trips for the youth teams?</t>
+        </is>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>A mano, desde la cuenta del club en la red social indicada. Solo si NO ha contestado al email 2. Mensaje corto, sin enlaces. ATENCIÓN: Solo si no hay respuesta al follow-up 2.</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="n"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="21" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>vie</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>Maidstone United (Girls Development Centre)</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>DM en redes (opcional)</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>Facebook/Instagram de Maidstone United</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>(mensaje directo)</t>
+        </is>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>Hi! I'm Joel from Always Up. We organise training weeks in Spain for youth clubs (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who is the best person to talk to about trips for the youth teams?</t>
+        </is>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>A mano, desde la cuenta del club en la red social indicada. Solo si NO ha contestado al email 2. Mensaje corto, sin enlaces. ATENCIÓN: Solo si no hay respuesta al follow-up 2.</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="n"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="21" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>vie</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>cuando puedas</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Whitehaven AFC (Juniors Girls U13-U15)</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>DM en redes (opcional)</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>Facebook de Whitehaven AFC</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>(mensaje directo)</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>Hi! I'm Joel from Always Up. We organise training weeks in Spain for youth clubs (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who is the best person to talk to about trips for the youth teams?</t>
+        </is>
+      </c>
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>A mano, desde la cuenta del club en la red social indicada. Solo si NO ha contestado al email 2. Mensaje corto, sin enlaces. ATENCIÓN: Solo si no hay respuesta al follow-up 2.</t>
+        </is>
+      </c>
+      <c r="K34" s="17" t="n"/>
+    </row>
+    <row r="35" ht="225" customHeight="1">
+      <c r="A35" s="26" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>Hastings United (Girls Academy)</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="inlineStr">
+        <is>
+          <t>Cierre (último)</t>
+        </is>
+      </c>
+      <c r="G35" s="27" t="inlineStr">
+        <is>
+          <t>georgia.townsend@hastingsunited.com</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="inlineStr">
+        <is>
+          <t>Re: Bringing Hastings United's Girls Academy to train with LaLiga clubs in Spain</t>
+        </is>
+      </c>
+      <c r="I35" s="27" t="inlineStr">
+        <is>
+          <t>Hi Georgia,
+I haven't heard back, so I'll assume the timing isn't right and I won't keep writing.
+If anything changes, or you'd like the overview for later, just reply to this email.
+Wishing Hastings United a great season.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J35" s="27" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal. ATENCIÓN: Tras esto, pasar a 'Perdido' / 'Retomar en 2027' en el CRM.</t>
+        </is>
+      </c>
+      <c r="K35" s="27" t="n"/>
+    </row>
+    <row r="36" ht="225" customHeight="1">
+      <c r="A36" s="26" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>Home Farm FC (chicas U13-U15)</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="inlineStr">
+        <is>
+          <t>Cierre (último)</t>
+        </is>
+      </c>
+      <c r="G36" s="27" t="inlineStr">
+        <is>
+          <t>homefarmfc@gmail.com</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="inlineStr">
+        <is>
+          <t>Re: Bringing Home Farm FC to train with Atlético de Madrid &amp; Real Sociedad in Spain</t>
+        </is>
+      </c>
+      <c r="I36" s="27" t="inlineStr">
+        <is>
+          <t>Hi all,
+I haven't heard back, so I'll assume the timing isn't right and I won't keep writing.
+If anything changes, or you'd like the overview for later, just reply to this email.
+Wishing Home Farm FC a great season.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J36" s="27" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal. ATENCIÓN: Tras esto, pasar a 'Perdido' / 'Retomar en 2027' en el CRM.</t>
+        </is>
+      </c>
+      <c r="K36" s="27" t="n"/>
+    </row>
+    <row r="37" ht="225" customHeight="1">
+      <c r="A37" s="26" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>Holbeach United</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="inlineStr">
+        <is>
+          <t>Cierre (último)</t>
+        </is>
+      </c>
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>callum@holbeachunitedacademy.com</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Holbeach United's academy</t>
+        </is>
+      </c>
+      <c r="I37" s="27" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+I haven't heard back, so I'll assume the timing isn't right and I won't keep writing.
+If anything changes, or you'd like the overview for later, just reply to this email.
+Wishing Holbeach United a great season.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J37" s="27" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal. ATENCIÓN: Tras esto, pasar a 'Perdido' / 'Retomar en 2027' en el CRM.</t>
+        </is>
+      </c>
+      <c r="K37" s="27" t="n"/>
+    </row>
+    <row r="38" ht="225" customHeight="1">
+      <c r="A38" s="26" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>mié</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>Søreide IL</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>Cierre (último)</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>fotball@soreideil.no</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Søreide IL's youth teams</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="inlineStr">
+        <is>
+          <t>Hi Marius and Gunn,
+I haven't heard back, so I'll assume the timing isn't right and I won't keep writing.
+If anything changes, or you'd like the overview for later, just reply to this email.
+Wishing Søreide IL a great season.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J38" s="27" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal. ATENCIÓN: Tras esto, pasar a 'Perdido' / 'Retomar en 2027' en el CRM.</t>
+        </is>
+      </c>
+      <c r="K38" s="27" t="n"/>
+    </row>
+    <row r="39" ht="225" customHeight="1">
+      <c r="A39" s="26" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="inlineStr">
+        <is>
+          <t>Cierre (último)</t>
+        </is>
+      </c>
+      <c r="G39" s="27" t="inlineStr">
+        <is>
+          <t>kfia@ia.is</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="inlineStr">
+        <is>
+          <t>Re: Question about youth trips to Spain</t>
+        </is>
+      </c>
+      <c r="I39" s="27" t="inlineStr">
+        <is>
+          <t>Hi ÍA team,
+I haven't heard back, so I'll assume the timing isn't right and I won't keep writing.
+If anything changes, or you'd like the overview for later, just reply to this email.
+Wishing ÍA Akranes a great season.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J39" s="27" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal. ATENCIÓN: Tras esto, pasar a 'Perdido' / 'Retomar en 2027' en el CRM.</t>
+        </is>
+      </c>
+      <c r="K39" s="27" t="n"/>
+    </row>
+    <row r="40" ht="225" customHeight="1">
+      <c r="A40" s="26" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>Maidstone United (Girls Development Centre)</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="inlineStr">
+        <is>
+          <t>Cierre (último)</t>
+        </is>
+      </c>
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>info@maidstoneunited.co.uk</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="inlineStr">
+        <is>
+          <t>Re: Question about the Girls Development Centre</t>
+        </is>
+      </c>
+      <c r="I40" s="27" t="inlineStr">
+        <is>
+          <t>Hi team,
+I haven't heard back, so I'll assume the timing isn't right and I won't keep writing.
+If anything changes, or you'd like the overview for later, just reply to this email.
+Wishing Maidstone United a great season.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J40" s="27" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal. ATENCIÓN: Tras esto, pasar a 'Perdido' / 'Retomar en 2027' en el CRM.</t>
+        </is>
+      </c>
+      <c r="K40" s="27" t="n"/>
+    </row>
+    <row r="41" ht="225" customHeight="1">
+      <c r="A41" s="26" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>jue</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D41" s="27" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>Whitehaven AFC (Juniors Girls U13-U15)</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="inlineStr">
+        <is>
+          <t>Cierre (último)</t>
+        </is>
+      </c>
+      <c r="G41" s="27" t="inlineStr">
+        <is>
+          <t>Luke.johnston@whitehavenafc.com</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="inlineStr">
+        <is>
+          <t>Re: Training week in Spain for Whitehaven's girls teams</t>
+        </is>
+      </c>
+      <c r="I41" s="27" t="inlineStr">
+        <is>
+          <t>Hi Luke,
+I haven't heard back, so I'll assume the timing isn't right and I won't keep writing.
+If anything changes, or you'd like the overview for later, just reply to this email.
+Wishing Whitehaven AFC a great season.
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
+      <c r="J41" s="27" t="inlineStr">
+        <is>
+          <t>Responde DENTRO del hilo del email anterior (carpeta Enviados &gt; abrir el correo &gt; Responder), no un correo nuevo. Sin adjuntos. Comprueba antes en el CRM que no ha contestado por otro canal. ATENCIÓN: Tras esto, pasar a 'Perdido' / 'Retomar en 2027' en el CRM.</t>
+        </is>
+      </c>
+      <c r="K41" s="27" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1136,13 +3375,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1315,7 +3554,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>Follow-up 1 el 27/10/2026 si no responde (mensaje corto que aporte algo, sin adjuntos). Si responde con interés: ficha Team Experience</t>
+          <t>Follow-up 1 el 20/10/2026 (en el mismo hilo). Textos en hoja 'Outreach - Copiar y pegar'.</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
@@ -1380,39 +3619,41 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Comité juvenil del club</t>
+          <t>Marius Engen / Gunn Eklund Breisnes</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>ungdomsutvalget@soreideil.no</t>
+          <t>fotball@soreideil.no</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Enviado</t>
+          <t>Listo para enviar</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Follow-up 1 el 27/10/2026 si no responde (mensaje corto que aporte algo, sin adjuntos). Si responde con interés: ficha Team Experience</t>
+          <t>Enviar el 14/10/2026 a las 09:30 hora local (Outlook: programar envío). Texto en hoja 'Outreach - Copiar y pegar'.</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Bringing Søreide IL to train with LaLiga clubs in Spain</t>
+          <t>Training week in Spain for Søreide IL's youth teams</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>Hi,
-I'm Joel, I run Always Up — we bring international youth clubs to Spain to train directly at the facilities of Atletico de Madrid, Real Sociedad and Sporting de Gijon.
-I saw Søreide IL is a confirmed participant in the Costa Daurada Cup 2026 and thought this could be a great fit for your squad.
-One of our longtime partner clubs credited their first-ever league title partly to their Atletico de Madrid experience with us — and with Spain now World Cup Champions, interest in trips like this is only growing.
-Would you have 15 minutes this week to hear more?
+          <t>Hi Marius and Gunn,
+I'm Joel, founder of Always Up. My first email bounced from your youth committee address, so I'm writing to you directly.
+We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams, and accommodation and meals included.
+I saw Søreide IL was listed for the Costa Daurada Cup in Salou this summer, so Spain may already be on your radar. A longtime partner club of ours won its first-ever league title after training with us.
+Would you be open to a short call next week, or would you prefer a one-page overview first?
 Best,
-Joel</t>
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
         </is>
       </c>
       <c r="M7" s="13" t="n">
@@ -1423,7 +3664,7 @@
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>También: fotball@soreideil.no (contacto general del club) | Enviado 13/10/2026 a las 15:31 (hora de Nueva York) desde joel.martinez@alwaysup.es, solo texto, sin firma ni adjuntos</t>
+          <t>13/10/2026: el email 1 REBOTÓ (ungdomsutvalget@soreideil.no reenvía a una cuenta inexistente en bergensskolen.com). Contactos reales (soreideil.no/fotball/kontaktinformasjon): Gunn Eklund Breisnes (Leder), Marius Engen (Sportslig leder), fotball@soreideil.no. Reenvío el 14/10 a fotball@soreideil.no.</t>
         </is>
       </c>
       <c r="P7" s="12" t="inlineStr">
@@ -1465,7 +3706,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Pendiente — solo hay teléfono</t>
+          <t>info@maidstoneunited.co.uk</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1475,16 +3716,31 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Pendiente investigar email</t>
+          <t>Listo para enviar</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>Llamar o buscar contacto vía redes del club</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr"/>
-      <c r="L8" s="12" t="inlineStr"/>
+          <t>Enviar el 15/10/2026 a las 09:30 hora local (Outlook: programar envío). Texto en hoja 'Outreach - Copiar y pegar'.</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Question about the Girls Development Centre</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>Hi team,
+I'm Joel, founder of Always Up. We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams and a stadium tour, with accommodation and meals included.
+I saw Maidstone United was in the Costa Daurada Cup line-up in Salou this summer and thought your Girls Development Centre could be a great fit. Could you point me to the right person to speak with about trips for the girls' teams?
+A longtime partner club of ours won its first-ever league title after training with us, so I'd be glad to share how it worked for them.
+Thanks a lot,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
       <c r="M8" s="13" t="inlineStr"/>
       <c r="N8" s="13" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr">
@@ -1526,27 +3782,42 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Sin nombre confirmado todavía</t>
+          <t>Luke Johnston (Chairman)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Sin email directo — solo formulario en whitehavenafc.com/contact</t>
+          <t>Luke.johnston@whitehavenafc.com</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Pendiente investigar decisor</t>
+          <t>Listo para enviar</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>Rellenar el formulario de contacto o buscar el nombre del responsable de chicas en redes del club antes de escribir</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr"/>
+          <t>Enviar el 15/10/2026 a las 09:30 hora local (Outlook: programar envío). Texto en hoja 'Outreach - Copiar y pegar'.</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>Training week in Spain for Whitehaven's girls teams</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>Hi Luke,
+I'm Joel, founder of Always Up. We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams and a stadium tour, with accommodation and meals included.
+I saw Whitehaven AFC was listed for the Costa Daurada Cup in Salou this summer, and the girls pathway (U13-U15) caught my eye. A longtime partner club of ours won its first-ever league title after training with us.
+Would a short call next week work, or would you prefer a one-page overview first? And if you're not the right person, could you point me to whoever organises trips for the girls' section?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
       <c r="M9" s="13" t="inlineStr"/>
       <c r="N9" s="13" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr">
@@ -1605,7 +3876,7 @@
       <c r="N10" s="13" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto.</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
@@ -1642,12 +3913,12 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Sin nombre confirmado todavía</t>
+          <t>Callum Lawe (Vice Chairman, Football &amp; Education Academy)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>info@holbeachunitedcsa.org.uk</t>
+          <t>callum@holbeachunitedacademy.com</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1657,16 +3928,32 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Pendiente investigar decisor</t>
+          <t>Listo para enviar</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>Escribir al email general pidiendo hablar con el responsable de viajes/categorías mayores antes de mandar la propuesta completa</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
+          <t>Enviar el 14/10/2026 a las 09:30 hora local (Outlook: programar envío). Texto en hoja 'Outreach - Copiar y pegar'.</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>Training week in Spain for Holbeach United's academy</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+I'm Joel, founder of Always Up. We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams and a stadium tour, with accommodation and meals included.
+I saw Holbeach United was listed for the Costa Daurada Cup in Salou this year, and your Football &amp; Education Academy stood out, so I thought a week in Spain could be a good fit for your older squads.
+A longtime partner club of ours won its first-ever league title after training with us, and its coaches credit part of it to the experience.
+Would you be open to a short call next week, or would you prefer I send a one-page overview first?
+Best,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
       <c r="M11" s="13" t="inlineStr"/>
       <c r="N11" s="13" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr">
@@ -1724,7 +4011,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Follow-up 1 el 27/10/2026 si no responde (mensaje corto que aporte algo, sin adjuntos). Si responde con interés: ficha Team Experience</t>
+          <t>Follow-up 1 el 20/10/2026 (en el mismo hilo). Textos en hoja 'Outreach - Copiar y pegar'.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1845,20 +4132,39 @@
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>kfia@ia.is</t>
+        </is>
+      </c>
       <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Pendiente investigar</t>
+          <t>Listo para enviar</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>Investigar contacto (parte de la cuota diaria de 5 búsquedas)</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr"/>
-      <c r="L14" s="12" t="inlineStr"/>
+          <t>Enviar el 15/10/2026 a las 09:30 hora local (Outlook: programar envío). Texto en hoja 'Outreach - Copiar y pegar'.</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>Question about youth trips to Spain</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>Hi ÍA team,
+I'm Joel, founder of Always Up. We organise training weeks in Spain for youth clubs: sessions at the facilities of Atlético de Madrid and Real Sociedad, matches against local academy teams and a stadium tour, with accommodation and meals included.
+I saw ÍA Akranes was listed for the Costa Daurada Cup in Salou this year. Could you point me to the person who organises trips abroad for your youth teams (yngri flokkar)?
+A longtime partner club of ours won its first-ever league title after training with us, and its coaches credit part of it to the experience, so I'd be glad to share how it worked for them.
+Thanks a lot,
+Joel Martinez
+Founder, Always Up
+joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
+        </is>
+      </c>
       <c r="M14" s="13" t="inlineStr"/>
       <c r="N14" s="13" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr"/>
@@ -1911,7 +4217,11 @@
       <c r="L15" s="12" t="inlineStr"/>
       <c r="M15" s="13" t="inlineStr"/>
       <c r="N15" s="13" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>13/10/2026: es un club profesional con academia (Joep Breimer, hoofd voetbalontwikkeling jeugdopleiding). Perfil distinto al club amateur viajero: prioridad baja, no incluir en la primera tanda.</t>
+        </is>
+      </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
           <t>1er email: NADA adjunto, solo texto (firma de texto plano). Si responde con interés: ficha Always-Up-Team-Experience.pdf. Antes de la llamada: deck de empresa (pendiente de crear), solo si hace falta. Tras la llamada: propuesta escrita.</t>
@@ -2047,8 +4357,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <autoFilter ref="A5:P17"/>
   <mergeCells count="3">
@@ -2060,7 +4368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2616,13 +4924,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3053,7 +5361,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Follow-up 13/10: lleva 14 días sin responder desde el 29/09; prometió vídeo y datos 'la próxima semana' (5/10) y no ha llegado. Pedir lo que tenga YA (aunque sea el del año pasado + notas) y empezar la primera lectura. NO ofrecer más descuento.</t>
+          <t>Follow-up enviado el 13/10. Si no contesta en 7 días (20/10): un último mensaje corto y pasar a 'frío'. No bajar más el precio.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -3063,7 +5371,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>Llamada realizada 15/09/2026. Resultado: la familia lo va a valorar 'en los próximos días', Joel manda evaluación/propuesta cuando den el okay. Joel ya envió foto de precios por WhatsApp + mensaje de cierre de llamada. Pendiente: confirmar si ya tienen el vídeo en mano, y si se aclaró en la llamada si buscan la misma universidad para los dos gemelos o están abiertos a separarse. | 17/09 objeción: precio alto 'x2', quiere evaluación antes de decidir (qué beca y qué división). 18/09 oferta de Joel por niño: pago único $2.000 (en vez de $2.500) o 2 plazos $250 + $2.500 (en vez de $3.500). 27/09 Omar: 'la próxima semana te envío vídeo y datos'. Sin datos desde entonces.</t>
+          <t>Llamada realizada 15/09/2026. Resultado: la familia lo va a valorar 'en los próximos días', Joel manda evaluación/propuesta cuando den el okay. Joel ya envió foto de precios por WhatsApp + mensaje de cierre de llamada. Pendiente: confirmar si ya tienen el vídeo en mano, y si se aclaró en la llamada si buscan la misma universidad para los dos gemelos o están abiertos a separarse. | 17/09 objeción: precio alto 'x2', quiere evaluación antes de decidir (qué beca y qué división). 18/09 oferta de Joel por niño: pago único $2.000 (en vez de $2.500) o 2 plazos $250 + $2.500 (en vez de $3.500). 27/09 Omar: 'la próxima semana te envío vídeo y datos'. Sin datos desde entonces. | 13/10: Joel envió el follow-up pidiendo vídeo/datos con salida elegante.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -3484,7 +5792,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
   </sheetData>
   <autoFilter ref="A5:K20"/>
   <mergeCells count="3">
@@ -3496,7 +5803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3657,7 +5964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -868,7 +868,7 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>Programa en Outlook los correos del día siguiente. El calendario te dice cuáles, a qué hora de Nueva York y de dónde copiar el texto.</t>
+          <t>Prepara los correos del día siguiente. Si tu correo permite programar, déjalos programados. Si no, los envías a mano a las 07:30 de Nueva York. El calendario te dice cuáles y de dónde copiar el texto.</t>
         </is>
       </c>
     </row>
@@ -990,84 +990,120 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>COMO PROGRAMAR UN CORREO EN OUTLOOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="47.5" customHeight="1">
+          <t>COMO ENVIAR A LA HORA CORRECTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33" customHeight="1">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>Paso a paso</t>
+          <t>Tu correo</t>
         </is>
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>Nuevo correo &gt; pega Para, Asunto y Texto &gt; flecha junto a Enviar &gt; Programar envío &gt; elige fecha y hora de Nueva York. Si usas Outlook de escritorio clásico, el ordenador debe estar encendido a esa hora. Con Outlook web o el Outlook nuevo sale solo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33" customHeight="1">
+          <t>joel.martinez@alwaysup.es está alojado en Hostinger, no en Microsoft. Outlook conectado a ese tipo de cuenta (IMAP) NO tiene 'Programar envío': ese botón solo funciona con cuentas de Microsoft. Por eso no lo veías.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="47.5" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>Por qué a las 09:30 locales</t>
+          <t>Opción 1 (la mejor)</t>
         </is>
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>Es el momento en que el responsable del club abre el correo en su jornada. Martes a jueves funcionan mejor que lunes (bandeja llena) y viernes (desconectan).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>REGLAS QUE NO SE ROMPEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33" customHeight="1">
+          <t>Entra al webmail de Hostinger (hpanel.hostinger.com &gt; Correo electrónico &gt; Abrir webmail, o mail.hostinger.com) con tu cuenta. Ahí, junto al botón Enviar, suele haber una flecha con 'Programar envío'. Funciona desde el servidor, aunque tu ordenador esté apagado. Pruébalo con un correo a ti mismo antes de usarlo con un club.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="47.5" customHeight="1">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>Opción 2</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Outlook de escritorio clásico: en el correo, pestaña Opciones &gt; Retrasar entrega &gt; 'No entregar antes de' + fecha y hora. Funciona, pero Outlook debe estar abierto y el ordenador encendido a esa hora. Outlook nuevo y Outlook web no tienen esta opción para cuentas IMAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="47.5" customHeight="1">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Plan B (sin programar)</t>
         </is>
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>Adjuntos en el primer correo. Nombrar al partner de becas. Prometer becas o fichajes. Inventar urgencia. Discutir precio por escrito sin tu decisión.</t>
+          <t>Envíalo tú a mano a las 07:30 de Nueva York. Son las 12:30 o 13:30 en Reino Unido, Irlanda, Noruega o Islandia: sigue siendo horario laboral, solo que a media mañana o mediodía en vez de a primera hora. La diferencia de respuesta es pequeña: no vale la pena perder un envío por esto.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33" customHeight="1">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>Si contestan</t>
+          <t>Regla</t>
         </is>
       </c>
       <c r="B22" s="32" t="inlineStr">
         <is>
-          <t>Paras la cadencia de ese club y abres 'Respuestas tipo' (hoja Textos para copiar). Menos de 4 horas de respuesta en horario del club.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>Si un correo rebota</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
-        <is>
-          <t>Me lo dices; busco otra dirección del club y te la dejo preparada.</t>
+          <t>Lo importante es enviar martes a jueves en horario laboral del club. La hora exacta de las 09:30 es una mejora, no una condición.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>REGLAS QUE NO SE ROMPEN</t>
         </is>
       </c>
     </row>
     <row r="24" ht="33" customHeight="1">
       <c r="A24" s="31" t="inlineStr">
         <is>
+          <t>Nunca</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Adjuntos en el primer correo. Nombrar al partner de becas. Prometer becas o fichajes. Inventar urgencia. Discutir precio por escrito sin tu decisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Si contestan</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>Paras la cadencia de ese club y abres 'Respuestas tipo' (hoja Textos para copiar). Menos de 4 horas de respuesta en horario del club.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Si un correo rebota</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>Me lo dices; busco otra dirección del club y te la dejo preparada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="33" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
           <t>Colores</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Azul claro = email 1, amarillo = follow-up 1, naranja = follow-up 2, gris = cierre, lila = LinkedIn o redes, rojo = pendiente atrasado.</t>
         </is>
@@ -1076,8 +1112,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1896,7 +1932,7 @@
       </c>
       <c r="J7" s="39" t="n"/>
     </row>
-    <row r="8" ht="149" customHeight="1">
+    <row r="8" ht="134.5" customHeight="1">
       <c r="A8" s="38" t="n">
         <v>46308</v>
       </c>
@@ -1917,15 +1953,14 @@
       </c>
       <c r="E8" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del miércoles 14/10</t>
+          <t>Preparar (y programar si puedes) los envíos del miércoles 14/10</t>
         </is>
       </c>
       <c r="F8" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 14/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 14/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • Holbeach United | Email 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 14/10.
-• Søreide IL | Email 1 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 14/10.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Søreide IL | Email 1 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 14/10.</t>
         </is>
       </c>
       <c r="G8" s="39" t="inlineStr">
@@ -1943,7 +1978,7 @@
       </c>
       <c r="J8" s="39" t="n"/>
     </row>
-    <row r="9" ht="33" customHeight="1">
+    <row r="9" ht="47.5" customHeight="1">
       <c r="A9" s="44" t="n">
         <v>46309</v>
       </c>
@@ -1969,7 +2004,7 @@
       </c>
       <c r="F9" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G9" s="45" t="inlineStr">
@@ -1985,7 +2020,7 @@
       </c>
       <c r="J9" s="45" t="n"/>
     </row>
-    <row r="10" ht="33" customHeight="1">
+    <row r="10" ht="47.5" customHeight="1">
       <c r="A10" s="44" t="n">
         <v>46309</v>
       </c>
@@ -2011,7 +2046,7 @@
       </c>
       <c r="F10" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G10" s="45" t="inlineStr">
@@ -2287,7 +2322,7 @@
       </c>
       <c r="J16" s="39" t="n"/>
     </row>
-    <row r="17" ht="178" customHeight="1">
+    <row r="17" ht="163.5" customHeight="1">
       <c r="A17" s="38" t="n">
         <v>46309</v>
       </c>
@@ -2308,16 +2343,15 @@
       </c>
       <c r="E17" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del jueves 15/10</t>
+          <t>Preparar (y programar si puedes) los envíos del jueves 15/10</t>
         </is>
       </c>
       <c r="F17" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 15/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 15/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • IA Akranes | Email 1 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 15/10.
 • Maidstone United | Email 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 15/10.
-• Whitehaven AFC | Email 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 15/10.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Whitehaven AFC | Email 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 15/10.</t>
         </is>
       </c>
       <c r="G17" s="39" t="inlineStr">
@@ -2335,7 +2369,7 @@
       </c>
       <c r="J17" s="39" t="n"/>
     </row>
-    <row r="18" ht="33" customHeight="1">
+    <row r="18" ht="47.5" customHeight="1">
       <c r="A18" s="44" t="n">
         <v>46310</v>
       </c>
@@ -2361,7 +2395,7 @@
       </c>
       <c r="F18" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G18" s="45" t="inlineStr">
@@ -2377,7 +2411,7 @@
       </c>
       <c r="J18" s="45" t="n"/>
     </row>
-    <row r="19" ht="33" customHeight="1">
+    <row r="19" ht="47.5" customHeight="1">
       <c r="A19" s="44" t="n">
         <v>46310</v>
       </c>
@@ -2403,7 +2437,7 @@
       </c>
       <c r="F19" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G19" s="45" t="inlineStr">
@@ -2419,7 +2453,7 @@
       </c>
       <c r="J19" s="45" t="n"/>
     </row>
-    <row r="20" ht="33" customHeight="1">
+    <row r="20" ht="47.5" customHeight="1">
       <c r="A20" s="44" t="n">
         <v>46310</v>
       </c>
@@ -2445,7 +2479,7 @@
       </c>
       <c r="F20" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G20" s="45" t="inlineStr">
@@ -3248,7 +3282,7 @@
       </c>
       <c r="J39" s="39" t="n"/>
     </row>
-    <row r="40" ht="207" customHeight="1">
+    <row r="40" ht="192.5" customHeight="1">
       <c r="A40" s="38" t="n">
         <v>46314</v>
       </c>
@@ -3269,17 +3303,16 @@
       </c>
       <c r="E40" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del martes 20/10</t>
+          <t>Preparar (y programar si puedes) los envíos del martes 20/10</t>
         </is>
       </c>
       <c r="F40" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 20/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 20/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • FC Porte d'Aquitaine | Email 1 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 20/10.
 • Hastings United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 20/10.
 • Home Farm FC | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 20/10.
-• Virtu Academy | Email 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 20/10.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Virtu Academy | Email 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 20/10.</t>
         </is>
       </c>
       <c r="G40" s="39" t="inlineStr">
@@ -3297,7 +3330,7 @@
       </c>
       <c r="J40" s="39" t="n"/>
     </row>
-    <row r="41" ht="33" customHeight="1">
+    <row r="41" ht="47.5" customHeight="1">
       <c r="A41" s="44" t="n">
         <v>46315</v>
       </c>
@@ -3323,7 +3356,7 @@
       </c>
       <c r="F41" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G41" s="45" t="inlineStr">
@@ -3339,7 +3372,7 @@
       </c>
       <c r="J41" s="45" t="n"/>
     </row>
-    <row r="42" ht="33" customHeight="1">
+    <row r="42" ht="47.5" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>46315</v>
       </c>
@@ -3365,7 +3398,7 @@
       </c>
       <c r="F42" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G42" s="45" t="inlineStr">
@@ -3381,7 +3414,7 @@
       </c>
       <c r="J42" s="45" t="n"/>
     </row>
-    <row r="43" ht="33" customHeight="1">
+    <row r="43" ht="47.5" customHeight="1">
       <c r="A43" s="44" t="n">
         <v>46315</v>
       </c>
@@ -3407,7 +3440,7 @@
       </c>
       <c r="F43" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G43" s="45" t="inlineStr">
@@ -3423,7 +3456,7 @@
       </c>
       <c r="J43" s="45" t="n"/>
     </row>
-    <row r="44" ht="33" customHeight="1">
+    <row r="44" ht="47.5" customHeight="1">
       <c r="A44" s="44" t="n">
         <v>46315</v>
       </c>
@@ -3449,7 +3482,7 @@
       </c>
       <c r="F44" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G44" s="45" t="inlineStr">
@@ -3597,7 +3630,7 @@
       </c>
       <c r="J47" s="39" t="n"/>
     </row>
-    <row r="48" ht="149" customHeight="1">
+    <row r="48" ht="134.5" customHeight="1">
       <c r="A48" s="38" t="n">
         <v>46315</v>
       </c>
@@ -3618,15 +3651,14 @@
       </c>
       <c r="E48" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del miércoles 21/10</t>
+          <t>Preparar (y programar si puedes) los envíos del miércoles 21/10</t>
         </is>
       </c>
       <c r="F48" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 21/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 21/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • Holbeach United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 21/10.
-• Søreide IL | Follow-up 1 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 21/10.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Søreide IL | Follow-up 1 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 21/10.</t>
         </is>
       </c>
       <c r="G48" s="39" t="inlineStr">
@@ -3644,7 +3676,7 @@
       </c>
       <c r="J48" s="39" t="n"/>
     </row>
-    <row r="49" ht="33" customHeight="1">
+    <row r="49" ht="47.5" customHeight="1">
       <c r="A49" s="44" t="n">
         <v>46316</v>
       </c>
@@ -3670,7 +3702,7 @@
       </c>
       <c r="F49" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G49" s="45" t="inlineStr">
@@ -3686,7 +3718,7 @@
       </c>
       <c r="J49" s="45" t="n"/>
     </row>
-    <row r="50" ht="33" customHeight="1">
+    <row r="50" ht="47.5" customHeight="1">
       <c r="A50" s="44" t="n">
         <v>46316</v>
       </c>
@@ -3712,7 +3744,7 @@
       </c>
       <c r="F50" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G50" s="45" t="inlineStr">
@@ -3856,7 +3888,7 @@
       </c>
       <c r="J53" s="39" t="n"/>
     </row>
-    <row r="54" ht="178" customHeight="1">
+    <row r="54" ht="163.5" customHeight="1">
       <c r="A54" s="38" t="n">
         <v>46316</v>
       </c>
@@ -3877,16 +3909,15 @@
       </c>
       <c r="E54" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del jueves 22/10</t>
+          <t>Preparar (y programar si puedes) los envíos del jueves 22/10</t>
         </is>
       </c>
       <c r="F54" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 22/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 22/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • IA Akranes | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 22/10.
 • Maidstone United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 22/10.
-• Whitehaven AFC | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 22/10.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Whitehaven AFC | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 22/10.</t>
         </is>
       </c>
       <c r="G54" s="39" t="inlineStr">
@@ -3904,7 +3935,7 @@
       </c>
       <c r="J54" s="39" t="n"/>
     </row>
-    <row r="55" ht="33" customHeight="1">
+    <row r="55" ht="47.5" customHeight="1">
       <c r="A55" s="44" t="n">
         <v>46317</v>
       </c>
@@ -3930,7 +3961,7 @@
       </c>
       <c r="F55" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G55" s="45" t="inlineStr">
@@ -3946,7 +3977,7 @@
       </c>
       <c r="J55" s="45" t="n"/>
     </row>
-    <row r="56" ht="33" customHeight="1">
+    <row r="56" ht="47.5" customHeight="1">
       <c r="A56" s="44" t="n">
         <v>46317</v>
       </c>
@@ -3972,7 +4003,7 @@
       </c>
       <c r="F56" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G56" s="45" t="inlineStr">
@@ -3988,7 +4019,7 @@
       </c>
       <c r="J56" s="45" t="n"/>
     </row>
-    <row r="57" ht="33" customHeight="1">
+    <row r="57" ht="47.5" customHeight="1">
       <c r="A57" s="44" t="n">
         <v>46317</v>
       </c>
@@ -4014,7 +4045,7 @@
       </c>
       <c r="F57" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G57" s="45" t="inlineStr">
@@ -4637,7 +4668,7 @@
       </c>
       <c r="J72" s="39" t="n"/>
     </row>
-    <row r="73" ht="207" customHeight="1">
+    <row r="73" ht="192.5" customHeight="1">
       <c r="A73" s="38" t="n">
         <v>46321</v>
       </c>
@@ -4658,17 +4689,16 @@
       </c>
       <c r="E73" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del martes 27/10</t>
+          <t>Preparar (y programar si puedes) los envíos del martes 27/10</t>
         </is>
       </c>
       <c r="F73" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 27/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 27/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • FC Porte d'Aquitaine | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 27/10.
 • Hastings United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 27/10.
 • Home Farm FC | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 27/10.
-• Virtu Academy | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 27/10.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Virtu Academy | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 27/10.</t>
         </is>
       </c>
       <c r="G73" s="39" t="inlineStr">
@@ -4686,7 +4716,7 @@
       </c>
       <c r="J73" s="39" t="n"/>
     </row>
-    <row r="74" ht="33" customHeight="1">
+    <row r="74" ht="47.5" customHeight="1">
       <c r="A74" s="44" t="n">
         <v>46322</v>
       </c>
@@ -4712,7 +4742,7 @@
       </c>
       <c r="F74" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G74" s="45" t="inlineStr">
@@ -4728,7 +4758,7 @@
       </c>
       <c r="J74" s="45" t="n"/>
     </row>
-    <row r="75" ht="33" customHeight="1">
+    <row r="75" ht="47.5" customHeight="1">
       <c r="A75" s="44" t="n">
         <v>46322</v>
       </c>
@@ -4754,7 +4784,7 @@
       </c>
       <c r="F75" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G75" s="45" t="inlineStr">
@@ -4770,7 +4800,7 @@
       </c>
       <c r="J75" s="45" t="n"/>
     </row>
-    <row r="76" ht="33" customHeight="1">
+    <row r="76" ht="47.5" customHeight="1">
       <c r="A76" s="44" t="n">
         <v>46322</v>
       </c>
@@ -4796,7 +4826,7 @@
       </c>
       <c r="F76" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G76" s="45" t="inlineStr">
@@ -4812,7 +4842,7 @@
       </c>
       <c r="J76" s="45" t="n"/>
     </row>
-    <row r="77" ht="33" customHeight="1">
+    <row r="77" ht="47.5" customHeight="1">
       <c r="A77" s="44" t="n">
         <v>46322</v>
       </c>
@@ -4838,7 +4868,7 @@
       </c>
       <c r="F77" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G77" s="45" t="inlineStr">
@@ -4986,7 +5016,7 @@
       </c>
       <c r="J80" s="39" t="n"/>
     </row>
-    <row r="81" ht="149" customHeight="1">
+    <row r="81" ht="134.5" customHeight="1">
       <c r="A81" s="38" t="n">
         <v>46322</v>
       </c>
@@ -5007,15 +5037,14 @@
       </c>
       <c r="E81" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del miércoles 28/10</t>
+          <t>Preparar (y programar si puedes) los envíos del miércoles 28/10</t>
         </is>
       </c>
       <c r="F81" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 28/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 28/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • Holbeach United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 28/10.
-• Søreide IL | Follow-up 2 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 28/10.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Søreide IL | Follow-up 2 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 28/10.</t>
         </is>
       </c>
       <c r="G81" s="39" t="inlineStr">
@@ -5033,7 +5062,7 @@
       </c>
       <c r="J81" s="39" t="n"/>
     </row>
-    <row r="82" ht="33" customHeight="1">
+    <row r="82" ht="47.5" customHeight="1">
       <c r="A82" s="44" t="n">
         <v>46323</v>
       </c>
@@ -5059,7 +5088,7 @@
       </c>
       <c r="F82" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G82" s="45" t="inlineStr">
@@ -5075,7 +5104,7 @@
       </c>
       <c r="J82" s="45" t="n"/>
     </row>
-    <row r="83" ht="33" customHeight="1">
+    <row r="83" ht="47.5" customHeight="1">
       <c r="A83" s="44" t="n">
         <v>46323</v>
       </c>
@@ -5101,7 +5130,7 @@
       </c>
       <c r="F83" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G83" s="45" t="inlineStr">
@@ -5377,7 +5406,7 @@
       </c>
       <c r="J89" s="39" t="n"/>
     </row>
-    <row r="90" ht="178" customHeight="1">
+    <row r="90" ht="163.5" customHeight="1">
       <c r="A90" s="38" t="n">
         <v>46323</v>
       </c>
@@ -5398,16 +5427,15 @@
       </c>
       <c r="E90" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del jueves 29/10</t>
+          <t>Preparar (y programar si puedes) los envíos del jueves 29/10</t>
         </is>
       </c>
       <c r="F90" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 29/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 29/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • IA Akranes | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 29/10.
 • Maidstone United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 29/10.
-• Whitehaven AFC | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 29/10.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Whitehaven AFC | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 29/10.</t>
         </is>
       </c>
       <c r="G90" s="39" t="inlineStr">
@@ -5425,7 +5453,7 @@
       </c>
       <c r="J90" s="39" t="n"/>
     </row>
-    <row r="91" ht="33" customHeight="1">
+    <row r="91" ht="47.5" customHeight="1">
       <c r="A91" s="44" t="n">
         <v>46324</v>
       </c>
@@ -5451,7 +5479,7 @@
       </c>
       <c r="F91" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G91" s="45" t="inlineStr">
@@ -5467,7 +5495,7 @@
       </c>
       <c r="J91" s="45" t="n"/>
     </row>
-    <row r="92" ht="33" customHeight="1">
+    <row r="92" ht="47.5" customHeight="1">
       <c r="A92" s="44" t="n">
         <v>46324</v>
       </c>
@@ -5493,7 +5521,7 @@
       </c>
       <c r="F92" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G92" s="45" t="inlineStr">
@@ -5509,7 +5537,7 @@
       </c>
       <c r="J92" s="45" t="n"/>
     </row>
-    <row r="93" ht="33" customHeight="1">
+    <row r="93" ht="47.5" customHeight="1">
       <c r="A93" s="44" t="n">
         <v>46324</v>
       </c>
@@ -5535,7 +5563,7 @@
       </c>
       <c r="F93" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G93" s="45" t="inlineStr">
@@ -6166,7 +6194,7 @@
       </c>
       <c r="J108" s="39" t="n"/>
     </row>
-    <row r="109" ht="207" customHeight="1">
+    <row r="109" ht="192.5" customHeight="1">
       <c r="A109" s="38" t="n">
         <v>46328</v>
       </c>
@@ -6187,17 +6215,16 @@
       </c>
       <c r="E109" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del martes 03/11</t>
+          <t>Preparar (y programar si puedes) los envíos del martes 03/11</t>
         </is>
       </c>
       <c r="F109" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 03/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 03/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • FC Porte d'Aquitaine | Follow-up 2 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 03/11.
 • Hastings United | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 03/11.
 • Home Farm FC | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 03/11.
-• Virtu Academy | Follow-up 2 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 03/11.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Virtu Academy | Follow-up 2 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 03/11.</t>
         </is>
       </c>
       <c r="G109" s="39" t="inlineStr">
@@ -6215,7 +6242,7 @@
       </c>
       <c r="J109" s="39" t="n"/>
     </row>
-    <row r="110" ht="33" customHeight="1">
+    <row r="110" ht="47.5" customHeight="1">
       <c r="A110" s="44" t="n">
         <v>46329</v>
       </c>
@@ -6241,7 +6268,7 @@
       </c>
       <c r="F110" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G110" s="45" t="inlineStr">
@@ -6257,7 +6284,7 @@
       </c>
       <c r="J110" s="45" t="n"/>
     </row>
-    <row r="111" ht="33" customHeight="1">
+    <row r="111" ht="47.5" customHeight="1">
       <c r="A111" s="44" t="n">
         <v>46329</v>
       </c>
@@ -6283,7 +6310,7 @@
       </c>
       <c r="F111" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G111" s="45" t="inlineStr">
@@ -6299,7 +6326,7 @@
       </c>
       <c r="J111" s="45" t="n"/>
     </row>
-    <row r="112" ht="33" customHeight="1">
+    <row r="112" ht="47.5" customHeight="1">
       <c r="A112" s="44" t="n">
         <v>46329</v>
       </c>
@@ -6325,7 +6352,7 @@
       </c>
       <c r="F112" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G112" s="45" t="inlineStr">
@@ -6341,7 +6368,7 @@
       </c>
       <c r="J112" s="45" t="n"/>
     </row>
-    <row r="113" ht="33" customHeight="1">
+    <row r="113" ht="47.5" customHeight="1">
       <c r="A113" s="44" t="n">
         <v>46329</v>
       </c>
@@ -6367,7 +6394,7 @@
       </c>
       <c r="F113" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G113" s="45" t="inlineStr">
@@ -6515,7 +6542,7 @@
       </c>
       <c r="J116" s="39" t="n"/>
     </row>
-    <row r="117" ht="149" customHeight="1">
+    <row r="117" ht="134.5" customHeight="1">
       <c r="A117" s="38" t="n">
         <v>46329</v>
       </c>
@@ -6536,15 +6563,14 @@
       </c>
       <c r="E117" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del miércoles 04/11</t>
+          <t>Preparar (y programar si puedes) los envíos del miércoles 04/11</t>
         </is>
       </c>
       <c r="F117" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 04/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 04/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • Holbeach United | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 04/11.
-• Søreide IL | Cierre | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 04/11.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Søreide IL | Cierre | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 04/11.</t>
         </is>
       </c>
       <c r="G117" s="39" t="inlineStr">
@@ -6562,7 +6588,7 @@
       </c>
       <c r="J117" s="39" t="n"/>
     </row>
-    <row r="118" ht="33" customHeight="1">
+    <row r="118" ht="47.5" customHeight="1">
       <c r="A118" s="44" t="n">
         <v>46330</v>
       </c>
@@ -6588,7 +6614,7 @@
       </c>
       <c r="F118" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G118" s="45" t="inlineStr">
@@ -6604,7 +6630,7 @@
       </c>
       <c r="J118" s="45" t="n"/>
     </row>
-    <row r="119" ht="33" customHeight="1">
+    <row r="119" ht="47.5" customHeight="1">
       <c r="A119" s="44" t="n">
         <v>46330</v>
       </c>
@@ -6630,7 +6656,7 @@
       </c>
       <c r="F119" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G119" s="45" t="inlineStr">
@@ -6862,7 +6888,7 @@
       </c>
       <c r="J124" s="39" t="n"/>
     </row>
-    <row r="125" ht="178" customHeight="1">
+    <row r="125" ht="163.5" customHeight="1">
       <c r="A125" s="38" t="n">
         <v>46330</v>
       </c>
@@ -6883,16 +6909,15 @@
       </c>
       <c r="E125" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del jueves 05/11</t>
+          <t>Preparar (y programar si puedes) los envíos del jueves 05/11</t>
         </is>
       </c>
       <c r="F125" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 05/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 05/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • IA Akranes | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 05/11.
 • Maidstone United | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 05/11.
-• Whitehaven AFC | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 05/11.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Whitehaven AFC | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 05/11.</t>
         </is>
       </c>
       <c r="G125" s="39" t="inlineStr">
@@ -6910,7 +6935,7 @@
       </c>
       <c r="J125" s="39" t="n"/>
     </row>
-    <row r="126" ht="33" customHeight="1">
+    <row r="126" ht="47.5" customHeight="1">
       <c r="A126" s="44" t="n">
         <v>46331</v>
       </c>
@@ -6936,7 +6961,7 @@
       </c>
       <c r="F126" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G126" s="45" t="inlineStr">
@@ -6952,7 +6977,7 @@
       </c>
       <c r="J126" s="45" t="n"/>
     </row>
-    <row r="127" ht="33" customHeight="1">
+    <row r="127" ht="47.5" customHeight="1">
       <c r="A127" s="44" t="n">
         <v>46331</v>
       </c>
@@ -6978,7 +7003,7 @@
       </c>
       <c r="F127" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G127" s="45" t="inlineStr">
@@ -6994,7 +7019,7 @@
       </c>
       <c r="J127" s="45" t="n"/>
     </row>
-    <row r="128" ht="33" customHeight="1">
+    <row r="128" ht="47.5" customHeight="1">
       <c r="A128" s="44" t="n">
         <v>46331</v>
       </c>
@@ -7020,7 +7045,7 @@
       </c>
       <c r="F128" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G128" s="45" t="inlineStr">
@@ -7519,7 +7544,7 @@
       </c>
       <c r="J140" s="39" t="n"/>
     </row>
-    <row r="141" ht="149" customHeight="1">
+    <row r="141" ht="134.5" customHeight="1">
       <c r="A141" s="38" t="n">
         <v>46335</v>
       </c>
@@ -7540,15 +7565,14 @@
       </c>
       <c r="E141" s="31" t="inlineStr">
         <is>
-          <t>Programar en Outlook los envíos del martes 10/11</t>
+          <t>Preparar (y programar si puedes) los envíos del martes 10/11</t>
         </is>
       </c>
       <c r="F141" s="39" t="inlineStr">
         <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 10/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada.
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 10/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • FC Porte d'Aquitaine | Cierre | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 10/11.
-• Virtu Academy | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 10/11.
-Importante: si usas Outlook de escritorio clásico, el ordenador debe estar encendido y con Outlook abierto a esa hora; con Outlook web o el Outlook nuevo, el envío sale solo desde el servidor.</t>
+• Virtu Academy | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 10/11.</t>
         </is>
       </c>
       <c r="G141" s="39" t="inlineStr">
@@ -7566,7 +7590,7 @@
       </c>
       <c r="J141" s="39" t="n"/>
     </row>
-    <row r="142" ht="33" customHeight="1">
+    <row r="142" ht="47.5" customHeight="1">
       <c r="A142" s="44" t="n">
         <v>46336</v>
       </c>
@@ -7592,7 +7616,7 @@
       </c>
       <c r="F142" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G142" s="45" t="inlineStr">
@@ -7608,7 +7632,7 @@
       </c>
       <c r="J142" s="45" t="n"/>
     </row>
-    <row r="143" ht="33" customHeight="1">
+    <row r="143" ht="47.5" customHeight="1">
       <c r="A143" s="44" t="n">
         <v>46336</v>
       </c>
@@ -7634,7 +7658,7 @@
       </c>
       <c r="F143" s="45" t="inlineStr">
         <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no lo programaste, envíalo cuando te despiertes. Texto en 'Textos para copiar'.</t>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="G143" s="45" t="inlineStr">
@@ -8550,7 +8574,7 @@
       </c>
       <c r="I5" s="51" t="inlineStr">
         <is>
-          <t>En Outlook: Nuevo correo. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Programar envío &gt; elige fecha y la hora de Nueva York de la columna D.</t>
+          <t>Nuevo correo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Si tu correo permite programar (webmail de Hostinger/Titan: flecha junto a Enviar &gt; Programar), hazlo para la hora de la columna D. Si no, plan B: envíalo a mano a las 07:30 de Nueva York (ver LEEME).</t>
         </is>
       </c>
       <c r="J5" s="51" t="n"/>
@@ -8609,7 +8633,7 @@
       </c>
       <c r="I6" s="51" t="inlineStr">
         <is>
-          <t>En Outlook: Nuevo correo. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Programar envío &gt; elige fecha y la hora de Nueva York de la columna D.</t>
+          <t>Nuevo correo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Si tu correo permite programar (webmail de Hostinger/Titan: flecha junto a Enviar &gt; Programar), hazlo para la hora de la columna D. Si no, plan B: envíalo a mano a las 07:30 de Nueva York (ver LEEME).</t>
         </is>
       </c>
       <c r="J6" s="51" t="n"/>
@@ -8718,7 +8742,7 @@
       </c>
       <c r="I8" s="51" t="inlineStr">
         <is>
-          <t>En Outlook: Nuevo correo. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Programar envío &gt; elige fecha y la hora de Nueva York de la columna D.</t>
+          <t>Nuevo correo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Si tu correo permite programar (webmail de Hostinger/Titan: flecha junto a Enviar &gt; Programar), hazlo para la hora de la columna D. Si no, plan B: envíalo a mano a las 07:30 de Nueva York (ver LEEME).</t>
         </is>
       </c>
       <c r="J8" s="51" t="n"/>
@@ -8776,7 +8800,7 @@
       </c>
       <c r="I9" s="51" t="inlineStr">
         <is>
-          <t>En Outlook: Nuevo correo. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Programar envío &gt; elige fecha y la hora de Nueva York de la columna D.</t>
+          <t>Nuevo correo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Si tu correo permite programar (webmail de Hostinger/Titan: flecha junto a Enviar &gt; Programar), hazlo para la hora de la columna D. Si no, plan B: envíalo a mano a las 07:30 de Nueva York (ver LEEME).</t>
         </is>
       </c>
       <c r="J9" s="51" t="n"/>
@@ -8834,7 +8858,7 @@
       </c>
       <c r="I10" s="51" t="inlineStr">
         <is>
-          <t>En Outlook: Nuevo correo. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Programar envío &gt; elige fecha y la hora de Nueva York de la columna D.</t>
+          <t>Nuevo correo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Si tu correo permite programar (webmail de Hostinger/Titan: flecha junto a Enviar &gt; Programar), hazlo para la hora de la columna D. Si no, plan B: envíalo a mano a las 07:30 de Nueva York (ver LEEME).</t>
         </is>
       </c>
       <c r="J10" s="51" t="n"/>
@@ -9045,7 +9069,7 @@
       </c>
       <c r="I14" s="51" t="inlineStr">
         <is>
-          <t>En Outlook: Nuevo correo. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Programar envío &gt; elige fecha y la hora de Nueva York de la columna D.</t>
+          <t>Nuevo correo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Si tu correo permite programar (webmail de Hostinger/Titan: flecha junto a Enviar &gt; Programar), hazlo para la hora de la columna D. Si no, plan B: envíalo a mano a las 07:30 de Nueva York (ver LEEME).</t>
         </is>
       </c>
       <c r="J14" s="51" t="n"/>
@@ -9104,7 +9128,7 @@
       </c>
       <c r="I15" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J15" s="57" t="n"/>
@@ -9163,7 +9187,7 @@
       </c>
       <c r="I16" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J16" s="57" t="n"/>
@@ -9221,7 +9245,7 @@
       </c>
       <c r="I17" s="51" t="inlineStr">
         <is>
-          <t>En Outlook: Nuevo correo. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Programar envío &gt; elige fecha y la hora de Nueva York de la columna D.</t>
+          <t>Nuevo correo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Si tu correo permite programar (webmail de Hostinger/Titan: flecha junto a Enviar &gt; Programar), hazlo para la hora de la columna D. Si no, plan B: envíalo a mano a las 07:30 de Nueva York (ver LEEME).</t>
         </is>
       </c>
       <c r="J17" s="51" t="n"/>
@@ -9280,7 +9304,7 @@
       </c>
       <c r="I18" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J18" s="57" t="n"/>
@@ -9339,7 +9363,7 @@
       </c>
       <c r="I19" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J19" s="57" t="n"/>
@@ -9397,7 +9421,7 @@
       </c>
       <c r="I20" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J20" s="57" t="n"/>
@@ -9455,7 +9479,7 @@
       </c>
       <c r="I21" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J21" s="57" t="n"/>
@@ -9514,7 +9538,7 @@
       </c>
       <c r="I22" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J22" s="57" t="n"/>
@@ -9573,7 +9597,7 @@
       </c>
       <c r="I23" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J23" s="57" t="n"/>
@@ -9630,7 +9654,7 @@
       </c>
       <c r="I24" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J24" s="60" t="n"/>
@@ -9687,7 +9711,7 @@
       </c>
       <c r="I25" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J25" s="60" t="n"/>
@@ -9745,7 +9769,7 @@
       </c>
       <c r="I26" s="57" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J26" s="57" t="n"/>
@@ -9853,7 +9877,7 @@
       </c>
       <c r="I28" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J28" s="60" t="n"/>
@@ -9961,7 +9985,7 @@
       </c>
       <c r="I30" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J30" s="60" t="n"/>
@@ -10069,7 +10093,7 @@
       </c>
       <c r="I32" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J32" s="60" t="n"/>
@@ -10126,7 +10150,7 @@
       </c>
       <c r="I33" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J33" s="60" t="n"/>
@@ -10234,7 +10258,7 @@
       </c>
       <c r="I35" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J35" s="60" t="n"/>
@@ -10444,7 +10468,7 @@
       </c>
       <c r="I39" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J39" s="60" t="n"/>
@@ -10502,7 +10526,7 @@
       </c>
       <c r="I40" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J40" s="63" t="n"/>
@@ -10560,7 +10584,7 @@
       </c>
       <c r="I41" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J41" s="63" t="n"/>
@@ -10617,7 +10641,7 @@
       </c>
       <c r="I42" s="60" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J42" s="60" t="n"/>
@@ -10726,7 +10750,7 @@
       </c>
       <c r="I44" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J44" s="63" t="n"/>
@@ -10784,7 +10808,7 @@
       </c>
       <c r="I45" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J45" s="63" t="n"/>
@@ -10893,7 +10917,7 @@
       </c>
       <c r="I47" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J47" s="63" t="n"/>
@@ -10951,7 +10975,7 @@
       </c>
       <c r="I48" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J48" s="63" t="n"/>
@@ -11009,7 +11033,7 @@
       </c>
       <c r="I49" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J49" s="63" t="n"/>
@@ -11067,7 +11091,7 @@
       </c>
       <c r="I50" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J50" s="63" t="n"/>
@@ -11125,7 +11149,7 @@
       </c>
       <c r="I51" s="63" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D. Antes de programar, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Programa el envío a la hora de la columna D o, si no puedes programar, envíalo a mano a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J51" s="63" t="n"/>
@@ -12696,7 +12720,7 @@
       <c r="N10" s="13" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -21,7 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Textos para copiar'!$A$4:$K$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Segmento A - Clubes'!$A$5:$P$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Segmento B - America'!$A$5:$O$13</definedName>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1002,23 +1002,23 @@
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>joel.martinez@alwaysup.es está alojado en Hostinger, no en Microsoft. Outlook conectado a ese tipo de cuenta (IMAP) NO tiene 'Programar envío': ese botón solo funciona con cuentas de Microsoft. Por eso no lo veías.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="47.5" customHeight="1">
+          <t>joel.martinez@alwaysup.es está alojado en Hostinger. Outlook con ese tipo de cuenta (IMAP) no tiene 'Programar envío', y el webmail de Hostinger lo cobra aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>Opción 1 (la mejor)</t>
+          <t>Opción 1 (la que has probado)</t>
         </is>
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>Entra al webmail de Hostinger (hpanel.hostinger.com &gt; Correo electrónico &gt; Abrir webmail, o mail.hostinger.com) con tu cuenta. Ahí, junto al botón Enviar, suele haber una flecha con 'Programar envío'. Funciona desde el servidor, aunque tu ordenador esté apagado. Pruébalo con un correo a ti mismo antes de usarlo con un club.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="47.5" customHeight="1">
+          <t>Mail de Apple: botón Enviar con la flecha &gt; Enviar más tarde. Pendiente de confirmar el 14/10: si Mail o el Mac están cerrados o dormidos a esa hora, puede que no salga. Mira Enviados a las 08:00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33" customHeight="1">
       <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Opción 2</t>
@@ -1026,95 +1026,139 @@
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>Outlook de escritorio clásico: en el correo, pestaña Opciones &gt; Retrasar entrega &gt; 'No entregar antes de' + fecha y hora. Funciona, pero Outlook debe estar abierto y el ordenador encendido a esa hora. Outlook nuevo y Outlook web no tienen esta opción para cuentas IMAP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="47.5" customHeight="1">
+          <t>Outlook de escritorio clásico: Opciones &gt; Retrasar entrega. Funciona solo con Outlook abierto y el ordenador encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33" customHeight="1">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>Plan B (sin programar)</t>
+          <t>Plan B (el más seguro)</t>
         </is>
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>Envíalo tú a mano a las 07:30 de Nueva York. Son las 12:30 o 13:30 en Reino Unido, Irlanda, Noruega o Islandia: sigue siendo horario laboral, solo que a media mañana o mediodía en vez de a primera hora. La diferencia de respuesta es pequeña: no vale la pena perder un envío por esto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="33" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>Regla</t>
-        </is>
-      </c>
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>Lo importante es enviar martes a jueves en horario laboral del club. La hora exacta de las 09:30 es una mejora, no una condición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
+          <t>Envío a mano a las 07:30 de Nueva York (12:30 o 13:30 en Europa). Sigue siendo horario laboral. La hora exacta de las 09:30 es una mejora, no una condición: lo importante es enviar de martes a jueves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>TUS FRANJAS DE LLAMADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>Lo que tienes en Calendly (hora Nueva York)</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>Dom 12:00 a 17:00 | Lun 17:30 a 21:00 | Mar 13:00 a 19:00 | Mié 11:00 a 12:30 | Jue 17:00 a 21:00 | Vie 14:00 a 18:00 | Sáb no disponible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="47.5" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>Clubes de Europa (+5 h en UK e Irlanda, +6 h en Noruega, Francia y Países Bajos; +4 y +5 del 25 al 31/10)</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Sirven: Martes 13:00 a 15:00 (18:00 a 20:00 en UK, buen horario para comités de voluntarios) y Miércoles 11:00 a 12:30 (16:00 a 17:30 en UK). Mal: Lunes y Jueves por la tarde (ya es de madrugada allí), Viernes (noche) y Domingo (tarde de domingo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>Familias de América (México, Latinoamérica, EEUU)</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>Sirven: Lunes y Jueves por la tarde y Martes 17:00 a 19:00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="47.5" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Recomendación</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>Dos agendas en Calendly: 'Europa' (martes 13:00 a 15:00 y miércoles 11:00 a 12:30) para 'Always Up Intro Call', y 'Américas' (lunes y jueves tarde, martes 17:00 a 19:00) para 'USA Scholarship Assessment'. Así un club nunca ve una hora de madrugada. Cambia también el nombre 'Assessment Call' para clubes: 'Assessment' es un término de becas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>REGLAS QUE NO SE ROMPEN</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="33" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+    <row r="28" ht="33" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>Nunca</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Adjuntos en el primer correo. Nombrar al partner de becas. Prometer becas o fichajes. Inventar urgencia. Discutir precio por escrito sin tu decisión.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="33" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>Si contestan</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>Paras la cadencia de ese club y abres 'Respuestas tipo' (hoja Textos para copiar). Menos de 4 horas de respuesta en horario del club.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>Si un correo rebota</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>Me lo dices; busco otra dirección del club y te la dejo preparada.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="33" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
+    <row r="31" ht="33" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>Colores</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>Azul claro = email 1, amarillo = follow-up 1, naranja = follow-up 2, gris = cierre, lila = LinkedIn o redes, rojo = pendiente atrasado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1758,7 +1802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1978,47 +2022,49 @@
       </c>
       <c r="J8" s="39" t="n"/>
     </row>
-    <row r="9" ht="47.5" customHeight="1">
-      <c r="A9" s="44" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B9" s="45" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C9" s="46" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="D9" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E9" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Email 1 a Søreide IL</t>
-        </is>
-      </c>
-      <c r="F9" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G9" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H9" s="45" t="n"/>
-      <c r="I9" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J9" s="45" t="n"/>
+    <row r="9" ht="91" customHeight="1">
+      <c r="A9" s="38" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>Prueba de entregabilidad (por qué tus correos caen en spam)</t>
+        </is>
+      </c>
+      <c r="F9" s="39" t="inlineStr">
+        <is>
+          <t>1) Desde joel.martinez@alwaysup.es manda a tu Gmail personal un correo con texto normal (pega el de Holbeach) y asunto normal. 2) Ábrelo en Gmail &gt; tres puntos &gt; Mostrar original: copia lo que ponga en SPF, DKIM y DMARC (deben decir PASS). 3) Entra en mail-tester.com, copia la dirección que te da, mándale desde alwaysup.es el mismo texto y pulsa 'Then check your score'. Pásame la nota y el resultado de SPF, DKIM y DMARC. No pegues nada más.</t>
+        </is>
+      </c>
+      <c r="G9" s="39" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
+      <c r="H9" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J9" s="39" t="n"/>
     </row>
     <row r="10" ht="47.5" customHeight="1">
       <c r="A10" s="44" t="n">
@@ -2031,7 +2077,7 @@
       </c>
       <c r="C10" s="46" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="D10" s="47" t="inlineStr">
@@ -2041,7 +2087,7 @@
       </c>
       <c r="E10" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Email 1 a Holbeach United</t>
+          <t>SALE (programado): Email 1 a Søreide IL</t>
         </is>
       </c>
       <c r="F10" s="45" t="inlineStr">
@@ -2062,51 +2108,49 @@
       </c>
       <c r="J10" s="45" t="n"/>
     </row>
-    <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="38" t="n">
+    <row r="11" ht="47.5" customHeight="1">
+      <c r="A11" s="44" t="n">
         <v>46309</v>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D11" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E11" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F11" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G11" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H11" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J11" s="39" t="n"/>
-    </row>
-    <row r="12" ht="47.5" customHeight="1">
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E11" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Email 1 a Holbeach United</t>
+        </is>
+      </c>
+      <c r="F11" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G11" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H11" s="45" t="n"/>
+      <c r="I11" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J11" s="45" t="n"/>
+    </row>
+    <row r="12" ht="62" customHeight="1">
       <c r="A12" s="38" t="n">
         <v>46309</v>
       </c>
@@ -2120,28 +2164,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D12" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E12" s="31" t="inlineStr">
         <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F12" s="39" t="inlineStr">
         <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G12" s="39" t="inlineStr">
         <is>
-          <t>Enviados / Recibidos</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H12" s="39" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
@@ -2161,27 +2205,27 @@
       </c>
       <c r="C13" s="40" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D13" s="48" t="inlineStr">
-        <is>
-          <t>Brasil/Campus</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>WhatsApp a Leonardo Uren para reactivar la conversación</t>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
         </is>
       </c>
       <c r="F13" s="39" t="inlineStr">
         <is>
-          <t>Copia el texto de 'Reactivar a Leonardo Uren' (hoja Textos para copiar, sección Respuestas tipo). Son las 11:00 en Brasilia. Es un posible partner, no un cliente normal: sin adjuntos.</t>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
         </is>
       </c>
       <c r="G13" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Enviados / Recibidos</t>
         </is>
       </c>
       <c r="H13" s="39" t="n">
@@ -2194,7 +2238,7 @@
       </c>
       <c r="J13" s="39" t="n"/>
     </row>
-    <row r="14" ht="33" customHeight="1">
+    <row r="14" ht="47.5" customHeight="1">
       <c r="A14" s="38" t="n">
         <v>46309</v>
       </c>
@@ -2215,17 +2259,17 @@
       </c>
       <c r="E14" s="31" t="inlineStr">
         <is>
-          <t>Pasarme tu horario de clases para montar el Calendly</t>
+          <t>Confirmar que Apple Mail envió los correos programados</t>
         </is>
       </c>
       <c r="F14" s="39" t="inlineStr">
         <is>
-          <t>Escríbeme tus horas libres reales entre semana (zona Nueva York). Con eso preparo las franjas de llamada y el enlace para la firma.</t>
+          <t>A las 08:00 mira Enviados en alwaysup.es: ¿salieron a la hora? Si no salieron, envíalos a mano (plan B 07:30). Cuéntame qué pasó para decidir si seguimos con Apple Mail.</t>
         </is>
       </c>
       <c r="G14" s="39" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Mail de Apple</t>
         </is>
       </c>
       <c r="H14" s="39" t="n">
@@ -2685,28 +2729,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D25" s="41" t="inlineStr">
+        <is>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Georgia Townsend (Hastings United)</t>
+          <t>Ajustar Calendly por mercado (franjas distintas para clubes y familias)</t>
         </is>
       </c>
       <c r="F25" s="39" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Georgia, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>Mira la tabla de franjas en LEEME. Resumen: para clubes de Europa solo sirven Martes 13:00 a 15:00 y Miércoles 11:00 a 12:30 (hora NY). Para familias de América sirven Lunes y Jueves por la tarde. Pasos: crea el evento 'Always Up Intro Call' (20 min, Zoom) con la agenda Europa, y deja 'USA Scholarship Assessment' con la agenda Américas. Luego pásame el enlace de cada uno.</t>
         </is>
       </c>
       <c r="G25" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Calendly</t>
         </is>
       </c>
       <c r="H25" s="39" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I25" s="39" t="inlineStr">
         <is>
@@ -2717,38 +2761,34 @@
     </row>
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="38" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D26" s="41" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Calentar el dominio: 5 correos reales a gente de confianza</t>
         </is>
       </c>
       <c r="F26" s="39" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G26" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
+          <t>Escribe desde alwaysup.es a 5 personas (familia, amigos, conocidos con Gmail, Outlook o iCloud) un correo normal con una pregunta, y pídeles que respondan. Si caen en spam, que lo marquen como 'No es spam'. Es la forma más rápida de mejorar la reputación de un dominio nuevo.</t>
+        </is>
+      </c>
+      <c r="G26" s="39" t="inlineStr"/>
       <c r="H26" s="39" t="n">
         <v>15</v>
       </c>
@@ -2759,13 +2799,13 @@
       </c>
       <c r="J26" s="39" t="n"/>
     </row>
-    <row r="27" ht="33" customHeight="1">
+    <row r="27" ht="76.5" customHeight="1">
       <c r="A27" s="38" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C27" s="40" t="inlineStr">
@@ -2773,28 +2813,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D27" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>Revisión semanal 1: qué ha pasado esta semana</t>
+          <t>LinkedIn: conectar con Georgia Townsend (Hastings United)</t>
         </is>
       </c>
       <c r="F27" s="39" t="inlineStr">
         <is>
-          <t>Mira la hoja Hoy y anota respuestas, rebotes y llamadas. Pásame un resumen de tres líneas: yo ajusto el plan.</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Georgia, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G27" s="39" t="inlineStr">
         <is>
-          <t>Hoy</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H27" s="39" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I27" s="39" t="inlineStr">
         <is>
@@ -2803,7 +2843,7 @@
       </c>
       <c r="J27" s="39" t="n"/>
     </row>
-    <row r="28" ht="76.5" customHeight="1">
+    <row r="28" ht="62" customHeight="1">
       <c r="A28" s="38" t="n">
         <v>46311</v>
       </c>
@@ -2814,31 +2854,31 @@
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D28" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Callum Lawe (Holbeach United)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F28" s="39" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Callum, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G28" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H28" s="39" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I28" s="39" t="inlineStr">
         <is>
@@ -2847,7 +2887,7 @@
       </c>
       <c r="J28" s="39" t="n"/>
     </row>
-    <row r="29" ht="76.5" customHeight="1">
+    <row r="29" ht="33" customHeight="1">
       <c r="A29" s="38" t="n">
         <v>46311</v>
       </c>
@@ -2861,28 +2901,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Marius Engen (Søreide IL)</t>
+          <t>Revisión semanal 1: qué ha pasado esta semana</t>
         </is>
       </c>
       <c r="F29" s="39" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Marius, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>Mira la hoja Hoy y anota respuestas, rebotes y llamadas. Pásame un resumen de tres líneas: yo ajusto el plan.</t>
         </is>
       </c>
       <c r="G29" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="H29" s="39" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I29" s="39" t="inlineStr">
         <is>
@@ -2891,7 +2931,7 @@
       </c>
       <c r="J29" s="39" t="n"/>
     </row>
-    <row r="30" ht="33" customHeight="1">
+    <row r="30" ht="76.5" customHeight="1">
       <c r="A30" s="38" t="n">
         <v>46311</v>
       </c>
@@ -2905,24 +2945,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D30" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>LinkedIn: conectar con Callum Lawe (Holbeach United)</t>
         </is>
       </c>
       <c r="F30" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G30" s="39" t="inlineStr"/>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Callum, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+        </is>
+      </c>
+      <c r="G30" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
       <c r="H30" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I30" s="39" t="inlineStr">
         <is>
@@ -2931,7 +2975,7 @@
       </c>
       <c r="J30" s="39" t="n"/>
     </row>
-    <row r="31" ht="33" customHeight="1">
+    <row r="31" ht="76.5" customHeight="1">
       <c r="A31" s="38" t="n">
         <v>46311</v>
       </c>
@@ -2945,28 +2989,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D31" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D31" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E31" s="31" t="inlineStr">
         <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+          <t>LinkedIn: conectar con Marius Engen (Søreide IL)</t>
         </is>
       </c>
       <c r="F31" s="39" t="inlineStr">
         <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Marius, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G31" s="39" t="inlineStr">
         <is>
-          <t>Segmento A, B, C</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H31" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I31" s="39" t="inlineStr">
         <is>
@@ -2977,144 +3021,140 @@
     </row>
     <row r="32" ht="33" customHeight="1">
       <c r="A32" s="38" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F32" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G32" s="39" t="inlineStr"/>
+      <c r="H32" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I32" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J32" s="39" t="n"/>
+    </row>
+    <row r="33" ht="33" customHeight="1">
+      <c r="A33" s="38" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D33" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+        </is>
+      </c>
+      <c r="F33" s="39" t="inlineStr">
+        <is>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G33" s="39" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
+      <c r="H33" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I33" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J33" s="39" t="n"/>
+    </row>
+    <row r="34" ht="33" customHeight="1">
+      <c r="A34" s="38" t="n">
         <v>46312</v>
       </c>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C34" s="40" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D32" s="49" t="inlineStr">
+      <c r="D34" s="49" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>Sesión de redes sociales y marca personal con Claude (60 min)</t>
         </is>
       </c>
-      <c r="F32" s="39" t="inlineStr">
+      <c r="F34" s="39" t="inlineStr">
         <is>
           <t>Objetivo: 10.000 seguidores antes de fin de 2026. Salir con un plan de contenido de 4 semanas y qué publicar esta semana. Sin fotos de menores identificables.</t>
         </is>
       </c>
-      <c r="G32" s="39" t="inlineStr">
+      <c r="G34" s="39" t="inlineStr">
         <is>
           <t>Chat con Claude</t>
         </is>
       </c>
-      <c r="H32" s="39" t="n">
+      <c r="H34" s="39" t="n">
         <v>60</v>
       </c>
-      <c r="I32" s="39" t="inlineStr">
+      <c r="I34" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J32" s="39" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="J34" s="39" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>SEMANA  19/10 a 25/10</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="62" customHeight="1">
-      <c r="A34" s="38" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C34" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D34" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F34" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G34" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H34" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I34" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J34" s="39" t="n"/>
-    </row>
-    <row r="35" ht="33" customHeight="1">
-      <c r="A35" s="38" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D35" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
-        </is>
-      </c>
-      <c r="F35" s="39" t="inlineStr">
-        <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
-        </is>
-      </c>
-      <c r="G35" s="39" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H35" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I35" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J35" s="39" t="n"/>
-    </row>
-    <row r="36" ht="33" customHeight="1">
+    <row r="36" ht="62" customHeight="1">
       <c r="A36" s="38" t="n">
         <v>46314</v>
       </c>
@@ -3125,31 +3165,31 @@
       </c>
       <c r="C36" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D36" s="42" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E36" s="31" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F36" s="39" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G36" s="39" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H36" s="39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I36" s="39" t="inlineStr">
         <is>
@@ -3158,7 +3198,7 @@
       </c>
       <c r="J36" s="39" t="n"/>
     </row>
-    <row r="37" ht="76.5" customHeight="1">
+    <row r="37" ht="33" customHeight="1">
       <c r="A37" s="38" t="n">
         <v>46314</v>
       </c>
@@ -3179,17 +3219,17 @@
       </c>
       <c r="E37" s="31" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Luke Johnston (Whitehaven AFC)</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F37" s="39" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Luke, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G37" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H37" s="39" t="n">
@@ -3216,24 +3256,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D38" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E38" s="31" t="inlineStr">
         <is>
-          <t>LinkedIn: 10 minutos de actividad</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F38" s="39" t="inlineStr">
         <is>
-          <t>Acepta conexiones, comenta tres publicaciones de entrenadores o clubes con algo de valor (no publicidad). Eso hace que te vean antes de que llegue el email.</t>
-        </is>
-      </c>
-      <c r="G38" s="39" t="inlineStr"/>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G38" s="39" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
       <c r="H38" s="39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I38" s="39" t="inlineStr">
         <is>
@@ -3242,7 +3286,7 @@
       </c>
       <c r="J38" s="39" t="n"/>
     </row>
-    <row r="39" ht="33" customHeight="1">
+    <row r="39" ht="76.5" customHeight="1">
       <c r="A39" s="38" t="n">
         <v>46314</v>
       </c>
@@ -3256,24 +3300,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D39" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E39" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>LinkedIn: conectar con Luke Johnston (Whitehaven AFC)</t>
         </is>
       </c>
       <c r="F39" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G39" s="39" t="inlineStr"/>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Luke, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+        </is>
+      </c>
+      <c r="G39" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
       <c r="H39" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I39" s="39" t="inlineStr">
         <is>
@@ -3282,7 +3330,7 @@
       </c>
       <c r="J39" s="39" t="n"/>
     </row>
-    <row r="40" ht="192.5" customHeight="1">
+    <row r="40" ht="33" customHeight="1">
       <c r="A40" s="38" t="n">
         <v>46314</v>
       </c>
@@ -3293,20 +3341,100 @@
       </c>
       <c r="C40" s="40" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>LinkedIn: 10 minutos de actividad</t>
+        </is>
+      </c>
+      <c r="F40" s="39" t="inlineStr">
+        <is>
+          <t>Acepta conexiones, comenta tres publicaciones de entrenadores o clubes con algo de valor (no publicidad). Eso hace que te vean antes de que llegue el email.</t>
+        </is>
+      </c>
+      <c r="G40" s="39" t="inlineStr"/>
+      <c r="H40" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="I40" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J40" s="39" t="n"/>
+    </row>
+    <row r="41" ht="33" customHeight="1">
+      <c r="A41" s="38" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D41" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F41" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G41" s="39" t="inlineStr"/>
+      <c r="H41" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I41" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J41" s="39" t="n"/>
+    </row>
+    <row r="42" ht="192.5" customHeight="1">
+      <c r="A42" s="38" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D40" s="43" t="inlineStr">
+      <c r="D42" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E40" s="31" t="inlineStr">
+      <c r="E42" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del martes 20/10</t>
         </is>
       </c>
-      <c r="F40" s="39" t="inlineStr">
+      <c r="F42" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 20/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • FC Porte d'Aquitaine | Email 1 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 20/10.
@@ -3315,104 +3443,20 @@
 • Virtu Academy | Email 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 20/10.</t>
         </is>
       </c>
-      <c r="G40" s="39" t="inlineStr">
+      <c r="G42" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H40" s="39" t="n">
+      <c r="H42" s="39" t="n">
         <v>35</v>
       </c>
-      <c r="I40" s="39" t="inlineStr">
+      <c r="I42" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J40" s="39" t="n"/>
-    </row>
-    <row r="41" ht="47.5" customHeight="1">
-      <c r="A41" s="44" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B41" s="45" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C41" s="46" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="D41" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E41" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Email 1 a FC Porte d'Aquitaine</t>
-        </is>
-      </c>
-      <c r="F41" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G41" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H41" s="45" t="n"/>
-      <c r="I41" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J41" s="45" t="n"/>
-    </row>
-    <row r="42" ht="47.5" customHeight="1">
-      <c r="A42" s="44" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B42" s="45" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C42" s="46" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D42" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E42" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Follow-up 1 a Hastings United</t>
-        </is>
-      </c>
-      <c r="F42" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G42" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H42" s="45" t="n"/>
-      <c r="I42" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J42" s="45" t="n"/>
+      <c r="J42" s="39" t="n"/>
     </row>
     <row r="43" ht="47.5" customHeight="1">
       <c r="A43" s="44" t="n">
@@ -3425,7 +3469,7 @@
       </c>
       <c r="C43" s="46" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="D43" s="47" t="inlineStr">
@@ -3435,7 +3479,7 @@
       </c>
       <c r="E43" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Follow-up 1 a Home Farm FC</t>
+          <t>SALE (programado): Email 1 a FC Porte d'Aquitaine</t>
         </is>
       </c>
       <c r="F43" s="45" t="inlineStr">
@@ -3477,7 +3521,7 @@
       </c>
       <c r="E44" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Email 1 a Virtu Academy</t>
+          <t>SALE (programado): Follow-up 1 a Hastings United</t>
         </is>
       </c>
       <c r="F44" s="45" t="inlineStr">
@@ -3498,95 +3542,91 @@
       </c>
       <c r="J44" s="45" t="n"/>
     </row>
-    <row r="45" ht="62" customHeight="1">
-      <c r="A45" s="38" t="n">
+    <row r="45" ht="47.5" customHeight="1">
+      <c r="A45" s="44" t="n">
         <v>46315</v>
       </c>
-      <c r="B45" s="39" t="inlineStr">
+      <c r="B45" s="45" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C45" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D45" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E45" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F45" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G45" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H45" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I45" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J45" s="39" t="n"/>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D45" s="47" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E45" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Follow-up 1 a Home Farm FC</t>
+        </is>
+      </c>
+      <c r="F45" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G45" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H45" s="45" t="n"/>
+      <c r="I45" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J45" s="45" t="n"/>
     </row>
     <row r="46" ht="47.5" customHeight="1">
-      <c r="A46" s="38" t="n">
+      <c r="A46" s="44" t="n">
         <v>46315</v>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B46" s="45" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C46" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D46" s="43" t="inlineStr">
+      <c r="C46" s="46" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E46" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F46" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G46" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H46" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I46" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J46" s="39" t="n"/>
-    </row>
-    <row r="47" ht="47.5" customHeight="1">
+      <c r="E46" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Email 1 a Virtu Academy</t>
+        </is>
+      </c>
+      <c r="F46" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G46" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H46" s="45" t="n"/>
+      <c r="I46" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J46" s="45" t="n"/>
+    </row>
+    <row r="47" ht="62" customHeight="1">
       <c r="A47" s="38" t="n">
         <v>46315</v>
       </c>
@@ -3597,31 +3637,31 @@
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D47" s="42" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D47" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E47" s="31" t="inlineStr">
         <is>
-          <t>Omar: último mensaje corto si sigue sin contestar</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F47" s="39" t="inlineStr">
         <is>
-          <t>«Hola Omar, no quiero atosigarte. Si en este momento no es prioridad, no pasa nada, lo dejamos aquí y lo retomamos cuando te venga bien. Si quieres seguir, mándame lo que tengas del vídeo y empezamos.» Después pásalo a 'Frío' en el CRM.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G47" s="39" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H47" s="39" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I47" s="39" t="inlineStr">
         <is>
@@ -3630,7 +3670,7 @@
       </c>
       <c r="J47" s="39" t="n"/>
     </row>
-    <row r="48" ht="134.5" customHeight="1">
+    <row r="48" ht="47.5" customHeight="1">
       <c r="A48" s="38" t="n">
         <v>46315</v>
       </c>
@@ -3641,214 +3681,214 @@
       </c>
       <c r="C48" s="40" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
+        </is>
+      </c>
+      <c r="F48" s="39" t="inlineStr">
+        <is>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
+        </is>
+      </c>
+      <c r="G48" s="39" t="inlineStr">
+        <is>
+          <t>Enviados / Recibidos</t>
+        </is>
+      </c>
+      <c r="H48" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I48" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J48" s="39" t="n"/>
+    </row>
+    <row r="49" ht="47.5" customHeight="1">
+      <c r="A49" s="38" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>Omar: último mensaje corto si sigue sin contestar</t>
+        </is>
+      </c>
+      <c r="F49" s="39" t="inlineStr">
+        <is>
+          <t>«Hola Omar, no quiero atosigarte. Si en este momento no es prioridad, no pasa nada, lo dejamos aquí y lo retomamos cuando te venga bien. Si quieres seguir, mándame lo que tengas del vídeo y empezamos.» Después pásalo a 'Frío' en el CRM.</t>
+        </is>
+      </c>
+      <c r="G49" s="39" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
+      <c r="H49" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I49" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J49" s="39" t="n"/>
+    </row>
+    <row r="50" ht="134.5" customHeight="1">
+      <c r="A50" s="38" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D48" s="43" t="inlineStr">
+      <c r="D50" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E48" s="31" t="inlineStr">
+      <c r="E50" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del miércoles 21/10</t>
         </is>
       </c>
-      <c r="F48" s="39" t="inlineStr">
+      <c r="F50" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 21/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • Holbeach United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 21/10.
 • Søreide IL | Follow-up 1 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 21/10.</t>
         </is>
       </c>
-      <c r="G48" s="39" t="inlineStr">
+      <c r="G50" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H48" s="39" t="n">
+      <c r="H50" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="I48" s="39" t="inlineStr">
+      <c r="I50" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J48" s="39" t="n"/>
-    </row>
-    <row r="49" ht="47.5" customHeight="1">
-      <c r="A49" s="44" t="n">
+      <c r="J50" s="39" t="n"/>
+    </row>
+    <row r="51" ht="47.5" customHeight="1">
+      <c r="A51" s="44" t="n">
         <v>46316</v>
       </c>
-      <c r="B49" s="45" t="inlineStr">
+      <c r="B51" s="45" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C49" s="46" t="inlineStr">
+      <c r="C51" s="46" t="inlineStr">
         <is>
           <t>03:30</t>
         </is>
       </c>
-      <c r="D49" s="47" t="inlineStr">
+      <c r="D51" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E49" s="45" t="inlineStr">
+      <c r="E51" s="45" t="inlineStr">
         <is>
           <t>SALE (programado): Follow-up 1 a Søreide IL</t>
         </is>
       </c>
-      <c r="F49" s="45" t="inlineStr">
+      <c r="F51" s="45" t="inlineStr">
         <is>
           <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
-      <c r="G49" s="45" t="inlineStr">
+      <c r="G51" s="45" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H49" s="45" t="n"/>
-      <c r="I49" s="45" t="inlineStr">
+      <c r="H51" s="45" t="n"/>
+      <c r="I51" s="45" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="J49" s="45" t="n"/>
-    </row>
-    <row r="50" ht="47.5" customHeight="1">
-      <c r="A50" s="44" t="n">
+      <c r="J51" s="45" t="n"/>
+    </row>
+    <row r="52" ht="47.5" customHeight="1">
+      <c r="A52" s="44" t="n">
         <v>46316</v>
       </c>
-      <c r="B50" s="45" t="inlineStr">
+      <c r="B52" s="45" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C50" s="46" t="inlineStr">
+      <c r="C52" s="46" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="D50" s="47" t="inlineStr">
+      <c r="D52" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E50" s="45" t="inlineStr">
+      <c r="E52" s="45" t="inlineStr">
         <is>
           <t>SALE (programado): Follow-up 1 a Holbeach United</t>
         </is>
       </c>
-      <c r="F50" s="45" t="inlineStr">
+      <c r="F52" s="45" t="inlineStr">
         <is>
           <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
-      <c r="G50" s="45" t="inlineStr">
+      <c r="G52" s="45" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H50" s="45" t="n"/>
-      <c r="I50" s="45" t="inlineStr">
+      <c r="H52" s="45" t="n"/>
+      <c r="I52" s="45" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="J50" s="45" t="n"/>
-    </row>
-    <row r="51" ht="62" customHeight="1">
-      <c r="A51" s="38" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B51" s="39" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C51" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D51" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F51" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G51" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H51" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I51" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J51" s="39" t="n"/>
-    </row>
-    <row r="52" ht="47.5" customHeight="1">
-      <c r="A52" s="38" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B52" s="39" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C52" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D52" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E52" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F52" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G52" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H52" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I52" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J52" s="39" t="n"/>
-    </row>
-    <row r="53" ht="33" customHeight="1">
+      <c r="J52" s="45" t="n"/>
+    </row>
+    <row r="53" ht="62" customHeight="1">
       <c r="A53" s="38" t="n">
         <v>46316</v>
       </c>
@@ -3859,25 +3899,29 @@
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D53" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D53" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E53" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F53" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G53" s="39" t="inlineStr"/>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G53" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
       <c r="H53" s="39" t="n">
         <v>15</v>
       </c>
@@ -3888,7 +3932,7 @@
       </c>
       <c r="J53" s="39" t="n"/>
     </row>
-    <row r="54" ht="163.5" customHeight="1">
+    <row r="54" ht="47.5" customHeight="1">
       <c r="A54" s="38" t="n">
         <v>46316</v>
       </c>
@@ -3899,20 +3943,104 @@
       </c>
       <c r="C54" s="40" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D54" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E54" s="31" t="inlineStr">
+        <is>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
+        </is>
+      </c>
+      <c r="F54" s="39" t="inlineStr">
+        <is>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
+        </is>
+      </c>
+      <c r="G54" s="39" t="inlineStr">
+        <is>
+          <t>Enviados / Recibidos</t>
+        </is>
+      </c>
+      <c r="H54" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J54" s="39" t="n"/>
+    </row>
+    <row r="55" ht="33" customHeight="1">
+      <c r="A55" s="38" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B55" s="39" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C55" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D55" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F55" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G55" s="39" t="inlineStr"/>
+      <c r="H55" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I55" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J55" s="39" t="n"/>
+    </row>
+    <row r="56" ht="163.5" customHeight="1">
+      <c r="A56" s="38" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B56" s="39" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C56" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D54" s="43" t="inlineStr">
+      <c r="D56" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E54" s="31" t="inlineStr">
+      <c r="E56" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del jueves 22/10</t>
         </is>
       </c>
-      <c r="F54" s="39" t="inlineStr">
+      <c r="F56" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 22/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • IA Akranes | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 22/10.
@@ -3920,104 +4048,20 @@
 • Whitehaven AFC | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 22/10.</t>
         </is>
       </c>
-      <c r="G54" s="39" t="inlineStr">
+      <c r="G56" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H54" s="39" t="n">
+      <c r="H56" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="I54" s="39" t="inlineStr">
+      <c r="I56" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J54" s="39" t="n"/>
-    </row>
-    <row r="55" ht="47.5" customHeight="1">
-      <c r="A55" s="44" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B55" s="45" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C55" s="46" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D55" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E55" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Follow-up 1 a Maidstone United</t>
-        </is>
-      </c>
-      <c r="F55" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G55" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H55" s="45" t="n"/>
-      <c r="I55" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J55" s="45" t="n"/>
-    </row>
-    <row r="56" ht="47.5" customHeight="1">
-      <c r="A56" s="44" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B56" s="45" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C56" s="46" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D56" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E56" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Follow-up 1 a Whitehaven AFC</t>
-        </is>
-      </c>
-      <c r="F56" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G56" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H56" s="45" t="n"/>
-      <c r="I56" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J56" s="45" t="n"/>
+      <c r="J56" s="39" t="n"/>
     </row>
     <row r="57" ht="47.5" customHeight="1">
       <c r="A57" s="44" t="n">
@@ -4030,7 +4074,7 @@
       </c>
       <c r="C57" s="46" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D57" s="47" t="inlineStr">
@@ -4040,7 +4084,7 @@
       </c>
       <c r="E57" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Follow-up 1 a IA Akranes</t>
+          <t>SALE (programado): Follow-up 1 a Maidstone United</t>
         </is>
       </c>
       <c r="F57" s="45" t="inlineStr">
@@ -4061,95 +4105,91 @@
       </c>
       <c r="J57" s="45" t="n"/>
     </row>
-    <row r="58" ht="62" customHeight="1">
-      <c r="A58" s="38" t="n">
+    <row r="58" ht="47.5" customHeight="1">
+      <c r="A58" s="44" t="n">
         <v>46317</v>
       </c>
-      <c r="B58" s="39" t="inlineStr">
+      <c r="B58" s="45" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C58" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D58" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E58" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F58" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G58" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H58" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I58" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J58" s="39" t="n"/>
+      <c r="C58" s="46" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D58" s="47" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E58" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Follow-up 1 a Whitehaven AFC</t>
+        </is>
+      </c>
+      <c r="F58" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G58" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H58" s="45" t="n"/>
+      <c r="I58" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J58" s="45" t="n"/>
     </row>
     <row r="59" ht="47.5" customHeight="1">
-      <c r="A59" s="38" t="n">
+      <c r="A59" s="44" t="n">
         <v>46317</v>
       </c>
-      <c r="B59" s="39" t="inlineStr">
+      <c r="B59" s="45" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C59" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D59" s="43" t="inlineStr">
+      <c r="C59" s="46" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D59" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E59" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F59" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G59" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H59" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I59" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J59" s="39" t="n"/>
-    </row>
-    <row r="60" ht="47.5" customHeight="1">
+      <c r="E59" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Follow-up 1 a IA Akranes</t>
+        </is>
+      </c>
+      <c r="F59" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G59" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H59" s="45" t="n"/>
+      <c r="I59" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J59" s="45" t="n"/>
+    </row>
+    <row r="60" ht="62" customHeight="1">
       <c r="A60" s="38" t="n">
         <v>46317</v>
       </c>
@@ -4160,124 +4200,124 @@
       </c>
       <c r="C60" s="40" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D60" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E60" s="31" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F60" s="39" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G60" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H60" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I60" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J60" s="39" t="n"/>
+    </row>
+    <row r="61" ht="47.5" customHeight="1">
+      <c r="A61" s="38" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B61" s="39" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E61" s="31" t="inlineStr">
+        <is>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
+        </is>
+      </c>
+      <c r="F61" s="39" t="inlineStr">
+        <is>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
+        </is>
+      </c>
+      <c r="G61" s="39" t="inlineStr">
+        <is>
+          <t>Enviados / Recibidos</t>
+        </is>
+      </c>
+      <c r="H61" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I61" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J61" s="39" t="n"/>
+    </row>
+    <row r="62" ht="47.5" customHeight="1">
+      <c r="A62" s="38" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B62" s="39" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C62" s="40" t="inlineStr">
+        <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D60" s="43" t="inlineStr">
+      <c r="D62" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E60" s="31" t="inlineStr">
+      <c r="E62" s="31" t="inlineStr">
         <is>
           <t>Preguntar a Atlético y Real Sociedad por las fechas reales de Semana Santa y verano 2027</t>
         </is>
       </c>
-      <c r="F60" s="39" t="inlineStr">
+      <c r="F62" s="39" t="inlineStr">
         <is>
           <t>Necesitamos saber qué semanas hay disponibles y hasta cuándo se pueden reservar. Con eso tendremos urgencia real y honesta para los follow-ups (hoy no la tenemos). Puede hacerlo Enrique.</t>
         </is>
       </c>
-      <c r="G60" s="39" t="inlineStr"/>
-      <c r="H60" s="39" t="n">
+      <c r="G62" s="39" t="inlineStr"/>
+      <c r="H62" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="I60" s="39" t="inlineStr">
+      <c r="I62" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J60" s="39" t="n"/>
-    </row>
-    <row r="61" ht="62" customHeight="1">
-      <c r="A61" s="38" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B61" s="39" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D61" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E61" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F61" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G61" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H61" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I61" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J61" s="39" t="n"/>
-    </row>
-    <row r="62" ht="62" customHeight="1">
-      <c r="A62" s="38" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B62" s="39" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C62" s="40" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D62" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E62" s="31" t="inlineStr">
-        <is>
-          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
-        </is>
-      </c>
-      <c r="F62" s="39" t="inlineStr">
-        <is>
-          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
-        </is>
-      </c>
-      <c r="G62" s="39" t="inlineStr">
-        <is>
-          <t>plan-outreach-30-dias.md sección 7</t>
-        </is>
-      </c>
-      <c r="H62" s="39" t="n">
-        <v>45</v>
-      </c>
-      <c r="I62" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J62" s="39" t="n"/>
     </row>
-    <row r="63" ht="33" customHeight="1">
+    <row r="63" ht="62" customHeight="1">
       <c r="A63" s="38" t="n">
         <v>46318</v>
       </c>
@@ -4288,27 +4328,31 @@
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D63" s="48" t="inlineStr">
-        <is>
-          <t>International Program</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D63" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E63" s="31" t="inlineStr">
         <is>
-          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F63" s="39" t="inlineStr">
         <is>
-          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
-        </is>
-      </c>
-      <c r="G63" s="39" t="inlineStr"/>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G63" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
       <c r="H63" s="39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I63" s="39" t="inlineStr">
         <is>
@@ -4317,7 +4361,7 @@
       </c>
       <c r="J63" s="39" t="n"/>
     </row>
-    <row r="64" ht="33" customHeight="1">
+    <row r="64" ht="62" customHeight="1">
       <c r="A64" s="38" t="n">
         <v>46318</v>
       </c>
@@ -4331,24 +4375,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D64" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E64" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
         </is>
       </c>
       <c r="F64" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G64" s="39" t="inlineStr"/>
+          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
+        </is>
+      </c>
+      <c r="G64" s="39" t="inlineStr">
+        <is>
+          <t>plan-outreach-30-dias.md sección 7</t>
+        </is>
+      </c>
       <c r="H64" s="39" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I64" s="39" t="inlineStr">
         <is>
@@ -4371,28 +4419,24 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D65" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D65" s="48" t="inlineStr">
+        <is>
+          <t>International Program</t>
         </is>
       </c>
       <c r="E65" s="31" t="inlineStr">
         <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
         </is>
       </c>
       <c r="F65" s="39" t="inlineStr">
         <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G65" s="39" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
+          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
+        </is>
+      </c>
+      <c r="G65" s="39" t="inlineStr"/>
       <c r="H65" s="39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I65" s="39" t="inlineStr">
         <is>
@@ -4403,144 +4447,140 @@
     </row>
     <row r="66" ht="33" customHeight="1">
       <c r="A66" s="38" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B66" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C66" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D66" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E66" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F66" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G66" s="39" t="inlineStr"/>
+      <c r="H66" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I66" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J66" s="39" t="n"/>
+    </row>
+    <row r="67" ht="33" customHeight="1">
+      <c r="A67" s="38" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B67" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C67" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D67" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E67" s="31" t="inlineStr">
+        <is>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+        </is>
+      </c>
+      <c r="F67" s="39" t="inlineStr">
+        <is>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G67" s="39" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
+      <c r="H67" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I67" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J67" s="39" t="n"/>
+    </row>
+    <row r="68" ht="33" customHeight="1">
+      <c r="A68" s="38" t="n">
         <v>46319</v>
       </c>
-      <c r="B66" s="39" t="inlineStr">
+      <c r="B68" s="39" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="C66" s="40" t="inlineStr">
+      <c r="C68" s="40" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D66" s="48" t="inlineStr">
+      <c r="D68" s="48" t="inlineStr">
         <is>
           <t>GEE / Fichas</t>
         </is>
       </c>
-      <c r="E66" s="31" t="inlineStr">
+      <c r="E68" s="31" t="inlineStr">
         <is>
           <t>Revisar las nuevas fichas (GEE, Campus Internacional, International Program)</t>
         </is>
       </c>
-      <c r="F66" s="39" t="inlineStr">
+      <c r="F68" s="39" t="inlineStr">
         <is>
           <t>Las preparo yo tras tu feedback de la ficha de Becas. Tú revisas y me dices qué cambiar.</t>
         </is>
       </c>
-      <c r="G66" s="39" t="inlineStr">
+      <c r="G68" s="39" t="inlineStr">
         <is>
           <t>02-sales/assets</t>
         </is>
       </c>
-      <c r="H66" s="39" t="n">
+      <c r="H68" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="I66" s="39" t="inlineStr">
+      <c r="I68" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J66" s="39" t="n"/>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="37" t="inlineStr">
+      <c r="J68" s="39" t="n"/>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="37" t="inlineStr">
         <is>
           <t>SEMANA  26/10 a 01/11</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="62" customHeight="1">
-      <c r="A68" s="38" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B68" s="39" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C68" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D68" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E68" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F68" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G68" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H68" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I68" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J68" s="39" t="n"/>
-    </row>
-    <row r="69" ht="33" customHeight="1">
-      <c r="A69" s="38" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B69" s="39" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C69" s="40" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D69" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E69" s="31" t="inlineStr">
-        <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
-        </is>
-      </c>
-      <c r="F69" s="39" t="inlineStr">
-        <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
-        </is>
-      </c>
-      <c r="G69" s="39" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H69" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I69" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J69" s="39" t="n"/>
-    </row>
-    <row r="70" ht="33" customHeight="1">
+    <row r="70" ht="62" customHeight="1">
       <c r="A70" s="38" t="n">
         <v>46321</v>
       </c>
@@ -4551,31 +4591,31 @@
       </c>
       <c r="C70" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D70" s="42" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E70" s="31" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F70" s="39" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G70" s="39" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H70" s="39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I70" s="39" t="inlineStr">
         <is>
@@ -4598,28 +4638,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D71" s="48" t="inlineStr">
-        <is>
-          <t>Campus Internacional</t>
+      <c r="D71" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E71" s="31" t="inlineStr">
         <is>
-          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F71" s="39" t="inlineStr">
         <is>
-          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G71" s="39" t="inlineStr">
         <is>
-          <t>Oportunidades y notas</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H71" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I71" s="39" t="inlineStr">
         <is>
@@ -4642,24 +4682,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D72" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D72" s="42" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E72" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F72" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G72" s="39" t="inlineStr"/>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G72" s="39" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
       <c r="H72" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I72" s="39" t="inlineStr">
         <is>
@@ -4668,7 +4712,7 @@
       </c>
       <c r="J72" s="39" t="n"/>
     </row>
-    <row r="73" ht="192.5" customHeight="1">
+    <row r="73" ht="33" customHeight="1">
       <c r="A73" s="38" t="n">
         <v>46321</v>
       </c>
@@ -4679,20 +4723,104 @@
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D73" s="48" t="inlineStr">
+        <is>
+          <t>Campus Internacional</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
+        </is>
+      </c>
+      <c r="F73" s="39" t="inlineStr">
+        <is>
+          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
+        </is>
+      </c>
+      <c r="G73" s="39" t="inlineStr">
+        <is>
+          <t>Oportunidades y notas</t>
+        </is>
+      </c>
+      <c r="H73" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I73" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J73" s="39" t="n"/>
+    </row>
+    <row r="74" ht="33" customHeight="1">
+      <c r="A74" s="38" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B74" s="39" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C74" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D74" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F74" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G74" s="39" t="inlineStr"/>
+      <c r="H74" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I74" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J74" s="39" t="n"/>
+    </row>
+    <row r="75" ht="192.5" customHeight="1">
+      <c r="A75" s="38" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B75" s="39" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C75" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D73" s="43" t="inlineStr">
+      <c r="D75" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E73" s="31" t="inlineStr">
+      <c r="E75" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del martes 27/10</t>
         </is>
       </c>
-      <c r="F73" s="39" t="inlineStr">
+      <c r="F75" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 27/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • FC Porte d'Aquitaine | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 27/10.
@@ -4701,104 +4829,20 @@
 • Virtu Academy | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 27/10.</t>
         </is>
       </c>
-      <c r="G73" s="39" t="inlineStr">
+      <c r="G75" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H73" s="39" t="n">
+      <c r="H75" s="39" t="n">
         <v>35</v>
       </c>
-      <c r="I73" s="39" t="inlineStr">
+      <c r="I75" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J73" s="39" t="n"/>
-    </row>
-    <row r="74" ht="47.5" customHeight="1">
-      <c r="A74" s="44" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B74" s="45" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C74" s="46" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D74" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E74" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Follow-up 1 a FC Porte d'Aquitaine</t>
-        </is>
-      </c>
-      <c r="F74" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G74" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H74" s="45" t="n"/>
-      <c r="I74" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J74" s="45" t="n"/>
-    </row>
-    <row r="75" ht="47.5" customHeight="1">
-      <c r="A75" s="44" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B75" s="45" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C75" s="46" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D75" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E75" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Follow-up 2 a Hastings United</t>
-        </is>
-      </c>
-      <c r="F75" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G75" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H75" s="45" t="n"/>
-      <c r="I75" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J75" s="45" t="n"/>
+      <c r="J75" s="39" t="n"/>
     </row>
     <row r="76" ht="47.5" customHeight="1">
       <c r="A76" s="44" t="n">
@@ -4811,7 +4855,7 @@
       </c>
       <c r="C76" s="46" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D76" s="47" t="inlineStr">
@@ -4821,7 +4865,7 @@
       </c>
       <c r="E76" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Follow-up 2 a Home Farm FC</t>
+          <t>SALE (programado): Follow-up 1 a FC Porte d'Aquitaine</t>
         </is>
       </c>
       <c r="F76" s="45" t="inlineStr">
@@ -4863,7 +4907,7 @@
       </c>
       <c r="E77" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Follow-up 1 a Virtu Academy</t>
+          <t>SALE (programado): Follow-up 2 a Hastings United</t>
         </is>
       </c>
       <c r="F77" s="45" t="inlineStr">
@@ -4884,95 +4928,91 @@
       </c>
       <c r="J77" s="45" t="n"/>
     </row>
-    <row r="78" ht="62" customHeight="1">
-      <c r="A78" s="38" t="n">
+    <row r="78" ht="47.5" customHeight="1">
+      <c r="A78" s="44" t="n">
         <v>46322</v>
       </c>
-      <c r="B78" s="39" t="inlineStr">
+      <c r="B78" s="45" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C78" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D78" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E78" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F78" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G78" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H78" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I78" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J78" s="39" t="n"/>
+      <c r="C78" s="46" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D78" s="47" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E78" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Follow-up 2 a Home Farm FC</t>
+        </is>
+      </c>
+      <c r="F78" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G78" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H78" s="45" t="n"/>
+      <c r="I78" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J78" s="45" t="n"/>
     </row>
     <row r="79" ht="47.5" customHeight="1">
-      <c r="A79" s="38" t="n">
+      <c r="A79" s="44" t="n">
         <v>46322</v>
       </c>
-      <c r="B79" s="39" t="inlineStr">
+      <c r="B79" s="45" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C79" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="inlineStr">
+      <c r="C79" s="46" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D79" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F79" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G79" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H79" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I79" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J79" s="39" t="n"/>
-    </row>
-    <row r="80" ht="33" customHeight="1">
+      <c r="E79" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Follow-up 1 a Virtu Academy</t>
+        </is>
+      </c>
+      <c r="F79" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G79" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H79" s="45" t="n"/>
+      <c r="I79" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J79" s="45" t="n"/>
+    </row>
+    <row r="80" ht="62" customHeight="1">
       <c r="A80" s="38" t="n">
         <v>46322</v>
       </c>
@@ -4983,31 +5023,31 @@
       </c>
       <c r="C80" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D80" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E80" s="31" t="inlineStr">
         <is>
-          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F80" s="39" t="inlineStr">
         <is>
-          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G80" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H80" s="39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I80" s="39" t="inlineStr">
         <is>
@@ -5016,7 +5056,7 @@
       </c>
       <c r="J80" s="39" t="n"/>
     </row>
-    <row r="81" ht="134.5" customHeight="1">
+    <row r="81" ht="47.5" customHeight="1">
       <c r="A81" s="38" t="n">
         <v>46322</v>
       </c>
@@ -5027,214 +5067,214 @@
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
+        </is>
+      </c>
+      <c r="F81" s="39" t="inlineStr">
+        <is>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
+        </is>
+      </c>
+      <c r="G81" s="39" t="inlineStr">
+        <is>
+          <t>Enviados / Recibidos</t>
+        </is>
+      </c>
+      <c r="H81" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I81" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J81" s="39" t="n"/>
+    </row>
+    <row r="82" ht="33" customHeight="1">
+      <c r="A82" s="38" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B82" s="39" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C82" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D82" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
+        </is>
+      </c>
+      <c r="F82" s="39" t="inlineStr">
+        <is>
+          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
+        </is>
+      </c>
+      <c r="G82" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H82" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="I82" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J82" s="39" t="n"/>
+    </row>
+    <row r="83" ht="134.5" customHeight="1">
+      <c r="A83" s="38" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C83" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D81" s="43" t="inlineStr">
+      <c r="D83" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E81" s="31" t="inlineStr">
+      <c r="E83" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del miércoles 28/10</t>
         </is>
       </c>
-      <c r="F81" s="39" t="inlineStr">
+      <c r="F83" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 28/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • Holbeach United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 28/10.
 • Søreide IL | Follow-up 2 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 28/10.</t>
         </is>
       </c>
-      <c r="G81" s="39" t="inlineStr">
+      <c r="G83" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H81" s="39" t="n">
+      <c r="H83" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="I81" s="39" t="inlineStr">
+      <c r="I83" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J81" s="39" t="n"/>
-    </row>
-    <row r="82" ht="47.5" customHeight="1">
-      <c r="A82" s="44" t="n">
+      <c r="J83" s="39" t="n"/>
+    </row>
+    <row r="84" ht="47.5" customHeight="1">
+      <c r="A84" s="44" t="n">
         <v>46323</v>
       </c>
-      <c r="B82" s="45" t="inlineStr">
+      <c r="B84" s="45" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C82" s="46" t="inlineStr">
+      <c r="C84" s="46" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="D82" s="47" t="inlineStr">
+      <c r="D84" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E82" s="45" t="inlineStr">
+      <c r="E84" s="45" t="inlineStr">
         <is>
           <t>SALE (programado): Follow-up 2 a Søreide IL</t>
         </is>
       </c>
-      <c r="F82" s="45" t="inlineStr">
+      <c r="F84" s="45" t="inlineStr">
         <is>
           <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
-      <c r="G82" s="45" t="inlineStr">
+      <c r="G84" s="45" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H82" s="45" t="n"/>
-      <c r="I82" s="45" t="inlineStr">
+      <c r="H84" s="45" t="n"/>
+      <c r="I84" s="45" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="J82" s="45" t="n"/>
-    </row>
-    <row r="83" ht="47.5" customHeight="1">
-      <c r="A83" s="44" t="n">
+      <c r="J84" s="45" t="n"/>
+    </row>
+    <row r="85" ht="47.5" customHeight="1">
+      <c r="A85" s="44" t="n">
         <v>46323</v>
       </c>
-      <c r="B83" s="45" t="inlineStr">
+      <c r="B85" s="45" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C83" s="46" t="inlineStr">
+      <c r="C85" s="46" t="inlineStr">
         <is>
           <t>05:30</t>
         </is>
       </c>
-      <c r="D83" s="47" t="inlineStr">
+      <c r="D85" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E83" s="45" t="inlineStr">
+      <c r="E85" s="45" t="inlineStr">
         <is>
           <t>SALE (programado): Follow-up 2 a Holbeach United</t>
         </is>
       </c>
-      <c r="F83" s="45" t="inlineStr">
+      <c r="F85" s="45" t="inlineStr">
         <is>
           <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
-      <c r="G83" s="45" t="inlineStr">
+      <c r="G85" s="45" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H83" s="45" t="n"/>
-      <c r="I83" s="45" t="inlineStr">
+      <c r="H85" s="45" t="n"/>
+      <c r="I85" s="45" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="J83" s="45" t="n"/>
-    </row>
-    <row r="84" ht="62" customHeight="1">
-      <c r="A84" s="38" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B84" s="39" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C84" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E84" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F84" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G84" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H84" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I84" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J84" s="39" t="n"/>
-    </row>
-    <row r="85" ht="47.5" customHeight="1">
-      <c r="A85" s="38" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B85" s="39" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C85" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D85" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E85" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F85" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G85" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H85" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I85" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J85" s="39" t="n"/>
-    </row>
-    <row r="86" ht="47.5" customHeight="1">
+      <c r="J85" s="45" t="n"/>
+    </row>
+    <row r="86" ht="62" customHeight="1">
       <c r="A86" s="38" t="n">
         <v>46323</v>
       </c>
@@ -5245,31 +5285,31 @@
       </c>
       <c r="C86" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D86" s="42" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D86" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E86" s="31" t="inlineStr">
         <is>
-          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F86" s="39" t="inlineStr">
         <is>
-          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G86" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H86" s="39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I86" s="39" t="inlineStr">
         <is>
@@ -5278,7 +5318,7 @@
       </c>
       <c r="J86" s="39" t="n"/>
     </row>
-    <row r="87" ht="76.5" customHeight="1">
+    <row r="87" ht="47.5" customHeight="1">
       <c r="A87" s="38" t="n">
         <v>46323</v>
       </c>
@@ -5289,7 +5329,7 @@
       </c>
       <c r="C87" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>8:00</t>
         </is>
       </c>
       <c r="D87" s="43" t="inlineStr">
@@ -5299,17 +5339,17 @@
       </c>
       <c r="E87" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
         </is>
       </c>
       <c r="F87" s="39" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
         </is>
       </c>
       <c r="G87" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Enviados / Recibidos</t>
         </is>
       </c>
       <c r="H87" s="39" t="n">
@@ -5322,7 +5362,7 @@
       </c>
       <c r="J87" s="39" t="n"/>
     </row>
-    <row r="88" ht="76.5" customHeight="1">
+    <row r="88" ht="47.5" customHeight="1">
       <c r="A88" s="38" t="n">
         <v>46323</v>
       </c>
@@ -5336,19 +5376,19 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D88" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D88" s="42" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E88" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
+          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
         </is>
       </c>
       <c r="F88" s="39" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
         </is>
       </c>
       <c r="G88" s="39" t="inlineStr">
@@ -5357,7 +5397,7 @@
         </is>
       </c>
       <c r="H88" s="39" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I88" s="39" t="inlineStr">
         <is>
@@ -5366,7 +5406,7 @@
       </c>
       <c r="J88" s="39" t="n"/>
     </row>
-    <row r="89" ht="33" customHeight="1">
+    <row r="89" ht="76.5" customHeight="1">
       <c r="A89" s="38" t="n">
         <v>46323</v>
       </c>
@@ -5380,24 +5420,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D89" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D89" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E89" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
         </is>
       </c>
       <c r="F89" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G89" s="39" t="inlineStr"/>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G89" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
       <c r="H89" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I89" s="39" t="inlineStr">
         <is>
@@ -5406,7 +5450,7 @@
       </c>
       <c r="J89" s="39" t="n"/>
     </row>
-    <row r="90" ht="163.5" customHeight="1">
+    <row r="90" ht="76.5" customHeight="1">
       <c r="A90" s="38" t="n">
         <v>46323</v>
       </c>
@@ -5417,20 +5461,104 @@
       </c>
       <c r="C90" s="40" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D90" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E90" s="31" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
+        </is>
+      </c>
+      <c r="F90" s="39" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G90" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H90" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I90" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J90" s="39" t="n"/>
+    </row>
+    <row r="91" ht="33" customHeight="1">
+      <c r="A91" s="38" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B91" s="39" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C91" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D91" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E91" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F91" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G91" s="39" t="inlineStr"/>
+      <c r="H91" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I91" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J91" s="39" t="n"/>
+    </row>
+    <row r="92" ht="163.5" customHeight="1">
+      <c r="A92" s="38" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B92" s="39" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C92" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D90" s="43" t="inlineStr">
+      <c r="D92" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E90" s="31" t="inlineStr">
+      <c r="E92" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del jueves 29/10</t>
         </is>
       </c>
-      <c r="F90" s="39" t="inlineStr">
+      <c r="F92" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 29/10). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • IA Akranes | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 29/10.
@@ -5438,104 +5566,20 @@
 • Whitehaven AFC | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 29/10.</t>
         </is>
       </c>
-      <c r="G90" s="39" t="inlineStr">
+      <c r="G92" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H90" s="39" t="n">
+      <c r="H92" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="I90" s="39" t="inlineStr">
+      <c r="I92" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J90" s="39" t="n"/>
-    </row>
-    <row r="91" ht="47.5" customHeight="1">
-      <c r="A91" s="44" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B91" s="45" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C91" s="46" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D91" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E91" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Follow-up 2 a IA Akranes</t>
-        </is>
-      </c>
-      <c r="F91" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G91" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H91" s="45" t="n"/>
-      <c r="I91" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J91" s="45" t="n"/>
-    </row>
-    <row r="92" ht="47.5" customHeight="1">
-      <c r="A92" s="44" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B92" s="45" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C92" s="46" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D92" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E92" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Follow-up 2 a Maidstone United</t>
-        </is>
-      </c>
-      <c r="F92" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G92" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H92" s="45" t="n"/>
-      <c r="I92" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J92" s="45" t="n"/>
+      <c r="J92" s="39" t="n"/>
     </row>
     <row r="93" ht="47.5" customHeight="1">
       <c r="A93" s="44" t="n">
@@ -5558,7 +5602,7 @@
       </c>
       <c r="E93" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Follow-up 2 a Whitehaven AFC</t>
+          <t>SALE (programado): Follow-up 2 a IA Akranes</t>
         </is>
       </c>
       <c r="F93" s="45" t="inlineStr">
@@ -5579,95 +5623,91 @@
       </c>
       <c r="J93" s="45" t="n"/>
     </row>
-    <row r="94" ht="62" customHeight="1">
-      <c r="A94" s="38" t="n">
+    <row r="94" ht="47.5" customHeight="1">
+      <c r="A94" s="44" t="n">
         <v>46324</v>
       </c>
-      <c r="B94" s="39" t="inlineStr">
+      <c r="B94" s="45" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C94" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D94" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E94" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F94" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G94" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H94" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I94" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J94" s="39" t="n"/>
+      <c r="C94" s="46" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D94" s="47" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E94" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Follow-up 2 a Maidstone United</t>
+        </is>
+      </c>
+      <c r="F94" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G94" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H94" s="45" t="n"/>
+      <c r="I94" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J94" s="45" t="n"/>
     </row>
     <row r="95" ht="47.5" customHeight="1">
-      <c r="A95" s="38" t="n">
+      <c r="A95" s="44" t="n">
         <v>46324</v>
       </c>
-      <c r="B95" s="39" t="inlineStr">
+      <c r="B95" s="45" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C95" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D95" s="43" t="inlineStr">
+      <c r="C95" s="46" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D95" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E95" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F95" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G95" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H95" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I95" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J95" s="39" t="n"/>
-    </row>
-    <row r="96" ht="76.5" customHeight="1">
+      <c r="E95" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Follow-up 2 a Whitehaven AFC</t>
+        </is>
+      </c>
+      <c r="F95" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G95" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H95" s="45" t="n"/>
+      <c r="I95" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J95" s="45" t="n"/>
+    </row>
+    <row r="96" ht="62" customHeight="1">
       <c r="A96" s="38" t="n">
         <v>46324</v>
       </c>
@@ -5678,31 +5718,31 @@
       </c>
       <c r="C96" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D96" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D96" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E96" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F96" s="39" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G96" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H96" s="39" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I96" s="39" t="inlineStr">
         <is>
@@ -5711,7 +5751,7 @@
       </c>
       <c r="J96" s="39" t="n"/>
     </row>
-    <row r="97" ht="76.5" customHeight="1">
+    <row r="97" ht="47.5" customHeight="1">
       <c r="A97" s="38" t="n">
         <v>46324</v>
       </c>
@@ -5722,7 +5762,7 @@
       </c>
       <c r="C97" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>8:00</t>
         </is>
       </c>
       <c r="D97" s="43" t="inlineStr">
@@ -5732,17 +5772,17 @@
       </c>
       <c r="E97" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
         </is>
       </c>
       <c r="F97" s="39" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
         </is>
       </c>
       <c r="G97" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Enviados / Recibidos</t>
         </is>
       </c>
       <c r="H97" s="39" t="n">
@@ -5755,42 +5795,42 @@
       </c>
       <c r="J97" s="39" t="n"/>
     </row>
-    <row r="98" ht="62" customHeight="1">
+    <row r="98" ht="76.5" customHeight="1">
       <c r="A98" s="38" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B98" s="39" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C98" s="40" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D98" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D98" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E98" s="31" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
         </is>
       </c>
       <c r="F98" s="39" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G98" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H98" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I98" s="39" t="inlineStr">
         <is>
@@ -5801,11 +5841,11 @@
     </row>
     <row r="99" ht="76.5" customHeight="1">
       <c r="A99" s="38" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B99" s="39" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C99" s="40" t="inlineStr">
@@ -5820,7 +5860,7 @@
       </c>
       <c r="E99" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
+          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
         </is>
       </c>
       <c r="F99" s="39" t="inlineStr">
@@ -5843,7 +5883,7 @@
       </c>
       <c r="J99" s="39" t="n"/>
     </row>
-    <row r="100" ht="76.5" customHeight="1">
+    <row r="100" ht="62" customHeight="1">
       <c r="A100" s="38" t="n">
         <v>46325</v>
       </c>
@@ -5854,31 +5894,31 @@
       </c>
       <c r="C100" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D100" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D100" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E100" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F100" s="39" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G100" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H100" s="39" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I100" s="39" t="inlineStr">
         <is>
@@ -5908,7 +5948,7 @@
       </c>
       <c r="E101" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
+          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
         </is>
       </c>
       <c r="F101" s="39" t="inlineStr">
@@ -5931,7 +5971,7 @@
       </c>
       <c r="J101" s="39" t="n"/>
     </row>
-    <row r="102" ht="33" customHeight="1">
+    <row r="102" ht="76.5" customHeight="1">
       <c r="A102" s="38" t="n">
         <v>46325</v>
       </c>
@@ -5945,24 +5985,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D102" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D102" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E102" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
         </is>
       </c>
       <c r="F102" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G102" s="39" t="inlineStr"/>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G102" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
       <c r="H102" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I102" s="39" t="inlineStr">
         <is>
@@ -5971,7 +6015,7 @@
       </c>
       <c r="J102" s="39" t="n"/>
     </row>
-    <row r="103" ht="33" customHeight="1">
+    <row r="103" ht="76.5" customHeight="1">
       <c r="A103" s="38" t="n">
         <v>46325</v>
       </c>
@@ -5985,75 +6029,108 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D103" s="41" t="inlineStr">
+      <c r="D103" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E103" s="31" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
+        </is>
+      </c>
+      <c r="F103" s="39" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G103" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H103" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I103" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J103" s="39" t="n"/>
+    </row>
+    <row r="104" ht="33" customHeight="1">
+      <c r="A104" s="38" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B104" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C104" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D104" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E104" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F104" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G104" s="39" t="inlineStr"/>
+      <c r="H104" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I104" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J104" s="39" t="n"/>
+    </row>
+    <row r="105" ht="33" customHeight="1">
+      <c r="A105" s="38" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B105" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C105" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D105" s="41" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E103" s="31" t="inlineStr">
+      <c r="E105" s="31" t="inlineStr">
         <is>
           <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
-      <c r="F103" s="39" t="inlineStr">
+      <c r="F105" s="39" t="inlineStr">
         <is>
           <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
-      <c r="G103" s="39" t="inlineStr">
+      <c r="G105" s="39" t="inlineStr">
         <is>
           <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H103" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I103" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J103" s="39" t="n"/>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="37" t="inlineStr">
-        <is>
-          <t>SEMANA  02/11 a 08/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="62" customHeight="1">
-      <c r="A105" s="38" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B105" s="39" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C105" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D105" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E105" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F105" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G105" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H105" s="39" t="n">
@@ -6066,51 +6143,14 @@
       </c>
       <c r="J105" s="39" t="n"/>
     </row>
-    <row r="106" ht="33" customHeight="1">
-      <c r="A106" s="38" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B106" s="39" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C106" s="40" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D106" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E106" s="31" t="inlineStr">
-        <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
-        </is>
-      </c>
-      <c r="F106" s="39" t="inlineStr">
-        <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
-        </is>
-      </c>
-      <c r="G106" s="39" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H106" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I106" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J106" s="39" t="n"/>
-    </row>
-    <row r="107" ht="33" customHeight="1">
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="37" t="inlineStr">
+        <is>
+          <t>SEMANA  02/11 a 08/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="62" customHeight="1">
       <c r="A107" s="38" t="n">
         <v>46328</v>
       </c>
@@ -6121,31 +6161,31 @@
       </c>
       <c r="C107" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D107" s="42" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E107" s="31" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F107" s="39" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G107" s="39" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H107" s="39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I107" s="39" t="inlineStr">
         <is>
@@ -6168,24 +6208,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D108" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D108" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E108" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F108" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G108" s="39" t="inlineStr"/>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+        </is>
+      </c>
+      <c r="G108" s="39" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
       <c r="H108" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I108" s="39" t="inlineStr">
         <is>
@@ -6194,7 +6238,7 @@
       </c>
       <c r="J108" s="39" t="n"/>
     </row>
-    <row r="109" ht="192.5" customHeight="1">
+    <row r="109" ht="33" customHeight="1">
       <c r="A109" s="38" t="n">
         <v>46328</v>
       </c>
@@ -6205,20 +6249,104 @@
       </c>
       <c r="C109" s="40" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D109" s="42" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E109" s="31" t="inlineStr">
+        <is>
+          <t>Revisar leads de becas con acción vencida</t>
+        </is>
+      </c>
+      <c r="F109" s="39" t="inlineStr">
+        <is>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G109" s="39" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
+      <c r="H109" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="I109" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J109" s="39" t="n"/>
+    </row>
+    <row r="110" ht="33" customHeight="1">
+      <c r="A110" s="38" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B110" s="39" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C110" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D110" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E110" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F110" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G110" s="39" t="inlineStr"/>
+      <c r="H110" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I110" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J110" s="39" t="n"/>
+    </row>
+    <row r="111" ht="192.5" customHeight="1">
+      <c r="A111" s="38" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B111" s="39" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D109" s="43" t="inlineStr">
+      <c r="D111" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E109" s="31" t="inlineStr">
+      <c r="E111" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del martes 03/11</t>
         </is>
       </c>
-      <c r="F109" s="39" t="inlineStr">
+      <c r="F111" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 03/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • FC Porte d'Aquitaine | Follow-up 2 | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 03/11.
@@ -6227,104 +6355,20 @@
 • Virtu Academy | Follow-up 2 | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 03/11.</t>
         </is>
       </c>
-      <c r="G109" s="39" t="inlineStr">
+      <c r="G111" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H109" s="39" t="n">
+      <c r="H111" s="39" t="n">
         <v>35</v>
       </c>
-      <c r="I109" s="39" t="inlineStr">
+      <c r="I111" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J109" s="39" t="n"/>
-    </row>
-    <row r="110" ht="47.5" customHeight="1">
-      <c r="A110" s="44" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B110" s="45" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C110" s="46" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="D110" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E110" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Follow-up 2 a FC Porte d'Aquitaine</t>
-        </is>
-      </c>
-      <c r="F110" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G110" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H110" s="45" t="n"/>
-      <c r="I110" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J110" s="45" t="n"/>
-    </row>
-    <row r="111" ht="47.5" customHeight="1">
-      <c r="A111" s="44" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B111" s="45" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C111" s="46" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D111" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E111" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Cierre a Hastings United</t>
-        </is>
-      </c>
-      <c r="F111" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G111" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H111" s="45" t="n"/>
-      <c r="I111" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J111" s="45" t="n"/>
+      <c r="J111" s="39" t="n"/>
     </row>
     <row r="112" ht="47.5" customHeight="1">
       <c r="A112" s="44" t="n">
@@ -6337,7 +6381,7 @@
       </c>
       <c r="C112" s="46" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="D112" s="47" t="inlineStr">
@@ -6347,7 +6391,7 @@
       </c>
       <c r="E112" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Cierre a Home Farm FC</t>
+          <t>SALE (programado): Follow-up 2 a FC Porte d'Aquitaine</t>
         </is>
       </c>
       <c r="F112" s="45" t="inlineStr">
@@ -6389,7 +6433,7 @@
       </c>
       <c r="E113" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Follow-up 2 a Virtu Academy</t>
+          <t>SALE (programado): Cierre a Hastings United</t>
         </is>
       </c>
       <c r="F113" s="45" t="inlineStr">
@@ -6410,95 +6454,91 @@
       </c>
       <c r="J113" s="45" t="n"/>
     </row>
-    <row r="114" ht="62" customHeight="1">
-      <c r="A114" s="38" t="n">
+    <row r="114" ht="47.5" customHeight="1">
+      <c r="A114" s="44" t="n">
         <v>46329</v>
       </c>
-      <c r="B114" s="39" t="inlineStr">
+      <c r="B114" s="45" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C114" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D114" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E114" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F114" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G114" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H114" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I114" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J114" s="39" t="n"/>
+      <c r="C114" s="46" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D114" s="47" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E114" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Cierre a Home Farm FC</t>
+        </is>
+      </c>
+      <c r="F114" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G114" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H114" s="45" t="n"/>
+      <c r="I114" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J114" s="45" t="n"/>
     </row>
     <row r="115" ht="47.5" customHeight="1">
-      <c r="A115" s="38" t="n">
+      <c r="A115" s="44" t="n">
         <v>46329</v>
       </c>
-      <c r="B115" s="39" t="inlineStr">
+      <c r="B115" s="45" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C115" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D115" s="43" t="inlineStr">
+      <c r="C115" s="46" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D115" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E115" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F115" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G115" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H115" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I115" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J115" s="39" t="n"/>
-    </row>
-    <row r="116" ht="30" customHeight="1">
+      <c r="E115" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Follow-up 2 a Virtu Academy</t>
+        </is>
+      </c>
+      <c r="F115" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G115" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H115" s="45" t="n"/>
+      <c r="I115" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J115" s="45" t="n"/>
+    </row>
+    <row r="116" ht="62" customHeight="1">
       <c r="A116" s="38" t="n">
         <v>46329</v>
       </c>
@@ -6509,31 +6549,31 @@
       </c>
       <c r="C116" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D116" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D116" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E116" s="31" t="inlineStr">
         <is>
-          <t>Enviar la tanda 4 de emails</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F116" s="39" t="inlineStr">
         <is>
-          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G116" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H116" s="39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I116" s="39" t="inlineStr">
         <is>
@@ -6542,7 +6582,7 @@
       </c>
       <c r="J116" s="39" t="n"/>
     </row>
-    <row r="117" ht="134.5" customHeight="1">
+    <row r="117" ht="47.5" customHeight="1">
       <c r="A117" s="38" t="n">
         <v>46329</v>
       </c>
@@ -6553,214 +6593,214 @@
       </c>
       <c r="C117" s="40" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D117" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E117" s="31" t="inlineStr">
+        <is>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
+        </is>
+      </c>
+      <c r="F117" s="39" t="inlineStr">
+        <is>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
+        </is>
+      </c>
+      <c r="G117" s="39" t="inlineStr">
+        <is>
+          <t>Enviados / Recibidos</t>
+        </is>
+      </c>
+      <c r="H117" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I117" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J117" s="39" t="n"/>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="38" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B118" s="39" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C118" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D118" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E118" s="31" t="inlineStr">
+        <is>
+          <t>Enviar la tanda 4 de emails</t>
+        </is>
+      </c>
+      <c r="F118" s="39" t="inlineStr">
+        <is>
+          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
+        </is>
+      </c>
+      <c r="G118" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H118" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="I118" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J118" s="39" t="n"/>
+    </row>
+    <row r="119" ht="134.5" customHeight="1">
+      <c r="A119" s="38" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B119" s="39" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C119" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D117" s="43" t="inlineStr">
+      <c r="D119" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E117" s="31" t="inlineStr">
+      <c r="E119" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del miércoles 04/11</t>
         </is>
       </c>
-      <c r="F117" s="39" t="inlineStr">
+      <c r="F119" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 04/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • Holbeach United | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 04/11.
 • Søreide IL | Cierre | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 04/11.</t>
         </is>
       </c>
-      <c r="G117" s="39" t="inlineStr">
+      <c r="G119" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H117" s="39" t="n">
+      <c r="H119" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="I117" s="39" t="inlineStr">
+      <c r="I119" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J117" s="39" t="n"/>
-    </row>
-    <row r="118" ht="47.5" customHeight="1">
-      <c r="A118" s="44" t="n">
+      <c r="J119" s="39" t="n"/>
+    </row>
+    <row r="120" ht="47.5" customHeight="1">
+      <c r="A120" s="44" t="n">
         <v>46330</v>
       </c>
-      <c r="B118" s="45" t="inlineStr">
+      <c r="B120" s="45" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C118" s="46" t="inlineStr">
+      <c r="C120" s="46" t="inlineStr">
         <is>
           <t>03:30</t>
         </is>
       </c>
-      <c r="D118" s="47" t="inlineStr">
+      <c r="D120" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E118" s="45" t="inlineStr">
+      <c r="E120" s="45" t="inlineStr">
         <is>
           <t>SALE (programado): Cierre a Søreide IL</t>
         </is>
       </c>
-      <c r="F118" s="45" t="inlineStr">
+      <c r="F120" s="45" t="inlineStr">
         <is>
           <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
-      <c r="G118" s="45" t="inlineStr">
+      <c r="G120" s="45" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H118" s="45" t="n"/>
-      <c r="I118" s="45" t="inlineStr">
+      <c r="H120" s="45" t="n"/>
+      <c r="I120" s="45" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="J118" s="45" t="n"/>
-    </row>
-    <row r="119" ht="47.5" customHeight="1">
-      <c r="A119" s="44" t="n">
+      <c r="J120" s="45" t="n"/>
+    </row>
+    <row r="121" ht="47.5" customHeight="1">
+      <c r="A121" s="44" t="n">
         <v>46330</v>
       </c>
-      <c r="B119" s="45" t="inlineStr">
+      <c r="B121" s="45" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C119" s="46" t="inlineStr">
+      <c r="C121" s="46" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="D119" s="47" t="inlineStr">
+      <c r="D121" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E119" s="45" t="inlineStr">
+      <c r="E121" s="45" t="inlineStr">
         <is>
           <t>SALE (programado): Cierre a Holbeach United</t>
         </is>
       </c>
-      <c r="F119" s="45" t="inlineStr">
+      <c r="F121" s="45" t="inlineStr">
         <is>
           <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
-      <c r="G119" s="45" t="inlineStr">
+      <c r="G121" s="45" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H119" s="45" t="n"/>
-      <c r="I119" s="45" t="inlineStr">
+      <c r="H121" s="45" t="n"/>
+      <c r="I121" s="45" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="J119" s="45" t="n"/>
-    </row>
-    <row r="120" ht="62" customHeight="1">
-      <c r="A120" s="38" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B120" s="39" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C120" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D120" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E120" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F120" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G120" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H120" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I120" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J120" s="39" t="n"/>
-    </row>
-    <row r="121" ht="47.5" customHeight="1">
-      <c r="A121" s="38" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B121" s="39" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C121" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D121" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E121" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F121" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G121" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H121" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I121" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J121" s="39" t="n"/>
-    </row>
-    <row r="122" ht="91" customHeight="1">
+      <c r="J121" s="45" t="n"/>
+    </row>
+    <row r="122" ht="62" customHeight="1">
       <c r="A122" s="38" t="n">
         <v>46330</v>
       </c>
@@ -6771,31 +6811,31 @@
       </c>
       <c r="C122" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D122" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D122" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E122" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F122" s="39" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G122" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H122" s="39" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I122" s="39" t="inlineStr">
         <is>
@@ -6804,7 +6844,7 @@
       </c>
       <c r="J122" s="39" t="n"/>
     </row>
-    <row r="123" ht="76.5" customHeight="1">
+    <row r="123" ht="47.5" customHeight="1">
       <c r="A123" s="38" t="n">
         <v>46330</v>
       </c>
@@ -6815,7 +6855,7 @@
       </c>
       <c r="C123" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>8:00</t>
         </is>
       </c>
       <c r="D123" s="43" t="inlineStr">
@@ -6825,17 +6865,17 @@
       </c>
       <c r="E123" s="31" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
         </is>
       </c>
       <c r="F123" s="39" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
         </is>
       </c>
       <c r="G123" s="39" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Enviados / Recibidos</t>
         </is>
       </c>
       <c r="H123" s="39" t="n">
@@ -6848,7 +6888,7 @@
       </c>
       <c r="J123" s="39" t="n"/>
     </row>
-    <row r="124" ht="33" customHeight="1">
+    <row r="124" ht="91" customHeight="1">
       <c r="A124" s="38" t="n">
         <v>46330</v>
       </c>
@@ -6862,24 +6902,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D124" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D124" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E124" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
         </is>
       </c>
       <c r="F124" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G124" s="39" t="inlineStr"/>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
+        </is>
+      </c>
+      <c r="G124" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
       <c r="H124" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I124" s="39" t="inlineStr">
         <is>
@@ -6888,7 +6932,7 @@
       </c>
       <c r="J124" s="39" t="n"/>
     </row>
-    <row r="125" ht="163.5" customHeight="1">
+    <row r="125" ht="76.5" customHeight="1">
       <c r="A125" s="38" t="n">
         <v>46330</v>
       </c>
@@ -6899,20 +6943,104 @@
       </c>
       <c r="C125" s="40" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D125" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E125" s="31" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
+        </is>
+      </c>
+      <c r="F125" s="39" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G125" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H125" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I125" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J125" s="39" t="n"/>
+    </row>
+    <row r="126" ht="33" customHeight="1">
+      <c r="A126" s="38" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B126" s="39" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C126" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D126" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E126" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F126" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G126" s="39" t="inlineStr"/>
+      <c r="H126" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I126" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J126" s="39" t="n"/>
+    </row>
+    <row r="127" ht="163.5" customHeight="1">
+      <c r="A127" s="38" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B127" s="39" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C127" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D125" s="43" t="inlineStr">
+      <c r="D127" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E125" s="31" t="inlineStr">
+      <c r="E127" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del jueves 05/11</t>
         </is>
       </c>
-      <c r="F125" s="39" t="inlineStr">
+      <c r="F127" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 05/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • IA Akranes | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 05/11.
@@ -6920,104 +7048,20 @@
 • Whitehaven AFC | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 05/11.</t>
         </is>
       </c>
-      <c r="G125" s="39" t="inlineStr">
+      <c r="G127" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H125" s="39" t="n">
+      <c r="H127" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="I125" s="39" t="inlineStr">
+      <c r="I127" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J125" s="39" t="n"/>
-    </row>
-    <row r="126" ht="47.5" customHeight="1">
-      <c r="A126" s="44" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B126" s="45" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C126" s="46" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D126" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E126" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Cierre a IA Akranes</t>
-        </is>
-      </c>
-      <c r="F126" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G126" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H126" s="45" t="n"/>
-      <c r="I126" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J126" s="45" t="n"/>
-    </row>
-    <row r="127" ht="47.5" customHeight="1">
-      <c r="A127" s="44" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B127" s="45" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C127" s="46" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D127" s="47" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E127" s="45" t="inlineStr">
-        <is>
-          <t>SALE (programado): Cierre a Maidstone United</t>
-        </is>
-      </c>
-      <c r="F127" s="45" t="inlineStr">
-        <is>
-          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
-        </is>
-      </c>
-      <c r="G127" s="45" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H127" s="45" t="n"/>
-      <c r="I127" s="45" t="inlineStr">
-        <is>
-          <t>Automático</t>
-        </is>
-      </c>
-      <c r="J127" s="45" t="n"/>
+      <c r="J127" s="39" t="n"/>
     </row>
     <row r="128" ht="47.5" customHeight="1">
       <c r="A128" s="44" t="n">
@@ -7040,7 +7084,7 @@
       </c>
       <c r="E128" s="45" t="inlineStr">
         <is>
-          <t>SALE (programado): Cierre a Whitehaven AFC</t>
+          <t>SALE (programado): Cierre a IA Akranes</t>
         </is>
       </c>
       <c r="F128" s="45" t="inlineStr">
@@ -7061,101 +7105,97 @@
       </c>
       <c r="J128" s="45" t="n"/>
     </row>
-    <row r="129" ht="62" customHeight="1">
-      <c r="A129" s="38" t="n">
+    <row r="129" ht="47.5" customHeight="1">
+      <c r="A129" s="44" t="n">
         <v>46331</v>
       </c>
-      <c r="B129" s="39" t="inlineStr">
+      <c r="B129" s="45" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C129" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D129" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E129" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F129" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G129" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H129" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I129" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J129" s="39" t="n"/>
+      <c r="C129" s="46" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D129" s="47" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E129" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Cierre a Maidstone United</t>
+        </is>
+      </c>
+      <c r="F129" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G129" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H129" s="45" t="n"/>
+      <c r="I129" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J129" s="45" t="n"/>
     </row>
     <row r="130" ht="47.5" customHeight="1">
-      <c r="A130" s="38" t="n">
+      <c r="A130" s="44" t="n">
         <v>46331</v>
       </c>
-      <c r="B130" s="39" t="inlineStr">
+      <c r="B130" s="45" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C130" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D130" s="43" t="inlineStr">
+      <c r="C130" s="46" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D130" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E130" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F130" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G130" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H130" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I130" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J130" s="39" t="n"/>
+      <c r="E130" s="45" t="inlineStr">
+        <is>
+          <t>SALE (programado): Cierre a Whitehaven AFC</t>
+        </is>
+      </c>
+      <c r="F130" s="45" t="inlineStr">
+        <is>
+          <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
+        </is>
+      </c>
+      <c r="G130" s="45" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H130" s="45" t="n"/>
+      <c r="I130" s="45" t="inlineStr">
+        <is>
+          <t>Automático</t>
+        </is>
+      </c>
+      <c r="J130" s="45" t="n"/>
     </row>
     <row r="131" ht="62" customHeight="1">
       <c r="A131" s="38" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B131" s="39" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C131" s="40" t="inlineStr">
@@ -7193,42 +7233,42 @@
       </c>
       <c r="J131" s="39" t="n"/>
     </row>
-    <row r="132" ht="33" customHeight="1">
+    <row r="132" ht="47.5" customHeight="1">
       <c r="A132" s="38" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B132" s="39" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C132" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D132" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D132" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E132" s="31" t="inlineStr">
         <is>
-          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
         </is>
       </c>
       <c r="F132" s="39" t="inlineStr">
         <is>
-          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
         </is>
       </c>
       <c r="G132" s="39" t="inlineStr">
         <is>
-          <t>Hoy</t>
+          <t>Enviados / Recibidos</t>
         </is>
       </c>
       <c r="H132" s="39" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I132" s="39" t="inlineStr">
         <is>
@@ -7237,7 +7277,7 @@
       </c>
       <c r="J132" s="39" t="n"/>
     </row>
-    <row r="133" ht="33" customHeight="1">
+    <row r="133" ht="62" customHeight="1">
       <c r="A133" s="38" t="n">
         <v>46332</v>
       </c>
@@ -7248,25 +7288,29 @@
       </c>
       <c r="C133" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D133" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D133" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E133" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F133" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G133" s="39" t="inlineStr"/>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G133" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
       <c r="H133" s="39" t="n">
         <v>15</v>
       </c>
@@ -7298,68 +7342,101 @@
       </c>
       <c r="E134" s="31" t="inlineStr">
         <is>
+          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
+        </is>
+      </c>
+      <c r="F134" s="39" t="inlineStr">
+        <is>
+          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
+        </is>
+      </c>
+      <c r="G134" s="39" t="inlineStr">
+        <is>
+          <t>Hoy</t>
+        </is>
+      </c>
+      <c r="H134" s="39" t="n">
+        <v>20</v>
+      </c>
+      <c r="I134" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J134" s="39" t="n"/>
+    </row>
+    <row r="135" ht="33" customHeight="1">
+      <c r="A135" s="38" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B135" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C135" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D135" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E135" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F135" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G135" s="39" t="inlineStr"/>
+      <c r="H135" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I135" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J135" s="39" t="n"/>
+    </row>
+    <row r="136" ht="33" customHeight="1">
+      <c r="A136" s="38" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B136" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C136" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D136" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E136" s="31" t="inlineStr">
+        <is>
           <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
-      <c r="F134" s="39" t="inlineStr">
+      <c r="F136" s="39" t="inlineStr">
         <is>
           <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
-      <c r="G134" s="39" t="inlineStr">
+      <c r="G136" s="39" t="inlineStr">
         <is>
           <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H134" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I134" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J134" s="39" t="n"/>
-    </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="37" t="inlineStr">
-        <is>
-          <t>SEMANA  09/11 a 15/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="62" customHeight="1">
-      <c r="A136" s="38" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B136" s="39" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C136" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D136" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E136" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F136" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G136" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H136" s="39" t="n">
@@ -7372,51 +7449,14 @@
       </c>
       <c r="J136" s="39" t="n"/>
     </row>
-    <row r="137" ht="33" customHeight="1">
-      <c r="A137" s="38" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B137" s="39" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C137" s="40" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D137" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E137" s="31" t="inlineStr">
-        <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
-        </is>
-      </c>
-      <c r="F137" s="39" t="inlineStr">
-        <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
-        </is>
-      </c>
-      <c r="G137" s="39" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H137" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I137" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J137" s="39" t="n"/>
-    </row>
-    <row r="138" ht="33" customHeight="1">
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="37" t="inlineStr">
+        <is>
+          <t>SEMANA  09/11 a 15/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="62" customHeight="1">
       <c r="A138" s="38" t="n">
         <v>46335</v>
       </c>
@@ -7427,31 +7467,31 @@
       </c>
       <c r="C138" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D138" s="42" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D138" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E138" s="31" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F138" s="39" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G138" s="39" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H138" s="39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I138" s="39" t="inlineStr">
         <is>
@@ -7474,19 +7514,19 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D139" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D139" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E139" s="31" t="inlineStr">
         <is>
-          <t>Revisión del mes con Claude (45 min)</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F139" s="39" t="inlineStr">
         <is>
-          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G139" s="39" t="inlineStr">
@@ -7495,7 +7535,7 @@
         </is>
       </c>
       <c r="H139" s="39" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="I139" s="39" t="inlineStr">
         <is>
@@ -7518,24 +7558,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D140" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+      <c r="D140" s="42" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E140" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F140" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G140" s="39" t="inlineStr"/>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G140" s="39" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
       <c r="H140" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I140" s="39" t="inlineStr">
         <is>
@@ -7544,7 +7588,7 @@
       </c>
       <c r="J140" s="39" t="n"/>
     </row>
-    <row r="141" ht="134.5" customHeight="1">
+    <row r="141" ht="33" customHeight="1">
       <c r="A141" s="38" t="n">
         <v>46335</v>
       </c>
@@ -7555,220 +7599,216 @@
       </c>
       <c r="C141" s="40" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D141" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E141" s="31" t="inlineStr">
+        <is>
+          <t>Revisión del mes con Claude (45 min)</t>
+        </is>
+      </c>
+      <c r="F141" s="39" t="inlineStr">
+        <is>
+          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real.</t>
+        </is>
+      </c>
+      <c r="G141" s="39" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
+      <c r="H141" s="39" t="n">
+        <v>45</v>
+      </c>
+      <c r="I141" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J141" s="39" t="n"/>
+    </row>
+    <row r="142" ht="33" customHeight="1">
+      <c r="A142" s="38" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B142" s="39" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C142" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D142" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E142" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F142" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G142" s="39" t="inlineStr"/>
+      <c r="H142" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I142" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J142" s="39" t="n"/>
+    </row>
+    <row r="143" ht="134.5" customHeight="1">
+      <c r="A143" s="38" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B143" s="39" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C143" s="40" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D141" s="43" t="inlineStr">
+      <c r="D143" s="43" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E141" s="31" t="inlineStr">
+      <c r="E143" s="31" t="inlineStr">
         <is>
           <t>Preparar (y programar si puedes) los envíos del martes 10/11</t>
         </is>
       </c>
-      <c r="F141" s="39" t="inlineStr">
+      <c r="F143" s="39" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 10/11). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Programa el envío a la hora indicada si tu correo lo permite (ver LEEME). Si no puedes programar, no pasa nada: mañana a las 07:30 de Nueva York los envías a mano.
 • FC Porte d'Aquitaine | Cierre | programar para las 03:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 10/11.
 • Virtu Academy | Cierre | programar para las 04:30 hora Nueva York (09:30 locales). Texto: fila de la hoja Textos para copiar del 10/11.</t>
         </is>
       </c>
-      <c r="G141" s="39" t="inlineStr">
+      <c r="G143" s="39" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H141" s="39" t="n">
+      <c r="H143" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="I141" s="39" t="inlineStr">
+      <c r="I143" s="39" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J141" s="39" t="n"/>
-    </row>
-    <row r="142" ht="47.5" customHeight="1">
-      <c r="A142" s="44" t="n">
+      <c r="J143" s="39" t="n"/>
+    </row>
+    <row r="144" ht="47.5" customHeight="1">
+      <c r="A144" s="44" t="n">
         <v>46336</v>
       </c>
-      <c r="B142" s="45" t="inlineStr">
+      <c r="B144" s="45" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C142" s="46" t="inlineStr">
+      <c r="C144" s="46" t="inlineStr">
         <is>
           <t>03:30</t>
         </is>
       </c>
-      <c r="D142" s="47" t="inlineStr">
+      <c r="D144" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E142" s="45" t="inlineStr">
+      <c r="E144" s="45" t="inlineStr">
         <is>
           <t>SALE (programado): Cierre a FC Porte d'Aquitaine</t>
         </is>
       </c>
-      <c r="F142" s="45" t="inlineStr">
+      <c r="F144" s="45" t="inlineStr">
         <is>
           <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
-      <c r="G142" s="45" t="inlineStr">
+      <c r="G144" s="45" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H142" s="45" t="n"/>
-      <c r="I142" s="45" t="inlineStr">
+      <c r="H144" s="45" t="n"/>
+      <c r="I144" s="45" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="J142" s="45" t="n"/>
-    </row>
-    <row r="143" ht="47.5" customHeight="1">
-      <c r="A143" s="44" t="n">
+      <c r="J144" s="45" t="n"/>
+    </row>
+    <row r="145" ht="47.5" customHeight="1">
+      <c r="A145" s="44" t="n">
         <v>46336</v>
       </c>
-      <c r="B143" s="45" t="inlineStr">
+      <c r="B145" s="45" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C143" s="46" t="inlineStr">
+      <c r="C145" s="46" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="D143" s="47" t="inlineStr">
+      <c r="D145" s="47" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E143" s="45" t="inlineStr">
+      <c r="E145" s="45" t="inlineStr">
         <is>
           <t>SALE (programado): Cierre a Virtu Academy</t>
         </is>
       </c>
-      <c r="F143" s="45" t="inlineStr">
+      <c r="F145" s="45" t="inlineStr">
         <is>
           <t>No tienes que hacer nada a esta hora si lo programaste la víspera. Si no pudiste programar, envíalo a mano a las 07:30 de Nueva York. Texto en 'Textos para copiar'.</t>
         </is>
       </c>
-      <c r="G143" s="45" t="inlineStr">
+      <c r="G145" s="45" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H143" s="45" t="n"/>
-      <c r="I143" s="45" t="inlineStr">
+      <c r="H145" s="45" t="n"/>
+      <c r="I145" s="45" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
-      <c r="J143" s="45" t="n"/>
-    </row>
-    <row r="144" ht="62" customHeight="1">
-      <c r="A144" s="38" t="n">
-        <v>46336</v>
-      </c>
-      <c r="B144" s="39" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C144" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D144" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E144" s="31" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F144" s="39" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G144" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H144" s="39" t="n">
-        <v>15</v>
-      </c>
-      <c r="I144" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J144" s="39" t="n"/>
-    </row>
-    <row r="145" ht="47.5" customHeight="1">
-      <c r="A145" s="38" t="n">
-        <v>46336</v>
-      </c>
-      <c r="B145" s="39" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C145" s="40" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D145" s="43" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E145" s="31" t="inlineStr">
-        <is>
-          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
-        </is>
-      </c>
-      <c r="F145" s="39" t="inlineStr">
-        <is>
-          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
-        </is>
-      </c>
-      <c r="G145" s="39" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H145" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="I145" s="39" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J145" s="39" t="n"/>
+      <c r="J145" s="45" t="n"/>
     </row>
     <row r="146" ht="62" customHeight="1">
       <c r="A146" s="38" t="n">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="B146" s="39" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="C146" s="40" t="inlineStr">
@@ -7806,38 +7846,42 @@
       </c>
       <c r="J146" s="39" t="n"/>
     </row>
-    <row r="147" ht="33" customHeight="1">
+    <row r="147" ht="47.5" customHeight="1">
       <c r="A147" s="38" t="n">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="B147" s="39" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="C147" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D147" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D147" s="43" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E147" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Comprobar que salieron los correos de hoy y que no hay rebotes</t>
         </is>
       </c>
       <c r="F147" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G147" s="39" t="inlineStr"/>
+          <t>Carpeta Enviados: confirma que están. Recibidos: busca avisos de rebote (suelen llegar en minutos). Si uno rebota: apunta cuál en la columna Notas de esta fila y avísame; busco otra dirección del club y te la preparo.</t>
+        </is>
+      </c>
+      <c r="G147" s="39" t="inlineStr">
+        <is>
+          <t>Enviados / Recibidos</t>
+        </is>
+      </c>
       <c r="H147" s="39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I147" s="39" t="inlineStr">
         <is>
@@ -7848,11 +7892,11 @@
     </row>
     <row r="148" ht="62" customHeight="1">
       <c r="A148" s="38" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B148" s="39" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C148" s="40" t="inlineStr">
@@ -7890,40 +7934,36 @@
       </c>
       <c r="J148" s="39" t="n"/>
     </row>
-    <row r="149" ht="62" customHeight="1">
+    <row r="149" ht="33" customHeight="1">
       <c r="A149" s="38" t="n">
-        <v>46339</v>
+        <v>46337</v>
       </c>
       <c r="B149" s="39" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C149" s="40" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D149" s="41" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D149" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E149" s="31" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Publicar o subir una story/post</t>
         </is>
       </c>
       <c r="F149" s="39" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G149" s="39" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G149" s="39" t="inlineStr"/>
       <c r="H149" s="39" t="n">
         <v>15</v>
       </c>
@@ -7934,36 +7974,40 @@
       </c>
       <c r="J149" s="39" t="n"/>
     </row>
-    <row r="150" ht="33" customHeight="1">
+    <row r="150" ht="62" customHeight="1">
       <c r="A150" s="38" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B150" s="39" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C150" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D150" s="49" t="inlineStr">
-        <is>
-          <t>Instagram</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D150" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E150" s="31" t="inlineStr">
         <is>
-          <t>Publicar o subir una story/post</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F150" s="39" t="inlineStr">
         <is>
-          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
-        </is>
-      </c>
-      <c r="G150" s="39" t="inlineStr"/>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G150" s="39" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
       <c r="H150" s="39" t="n">
         <v>15</v>
       </c>
@@ -7974,7 +8018,7 @@
       </c>
       <c r="J150" s="39" t="n"/>
     </row>
-    <row r="151" ht="33" customHeight="1">
+    <row r="151" ht="62" customHeight="1">
       <c r="A151" s="38" t="n">
         <v>46339</v>
       </c>
@@ -7985,7 +8029,7 @@
       </c>
       <c r="C151" s="40" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>8:00</t>
         </is>
       </c>
       <c r="D151" s="41" t="inlineStr">
@@ -7995,17 +8039,17 @@
       </c>
       <c r="E151" s="31" t="inlineStr">
         <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F151" s="39" t="inlineStr">
         <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G151" s="39" t="inlineStr">
         <is>
-          <t>Segmento A, B, C</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H151" s="39" t="n">
@@ -8018,17 +8062,101 @@
       </c>
       <c r="J151" s="39" t="n"/>
     </row>
+    <row r="152" ht="33" customHeight="1">
+      <c r="A152" s="38" t="n">
+        <v>46339</v>
+      </c>
+      <c r="B152" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C152" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D152" s="49" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E152" s="31" t="inlineStr">
+        <is>
+          <t>Publicar o subir una story/post</t>
+        </is>
+      </c>
+      <c r="F152" s="39" t="inlineStr">
+        <is>
+          <t>Lo que tengas de la experiencia (partidos, estadio, instalaciones, sin menores identificables) o el plan que salga de la sesión del 17/10. Mínimo una story.</t>
+        </is>
+      </c>
+      <c r="G152" s="39" t="inlineStr"/>
+      <c r="H152" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I152" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J152" s="39" t="n"/>
+    </row>
+    <row r="153" ht="33" customHeight="1">
+      <c r="A153" s="38" t="n">
+        <v>46339</v>
+      </c>
+      <c r="B153" s="39" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C153" s="40" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D153" s="41" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E153" s="31" t="inlineStr">
+        <is>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+        </is>
+      </c>
+      <c r="F153" s="39" t="inlineStr">
+        <is>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G153" s="39" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
+      <c r="H153" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I153" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J153" s="39" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J151"/>
+  <autoFilter ref="A4:J153"/>
   <mergeCells count="6">
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A135:J135"/>
-    <mergeCell ref="A67:J67"/>
-    <mergeCell ref="A104:J104"/>
-    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A137:J137"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J151">
+  <conditionalFormatting sqref="A5:J153">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$I5="Hecho"</formula>
     </cfRule>
@@ -8036,13 +8164,13 @@
       <formula>$A5=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I151">
+  <conditionalFormatting sqref="I5:I153">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>AND(ISNUMBER($A5),$A5&lt;TODAY(),$I5="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I6 I7 I8 I11 I12 I13 I14 I15 I16 I17 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I34 I35 I36 I37 I38 I39 I40 I45 I46 I47 I48 I51 I52 I53 I54 I58 I59 I60 I61 I62 I63 I64 I65 I66 I68 I69 I70 I71 I72 I73 I78 I79 I80 I81 I84 I85 I86 I87 I88 I89 I90 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I105 I106 I107 I108 I109 I114 I115 I116 I117 I120 I121 I122 I123 I124 I125 I129 I130 I131 I132 I133 I134 I136 I137 I138 I139 I140 I141 I144 I145 I146 I147 I148 I149 I150 I151" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6 I7 I8 I9 I12 I13 I14 I15 I16 I17 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I47 I48 I49 I50 I53 I54 I55 I56 I60 I61 I62 I63 I64 I65 I66 I67 I68 I70 I71 I72 I73 I74 I75 I80 I81 I82 I83 I86 I87 I88 I89 I90 I91 I92 I96 I97 I98 I99 I100 I101 I102 I103 I104 I105 I107 I108 I109 I110 I111 I116 I117 I118 I119 I122 I123 I124 I125 I126 I127 I131 I132 I133 I134 I135 I136 I138 I139 I140 I141 I142 I143 I146 I147 I148 I149 I150 I151 I152 I153" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Hecho,Saltado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8438,7 +8566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11174,7 +11302,7 @@
       </c>
       <c r="H55" s="32" t="inlineStr">
         <is>
-          <t>Great, thanks for getting back to me. Here are two times that could work for a call: {A} or {B} (your time). If neither suits, tell me what does and I'll adapt. I'll send a calendar invite as soon as we pick one.
+          <t>Great, thanks for getting back to me. Here is a link to my calendar where you can pick a time that suits you (it shows your local time): {Calendly}. If you'd rather, tell me a couple of times that work and I'll adapt.
 Best,
 Joel Martinez
 Founder, Always Up
@@ -11183,7 +11311,7 @@
       </c>
       <c r="I55" s="32" t="inlineStr">
         <is>
-          <t>Menos de 4 horas. Sustituye {A} y {B} por dos horarios reales en su zona horaria.</t>
+          <t>Menos de 4 horas. Sustituye {Calendly} por el enlace del evento 'Always Up Intro Call' (cuando lo tengas). Mientras tanto, ofrece dos horarios de la tabla de LEEME convertidos a su hora.</t>
         </is>
       </c>
     </row>
@@ -11286,26 +11414,6 @@
       <c r="I60" s="32" t="inlineStr">
         <is>
           <t>Mándalo tú o Enrique, por WhatsApp. El nombre del contacto lo pones tú. Si dice que sí, pídele una foto del trofeo con los jugadores (con permiso del club).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="207" customHeight="1">
-      <c r="D61" s="31" t="inlineStr">
-        <is>
-          <t>Reactivar a Leonardo Uren (WhatsApp)</t>
-        </is>
-      </c>
-      <c r="H61" s="32" t="inlineStr">
-        <is>
-          <t>Hi Leonardo! Hope you and the team are doing well.
-It's been a while since we last spoke, and a lot has happened on our side too. We've been growing our international work, and with Spain being World Cup champions there's a lot more interest from clubs and academies in connecting with Spanish football, so it felt like a good moment to pick this back up.
-I still think there's real potential in a Brazil and Spain connection, with players and teams coming to train in Spain and maybe the other way around too. Would you be up for reopening the conversation? My dad would join again as well. It doesn't need to be tied to a specific trip this time. Even 20 or 30 minutes whenever suits you would be great.
-Let me know!</t>
-        </is>
-      </c>
-      <c r="I61" s="32" t="inlineStr">
-        <is>
-          <t>WhatsApp, miércoles 14/10 hacia las 10:00 de Nueva York (11:00 en Brasilia).</t>
         </is>
       </c>
     </row>
@@ -12720,7 +12828,7 @@
       <c r="N10" s="13" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
@@ -13165,12 +13273,12 @@
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Listo para enviar (reactivación)</t>
+          <t>Perdido</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>Enviar el WhatsApp de reactivación el 14/10 a las 10:00 hora Nueva York.</t>
+          <t>Decisión de Joel (13/10/2026): no insistir. Reabrir solo si él escribe.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -13192,7 +13300,7 @@
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa.</t>
+          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -2061,10 +2061,14 @@
       </c>
       <c r="I9" s="39" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J9" s="39" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="J9" s="39" t="inlineStr">
+        <is>
+          <t>SPF/DKIM/DMARC PASS en Gmail</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="47.5" customHeight="1">
       <c r="A10" s="44" t="n">
@@ -12828,7 +12832,7 @@
       <c r="N10" s="13" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
@@ -13300,7 +13304,7 @@
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
+          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Textos para copiar'!$A$4:$K$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Segmento A - Clubes'!$A$5:$P$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Segmento B - America'!$A$5:$O$13</definedName>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="50" min="1" max="1"/>
@@ -1248,144 +1248,180 @@
     <row r="18" ht="33" customHeight="1" s="50">
       <c r="A18" s="62" t="inlineStr">
         <is>
-          <t>Regla actual (14/10/2026)</t>
+          <t>Qué se ha comprobado (14/10/2026)</t>
         </is>
       </c>
       <c r="B18" s="63" t="inlineStr">
         <is>
-          <t>Los correos se envían a mano a las 07:30 de Nueva York (12:30 o 13:30 en Europa). El 14/10 el envío programado con Apple Mail no salió, y no se programa nada hasta entender el motivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33" customHeight="1" s="50">
+          <t>El envío programado con Mail de Apple SÍ sale: llegó con Mail abierto, con Mail cerrado y con el Mac en reposo. Puede retrasarse unos 10 minutos y no avisa. Los correos programados del 14/10 sí salieron (Holbeach, 04:41).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="47.5" customHeight="1" s="50">
       <c r="A19" s="62" t="inlineStr">
         <is>
-          <t>Por qué sirve</t>
+          <t>Por qué parecía que no salían</t>
         </is>
       </c>
       <c r="B19" s="63" t="inlineStr">
         <is>
-          <t>Es horario laboral del club. Lo que importa es enviar de martes a jueves, no la hora exacta de las 09:30. Y te encaja con tu revisión de las 08:00.</t>
+          <t>El correo enviado se guarda en carpetas distintas según el programa: 'Sent' (Outlook), 'INBOX.Sent' (servidor) y 'Sent Messages' (Mail). No lo ves donde miras. Para comprobar: Outlook &gt; buscador &gt; escribe el destinatario &gt; All folders.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="33" customHeight="1" s="50">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>Si encuentras un método fiable</t>
+          <t>Cómo se programa</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr">
         <is>
-          <t>Si tras tus pruebas encuentras una forma de programar que funcione con el ordenador apagado, se puede volver a usar. Mientras tanto, a mano.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" s="50">
-      <c r="A21" s="61" t="inlineStr">
-        <is>
-          <t>TUS FRANJAS DE LLAMADA</t>
+          <t>Mail: correo nuevo, pega todo, flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora de la columna 'Programar para (NY)'. Se programa la víspera por la tarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33" customHeight="1" s="50">
+      <c r="A21" s="62" t="inlineStr">
+        <is>
+          <t>Regla para no duplicar</t>
+        </is>
+      </c>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>Una vez programado un correo, no lo envíes a mano. A las 08:00 busca al destinatario en todas las carpetas: si aparece, marca Hecho; solo si no aparece, lo envías a mano.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="33" customHeight="1" s="50">
       <c r="A22" s="62" t="inlineStr">
         <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="B22" s="63" t="inlineStr">
+        <is>
+          <t>La fuente de verdad es esta hoja: columna 'Hecho (fecha real)' de 'Textos para copiar' y el CRM. No dependas de la carpeta Enviados de ningún programa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33" customHeight="1" s="50">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>Truco opcional</t>
+        </is>
+      </c>
+      <c r="B23" s="63" t="inlineStr">
+        <is>
+          <t>Pon tu Gmail personal en copia oculta (CCO) de cada correo a un club: recibirás una copia como prueba de que salió, y verás en Gmail si entra en bandeja. El club no lo ve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="50">
+      <c r="A24" s="61" t="inlineStr">
+        <is>
+          <t>TUS FRANJAS DE LLAMADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="33" customHeight="1" s="50">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
           <t>Lo que tienes en Calendly (hora Nueva York)</t>
         </is>
       </c>
-      <c r="B22" s="63" t="inlineStr">
+      <c r="B25" s="63" t="inlineStr">
         <is>
           <t>Dom 12:00 a 17:00 | Lun 17:30 a 21:00 | Mar 13:00 a 19:00 | Mié 11:00 a 12:30 | Jue 17:00 a 21:00 | Vie 14:00 a 18:00 | Sáb no disponible.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="47.5" customHeight="1" s="50">
-      <c r="A23" s="62" t="inlineStr">
+    <row r="26" ht="47.5" customHeight="1" s="50">
+      <c r="A26" s="62" t="inlineStr">
         <is>
           <t>Clubes de Europa (+5 h en UK e Irlanda, +6 h en Noruega, Francia y Países Bajos; +4 y +5 del 25 al 31/10)</t>
         </is>
       </c>
-      <c r="B23" s="63" t="inlineStr">
+      <c r="B26" s="63" t="inlineStr">
         <is>
           <t>Sirven: Martes 13:00 a 15:00 (18:00 a 20:00 en UK, buen horario para comités de voluntarios) y Miércoles 11:00 a 12:30 (16:00 a 17:30 en UK). Mal: Lunes y Jueves por la tarde (ya es de madrugada allí), Viernes (noche) y Domingo (tarde de domingo).</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1" s="50">
-      <c r="A24" s="62" t="inlineStr">
+    <row r="27" ht="20" customHeight="1" s="50">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>Familias de América (México, Latinoamérica, EEUU)</t>
         </is>
       </c>
-      <c r="B24" s="63" t="inlineStr">
+      <c r="B27" s="63" t="inlineStr">
         <is>
           <t>Sirven: Lunes y Jueves por la tarde y Martes 17:00 a 19:00.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="47.5" customHeight="1" s="50">
-      <c r="A25" s="62" t="inlineStr">
+    <row r="28" ht="47.5" customHeight="1" s="50">
+      <c r="A28" s="62" t="inlineStr">
         <is>
           <t>Recomendación</t>
         </is>
       </c>
-      <c r="B25" s="63" t="inlineStr">
+      <c r="B28" s="63" t="inlineStr">
         <is>
           <t>Dos agendas en Calendly: 'Europa' (martes 13:00 a 15:00 y miércoles 11:00 a 12:30) para 'Always Up Intro Call', y 'Américas' (lunes y jueves tarde, martes 17:00 a 19:00) para 'USA Scholarship Assessment'. Así un club nunca ve una hora de madrugada. Cambia también el nombre 'Assessment Call' para clubes: 'Assessment' es un término de becas.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1" s="50">
-      <c r="A26" s="61" t="inlineStr">
+    <row r="29" ht="22" customHeight="1" s="50">
+      <c r="A29" s="61" t="inlineStr">
         <is>
           <t>REGLAS QUE NO SE ROMPEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="33" customHeight="1" s="50">
-      <c r="A27" s="62" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="B27" s="63" t="inlineStr">
-        <is>
-          <t>Adjuntos en el primer correo. Nombrar al partner de becas. Prometer becas o fichajes. Inventar urgencia. Discutir precio por escrito sin tu decisión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="33" customHeight="1" s="50">
-      <c r="A28" s="62" t="inlineStr">
-        <is>
-          <t>Si contestan</t>
-        </is>
-      </c>
-      <c r="B28" s="63" t="inlineStr">
-        <is>
-          <t>Paras la cadencia de ese club y abres 'Respuestas tipo' (hoja Textos para copiar). Menos de 4 horas de respuesta en horario del club.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1" s="50">
-      <c r="A29" s="62" t="inlineStr">
-        <is>
-          <t>Si un correo rebota</t>
-        </is>
-      </c>
-      <c r="B29" s="63" t="inlineStr">
-        <is>
-          <t>Me lo dices; busco otra dirección del club y te la dejo preparada.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="33" customHeight="1" s="50">
       <c r="A30" s="62" t="inlineStr">
         <is>
+          <t>Nunca</t>
+        </is>
+      </c>
+      <c r="B30" s="63" t="inlineStr">
+        <is>
+          <t>Adjuntos en el primer correo. Nombrar al partner de becas. Prometer becas o fichajes. Inventar urgencia. Discutir precio por escrito sin tu decisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="33" customHeight="1" s="50">
+      <c r="A31" s="62" t="inlineStr">
+        <is>
+          <t>Si contestan</t>
+        </is>
+      </c>
+      <c r="B31" s="63" t="inlineStr">
+        <is>
+          <t>Paras la cadencia de ese club y abres 'Respuestas tipo' (hoja Textos para copiar). Menos de 4 horas de respuesta en horario del club.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="50">
+      <c r="A32" s="62" t="inlineStr">
+        <is>
+          <t>Si un correo rebota</t>
+        </is>
+      </c>
+      <c r="B32" s="63" t="inlineStr">
+        <is>
+          <t>Me lo dices; busco otra dirección del club y te la dejo preparada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="33" customHeight="1" s="50">
+      <c r="A33" s="62" t="inlineStr">
+        <is>
           <t>Colores</t>
         </is>
       </c>
-      <c r="B30" s="63" t="inlineStr">
+      <c r="B33" s="63" t="inlineStr">
         <is>
           <t>Azul claro = email 1, amarillo = follow-up 1, naranja = follow-up 2, gris = cierre, lila = LinkedIn o redes, rojo = pendiente atrasado.</t>
         </is>
@@ -1394,8 +1430,8 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A9:B9"/>
   </mergeCells>
@@ -2040,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="50" min="1" max="1"/>
@@ -2065,7 +2101,7 @@
     <row r="2" ht="46" customHeight="1" s="50">
       <c r="A2" s="65" t="inlineStr">
         <is>
-          <t>Qué haces tú cada día, a qué hora y cómo. Las horas son de Nueva York. Los correos se envían a mano a las 07:30 (hora de Nueva York), que son las 12:30 o 13:30 en Europa. Cambia la columna Estado a Hecho al terminar. Hoy se marca en amarillo. Si algo queda Pendiente de un día anterior, sale en rojo.</t>
+          <t>Qué haces tú cada día, a qué hora y cómo. Las horas son de Nueva York. Los correos se programan la víspera en Apple Mail (Enviar más tarde) para las 09:30 de cada club; a las 08:00 compruebas que salieron. Cambia la columna Estado a Hecho al terminar. Hoy se marca en amarillo. Si algo queda Pendiente de un día anterior, sale en rojo.</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2294,7 @@
       </c>
       <c r="J8" s="70" t="n"/>
     </row>
-    <row r="9" ht="62" customHeight="1" s="50">
+    <row r="9" ht="47.5" customHeight="1" s="50">
       <c r="A9" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2269,7 +2305,7 @@
       </c>
       <c r="C9" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="D9" s="74" t="inlineStr">
@@ -2279,12 +2315,12 @@
       </c>
       <c r="E9" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a Holbeach United</t>
+          <t>ENVIAR email 1 a Søreide IL</t>
         </is>
       </c>
       <c r="F9" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G9" s="70" t="inlineStr">
@@ -2292,9 +2328,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H9" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H9" s="70" t="n"/>
       <c r="I9" s="70" t="inlineStr">
         <is>
           <t>Hecho</t>
@@ -2306,7 +2340,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="62" customHeight="1" s="50">
+    <row r="10" ht="47.5" customHeight="1" s="50">
       <c r="A10" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2317,7 +2351,7 @@
       </c>
       <c r="C10" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D10" s="74" t="inlineStr">
@@ -2327,12 +2361,12 @@
       </c>
       <c r="E10" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a Søreide IL</t>
+          <t>ENVIAR email 1 a Holbeach United</t>
         </is>
       </c>
       <c r="F10" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 13:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G10" s="70" t="inlineStr">
@@ -2340,9 +2374,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H10" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H10" s="70" t="n"/>
       <c r="I10" s="70" t="inlineStr">
         <is>
           <t>Hecho</t>
@@ -2365,31 +2397,31 @@
       </c>
       <c r="C11" s="71" t="inlineStr">
         <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D11" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D11" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E11" s="62" t="inlineStr">
         <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F11" s="70" t="inlineStr">
         <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G11" s="70" t="inlineStr">
         <is>
-          <t>Enviados / Recibidos</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H11" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I11" s="70" t="inlineStr">
         <is>
@@ -2398,7 +2430,7 @@
       </c>
       <c r="J11" s="70" t="n"/>
     </row>
-    <row r="12" ht="62" customHeight="1" s="50">
+    <row r="12" ht="76.5" customHeight="1" s="50">
       <c r="A12" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2412,28 +2444,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D12" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D12" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E12" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F12" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G12" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H12" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I12" s="70" t="inlineStr">
         <is>
@@ -2442,7 +2474,7 @@
       </c>
       <c r="J12" s="70" t="n"/>
     </row>
-    <row r="13" ht="47.5" customHeight="1" s="50">
+    <row r="13" ht="62" customHeight="1" s="50">
       <c r="A13" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2456,28 +2488,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D13" s="72" t="inlineStr">
-        <is>
-          <t>Transversal</t>
+      <c r="D13" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E13" s="62" t="inlineStr">
         <is>
-          <t>Opcional: pruebas de envío programado en Apple Mail (máx. 15 min)</t>
+          <t>Comprobar si Søreide y Holbeach recibieron el correo una o dos veces</t>
         </is>
       </c>
       <c r="F13" s="70" t="inlineStr">
         <is>
-          <t>Programa un correo a ti mismo a 10 minutos con (1) Mail abierto y el Mac despierto, (2) Mail cerrado, (3) Mac en reposo. Anota cuál sale. Si ninguno funciona con el Mac apagado, no se programa: se envía a mano a las 07:30.</t>
+          <t>En Outlook: buscador &gt; 'fotball@soreideil.no' y luego 'callum@holbeachunitedacademy.com' &gt; All folders. Cuenta cuántas copias hay y a qué hora salió cada una. Dime el resultado: si hay duplicado, no escribas nada al club (disculparse llama más la atención); solo se responde con naturalidad si ellos lo mencionan.</t>
         </is>
       </c>
       <c r="G13" s="70" t="inlineStr">
         <is>
-          <t>Mail de Apple</t>
+          <t>Outlook buscador</t>
         </is>
       </c>
       <c r="H13" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I13" s="70" t="inlineStr">
         <is>
@@ -2486,7 +2518,7 @@
       </c>
       <c r="J13" s="70" t="n"/>
     </row>
-    <row r="14" ht="76.5" customHeight="1" s="50">
+    <row r="14" ht="47.5" customHeight="1" s="50">
       <c r="A14" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2507,30 +2539,34 @@
       </c>
       <c r="E14" s="62" t="inlineStr">
         <is>
-          <t>Prueba de spam con Microsoft (antes del lote del jueves)</t>
+          <t>Opcional: pruebas de envío programado en Apple Mail (máx. 15 min)</t>
         </is>
       </c>
       <c r="F14" s="70" t="inlineStr">
         <is>
-          <t>Tres de los cinco clubes del jueves y Hastings usan correo Microsoft 365, que es el filtro más estricto con dominios nuevos. Manda el correo de Whitehaven (texto normal) a una cuenta Outlook o Hotmail (la tuya, de un amigo o una gratuita que crees tú) y mira si cae en Recibidos o en Correo no deseado. Cuéntame el resultado. Si cae en spam, lo marcas 'No es spam' y repetimos mañana.</t>
+          <t>Programa un correo a ti mismo a 10 minutos con (1) Mail abierto y el Mac despierto, (2) Mail cerrado, (3) Mac en reposo. Anota cuál sale. Si ninguno funciona con el Mac apagado, no se programa: se envía a mano a las 07:30.</t>
         </is>
       </c>
       <c r="G14" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Mail de Apple</t>
         </is>
       </c>
       <c r="H14" s="70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I14" s="70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J14" s="70" t="n"/>
-    </row>
-    <row r="15" ht="47.5" customHeight="1" s="50">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="J14" s="70" t="inlineStr">
+        <is>
+          <t>Sale con Mail cerrado y Mac en reposo; no aparece en 'Sent' de Outlook (otra carpeta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76.5" customHeight="1" s="50">
       <c r="A15" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2544,68 +2580,72 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D15" s="73" t="inlineStr">
+      <c r="D15" s="72" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E15" s="62" t="inlineStr">
+        <is>
+          <t>Prueba de spam con Microsoft (antes del lote del jueves)</t>
+        </is>
+      </c>
+      <c r="F15" s="70" t="inlineStr">
+        <is>
+          <t>Tres de los cinco clubes del jueves y Hastings usan correo Microsoft 365, que es el filtro más estricto con dominios nuevos. Manda el correo de Whitehaven (texto normal) a una cuenta Outlook o Hotmail (la tuya, de un amigo o una gratuita que crees tú) y mira si cae en Recibidos o en Correo no deseado. Cuéntame el resultado. Si cae en spam, lo marcas 'No es spam' y repetimos mañana.</t>
+        </is>
+      </c>
+      <c r="G15" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
+      <c r="H15" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="70" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="J15" s="70" t="inlineStr">
+        <is>
+          <t>3 cuentas Outlook: todas en bandeja principal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="47.5" customHeight="1" s="50">
+      <c r="A16" s="94" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B16" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C16" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D16" s="73" t="inlineStr">
         <is>
           <t>Becas</t>
         </is>
       </c>
-      <c r="E15" s="62" t="inlineStr">
+      <c r="E16" s="62" t="inlineStr">
         <is>
           <t>Daniel (MLS NEXT): apuntar su @usuario en el CRM</t>
         </is>
       </c>
-      <c r="F15" s="70" t="inlineStr">
+      <c r="F16" s="70" t="inlineStr">
         <is>
           <t>Abre la conversación de Instagram con Daniel, copia su @usuario y pégalo en la fila 20 de Segmento C (columna del contacto). Solo sirve para tenerlo localizado: no bloquea nada. Si no le has contestado todavía, dímelo y preparamos la respuesta.</t>
         </is>
       </c>
-      <c r="G15" s="70" t="inlineStr">
+      <c r="G16" s="70" t="inlineStr">
         <is>
           <t>Segmento C - Becas</t>
-        </is>
-      </c>
-      <c r="H15" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J15" s="70" t="n"/>
-    </row>
-    <row r="16" ht="62" customHeight="1" s="50">
-      <c r="A16" s="94" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B16" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C16" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D16" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E16" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR email 1 a IA Akranes</t>
-        </is>
-      </c>
-      <c r="F16" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G16" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H16" s="70" t="n">
@@ -2618,18 +2658,18 @@
       </c>
       <c r="J16" s="70" t="n"/>
     </row>
-    <row r="17" ht="62" customHeight="1" s="50">
+    <row r="17" ht="134.5" customHeight="1" s="50">
       <c r="A17" s="94" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B17" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C17" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D17" s="74" t="inlineStr">
@@ -2639,12 +2679,15 @@
       </c>
       <c r="E17" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a Maidstone United</t>
+          <t>Programar en Apple Mail los envíos del miércoles 14/10</t>
         </is>
       </c>
       <c r="F17" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 14/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• Holbeach United | Email 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+• Søreide IL | Email 1 | programar para las 03:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
       <c r="G17" s="70" t="inlineStr">
@@ -2653,7 +2696,7 @@
         </is>
       </c>
       <c r="H17" s="70" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I17" s="70" t="inlineStr">
         <is>
@@ -2662,18 +2705,18 @@
       </c>
       <c r="J17" s="70" t="n"/>
     </row>
-    <row r="18" ht="62" customHeight="1" s="50">
+    <row r="18" ht="163.5" customHeight="1" s="50">
       <c r="A18" s="94" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B18" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C18" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D18" s="74" t="inlineStr">
@@ -2683,12 +2726,16 @@
       </c>
       <c r="E18" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a Whitehaven AFC</t>
+          <t>Programar en Apple Mail los envíos del jueves 15/10</t>
         </is>
       </c>
       <c r="F18" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 15/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• IA Akranes | Email 1 | programar para las 05:30 hora Nueva York (09:30 allí)
+• Maidstone United | Email 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+• Whitehaven AFC | Email 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
       <c r="G18" s="70" t="inlineStr">
@@ -2697,7 +2744,7 @@
         </is>
       </c>
       <c r="H18" s="70" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I18" s="70" t="inlineStr">
         <is>
@@ -2706,7 +2753,7 @@
       </c>
       <c r="J18" s="70" t="n"/>
     </row>
-    <row r="19" ht="62" customHeight="1" s="50">
+    <row r="19" ht="47.5" customHeight="1" s="50">
       <c r="A19" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2717,7 +2764,7 @@
       </c>
       <c r="C19" s="71" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D19" s="74" t="inlineStr">
@@ -2727,22 +2774,20 @@
       </c>
       <c r="E19" s="62" t="inlineStr">
         <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
+          <t>ENVIAR email 1 a Maidstone United</t>
         </is>
       </c>
       <c r="F19" s="70" t="inlineStr">
         <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G19" s="70" t="inlineStr">
         <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H19" s="70" t="n">
-        <v>5</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H19" s="70" t="n"/>
       <c r="I19" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2750,7 +2795,7 @@
       </c>
       <c r="J19" s="70" t="n"/>
     </row>
-    <row r="20" ht="62" customHeight="1" s="50">
+    <row r="20" ht="47.5" customHeight="1" s="50">
       <c r="A20" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2761,32 +2806,30 @@
       </c>
       <c r="C20" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D20" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D20" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E20" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>ENVIAR email 1 a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F20" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G20" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H20" s="70" t="n">
-        <v>15</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H20" s="70" t="n"/>
       <c r="I20" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2794,7 +2837,7 @@
       </c>
       <c r="J20" s="70" t="n"/>
     </row>
-    <row r="21" ht="33" customHeight="1" s="50">
+    <row r="21" ht="47.5" customHeight="1" s="50">
       <c r="A21" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2805,32 +2848,30 @@
       </c>
       <c r="C21" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D21" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D21" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E21" s="62" t="inlineStr">
         <is>
-          <t>Darme tu feedback sobre la ficha de Becas EEUU</t>
+          <t>ENVIAR email 1 a IA Akranes</t>
         </is>
       </c>
       <c r="F21" s="70" t="inlineStr">
         <is>
-          <t>Ábrela (02-sales/assets/Always-Up-Becas-EEUU.pdf) y dime qué cambiarías. Antes de cambiar nada te digo si me parece buena idea.</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G21" s="70" t="inlineStr">
         <is>
-          <t>02-sales/assets</t>
-        </is>
-      </c>
-      <c r="H21" s="70" t="n">
-        <v>15</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H21" s="70" t="n"/>
       <c r="I21" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2838,7 +2879,7 @@
       </c>
       <c r="J21" s="70" t="n"/>
     </row>
-    <row r="22" ht="33" customHeight="1" s="50">
+    <row r="22" ht="62" customHeight="1" s="50">
       <c r="A22" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2849,27 +2890,27 @@
       </c>
       <c r="C22" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D22" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D22" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E22" s="62" t="inlineStr">
         <is>
-          <t>Pedir al club irlandés testimonio y presentaciones</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F22" s="70" t="inlineStr">
         <is>
-          <t>Es lo que más puede acelerar ventas: un club que ya compró habla mejor de nosotros que cualquier email. Texto en 'Respuestas tipo'. Puedes mandarlo tú o Enrique.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G22" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (Respuestas tipo)</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H22" s="70" t="n">
@@ -2893,31 +2934,31 @@
       </c>
       <c r="C23" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D23" s="72" t="inlineStr">
-        <is>
-          <t>Transversal</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D23" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E23" s="62" t="inlineStr">
         <is>
-          <t>Ajustar Calendly por mercado (franjas distintas para clubes y familias)</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F23" s="70" t="inlineStr">
         <is>
-          <t>Mira la tabla de franjas en LEEME. Resumen: para clubes de Europa solo sirven Martes 13:00 a 15:00 y Miércoles 11:00 a 12:30 (hora NY). Para familias de América sirven Lunes y Jueves por la tarde. Pasos: crea el evento 'Always Up Intro Call' (20 min, Zoom) con la agenda Europa, y deja 'USA Scholarship Assessment' con la agenda Américas. Luego pásame el enlace de cada uno.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G23" s="70" t="inlineStr">
         <is>
-          <t>Calendly</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H23" s="70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I23" s="70" t="inlineStr">
         <is>
@@ -2926,7 +2967,7 @@
       </c>
       <c r="J23" s="70" t="n"/>
     </row>
-    <row r="24" ht="62" customHeight="1" s="50">
+    <row r="24" ht="33" customHeight="1" s="50">
       <c r="A24" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2940,22 +2981,26 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D24" s="72" t="inlineStr">
-        <is>
-          <t>Transversal</t>
+      <c r="D24" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E24" s="62" t="inlineStr">
         <is>
-          <t>Calentar el dominio: 2 o 3 correos reales más a gente de confianza (ya hiciste 3)</t>
+          <t>Darme tu feedback sobre la ficha de Becas EEUU</t>
         </is>
       </c>
       <c r="F24" s="70" t="inlineStr">
         <is>
-          <t>Escribe desde alwaysup.es a 2 o 3 personas más (familia, amigos, conocidos con Gmail, Outlook o iCloud) un correo normal con una pregunta, y pídeles que respondan. Si caen en spam, que lo marquen como 'No es spam'. Es la forma más rápida de mejorar la reputación de un dominio nuevo.</t>
-        </is>
-      </c>
-      <c r="G24" s="70" t="inlineStr"/>
+          <t>Ábrela (02-sales/assets/Always-Up-Becas-EEUU.pdf) y dime qué cambiarías. Antes de cambiar nada te digo si me parece buena idea.</t>
+        </is>
+      </c>
+      <c r="G24" s="70" t="inlineStr">
+        <is>
+          <t>02-sales/assets</t>
+        </is>
+      </c>
       <c r="H24" s="70" t="n">
         <v>15</v>
       </c>
@@ -2966,7 +3011,7 @@
       </c>
       <c r="J24" s="70" t="n"/>
     </row>
-    <row r="25" ht="76.5" customHeight="1" s="50">
+    <row r="25" ht="33" customHeight="1" s="50">
       <c r="A25" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2987,21 +3032,21 @@
       </c>
       <c r="E25" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Georgia Townsend (Hastings United)</t>
+          <t>Pedir al club irlandés testimonio y presentaciones</t>
         </is>
       </c>
       <c r="F25" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Georgia, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>Es lo que más puede acelerar ventas: un club que ya compró habla mejor de nosotros que cualquier email. Texto en 'Respuestas tipo'. Puedes mandarlo tú o Enrique.</t>
         </is>
       </c>
       <c r="G25" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (Respuestas tipo)</t>
         </is>
       </c>
       <c r="H25" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I25" s="70" t="inlineStr">
         <is>
@@ -3010,86 +3055,82 @@
       </c>
       <c r="J25" s="70" t="n"/>
     </row>
-    <row r="26" ht="62" customHeight="1" s="50">
+    <row r="26" ht="76.5" customHeight="1" s="50">
       <c r="A26" s="94" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B26" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C26" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D26" s="72" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="E26" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Ajustar Calendly por mercado (franjas distintas para clubes y familias)</t>
         </is>
       </c>
       <c r="F26" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Mira la tabla de franjas en LEEME. Resumen: para clubes de Europa solo sirven Martes 13:00 a 15:00 y Miércoles 11:00 a 12:30 (hora NY). Para familias de América sirven Lunes y Jueves por la tarde. Pasos: crea el evento 'Always Up Intro Call' (20 min, Zoom) con la agenda Europa, y deja 'USA Scholarship Assessment' con la agenda Américas. Luego pásame el enlace de cada uno.</t>
         </is>
       </c>
       <c r="G26" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Calendly</t>
         </is>
       </c>
       <c r="H26" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I26" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J26" s="70" t="n"/>
+    </row>
+    <row r="27" ht="62" customHeight="1" s="50">
+      <c r="A27" s="94" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C27" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D27" s="72" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E27" s="62" t="inlineStr">
+        <is>
+          <t>Calentar el dominio: 2 o 3 correos reales más a gente de confianza (ya hiciste 3)</t>
+        </is>
+      </c>
+      <c r="F27" s="70" t="inlineStr">
+        <is>
+          <t>Escribe desde alwaysup.es a 2 o 3 personas más (familia, amigos, conocidos con Gmail, Outlook o iCloud) un correo normal con una pregunta, y pídeles que respondan. Si caen en spam, que lo marquen como 'No es spam'. Es la forma más rápida de mejorar la reputación de un dominio nuevo.</t>
+        </is>
+      </c>
+      <c r="G27" s="70" t="inlineStr"/>
+      <c r="H27" s="70" t="n">
         <v>15</v>
-      </c>
-      <c r="I26" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J26" s="70" t="n"/>
-    </row>
-    <row r="27" ht="33" customHeight="1" s="50">
-      <c r="A27" s="94" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B27" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C27" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D27" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E27" s="62" t="inlineStr">
-        <is>
-          <t>Revisión semanal 1: qué ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F27" s="70" t="inlineStr">
-        <is>
-          <t>Mira la hoja Hoy y anota respuestas, rebotes y llamadas. Pásame un resumen de tres líneas: yo ajusto el plan.</t>
-        </is>
-      </c>
-      <c r="G27" s="70" t="inlineStr">
-        <is>
-          <t>Hoy</t>
-        </is>
-      </c>
-      <c r="H27" s="70" t="n">
-        <v>20</v>
       </c>
       <c r="I27" s="70" t="inlineStr">
         <is>
@@ -3100,11 +3141,11 @@
     </row>
     <row r="28" ht="76.5" customHeight="1" s="50">
       <c r="A28" s="94" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B28" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C28" s="71" t="inlineStr">
@@ -3119,12 +3160,12 @@
       </c>
       <c r="E28" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Callum Lawe (Holbeach United)</t>
+          <t>LinkedIn: conectar con Georgia Townsend (Hastings United)</t>
         </is>
       </c>
       <c r="F28" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Callum, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Georgia, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G28" s="70" t="inlineStr">
@@ -3142,7 +3183,7 @@
       </c>
       <c r="J28" s="70" t="n"/>
     </row>
-    <row r="29" ht="76.5" customHeight="1" s="50">
+    <row r="29" ht="62" customHeight="1" s="50">
       <c r="A29" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3153,31 +3194,31 @@
       </c>
       <c r="C29" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D29" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D29" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E29" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Marius Engen (Søreide IL)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F29" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Marius, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G29" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H29" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I29" s="70" t="inlineStr">
         <is>
@@ -3207,112 +3248,149 @@
       </c>
       <c r="E30" s="62" t="inlineStr">
         <is>
+          <t>Revisión semanal 1: qué ha pasado esta semana</t>
+        </is>
+      </c>
+      <c r="F30" s="70" t="inlineStr">
+        <is>
+          <t>Mira la hoja Hoy y anota respuestas, rebotes y llamadas. Pásame un resumen de tres líneas: yo ajusto el plan.</t>
+        </is>
+      </c>
+      <c r="G30" s="70" t="inlineStr">
+        <is>
+          <t>Hoy</t>
+        </is>
+      </c>
+      <c r="H30" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I30" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J30" s="70" t="n"/>
+    </row>
+    <row r="31" ht="76.5" customHeight="1" s="50">
+      <c r="A31" s="94" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B31" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C31" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D31" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E31" s="62" t="inlineStr">
+        <is>
+          <t>LinkedIn: conectar con Callum Lawe (Holbeach United)</t>
+        </is>
+      </c>
+      <c r="F31" s="70" t="inlineStr">
+        <is>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Callum, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+        </is>
+      </c>
+      <c r="G31" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H31" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J31" s="70" t="n"/>
+    </row>
+    <row r="32" ht="76.5" customHeight="1" s="50">
+      <c r="A32" s="94" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B32" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C32" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D32" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E32" s="62" t="inlineStr">
+        <is>
+          <t>LinkedIn: conectar con Marius Engen (Søreide IL)</t>
+        </is>
+      </c>
+      <c r="F32" s="70" t="inlineStr">
+        <is>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Marius, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+        </is>
+      </c>
+      <c r="G32" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H32" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J32" s="70" t="n"/>
+    </row>
+    <row r="33" ht="33" customHeight="1" s="50">
+      <c r="A33" s="94" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B33" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D33" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E33" s="62" t="inlineStr">
+        <is>
           <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
-      <c r="F30" s="70" t="inlineStr">
+      <c r="F33" s="70" t="inlineStr">
         <is>
           <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
-      <c r="G30" s="70" t="inlineStr">
+      <c r="G33" s="70" t="inlineStr">
         <is>
           <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H30" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I30" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J30" s="70" t="n"/>
-    </row>
-    <row r="31" ht="47.5" customHeight="1" s="50">
-      <c r="A31" s="94" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B31" s="70" t="inlineStr">
-        <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="C31" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D31" s="75" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="E31" s="62" t="inlineStr">
-        <is>
-          <t>Sesión de redes sociales y marca personal con Claude (30 a 60 min)</t>
-        </is>
-      </c>
-      <c r="F31" s="70" t="inlineStr">
-        <is>
-          <t>Objetivo: 10.000 seguidores antes de fin de 2026. Salir con un plan de contenido de 4 semanas. Hasta tener este plan no se publica nada. Sin fotos de menores identificables.</t>
-        </is>
-      </c>
-      <c r="G31" s="70" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H31" s="70" t="n">
-        <v>60</v>
-      </c>
-      <c r="I31" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J31" s="70" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" s="50">
-      <c r="A32" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  19/10 a 25/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="62" customHeight="1" s="50">
-      <c r="A33" s="94" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B33" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C33" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D33" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E33" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F33" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G33" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H33" s="70" t="n">
@@ -3325,13 +3403,13 @@
       </c>
       <c r="J33" s="70" t="n"/>
     </row>
-    <row r="34" ht="33" customHeight="1" s="50">
+    <row r="34" ht="47.5" customHeight="1" s="50">
       <c r="A34" s="94" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B34" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="C34" s="71" t="inlineStr">
@@ -3339,19 +3417,19 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D34" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D34" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E34" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Sesión de redes sociales y marca personal con Claude (30 a 60 min)</t>
         </is>
       </c>
       <c r="F34" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Objetivo: 10.000 seguidores antes de fin de 2026. Salir con un plan de contenido de 4 semanas. Hasta tener este plan no se publica nada. Sin fotos de menores identificables.</t>
         </is>
       </c>
       <c r="G34" s="70" t="inlineStr">
@@ -3360,7 +3438,7 @@
         </is>
       </c>
       <c r="H34" s="70" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="I34" s="70" t="inlineStr">
         <is>
@@ -3369,51 +3447,14 @@
       </c>
       <c r="J34" s="70" t="n"/>
     </row>
-    <row r="35" ht="33" customHeight="1" s="50">
-      <c r="A35" s="94" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B35" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C35" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D35" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
-        </is>
-      </c>
-      <c r="E35" s="62" t="inlineStr">
-        <is>
-          <t>Revisar leads de becas con acción vencida</t>
-        </is>
-      </c>
-      <c r="F35" s="70" t="inlineStr">
-        <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
-        </is>
-      </c>
-      <c r="G35" s="70" t="inlineStr">
-        <is>
-          <t>Segmento C - Becas</t>
-        </is>
-      </c>
-      <c r="H35" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I35" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J35" s="70" t="n"/>
-    </row>
-    <row r="36" ht="76.5" customHeight="1" s="50">
+    <row r="35" ht="22" customHeight="1" s="50">
+      <c r="A35" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  19/10 a 25/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="62" customHeight="1" s="50">
       <c r="A36" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3424,31 +3465,31 @@
       </c>
       <c r="C36" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D36" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D36" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E36" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Luke Johnston (Whitehaven AFC)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F36" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Luke, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G36" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H36" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I36" s="70" t="inlineStr">
         <is>
@@ -3478,17 +3519,21 @@
       </c>
       <c r="E37" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: 10 minutos de actividad</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F37" s="70" t="inlineStr">
         <is>
-          <t>Acepta conexiones, comenta tres publicaciones de entrenadores o clubes con algo de valor (no publicidad). Eso hace que te vean antes de que llegue el email.</t>
-        </is>
-      </c>
-      <c r="G37" s="70" t="inlineStr"/>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+        </is>
+      </c>
+      <c r="G37" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
       <c r="H37" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I37" s="70" t="inlineStr">
         <is>
@@ -3497,77 +3542,77 @@
       </c>
       <c r="J37" s="70" t="n"/>
     </row>
-    <row r="38" ht="62" customHeight="1" s="50">
+    <row r="38" ht="33" customHeight="1" s="50">
       <c r="A38" s="94" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B38" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="C38" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D38" s="74" t="inlineStr">
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D38" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E38" s="62" t="inlineStr">
+        <is>
+          <t>Revisar leads de becas con acción vencida</t>
+        </is>
+      </c>
+      <c r="F38" s="70" t="inlineStr">
+        <is>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G38" s="70" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
+      <c r="H38" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I38" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J38" s="70" t="n"/>
+    </row>
+    <row r="39" ht="76.5" customHeight="1" s="50">
+      <c r="A39" s="94" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B39" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C39" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D39" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E38" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR email 1 a FC Porte d'Aquitaine</t>
-        </is>
-      </c>
-      <c r="F38" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 13:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G38" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H38" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I38" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J38" s="70" t="n"/>
-    </row>
-    <row r="39" ht="62" customHeight="1" s="50">
-      <c r="A39" s="94" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B39" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C39" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D39" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
       <c r="E39" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Hastings United</t>
+          <t>LinkedIn: conectar con Luke Johnston (Whitehaven AFC)</t>
         </is>
       </c>
       <c r="F39" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Luke, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G39" s="70" t="inlineStr">
@@ -3585,18 +3630,18 @@
       </c>
       <c r="J39" s="70" t="n"/>
     </row>
-    <row r="40" ht="62" customHeight="1" s="50">
+    <row r="40" ht="33" customHeight="1" s="50">
       <c r="A40" s="94" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B40" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="C40" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D40" s="74" t="inlineStr">
@@ -3606,74 +3651,75 @@
       </c>
       <c r="E40" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Home Farm FC</t>
+          <t>LinkedIn: 10 minutos de actividad</t>
         </is>
       </c>
       <c r="F40" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G40" s="70" t="inlineStr">
+          <t>Acepta conexiones, comenta tres publicaciones de entrenadores o clubes con algo de valor (no publicidad). Eso hace que te vean antes de que llegue el email.</t>
+        </is>
+      </c>
+      <c r="G40" s="70" t="inlineStr"/>
+      <c r="H40" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I40" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J40" s="70" t="n"/>
+    </row>
+    <row r="41" ht="192.5" customHeight="1" s="50">
+      <c r="A41" s="94" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B41" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C41" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D41" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E41" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del martes 20/10</t>
+        </is>
+      </c>
+      <c r="F41" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 20/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• FC Porte d'Aquitaine | Email 1 | programar para las 03:30 hora Nueva York (09:30 allí)
+• Hastings United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+• Home Farm FC | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+• Virtu Academy | Email 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G41" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H40" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I40" s="70" t="inlineStr">
+      <c r="H41" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I41" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J40" s="70" t="n"/>
-    </row>
-    <row r="41" ht="62" customHeight="1" s="50">
-      <c r="A41" s="94" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B41" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C41" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D41" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E41" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR email 1 a Virtu Academy</t>
-        </is>
-      </c>
-      <c r="F41" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G41" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H41" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I41" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J41" s="70" t="n"/>
     </row>
-    <row r="42" ht="62" customHeight="1" s="50">
+    <row r="42" ht="47.5" customHeight="1" s="50">
       <c r="A42" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3684,7 +3730,7 @@
       </c>
       <c r="C42" s="71" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="D42" s="74" t="inlineStr">
@@ -3694,22 +3740,20 @@
       </c>
       <c r="E42" s="62" t="inlineStr">
         <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
+          <t>ENVIAR email 1 a FC Porte d'Aquitaine</t>
         </is>
       </c>
       <c r="F42" s="70" t="inlineStr">
         <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G42" s="70" t="inlineStr">
         <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H42" s="70" t="n">
-        <v>5</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H42" s="70" t="n"/>
       <c r="I42" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3717,7 +3761,7 @@
       </c>
       <c r="J42" s="70" t="n"/>
     </row>
-    <row r="43" ht="62" customHeight="1" s="50">
+    <row r="43" ht="47.5" customHeight="1" s="50">
       <c r="A43" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3728,32 +3772,30 @@
       </c>
       <c r="C43" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D43" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D43" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E43" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>ENVIAR follow-up 1 a Hastings United</t>
         </is>
       </c>
       <c r="F43" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G43" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H43" s="70" t="n">
-        <v>15</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H43" s="70" t="n"/>
       <c r="I43" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3772,32 +3814,30 @@
       </c>
       <c r="C44" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D44" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D44" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E44" s="62" t="inlineStr">
         <is>
-          <t>Omar: último mensaje corto si sigue sin contestar</t>
+          <t>ENVIAR follow-up 1 a Home Farm FC</t>
         </is>
       </c>
       <c r="F44" s="70" t="inlineStr">
         <is>
-          <t>«Hola Omar, no quiero atosigarte. Si en este momento no es prioridad, no pasa nada, lo dejamos aquí y lo retomamos cuando te venga bien. Si quieres seguir, mándame lo que tengas del vídeo y empezamos.» Después pásalo a 'Frío' en el CRM.</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G44" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
-        </is>
-      </c>
-      <c r="H44" s="70" t="n">
-        <v>5</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H44" s="70" t="n"/>
       <c r="I44" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3805,18 +3845,18 @@
       </c>
       <c r="J44" s="70" t="n"/>
     </row>
-    <row r="45" ht="62" customHeight="1" s="50">
+    <row r="45" ht="47.5" customHeight="1" s="50">
       <c r="A45" s="94" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B45" s="70" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="C45" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D45" s="74" t="inlineStr">
@@ -3826,12 +3866,12 @@
       </c>
       <c r="E45" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Holbeach United</t>
+          <t>ENVIAR email 1 a Virtu Academy</t>
         </is>
       </c>
       <c r="F45" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G45" s="70" t="inlineStr">
@@ -3839,9 +3879,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H45" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H45" s="70" t="n"/>
       <c r="I45" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3851,261 +3889,260 @@
     </row>
     <row r="46" ht="62" customHeight="1" s="50">
       <c r="A46" s="94" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B46" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C46" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D46" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E46" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F46" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G46" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H46" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I46" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J46" s="70" t="n"/>
+    </row>
+    <row r="47" ht="76.5" customHeight="1" s="50">
+      <c r="A47" s="94" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B47" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C47" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D47" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E47" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F47" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G47" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H47" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I47" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J47" s="70" t="n"/>
+    </row>
+    <row r="48" ht="47.5" customHeight="1" s="50">
+      <c r="A48" s="94" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B48" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C48" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D48" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E48" s="62" t="inlineStr">
+        <is>
+          <t>Omar: último mensaje corto si sigue sin contestar</t>
+        </is>
+      </c>
+      <c r="F48" s="70" t="inlineStr">
+        <is>
+          <t>«Hola Omar, no quiero atosigarte. Si en este momento no es prioridad, no pasa nada, lo dejamos aquí y lo retomamos cuando te venga bien. Si quieres seguir, mándame lo que tengas del vídeo y empezamos.» Después pásalo a 'Frío' en el CRM.</t>
+        </is>
+      </c>
+      <c r="G48" s="70" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
+      <c r="H48" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I48" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J48" s="70" t="n"/>
+    </row>
+    <row r="49" ht="149" customHeight="1" s="50">
+      <c r="A49" s="94" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B49" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C49" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D49" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E49" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del miércoles 21/10</t>
+        </is>
+      </c>
+      <c r="F49" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 21/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• Holbeach United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+• Søreide IL | Follow-up 1 | programar para las 03:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G49" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H49" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I49" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J49" s="70" t="n"/>
+    </row>
+    <row r="50" ht="47.5" customHeight="1" s="50">
+      <c r="A50" s="94" t="n">
         <v>46316</v>
       </c>
-      <c r="B46" s="70" t="inlineStr">
+      <c r="B50" s="70" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C46" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D46" s="74" t="inlineStr">
+      <c r="C50" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D50" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E46" s="62" t="inlineStr">
+      <c r="E50" s="62" t="inlineStr">
         <is>
           <t>ENVIAR follow-up 1 a Søreide IL</t>
         </is>
       </c>
-      <c r="F46" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 13:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G46" s="70" t="inlineStr">
+      <c r="F50" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G50" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H46" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I46" s="70" t="inlineStr">
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J46" s="70" t="n"/>
-    </row>
-    <row r="47" ht="62" customHeight="1" s="50">
-      <c r="A47" s="94" t="n">
+      <c r="J50" s="70" t="n"/>
+    </row>
+    <row r="51" ht="47.5" customHeight="1" s="50">
+      <c r="A51" s="94" t="n">
         <v>46316</v>
       </c>
-      <c r="B47" s="70" t="inlineStr">
+      <c r="B51" s="70" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C47" s="71" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D47" s="74" t="inlineStr">
+      <c r="C51" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D51" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E47" s="62" t="inlineStr">
-        <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
-        </is>
-      </c>
-      <c r="F47" s="70" t="inlineStr">
-        <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
-        </is>
-      </c>
-      <c r="G47" s="70" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H47" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I47" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J47" s="70" t="n"/>
-    </row>
-    <row r="48" ht="62" customHeight="1" s="50">
-      <c r="A48" s="94" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B48" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C48" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D48" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E48" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F48" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G48" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H48" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I48" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J48" s="70" t="n"/>
-    </row>
-    <row r="49" ht="62" customHeight="1" s="50">
-      <c r="A49" s="94" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B49" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C49" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D49" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E49" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 1 a IA Akranes</t>
-        </is>
-      </c>
-      <c r="F49" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G49" s="70" t="inlineStr">
+      <c r="E51" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a Holbeach United</t>
+        </is>
+      </c>
+      <c r="F51" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G51" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H49" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I49" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J49" s="70" t="n"/>
-    </row>
-    <row r="50" ht="62" customHeight="1" s="50">
-      <c r="A50" s="94" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B50" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C50" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D50" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E50" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 1 a Maidstone United</t>
-        </is>
-      </c>
-      <c r="F50" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G50" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H50" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I50" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J50" s="70" t="n"/>
-    </row>
-    <row r="51" ht="62" customHeight="1" s="50">
-      <c r="A51" s="94" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B51" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C51" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D51" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E51" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 1 a Whitehaven AFC</t>
-        </is>
-      </c>
-      <c r="F51" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G51" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H51" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H51" s="70" t="n"/>
       <c r="I51" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4115,292 +4152,298 @@
     </row>
     <row r="52" ht="62" customHeight="1" s="50">
       <c r="A52" s="94" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B52" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C52" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D52" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E52" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F52" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G52" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H52" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I52" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J52" s="70" t="n"/>
+    </row>
+    <row r="53" ht="76.5" customHeight="1" s="50">
+      <c r="A53" s="94" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B53" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C53" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D53" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E53" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F53" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G53" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H53" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J53" s="70" t="n"/>
+    </row>
+    <row r="54" ht="178" customHeight="1" s="50">
+      <c r="A54" s="94" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B54" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C54" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D54" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E54" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del jueves 22/10</t>
+        </is>
+      </c>
+      <c r="F54" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 22/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• IA Akranes | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 allí)
+• Maidstone United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+• Whitehaven AFC | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G54" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H54" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J54" s="70" t="n"/>
+    </row>
+    <row r="55" ht="47.5" customHeight="1" s="50">
+      <c r="A55" s="94" t="n">
         <v>46317</v>
       </c>
-      <c r="B52" s="70" t="inlineStr">
+      <c r="B55" s="70" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C52" s="71" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D52" s="74" t="inlineStr">
+      <c r="C55" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D55" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E52" s="62" t="inlineStr">
-        <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
-        </is>
-      </c>
-      <c r="F52" s="70" t="inlineStr">
-        <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
-        </is>
-      </c>
-      <c r="G52" s="70" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H52" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I52" s="70" t="inlineStr">
+      <c r="E55" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a Maidstone United</t>
+        </is>
+      </c>
+      <c r="F55" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G55" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H55" s="70" t="n"/>
+      <c r="I55" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J52" s="70" t="n"/>
-    </row>
-    <row r="53" ht="62" customHeight="1" s="50">
-      <c r="A53" s="94" t="n">
+      <c r="J55" s="70" t="n"/>
+    </row>
+    <row r="56" ht="47.5" customHeight="1" s="50">
+      <c r="A56" s="94" t="n">
         <v>46317</v>
       </c>
-      <c r="B53" s="70" t="inlineStr">
+      <c r="B56" s="70" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C53" s="71" t="inlineStr">
+      <c r="C56" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D56" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E56" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a Whitehaven AFC</t>
+        </is>
+      </c>
+      <c r="F56" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G56" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H56" s="70" t="n"/>
+      <c r="I56" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J56" s="70" t="n"/>
+    </row>
+    <row r="57" ht="47.5" customHeight="1" s="50">
+      <c r="A57" s="94" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B57" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C57" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D57" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E57" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a IA Akranes</t>
+        </is>
+      </c>
+      <c r="F57" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G57" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H57" s="70" t="n"/>
+      <c r="I57" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J57" s="70" t="n"/>
+    </row>
+    <row r="58" ht="62" customHeight="1" s="50">
+      <c r="A58" s="94" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B58" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C58" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D53" s="72" t="inlineStr">
+      <c r="D58" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E53" s="62" t="inlineStr">
+      <c r="E58" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F53" s="70" t="inlineStr">
+      <c r="F58" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G53" s="70" t="inlineStr">
+      <c r="G58" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H53" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I53" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J53" s="70" t="n"/>
-    </row>
-    <row r="54" ht="47.5" customHeight="1" s="50">
-      <c r="A54" s="94" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B54" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C54" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D54" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E54" s="62" t="inlineStr">
-        <is>
-          <t>Preguntar a Atlético y Real Sociedad por las fechas reales de Semana Santa y verano 2027</t>
-        </is>
-      </c>
-      <c r="F54" s="70" t="inlineStr">
-        <is>
-          <t>Necesitamos saber qué semanas hay disponibles y hasta cuándo se pueden reservar. Con eso tendremos urgencia real y honesta para los follow-ups (hoy no la tenemos). Puede hacerlo Enrique.</t>
-        </is>
-      </c>
-      <c r="G54" s="70" t="inlineStr"/>
-      <c r="H54" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I54" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J54" s="70" t="n"/>
-    </row>
-    <row r="55" ht="62" customHeight="1" s="50">
-      <c r="A55" s="94" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B55" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C55" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D55" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E55" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F55" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G55" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H55" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I55" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J55" s="70" t="n"/>
-    </row>
-    <row r="56" ht="62" customHeight="1" s="50">
-      <c r="A56" s="94" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B56" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C56" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D56" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E56" s="62" t="inlineStr">
-        <is>
-          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
-        </is>
-      </c>
-      <c r="F56" s="70" t="inlineStr">
-        <is>
-          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
-        </is>
-      </c>
-      <c r="G56" s="70" t="inlineStr">
-        <is>
-          <t>plan-outreach-30-dias.md sección 7</t>
-        </is>
-      </c>
-      <c r="H56" s="70" t="n">
-        <v>45</v>
-      </c>
-      <c r="I56" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J56" s="70" t="n"/>
-    </row>
-    <row r="57" ht="33" customHeight="1" s="50">
-      <c r="A57" s="94" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B57" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C57" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D57" s="76" t="inlineStr">
-        <is>
-          <t>International Program</t>
-        </is>
-      </c>
-      <c r="E57" s="62" t="inlineStr">
-        <is>
-          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
-        </is>
-      </c>
-      <c r="F57" s="70" t="inlineStr">
-        <is>
-          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
-        </is>
-      </c>
-      <c r="G57" s="70" t="inlineStr"/>
-      <c r="H57" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I57" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J57" s="70" t="n"/>
-    </row>
-    <row r="58" ht="33" customHeight="1" s="50">
-      <c r="A58" s="94" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B58" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C58" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D58" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E58" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F58" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G58" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H58" s="70" t="n">
@@ -4413,64 +4456,97 @@
       </c>
       <c r="J58" s="70" t="n"/>
     </row>
-    <row r="59" ht="33" customHeight="1" s="50">
+    <row r="59" ht="76.5" customHeight="1" s="50">
       <c r="A59" s="94" t="n">
-        <v>46319</v>
+        <v>46317</v>
       </c>
       <c r="B59" s="70" t="inlineStr">
         <is>
-          <t>Sábado</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C59" s="71" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D59" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E59" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F59" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G59" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H59" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I59" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J59" s="70" t="n"/>
+    </row>
+    <row r="60" ht="47.5" customHeight="1" s="50">
+      <c r="A60" s="94" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B60" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C60" s="71" t="inlineStr">
+        <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D59" s="76" t="inlineStr">
-        <is>
-          <t>GEE / Fichas</t>
-        </is>
-      </c>
-      <c r="E59" s="62" t="inlineStr">
-        <is>
-          <t>Revisar las nuevas fichas (GEE, Campus Internacional, International Program)</t>
-        </is>
-      </c>
-      <c r="F59" s="70" t="inlineStr">
-        <is>
-          <t>Las preparo yo tras tu feedback de la ficha de Becas. Tú revisas y me dices qué cambiar.</t>
-        </is>
-      </c>
-      <c r="G59" s="70" t="inlineStr">
-        <is>
-          <t>02-sales/assets</t>
-        </is>
-      </c>
-      <c r="H59" s="70" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="70" t="inlineStr">
+      <c r="D60" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E60" s="62" t="inlineStr">
+        <is>
+          <t>Preguntar a Atlético y Real Sociedad por las fechas reales de Semana Santa y verano 2027</t>
+        </is>
+      </c>
+      <c r="F60" s="70" t="inlineStr">
+        <is>
+          <t>Necesitamos saber qué semanas hay disponibles y hasta cuándo se pueden reservar. Con eso tendremos urgencia real y honesta para los follow-ups (hoy no la tenemos). Puede hacerlo Enrique.</t>
+        </is>
+      </c>
+      <c r="G60" s="70" t="inlineStr"/>
+      <c r="H60" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I60" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J59" s="70" t="n"/>
-    </row>
-    <row r="60" ht="22" customHeight="1" s="50">
-      <c r="A60" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  26/10 a 01/11</t>
-        </is>
-      </c>
+      <c r="J60" s="70" t="n"/>
     </row>
     <row r="61" ht="62" customHeight="1" s="50">
       <c r="A61" s="94" t="n">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="B61" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C61" s="71" t="inlineStr">
@@ -4508,13 +4584,13 @@
       </c>
       <c r="J61" s="70" t="n"/>
     </row>
-    <row r="62" ht="33" customHeight="1" s="50">
+    <row r="62" ht="62" customHeight="1" s="50">
       <c r="A62" s="94" t="n">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="B62" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C62" s="71" t="inlineStr">
@@ -4522,28 +4598,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D62" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D62" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E62" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
         </is>
       </c>
       <c r="F62" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
         </is>
       </c>
       <c r="G62" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>plan-outreach-30-dias.md sección 7</t>
         </is>
       </c>
       <c r="H62" s="70" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="I62" s="70" t="inlineStr">
         <is>
@@ -4554,11 +4630,11 @@
     </row>
     <row r="63" ht="33" customHeight="1" s="50">
       <c r="A63" s="94" t="n">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="B63" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C63" s="71" t="inlineStr">
@@ -4566,28 +4642,24 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D63" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D63" s="76" t="inlineStr">
+        <is>
+          <t>International Program</t>
         </is>
       </c>
       <c r="E63" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
         </is>
       </c>
       <c r="F63" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
-        </is>
-      </c>
-      <c r="G63" s="70" t="inlineStr">
-        <is>
-          <t>Segmento C - Becas</t>
-        </is>
-      </c>
+          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
+        </is>
+      </c>
+      <c r="G63" s="70" t="inlineStr"/>
       <c r="H63" s="70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I63" s="70" t="inlineStr">
         <is>
@@ -4598,11 +4670,11 @@
     </row>
     <row r="64" ht="33" customHeight="1" s="50">
       <c r="A64" s="94" t="n">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="B64" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C64" s="71" t="inlineStr">
@@ -4610,24 +4682,24 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D64" s="76" t="inlineStr">
-        <is>
-          <t>Campus Internacional</t>
+      <c r="D64" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E64" s="62" t="inlineStr">
         <is>
-          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F64" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G64" s="70" t="inlineStr">
         <is>
-          <t>Oportunidades y notas</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H64" s="70" t="n">
@@ -4640,42 +4712,42 @@
       </c>
       <c r="J64" s="70" t="n"/>
     </row>
-    <row r="65" ht="62" customHeight="1" s="50">
+    <row r="65" ht="33" customHeight="1" s="50">
       <c r="A65" s="94" t="n">
-        <v>46322</v>
+        <v>46319</v>
       </c>
       <c r="B65" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="C65" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D65" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D65" s="76" t="inlineStr">
+        <is>
+          <t>GEE / Fichas</t>
         </is>
       </c>
       <c r="E65" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a FC Porte d'Aquitaine</t>
+          <t>Revisar las nuevas fichas (GEE, Campus Internacional, International Program)</t>
         </is>
       </c>
       <c r="F65" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Las preparo yo tras tu feedback de la ficha de Becas. Tú revisas y me dices qué cambiar.</t>
         </is>
       </c>
       <c r="G65" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>02-sales/assets</t>
         </is>
       </c>
       <c r="H65" s="70" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I65" s="70" t="inlineStr">
         <is>
@@ -4684,126 +4756,89 @@
       </c>
       <c r="J65" s="70" t="n"/>
     </row>
-    <row r="66" ht="62" customHeight="1" s="50">
-      <c r="A66" s="94" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B66" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C66" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D66" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E66" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Hastings United</t>
-        </is>
-      </c>
-      <c r="F66" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G66" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H66" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I66" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J66" s="70" t="n"/>
+    <row r="66" ht="22" customHeight="1" s="50">
+      <c r="A66" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  26/10 a 01/11</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="62" customHeight="1" s="50">
       <c r="A67" s="94" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B67" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="C67" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D67" s="74" t="inlineStr">
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D67" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E67" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F67" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G67" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H67" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I67" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J67" s="70" t="n"/>
+    </row>
+    <row r="68" ht="33" customHeight="1" s="50">
+      <c r="A68" s="94" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B68" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C68" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D68" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E67" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Home Farm FC</t>
-        </is>
-      </c>
-      <c r="F67" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G67" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H67" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I67" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J67" s="70" t="n"/>
-    </row>
-    <row r="68" ht="62" customHeight="1" s="50">
-      <c r="A68" s="94" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B68" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C68" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D68" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
       <c r="E68" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Virtu Academy</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F68" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G68" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H68" s="70" t="n">
@@ -4816,42 +4851,42 @@
       </c>
       <c r="J68" s="70" t="n"/>
     </row>
-    <row r="69" ht="62" customHeight="1" s="50">
+    <row r="69" ht="33" customHeight="1" s="50">
       <c r="A69" s="94" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B69" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="C69" s="71" t="inlineStr">
         <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D69" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D69" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E69" s="62" t="inlineStr">
         <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F69" s="70" t="inlineStr">
         <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G69" s="70" t="inlineStr">
         <is>
-          <t>Enviados / Recibidos</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H69" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I69" s="70" t="inlineStr">
         <is>
@@ -4860,38 +4895,38 @@
       </c>
       <c r="J69" s="70" t="n"/>
     </row>
-    <row r="70" ht="62" customHeight="1" s="50">
+    <row r="70" ht="33" customHeight="1" s="50">
       <c r="A70" s="94" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B70" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="C70" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D70" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D70" s="76" t="inlineStr">
+        <is>
+          <t>Campus Internacional</t>
         </is>
       </c>
       <c r="E70" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
         </is>
       </c>
       <c r="F70" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
         </is>
       </c>
       <c r="G70" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Oportunidades y notas</t>
         </is>
       </c>
       <c r="H70" s="70" t="n">
@@ -4904,262 +4939,259 @@
       </c>
       <c r="J70" s="70" t="n"/>
     </row>
-    <row r="71" ht="33" customHeight="1" s="50">
+    <row r="71" ht="207" customHeight="1" s="50">
       <c r="A71" s="94" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C71" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D71" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E71" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del martes 27/10</t>
+        </is>
+      </c>
+      <c r="F71" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 27/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• FC Porte d'Aquitaine | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
+• Hastings United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
+• Home Farm FC | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
+• Virtu Academy | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G71" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H71" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I71" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J71" s="70" t="n"/>
+    </row>
+    <row r="72" ht="47.5" customHeight="1" s="50">
+      <c r="A72" s="94" t="n">
         <v>46322</v>
       </c>
-      <c r="B71" s="70" t="inlineStr">
+      <c r="B72" s="70" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C71" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D71" s="74" t="inlineStr">
+      <c r="C72" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D72" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E71" s="62" t="inlineStr">
-        <is>
-          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
-        </is>
-      </c>
-      <c r="F71" s="70" t="inlineStr">
-        <is>
-          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
-        </is>
-      </c>
-      <c r="G71" s="70" t="inlineStr">
+      <c r="E72" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F72" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G72" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H71" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I71" s="70" t="inlineStr">
+      <c r="H72" s="70" t="n"/>
+      <c r="I72" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J71" s="70" t="n"/>
-    </row>
-    <row r="72" ht="62" customHeight="1" s="50">
-      <c r="A72" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B72" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C72" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D72" s="74" t="inlineStr">
+      <c r="J72" s="70" t="n"/>
+    </row>
+    <row r="73" ht="47.5" customHeight="1" s="50">
+      <c r="A73" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B73" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C73" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D73" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E72" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Holbeach United</t>
-        </is>
-      </c>
-      <c r="F72" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G72" s="70" t="inlineStr">
+      <c r="E73" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Hastings United</t>
+        </is>
+      </c>
+      <c r="F73" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G73" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H72" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I72" s="70" t="inlineStr">
+      <c r="H73" s="70" t="n"/>
+      <c r="I73" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J72" s="70" t="n"/>
-    </row>
-    <row r="73" ht="62" customHeight="1" s="50">
-      <c r="A73" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B73" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C73" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D73" s="74" t="inlineStr">
+      <c r="J73" s="70" t="n"/>
+    </row>
+    <row r="74" ht="47.5" customHeight="1" s="50">
+      <c r="A74" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B74" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C74" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D74" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E73" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Søreide IL</t>
-        </is>
-      </c>
-      <c r="F73" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G73" s="70" t="inlineStr">
+      <c r="E74" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Home Farm FC</t>
+        </is>
+      </c>
+      <c r="F74" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G74" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H73" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I73" s="70" t="inlineStr">
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J73" s="70" t="n"/>
-    </row>
-    <row r="74" ht="62" customHeight="1" s="50">
-      <c r="A74" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B74" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C74" s="71" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D74" s="74" t="inlineStr">
+      <c r="J74" s="70" t="n"/>
+    </row>
+    <row r="75" ht="47.5" customHeight="1" s="50">
+      <c r="A75" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B75" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C75" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D75" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E74" s="62" t="inlineStr">
-        <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
-        </is>
-      </c>
-      <c r="F74" s="70" t="inlineStr">
-        <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
-        </is>
-      </c>
-      <c r="G74" s="70" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H74" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I74" s="70" t="inlineStr">
+      <c r="E75" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a Virtu Academy</t>
+        </is>
+      </c>
+      <c r="F75" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G75" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H75" s="70" t="n"/>
+      <c r="I75" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J74" s="70" t="n"/>
-    </row>
-    <row r="75" ht="62" customHeight="1" s="50">
-      <c r="A75" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B75" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C75" s="71" t="inlineStr">
+      <c r="J75" s="70" t="n"/>
+    </row>
+    <row r="76" ht="62" customHeight="1" s="50">
+      <c r="A76" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B76" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C76" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D76" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E75" s="62" t="inlineStr">
+      <c r="E76" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F75" s="70" t="inlineStr">
+      <c r="F76" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G75" s="70" t="inlineStr">
+      <c r="G76" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H75" s="70" t="n">
+      <c r="H76" s="70" t="n">
         <v>15</v>
-      </c>
-      <c r="I75" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J75" s="70" t="n"/>
-    </row>
-    <row r="76" ht="47.5" customHeight="1" s="50">
-      <c r="A76" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B76" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C76" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D76" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
-        </is>
-      </c>
-      <c r="E76" s="62" t="inlineStr">
-        <is>
-          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
-        </is>
-      </c>
-      <c r="F76" s="70" t="inlineStr">
-        <is>
-          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
-        </is>
-      </c>
-      <c r="G76" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H76" s="70" t="n">
-        <v>25</v>
       </c>
       <c r="I76" s="70" t="inlineStr">
         <is>
@@ -5170,217 +5202,216 @@
     </row>
     <row r="77" ht="76.5" customHeight="1" s="50">
       <c r="A77" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C77" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D77" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E77" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F77" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G77" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H77" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I77" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J77" s="70" t="n"/>
+    </row>
+    <row r="78" ht="33" customHeight="1" s="50">
+      <c r="A78" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B78" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C78" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D78" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E78" s="62" t="inlineStr">
+        <is>
+          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
+        </is>
+      </c>
+      <c r="F78" s="70" t="inlineStr">
+        <is>
+          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
+        </is>
+      </c>
+      <c r="G78" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H78" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I78" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J78" s="70" t="n"/>
+    </row>
+    <row r="79" ht="149" customHeight="1" s="50">
+      <c r="A79" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B79" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C79" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D79" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E79" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del miércoles 28/10</t>
+        </is>
+      </c>
+      <c r="F79" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 28/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• Holbeach United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
+• Søreide IL | Follow-up 2 | programar para las 04:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G79" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H79" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I79" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J79" s="70" t="n"/>
+    </row>
+    <row r="80" ht="47.5" customHeight="1" s="50">
+      <c r="A80" s="94" t="n">
         <v>46323</v>
       </c>
-      <c r="B77" s="70" t="inlineStr">
+      <c r="B80" s="70" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C77" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D77" s="74" t="inlineStr">
+      <c r="C80" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D80" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E77" s="62" t="inlineStr">
-        <is>
-          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
-        </is>
-      </c>
-      <c r="F77" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G77" s="70" t="inlineStr">
+      <c r="E80" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Søreide IL</t>
+        </is>
+      </c>
+      <c r="F80" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G80" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H77" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I77" s="70" t="inlineStr">
+      <c r="H80" s="70" t="n"/>
+      <c r="I80" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J77" s="70" t="n"/>
-    </row>
-    <row r="78" ht="76.5" customHeight="1" s="50">
-      <c r="A78" s="94" t="n">
+      <c r="J80" s="70" t="n"/>
+    </row>
+    <row r="81" ht="47.5" customHeight="1" s="50">
+      <c r="A81" s="94" t="n">
         <v>46323</v>
       </c>
-      <c r="B78" s="70" t="inlineStr">
+      <c r="B81" s="70" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C78" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D78" s="74" t="inlineStr">
+      <c r="C81" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D81" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E78" s="62" t="inlineStr">
-        <is>
-          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
-        </is>
-      </c>
-      <c r="F78" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G78" s="70" t="inlineStr">
+      <c r="E81" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Holbeach United</t>
+        </is>
+      </c>
+      <c r="F81" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G81" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H78" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I78" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J78" s="70" t="n"/>
-    </row>
-    <row r="79" ht="62" customHeight="1" s="50">
-      <c r="A79" s="94" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B79" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C79" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D79" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E79" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a IA Akranes</t>
-        </is>
-      </c>
-      <c r="F79" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G79" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H79" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I79" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J79" s="70" t="n"/>
-    </row>
-    <row r="80" ht="62" customHeight="1" s="50">
-      <c r="A80" s="94" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B80" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C80" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D80" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E80" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Maidstone United</t>
-        </is>
-      </c>
-      <c r="F80" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G80" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H80" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I80" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J80" s="70" t="n"/>
-    </row>
-    <row r="81" ht="62" customHeight="1" s="50">
-      <c r="A81" s="94" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B81" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C81" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D81" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E81" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Whitehaven AFC</t>
-        </is>
-      </c>
-      <c r="F81" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 11:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G81" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H81" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H81" s="70" t="n"/>
       <c r="I81" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5390,99 +5421,99 @@
     </row>
     <row r="82" ht="62" customHeight="1" s="50">
       <c r="A82" s="94" t="n">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="B82" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C82" s="71" t="inlineStr">
         <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D82" s="74" t="inlineStr">
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D82" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E82" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F82" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G82" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H82" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I82" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J82" s="70" t="n"/>
+    </row>
+    <row r="83" ht="76.5" customHeight="1" s="50">
+      <c r="A83" s="94" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B83" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C83" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D83" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E82" s="62" t="inlineStr">
-        <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
-        </is>
-      </c>
-      <c r="F82" s="70" t="inlineStr">
-        <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
-        </is>
-      </c>
-      <c r="G82" s="70" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H82" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I82" s="70" t="inlineStr">
+      <c r="E83" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F83" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G83" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H83" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I83" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J82" s="70" t="n"/>
-    </row>
-    <row r="83" ht="62" customHeight="1" s="50">
-      <c r="A83" s="94" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B83" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C83" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D83" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E83" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F83" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G83" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H83" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I83" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J83" s="70" t="n"/>
     </row>
-    <row r="84" ht="76.5" customHeight="1" s="50">
+    <row r="84" ht="47.5" customHeight="1" s="50">
       <c r="A84" s="94" t="n">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="B84" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C84" s="71" t="inlineStr">
@@ -5490,19 +5521,19 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D84" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D84" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E84" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
+          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
         </is>
       </c>
       <c r="F84" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
         </is>
       </c>
       <c r="G84" s="70" t="inlineStr">
@@ -5511,7 +5542,7 @@
         </is>
       </c>
       <c r="H84" s="70" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I84" s="70" t="inlineStr">
         <is>
@@ -5522,11 +5553,11 @@
     </row>
     <row r="85" ht="76.5" customHeight="1" s="50">
       <c r="A85" s="94" t="n">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="B85" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C85" s="71" t="inlineStr">
@@ -5541,7 +5572,7 @@
       </c>
       <c r="E85" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
+          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
         </is>
       </c>
       <c r="F85" s="70" t="inlineStr">
@@ -5564,309 +5595,344 @@
       </c>
       <c r="J85" s="70" t="n"/>
     </row>
-    <row r="86" ht="62" customHeight="1" s="50">
+    <row r="86" ht="76.5" customHeight="1" s="50">
       <c r="A86" s="94" t="n">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="B86" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C86" s="71" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D86" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E86" s="62" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
+        </is>
+      </c>
+      <c r="F86" s="70" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G86" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H86" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J86" s="70" t="n"/>
+    </row>
+    <row r="87" ht="178" customHeight="1" s="50">
+      <c r="A87" s="94" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B87" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C87" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D87" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E87" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del jueves 29/10</t>
+        </is>
+      </c>
+      <c r="F87" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 29/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• IA Akranes | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
+• Maidstone United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
+• Whitehaven AFC | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G87" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H87" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J87" s="70" t="n"/>
+    </row>
+    <row r="88" ht="47.5" customHeight="1" s="50">
+      <c r="A88" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B88" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C88" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D88" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E88" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a IA Akranes</t>
+        </is>
+      </c>
+      <c r="F88" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G88" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H88" s="70" t="n"/>
+      <c r="I88" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J88" s="70" t="n"/>
+    </row>
+    <row r="89" ht="47.5" customHeight="1" s="50">
+      <c r="A89" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B89" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C89" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D89" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E89" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Maidstone United</t>
+        </is>
+      </c>
+      <c r="F89" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G89" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H89" s="70" t="n"/>
+      <c r="I89" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J89" s="70" t="n"/>
+    </row>
+    <row r="90" ht="47.5" customHeight="1" s="50">
+      <c r="A90" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B90" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C90" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D90" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E90" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Whitehaven AFC</t>
+        </is>
+      </c>
+      <c r="F90" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G90" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H90" s="70" t="n"/>
+      <c r="I90" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J90" s="70" t="n"/>
+    </row>
+    <row r="91" ht="62" customHeight="1" s="50">
+      <c r="A91" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B91" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C91" s="71" t="inlineStr">
+        <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D86" s="72" t="inlineStr">
+      <c r="D91" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E86" s="62" t="inlineStr">
+      <c r="E91" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F86" s="70" t="inlineStr">
+      <c r="F91" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G86" s="70" t="inlineStr">
+      <c r="G91" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H86" s="70" t="n">
+      <c r="H91" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I86" s="70" t="inlineStr">
+      <c r="I91" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J86" s="70" t="n"/>
-    </row>
-    <row r="87" ht="76.5" customHeight="1" s="50">
-      <c r="A87" s="94" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B87" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C87" s="71" t="inlineStr">
+      <c r="J91" s="70" t="n"/>
+    </row>
+    <row r="92" ht="76.5" customHeight="1" s="50">
+      <c r="A92" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B92" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C92" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D92" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E92" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F92" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G92" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H92" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I92" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J92" s="70" t="n"/>
+    </row>
+    <row r="93" ht="76.5" customHeight="1" s="50">
+      <c r="A93" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B93" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C93" s="71" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D87" s="74" t="inlineStr">
+      <c r="D93" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E87" s="62" t="inlineStr">
-        <is>
-          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
-        </is>
-      </c>
-      <c r="F87" s="70" t="inlineStr">
+      <c r="E93" s="62" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
+        </is>
+      </c>
+      <c r="F93" s="70" t="inlineStr">
         <is>
           <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
-      <c r="G87" s="70" t="inlineStr">
+      <c r="G93" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H87" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I87" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J87" s="70" t="n"/>
-    </row>
-    <row r="88" ht="76.5" customHeight="1" s="50">
-      <c r="A88" s="94" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B88" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C88" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D88" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E88" s="62" t="inlineStr">
-        <is>
-          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
-        </is>
-      </c>
-      <c r="F88" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G88" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H88" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I88" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J88" s="70" t="n"/>
-    </row>
-    <row r="89" ht="76.5" customHeight="1" s="50">
-      <c r="A89" s="94" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B89" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C89" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D89" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E89" s="62" t="inlineStr">
-        <is>
-          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
-        </is>
-      </c>
-      <c r="F89" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G89" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H89" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I89" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J89" s="70" t="n"/>
-    </row>
-    <row r="90" ht="33" customHeight="1" s="50">
-      <c r="A90" s="94" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B90" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C90" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D90" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E90" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F90" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G90" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H90" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I90" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J90" s="70" t="n"/>
-    </row>
-    <row r="91" ht="22" customHeight="1" s="50">
-      <c r="A91" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  02/11 a 08/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="62" customHeight="1" s="50">
-      <c r="A92" s="94" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B92" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C92" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D92" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E92" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F92" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G92" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H92" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I92" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J92" s="70" t="n"/>
-    </row>
-    <row r="93" ht="33" customHeight="1" s="50">
-      <c r="A93" s="94" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B93" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C93" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D93" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E93" s="62" t="inlineStr">
-        <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
-        </is>
-      </c>
-      <c r="F93" s="70" t="inlineStr">
-        <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
-        </is>
-      </c>
-      <c r="G93" s="70" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H93" s="70" t="n">
@@ -5879,13 +5945,13 @@
       </c>
       <c r="J93" s="70" t="n"/>
     </row>
-    <row r="94" ht="33" customHeight="1" s="50">
+    <row r="94" ht="76.5" customHeight="1" s="50">
       <c r="A94" s="94" t="n">
-        <v>46328</v>
+        <v>46324</v>
       </c>
       <c r="B94" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C94" s="71" t="inlineStr">
@@ -5893,28 +5959,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D94" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D94" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E94" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
         </is>
       </c>
       <c r="F94" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G94" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H94" s="70" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I94" s="70" t="inlineStr">
         <is>
@@ -5925,75 +5991,75 @@
     </row>
     <row r="95" ht="62" customHeight="1" s="50">
       <c r="A95" s="94" t="n">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="B95" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C95" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D95" s="74" t="inlineStr">
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D95" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E95" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F95" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G95" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H95" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I95" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J95" s="70" t="n"/>
+    </row>
+    <row r="96" ht="76.5" customHeight="1" s="50">
+      <c r="A96" s="94" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B96" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C96" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D96" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E95" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a FC Porte d'Aquitaine</t>
-        </is>
-      </c>
-      <c r="F95" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 13:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G95" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H95" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I95" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J95" s="70" t="n"/>
-    </row>
-    <row r="96" ht="62" customHeight="1" s="50">
-      <c r="A96" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B96" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C96" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D96" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
       <c r="E96" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Hastings United</t>
+          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
         </is>
       </c>
       <c r="F96" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G96" s="70" t="inlineStr">
@@ -6011,18 +6077,18 @@
       </c>
       <c r="J96" s="70" t="n"/>
     </row>
-    <row r="97" ht="62" customHeight="1" s="50">
+    <row r="97" ht="76.5" customHeight="1" s="50">
       <c r="A97" s="94" t="n">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="B97" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C97" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D97" s="74" t="inlineStr">
@@ -6032,12 +6098,12 @@
       </c>
       <c r="E97" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Home Farm FC</t>
+          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
         </is>
       </c>
       <c r="F97" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G97" s="70" t="inlineStr">
@@ -6055,18 +6121,18 @@
       </c>
       <c r="J97" s="70" t="n"/>
     </row>
-    <row r="98" ht="62" customHeight="1" s="50">
+    <row r="98" ht="76.5" customHeight="1" s="50">
       <c r="A98" s="94" t="n">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="B98" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C98" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D98" s="74" t="inlineStr">
@@ -6076,12 +6142,12 @@
       </c>
       <c r="E98" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Virtu Academy</t>
+          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
         </is>
       </c>
       <c r="F98" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G98" s="70" t="inlineStr">
@@ -6099,170 +6165,133 @@
       </c>
       <c r="J98" s="70" t="n"/>
     </row>
-    <row r="99" ht="62" customHeight="1" s="50">
+    <row r="99" ht="33" customHeight="1" s="50">
       <c r="A99" s="94" t="n">
-        <v>46329</v>
+        <v>46325</v>
       </c>
       <c r="B99" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C99" s="71" t="inlineStr">
         <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D99" s="74" t="inlineStr">
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D99" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E99" s="62" t="inlineStr">
+        <is>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+        </is>
+      </c>
+      <c r="F99" s="70" t="inlineStr">
+        <is>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G99" s="70" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
+      <c r="H99" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I99" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J99" s="70" t="n"/>
+    </row>
+    <row r="100" ht="22" customHeight="1" s="50">
+      <c r="A100" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  02/11 a 08/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="62" customHeight="1" s="50">
+      <c r="A101" s="94" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B101" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C101" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D101" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E101" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F101" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G101" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H101" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I101" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J101" s="70" t="n"/>
+    </row>
+    <row r="102" ht="33" customHeight="1" s="50">
+      <c r="A102" s="94" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B102" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C102" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D102" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E99" s="62" t="inlineStr">
-        <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
-        </is>
-      </c>
-      <c r="F99" s="70" t="inlineStr">
-        <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
-        </is>
-      </c>
-      <c r="G99" s="70" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H99" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I99" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J99" s="70" t="n"/>
-    </row>
-    <row r="100" ht="62" customHeight="1" s="50">
-      <c r="A100" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B100" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C100" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D100" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E100" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F100" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G100" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H100" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I100" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J100" s="70" t="n"/>
-    </row>
-    <row r="101" ht="30" customHeight="1" s="50">
-      <c r="A101" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B101" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C101" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D101" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E101" s="62" t="inlineStr">
-        <is>
-          <t>Enviar la tanda 4 de emails</t>
-        </is>
-      </c>
-      <c r="F101" s="70" t="inlineStr">
-        <is>
-          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
-        </is>
-      </c>
-      <c r="G101" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H101" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I101" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J101" s="70" t="n"/>
-    </row>
-    <row r="102" ht="62" customHeight="1" s="50">
-      <c r="A102" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B102" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C102" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D102" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
       <c r="E102" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Holbeach United</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F102" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G102" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H102" s="70" t="n">
@@ -6275,263 +6304,260 @@
       </c>
       <c r="J102" s="70" t="n"/>
     </row>
-    <row r="103" ht="62" customHeight="1" s="50">
+    <row r="103" ht="33" customHeight="1" s="50">
       <c r="A103" s="94" t="n">
-        <v>46330</v>
+        <v>46328</v>
       </c>
       <c r="B103" s="70" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Lunes</t>
         </is>
       </c>
       <c r="C103" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D103" s="74" t="inlineStr">
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D103" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E103" s="62" t="inlineStr">
+        <is>
+          <t>Revisar leads de becas con acción vencida</t>
+        </is>
+      </c>
+      <c r="F103" s="70" t="inlineStr">
+        <is>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G103" s="70" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
+      <c r="H103" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I103" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J103" s="70" t="n"/>
+    </row>
+    <row r="104" ht="192.5" customHeight="1" s="50">
+      <c r="A104" s="94" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B104" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C104" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D104" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E103" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR cierre a Søreide IL</t>
-        </is>
-      </c>
-      <c r="F103" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 13:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G103" s="70" t="inlineStr">
+      <c r="E104" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del martes 03/11</t>
+        </is>
+      </c>
+      <c r="F104" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 03/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• FC Porte d'Aquitaine | Follow-up 2 | programar para las 03:30 hora Nueva York (09:30 allí)
+• Hastings United | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
+• Home Farm FC | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
+• Virtu Academy | Follow-up 2 | programar para las 04:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G104" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H103" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I103" s="70" t="inlineStr">
+      <c r="H104" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I104" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J103" s="70" t="n"/>
-    </row>
-    <row r="104" ht="62" customHeight="1" s="50">
-      <c r="A104" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B104" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C104" s="71" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D104" s="74" t="inlineStr">
+      <c r="J104" s="70" t="n"/>
+    </row>
+    <row r="105" ht="47.5" customHeight="1" s="50">
+      <c r="A105" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B105" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C105" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D105" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E104" s="62" t="inlineStr">
-        <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
-        </is>
-      </c>
-      <c r="F104" s="70" t="inlineStr">
-        <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
-        </is>
-      </c>
-      <c r="G104" s="70" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H104" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I104" s="70" t="inlineStr">
+      <c r="E105" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F105" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G105" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H105" s="70" t="n"/>
+      <c r="I105" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J104" s="70" t="n"/>
-    </row>
-    <row r="105" ht="62" customHeight="1" s="50">
-      <c r="A105" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B105" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C105" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D105" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E105" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F105" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G105" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H105" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I105" s="70" t="inlineStr">
+      <c r="J105" s="70" t="n"/>
+    </row>
+    <row r="106" ht="47.5" customHeight="1" s="50">
+      <c r="A106" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B106" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C106" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D106" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E106" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a Hastings United</t>
+        </is>
+      </c>
+      <c r="F106" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G106" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H106" s="70" t="n"/>
+      <c r="I106" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J105" s="70" t="n"/>
-    </row>
-    <row r="106" ht="91" customHeight="1" s="50">
-      <c r="A106" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B106" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C106" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D106" s="74" t="inlineStr">
+      <c r="J106" s="70" t="n"/>
+    </row>
+    <row r="107" ht="47.5" customHeight="1" s="50">
+      <c r="A107" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B107" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C107" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D107" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E106" s="62" t="inlineStr">
-        <is>
-          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
-        </is>
-      </c>
-      <c r="F106" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
-        </is>
-      </c>
-      <c r="G106" s="70" t="inlineStr">
+      <c r="E107" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a Home Farm FC</t>
+        </is>
+      </c>
+      <c r="F107" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G107" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H106" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I106" s="70" t="inlineStr">
+      <c r="H107" s="70" t="n"/>
+      <c r="I107" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J106" s="70" t="n"/>
-    </row>
-    <row r="107" ht="76.5" customHeight="1" s="50">
-      <c r="A107" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B107" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C107" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D107" s="74" t="inlineStr">
+      <c r="J107" s="70" t="n"/>
+    </row>
+    <row r="108" ht="47.5" customHeight="1" s="50">
+      <c r="A108" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B108" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C108" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D108" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E107" s="62" t="inlineStr">
-        <is>
-          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
-        </is>
-      </c>
-      <c r="F107" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G107" s="70" t="inlineStr">
+      <c r="E108" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Virtu Academy</t>
+        </is>
+      </c>
+      <c r="F108" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G108" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H107" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I107" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J107" s="70" t="n"/>
-    </row>
-    <row r="108" ht="62" customHeight="1" s="50">
-      <c r="A108" s="94" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B108" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C108" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D108" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E108" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR cierre a IA Akranes</t>
-        </is>
-      </c>
-      <c r="F108" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G108" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H108" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H108" s="70" t="n"/>
       <c r="I108" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6541,300 +6567,299 @@
     </row>
     <row r="109" ht="62" customHeight="1" s="50">
       <c r="A109" s="94" t="n">
-        <v>46331</v>
+        <v>46329</v>
       </c>
       <c r="B109" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Martes</t>
         </is>
       </c>
       <c r="C109" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D109" s="74" t="inlineStr">
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D109" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E109" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F109" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G109" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H109" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I109" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J109" s="70" t="n"/>
+    </row>
+    <row r="110" ht="76.5" customHeight="1" s="50">
+      <c r="A110" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B110" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C110" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D110" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E109" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR cierre a Maidstone United</t>
-        </is>
-      </c>
-      <c r="F109" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G109" s="70" t="inlineStr">
+      <c r="E110" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F110" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G110" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H110" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I110" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J110" s="70" t="n"/>
+    </row>
+    <row r="111" ht="30" customHeight="1" s="50">
+      <c r="A111" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B111" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C111" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D111" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E111" s="62" t="inlineStr">
+        <is>
+          <t>Enviar la tanda 4 de emails</t>
+        </is>
+      </c>
+      <c r="F111" s="70" t="inlineStr">
+        <is>
+          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
+        </is>
+      </c>
+      <c r="G111" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H109" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I109" s="70" t="inlineStr">
+      <c r="H111" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I111" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J109" s="70" t="n"/>
-    </row>
-    <row r="110" ht="62" customHeight="1" s="50">
-      <c r="A110" s="94" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B110" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C110" s="71" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="D110" s="74" t="inlineStr">
+      <c r="J111" s="70" t="n"/>
+    </row>
+    <row r="112" ht="134.5" customHeight="1" s="50">
+      <c r="A112" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B112" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C112" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D112" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E110" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR cierre a Whitehaven AFC</t>
-        </is>
-      </c>
-      <c r="F110" s="70" t="inlineStr">
-        <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
-        </is>
-      </c>
-      <c r="G110" s="70" t="inlineStr">
+      <c r="E112" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del miércoles 04/11</t>
+        </is>
+      </c>
+      <c r="F112" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 04/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• Holbeach United | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
+• Søreide IL | Cierre | programar para las 03:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G112" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H110" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I110" s="70" t="inlineStr">
+      <c r="H112" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I112" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J110" s="70" t="n"/>
-    </row>
-    <row r="111" ht="62" customHeight="1" s="50">
-      <c r="A111" s="94" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B111" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C111" s="71" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D111" s="74" t="inlineStr">
+      <c r="J112" s="70" t="n"/>
+    </row>
+    <row r="113" ht="47.5" customHeight="1" s="50">
+      <c r="A113" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B113" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C113" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D113" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E111" s="62" t="inlineStr">
-        <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
-        </is>
-      </c>
-      <c r="F111" s="70" t="inlineStr">
-        <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
-        </is>
-      </c>
-      <c r="G111" s="70" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H111" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I111" s="70" t="inlineStr">
+      <c r="E113" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a Søreide IL</t>
+        </is>
+      </c>
+      <c r="F113" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G113" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H113" s="70" t="n"/>
+      <c r="I113" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J111" s="70" t="n"/>
-    </row>
-    <row r="112" ht="62" customHeight="1" s="50">
-      <c r="A112" s="94" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B112" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C112" s="71" t="inlineStr">
+      <c r="J113" s="70" t="n"/>
+    </row>
+    <row r="114" ht="47.5" customHeight="1" s="50">
+      <c r="A114" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B114" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C114" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D114" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E114" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a Holbeach United</t>
+        </is>
+      </c>
+      <c r="F114" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G114" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H114" s="70" t="n"/>
+      <c r="I114" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J114" s="70" t="n"/>
+    </row>
+    <row r="115" ht="62" customHeight="1" s="50">
+      <c r="A115" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B115" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C115" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D112" s="72" t="inlineStr">
+      <c r="D115" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E112" s="62" t="inlineStr">
+      <c r="E115" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F112" s="70" t="inlineStr">
+      <c r="F115" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G112" s="70" t="inlineStr">
+      <c r="G115" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H112" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I112" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J112" s="70" t="n"/>
-    </row>
-    <row r="113" ht="62" customHeight="1" s="50">
-      <c r="A113" s="94" t="n">
-        <v>46332</v>
-      </c>
-      <c r="B113" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C113" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D113" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E113" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F113" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G113" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H113" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I113" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J113" s="70" t="n"/>
-    </row>
-    <row r="114" ht="33" customHeight="1" s="50">
-      <c r="A114" s="94" t="n">
-        <v>46332</v>
-      </c>
-      <c r="B114" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C114" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D114" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E114" s="62" t="inlineStr">
-        <is>
-          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
-        </is>
-      </c>
-      <c r="F114" s="70" t="inlineStr">
-        <is>
-          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
-        </is>
-      </c>
-      <c r="G114" s="70" t="inlineStr">
-        <is>
-          <t>Hoy</t>
-        </is>
-      </c>
-      <c r="H114" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I114" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J114" s="70" t="n"/>
-    </row>
-    <row r="115" ht="33" customHeight="1" s="50">
-      <c r="A115" s="94" t="n">
-        <v>46332</v>
-      </c>
-      <c r="B115" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C115" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D115" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E115" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F115" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G115" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H115" s="70" t="n">
@@ -6847,49 +6872,86 @@
       </c>
       <c r="J115" s="70" t="n"/>
     </row>
-    <row r="116" ht="22" customHeight="1" s="50">
-      <c r="A116" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  09/11 a 15/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="62" customHeight="1" s="50">
+    <row r="116" ht="76.5" customHeight="1" s="50">
+      <c r="A116" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B116" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C116" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D116" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E116" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F116" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G116" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H116" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I116" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J116" s="70" t="n"/>
+    </row>
+    <row r="117" ht="91" customHeight="1" s="50">
       <c r="A117" s="94" t="n">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="B117" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C117" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D117" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D117" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E117" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
         </is>
       </c>
       <c r="F117" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
         </is>
       </c>
       <c r="G117" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H117" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I117" s="70" t="inlineStr">
         <is>
@@ -6898,13 +6960,13 @@
       </c>
       <c r="J117" s="70" t="n"/>
     </row>
-    <row r="118" ht="33" customHeight="1" s="50">
+    <row r="118" ht="76.5" customHeight="1" s="50">
       <c r="A118" s="94" t="n">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="B118" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C118" s="71" t="inlineStr">
@@ -6919,17 +6981,17 @@
       </c>
       <c r="E118" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
         </is>
       </c>
       <c r="F118" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G118" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H118" s="70" t="n">
@@ -6942,42 +7004,46 @@
       </c>
       <c r="J118" s="70" t="n"/>
     </row>
-    <row r="119" ht="33" customHeight="1" s="50">
+    <row r="119" ht="149" customHeight="1" s="50">
       <c r="A119" s="94" t="n">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="B119" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Miércoles</t>
         </is>
       </c>
       <c r="C119" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D119" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D119" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E119" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Programar en Apple Mail los envíos del jueves 05/11</t>
         </is>
       </c>
       <c r="F119" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 05/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• IA Akranes | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
+• Maidstone United | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
+• Whitehaven AFC | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
       <c r="G119" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H119" s="70" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I119" s="70" t="inlineStr">
         <is>
@@ -6986,43 +7052,41 @@
       </c>
       <c r="J119" s="70" t="n"/>
     </row>
-    <row r="120" ht="33" customHeight="1" s="50">
+    <row r="120" ht="47.5" customHeight="1" s="50">
       <c r="A120" s="94" t="n">
-        <v>46335</v>
+        <v>46331</v>
       </c>
       <c r="B120" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C120" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D120" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D120" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E120" s="62" t="inlineStr">
         <is>
-          <t>Revisión del mes con Claude (45 min)</t>
+          <t>ENVIAR cierre a IA Akranes</t>
         </is>
       </c>
       <c r="F120" s="70" t="inlineStr">
         <is>
-          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real.</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G120" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H120" s="70" t="n">
-        <v>45</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H120" s="70" t="n"/>
       <c r="I120" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7030,18 +7094,18 @@
       </c>
       <c r="J120" s="70" t="n"/>
     </row>
-    <row r="121" ht="62" customHeight="1" s="50">
+    <row r="121" ht="47.5" customHeight="1" s="50">
       <c r="A121" s="94" t="n">
-        <v>46336</v>
+        <v>46331</v>
       </c>
       <c r="B121" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C121" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D121" s="74" t="inlineStr">
@@ -7051,12 +7115,12 @@
       </c>
       <c r="E121" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a FC Porte d'Aquitaine</t>
+          <t>ENVIAR cierre a Maidstone United</t>
         </is>
       </c>
       <c r="F121" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 13:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G121" s="70" t="inlineStr">
@@ -7064,9 +7128,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H121" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H121" s="70" t="n"/>
       <c r="I121" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7074,18 +7136,18 @@
       </c>
       <c r="J121" s="70" t="n"/>
     </row>
-    <row r="122" ht="62" customHeight="1" s="50">
+    <row r="122" ht="47.5" customHeight="1" s="50">
       <c r="A122" s="94" t="n">
-        <v>46336</v>
+        <v>46331</v>
       </c>
       <c r="B122" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C122" s="71" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D122" s="74" t="inlineStr">
@@ -7095,12 +7157,12 @@
       </c>
       <c r="E122" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Virtu Academy</t>
+          <t>ENVIAR cierre a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F122" s="70" t="inlineStr">
         <is>
-          <t>Copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha de hoy). Revisa en 30 segundos: saludo, nombre del club, firma abajo, sin adjuntos. Envía. Allí son las 12:30, horario laboral. Si es un follow-up, responde dentro del hilo del correo anterior (Enviados &gt; abrir &gt; Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G122" s="70" t="inlineStr">
@@ -7108,9 +7170,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H122" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H122" s="70" t="n"/>
       <c r="I122" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7120,84 +7180,84 @@
     </row>
     <row r="123" ht="62" customHeight="1" s="50">
       <c r="A123" s="94" t="n">
-        <v>46336</v>
+        <v>46331</v>
       </c>
       <c r="B123" s="70" t="inlineStr">
         <is>
-          <t>Martes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C123" s="71" t="inlineStr">
         <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="D123" s="74" t="inlineStr">
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D123" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E123" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F123" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G123" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H123" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I123" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J123" s="70" t="n"/>
+    </row>
+    <row r="124" ht="76.5" customHeight="1" s="50">
+      <c r="A124" s="94" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B124" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C124" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D124" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E123" s="62" t="inlineStr">
-        <is>
-          <t>Comprobar rebotes de los correos que acabas de enviar</t>
-        </is>
-      </c>
-      <c r="F123" s="70" t="inlineStr">
-        <is>
-          <t>Cinco minutos después de enviar, mira Recibidos: los rebotes llegan casi al instante (mensaje del sistema con 'Undeliverable' o 'permanent fatal errors'). Si hay uno, anótalo en la columna Notas y avísame: busco otra dirección del club y te la dejo preparada. Mira también Enviados para confirmar que salieron.</t>
-        </is>
-      </c>
-      <c r="G123" s="70" t="inlineStr">
-        <is>
-          <t>Enviados / Recibidos</t>
-        </is>
-      </c>
-      <c r="H123" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I123" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J123" s="70" t="n"/>
-    </row>
-    <row r="124" ht="62" customHeight="1" s="50">
-      <c r="A124" s="94" t="n">
-        <v>46336</v>
-      </c>
-      <c r="B124" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C124" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D124" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
       <c r="E124" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F124" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G124" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H124" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I124" s="70" t="inlineStr">
         <is>
@@ -7208,11 +7268,11 @@
     </row>
     <row r="125" ht="62" customHeight="1" s="50">
       <c r="A125" s="94" t="n">
-        <v>46337</v>
+        <v>46332</v>
       </c>
       <c r="B125" s="70" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C125" s="71" t="inlineStr">
@@ -7250,18 +7310,18 @@
       </c>
       <c r="J125" s="70" t="n"/>
     </row>
-    <row r="126" ht="62" customHeight="1" s="50">
+    <row r="126" ht="33" customHeight="1" s="50">
       <c r="A126" s="94" t="n">
-        <v>46338</v>
+        <v>46332</v>
       </c>
       <c r="B126" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C126" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D126" s="72" t="inlineStr">
@@ -7271,21 +7331,21 @@
       </c>
       <c r="E126" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
         </is>
       </c>
       <c r="F126" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
         </is>
       </c>
       <c r="G126" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="H126" s="70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I126" s="70" t="inlineStr">
         <is>
@@ -7294,9 +7354,9 @@
       </c>
       <c r="J126" s="70" t="n"/>
     </row>
-    <row r="127" ht="62" customHeight="1" s="50">
+    <row r="127" ht="33" customHeight="1" s="50">
       <c r="A127" s="94" t="n">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="B127" s="70" t="inlineStr">
         <is>
@@ -7305,7 +7365,7 @@
       </c>
       <c r="C127" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D127" s="72" t="inlineStr">
@@ -7315,17 +7375,17 @@
       </c>
       <c r="E127" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F127" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G127" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H127" s="70" t="n">
@@ -7338,61 +7398,595 @@
       </c>
       <c r="J127" s="70" t="n"/>
     </row>
-    <row r="128" ht="33" customHeight="1" s="50">
-      <c r="A128" s="94" t="n">
+    <row r="128" ht="22" customHeight="1" s="50">
+      <c r="A128" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  09/11 a 15/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="62" customHeight="1" s="50">
+      <c r="A129" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B129" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C129" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D129" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E129" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F129" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G129" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H129" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I129" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J129" s="70" t="n"/>
+    </row>
+    <row r="130" ht="33" customHeight="1" s="50">
+      <c r="A130" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B130" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C130" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D130" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E130" s="62" t="inlineStr">
+        <is>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+        </is>
+      </c>
+      <c r="F130" s="70" t="inlineStr">
+        <is>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+        </is>
+      </c>
+      <c r="G130" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
+      <c r="H130" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I130" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J130" s="70" t="n"/>
+    </row>
+    <row r="131" ht="33" customHeight="1" s="50">
+      <c r="A131" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B131" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C131" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D131" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E131" s="62" t="inlineStr">
+        <is>
+          <t>Revisar leads de becas con acción vencida</t>
+        </is>
+      </c>
+      <c r="F131" s="70" t="inlineStr">
+        <is>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G131" s="70" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
+      <c r="H131" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I131" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J131" s="70" t="n"/>
+    </row>
+    <row r="132" ht="33" customHeight="1" s="50">
+      <c r="A132" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B132" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C132" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D132" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E132" s="62" t="inlineStr">
+        <is>
+          <t>Revisión del mes con Claude (45 min)</t>
+        </is>
+      </c>
+      <c r="F132" s="70" t="inlineStr">
+        <is>
+          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real.</t>
+        </is>
+      </c>
+      <c r="G132" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
+      <c r="H132" s="70" t="n">
+        <v>45</v>
+      </c>
+      <c r="I132" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J132" s="70" t="n"/>
+    </row>
+    <row r="133" ht="134.5" customHeight="1" s="50">
+      <c r="A133" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B133" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C133" s="71" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D133" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E133" s="62" t="inlineStr">
+        <is>
+          <t>Programar en Apple Mail los envíos del martes 10/11</t>
+        </is>
+      </c>
+      <c r="F133" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 10/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
+• FC Porte d'Aquitaine | Cierre | programar para las 03:30 hora Nueva York (09:30 allí)
+• Virtu Academy | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
+Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
+        </is>
+      </c>
+      <c r="G133" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H133" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I133" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J133" s="70" t="n"/>
+    </row>
+    <row r="134" ht="47.5" customHeight="1" s="50">
+      <c r="A134" s="94" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B134" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C134" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D134" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E134" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F134" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G134" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H134" s="70" t="n"/>
+      <c r="I134" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J134" s="70" t="n"/>
+    </row>
+    <row r="135" ht="47.5" customHeight="1" s="50">
+      <c r="A135" s="94" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B135" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C135" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D135" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E135" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a Virtu Academy</t>
+        </is>
+      </c>
+      <c r="F135" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G135" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H135" s="70" t="n"/>
+      <c r="I135" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J135" s="70" t="n"/>
+    </row>
+    <row r="136" ht="62" customHeight="1" s="50">
+      <c r="A136" s="94" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B136" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C136" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D136" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E136" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F136" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G136" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H136" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I136" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J136" s="70" t="n"/>
+    </row>
+    <row r="137" ht="76.5" customHeight="1" s="50">
+      <c r="A137" s="94" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B137" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C137" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D137" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E137" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F137" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G137" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H137" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I137" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J137" s="70" t="n"/>
+    </row>
+    <row r="138" ht="62" customHeight="1" s="50">
+      <c r="A138" s="94" t="n">
+        <v>46337</v>
+      </c>
+      <c r="B138" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C138" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D138" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E138" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F138" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G138" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H138" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I138" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J138" s="70" t="n"/>
+    </row>
+    <row r="139" ht="62" customHeight="1" s="50">
+      <c r="A139" s="94" t="n">
+        <v>46338</v>
+      </c>
+      <c r="B139" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C139" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D139" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E139" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F139" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G139" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H139" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I139" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J139" s="70" t="n"/>
+    </row>
+    <row r="140" ht="62" customHeight="1" s="50">
+      <c r="A140" s="94" t="n">
         <v>46339</v>
       </c>
-      <c r="B128" s="70" t="inlineStr">
+      <c r="B140" s="70" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="C128" s="71" t="inlineStr">
+      <c r="C140" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D140" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E140" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F140" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G140" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H140" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I140" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J140" s="70" t="n"/>
+    </row>
+    <row r="141" ht="33" customHeight="1" s="50">
+      <c r="A141" s="94" t="n">
+        <v>46339</v>
+      </c>
+      <c r="B141" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C141" s="71" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D128" s="72" t="inlineStr">
+      <c r="D141" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E128" s="62" t="inlineStr">
+      <c r="E141" s="62" t="inlineStr">
         <is>
           <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
-      <c r="F128" s="70" t="inlineStr">
+      <c r="F141" s="70" t="inlineStr">
         <is>
           <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
-      <c r="G128" s="70" t="inlineStr">
+      <c r="G141" s="70" t="inlineStr">
         <is>
           <t>Segmento A, B, C</t>
         </is>
       </c>
-      <c r="H128" s="70" t="n">
+      <c r="H141" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I128" s="70" t="inlineStr">
+      <c r="I141" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J128" s="70" t="n"/>
+      <c r="J141" s="70" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J128"/>
+  <autoFilter ref="A4:J141"/>
   <mergeCells count="6">
-    <mergeCell ref="A116:J116"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A32:J32"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A91:J91"/>
-    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A128:J128"/>
+    <mergeCell ref="A66:J66"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J128">
+  <conditionalFormatting sqref="A5:J141">
     <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="1">
       <formula>$I5="Hecho"</formula>
     </cfRule>
@@ -7400,13 +7994,13 @@
       <formula>$A5=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I128">
+  <conditionalFormatting sqref="I5:I141">
     <cfRule type="expression" priority="3" dxfId="5">
       <formula>AND(ISNUMBER($A5),$A5&lt;TODAY(),$I5="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140 I141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Hecho,Saltado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7826,7 +8420,7 @@
     <row r="2" ht="46" customHeight="1" s="50">
       <c r="A2" s="65" t="inlineStr">
         <is>
-          <t>Una fila por envío, ordenada por fecha. Filtra la columna Fecha para ver solo el día que toca. Copia Para, Asunto y Texto sin cambiar nada: la firma ya va incluida. Hora = cuándo enviarlo a mano (07:30 de Nueva York; entre paréntesis, la hora allí). Los textos están revisados por Claude: sin guiones largos, sin placeholders, saludo a una sola persona.</t>
+          <t>Una fila por envío, ordenada por fecha. Filtra la columna Fecha para ver solo el día que toca. Copia Para, Asunto y Texto sin cambiar nada: la firma ya va incluida. Hora = a qué hora de Nueva York programar el envío (son las 09:30 en el país del club). Los textos están revisados por Claude: sin guiones largos, sin placeholders, saludo a una sola persona.</t>
         </is>
       </c>
     </row>
@@ -7843,7 +8437,7 @@
       </c>
       <c r="C4" s="66" t="inlineStr">
         <is>
-          <t>Enviar a las (NY)</t>
+          <t>Programar para (NY)</t>
         </is>
       </c>
       <c r="D4" s="66" t="inlineStr">
@@ -7898,7 +8492,7 @@
       </c>
       <c r="C5" s="79" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D5" s="78" t="inlineStr">
@@ -7936,7 +8530,7 @@
       </c>
       <c r="I5" s="78" t="inlineStr">
         <is>
-          <t>Correo nuevo desde joel.martinez@alwaysup.es en Mail. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Envíalo a mano a las 07:30 de Nueva York.</t>
+          <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
       <c r="J5" s="102" t="n">
@@ -7959,7 +8553,7 @@
       </c>
       <c r="C6" s="79" t="inlineStr">
         <is>
-          <t>07:30 (allí 13:30)</t>
+          <t>03:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D6" s="78" t="inlineStr">
@@ -7997,7 +8591,7 @@
       </c>
       <c r="I6" s="78" t="inlineStr">
         <is>
-          <t>Correo nuevo desde joel.martinez@alwaysup.es en Mail. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Envíalo a mano a las 07:30 de Nueva York.</t>
+          <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
       <c r="J6" s="102" t="n">
@@ -8071,7 +8665,7 @@
       </c>
       <c r="C8" s="79" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D8" s="78" t="inlineStr">
@@ -8108,7 +8702,7 @@
       </c>
       <c r="I8" s="78" t="inlineStr">
         <is>
-          <t>Correo nuevo desde joel.martinez@alwaysup.es en Mail. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Envíalo a mano a las 07:30 de Nueva York.</t>
+          <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
       <c r="J8" s="78" t="n"/>
@@ -8129,7 +8723,7 @@
       </c>
       <c r="C9" s="79" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D9" s="78" t="inlineStr">
@@ -8166,7 +8760,7 @@
       </c>
       <c r="I9" s="78" t="inlineStr">
         <is>
-          <t>Correo nuevo desde joel.martinez@alwaysup.es en Mail. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Envíalo a mano a las 07:30 de Nueva York.</t>
+          <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
       <c r="J9" s="78" t="n"/>
@@ -8187,7 +8781,7 @@
       </c>
       <c r="C10" s="79" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D10" s="78" t="inlineStr">
@@ -8224,7 +8818,7 @@
       </c>
       <c r="I10" s="78" t="inlineStr">
         <is>
-          <t>Correo nuevo desde joel.martinez@alwaysup.es en Mail. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Envíalo a mano a las 07:30 de Nueva York.</t>
+          <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
       <c r="J10" s="78" t="n"/>
@@ -8398,7 +8992,7 @@
       </c>
       <c r="C14" s="79" t="inlineStr">
         <is>
-          <t>07:30 (allí 13:30)</t>
+          <t>03:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D14" s="78" t="inlineStr">
@@ -8435,7 +9029,7 @@
       </c>
       <c r="I14" s="78" t="inlineStr">
         <is>
-          <t>Correo nuevo desde joel.martinez@alwaysup.es en Mail. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Envíalo a mano a las 07:30 de Nueva York.</t>
+          <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
       <c r="J14" s="78" t="n"/>
@@ -8456,7 +9050,7 @@
       </c>
       <c r="C15" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D15" s="84" t="inlineStr">
@@ -8494,7 +9088,7 @@
       </c>
       <c r="I15" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J15" s="84" t="n"/>
@@ -8515,7 +9109,7 @@
       </c>
       <c r="C16" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D16" s="84" t="inlineStr">
@@ -8553,7 +9147,7 @@
       </c>
       <c r="I16" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J16" s="84" t="n"/>
@@ -8574,7 +9168,7 @@
       </c>
       <c r="C17" s="79" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D17" s="78" t="inlineStr">
@@ -8611,7 +9205,7 @@
       </c>
       <c r="I17" s="78" t="inlineStr">
         <is>
-          <t>Correo nuevo desde joel.martinez@alwaysup.es en Mail. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Envíalo a mano a las 07:30 de Nueva York.</t>
+          <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
       <c r="J17" s="78" t="n"/>
@@ -8632,7 +9226,7 @@
       </c>
       <c r="C18" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D18" s="84" t="inlineStr">
@@ -8670,7 +9264,7 @@
       </c>
       <c r="I18" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J18" s="84" t="n"/>
@@ -8691,7 +9285,7 @@
       </c>
       <c r="C19" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 13:30)</t>
+          <t>03:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D19" s="84" t="inlineStr">
@@ -8729,7 +9323,7 @@
       </c>
       <c r="I19" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J19" s="84" t="n"/>
@@ -8750,7 +9344,7 @@
       </c>
       <c r="C20" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D20" s="84" t="inlineStr">
@@ -8787,7 +9381,7 @@
       </c>
       <c r="I20" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J20" s="84" t="n"/>
@@ -8808,7 +9402,7 @@
       </c>
       <c r="C21" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D21" s="84" t="inlineStr">
@@ -8845,7 +9439,7 @@
       </c>
       <c r="I21" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J21" s="84" t="n"/>
@@ -8866,7 +9460,7 @@
       </c>
       <c r="C22" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D22" s="84" t="inlineStr">
@@ -8904,7 +9498,7 @@
       </c>
       <c r="I22" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J22" s="84" t="n"/>
@@ -8925,7 +9519,7 @@
       </c>
       <c r="C23" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D23" s="84" t="inlineStr">
@@ -8963,7 +9557,7 @@
       </c>
       <c r="I23" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J23" s="84" t="n"/>
@@ -8984,7 +9578,7 @@
       </c>
       <c r="C24" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D24" s="87" t="inlineStr">
@@ -9020,7 +9614,7 @@
       </c>
       <c r="I24" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J24" s="87" t="n"/>
@@ -9041,7 +9635,7 @@
       </c>
       <c r="C25" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D25" s="87" t="inlineStr">
@@ -9077,7 +9671,7 @@
       </c>
       <c r="I25" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J25" s="87" t="n"/>
@@ -9098,7 +9692,7 @@
       </c>
       <c r="C26" s="85" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D26" s="84" t="inlineStr">
@@ -9135,7 +9729,7 @@
       </c>
       <c r="I26" s="84" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J26" s="84" t="n"/>
@@ -9207,7 +9801,7 @@
       </c>
       <c r="C28" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D28" s="87" t="inlineStr">
@@ -9243,7 +9837,7 @@
       </c>
       <c r="I28" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J28" s="87" t="n"/>
@@ -9315,7 +9909,7 @@
       </c>
       <c r="C30" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D30" s="87" t="inlineStr">
@@ -9351,7 +9945,7 @@
       </c>
       <c r="I30" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J30" s="87" t="n"/>
@@ -9423,7 +10017,7 @@
       </c>
       <c r="C32" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D32" s="87" t="inlineStr">
@@ -9459,7 +10053,7 @@
       </c>
       <c r="I32" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J32" s="87" t="n"/>
@@ -9480,7 +10074,7 @@
       </c>
       <c r="C33" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D33" s="87" t="inlineStr">
@@ -9516,7 +10110,7 @@
       </c>
       <c r="I33" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J33" s="87" t="n"/>
@@ -9588,7 +10182,7 @@
       </c>
       <c r="C35" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 11:30)</t>
+          <t>05:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D35" s="87" t="inlineStr">
@@ -9624,7 +10218,7 @@
       </c>
       <c r="I35" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J35" s="87" t="n"/>
@@ -9798,7 +10392,7 @@
       </c>
       <c r="C39" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 13:30)</t>
+          <t>03:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D39" s="87" t="inlineStr">
@@ -9834,7 +10428,7 @@
       </c>
       <c r="I39" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J39" s="87" t="n"/>
@@ -9855,7 +10449,7 @@
       </c>
       <c r="C40" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D40" s="90" t="inlineStr">
@@ -9892,7 +10486,7 @@
       </c>
       <c r="I40" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J40" s="90" t="n"/>
@@ -9913,7 +10507,7 @@
       </c>
       <c r="C41" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D41" s="90" t="inlineStr">
@@ -9950,7 +10544,7 @@
       </c>
       <c r="I41" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J41" s="90" t="n"/>
@@ -9971,7 +10565,7 @@
       </c>
       <c r="C42" s="88" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D42" s="87" t="inlineStr">
@@ -10007,7 +10601,7 @@
       </c>
       <c r="I42" s="87" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J42" s="87" t="n"/>
@@ -10079,7 +10673,7 @@
       </c>
       <c r="C44" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D44" s="90" t="inlineStr">
@@ -10116,7 +10710,7 @@
       </c>
       <c r="I44" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J44" s="90" t="n"/>
@@ -10137,7 +10731,7 @@
       </c>
       <c r="C45" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 13:30)</t>
+          <t>03:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D45" s="90" t="inlineStr">
@@ -10174,7 +10768,7 @@
       </c>
       <c r="I45" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J45" s="90" t="n"/>
@@ -10246,7 +10840,7 @@
       </c>
       <c r="C47" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D47" s="90" t="inlineStr">
@@ -10283,7 +10877,7 @@
       </c>
       <c r="I47" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J47" s="90" t="n"/>
@@ -10304,7 +10898,7 @@
       </c>
       <c r="C48" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D48" s="90" t="inlineStr">
@@ -10341,7 +10935,7 @@
       </c>
       <c r="I48" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J48" s="90" t="n"/>
@@ -10362,7 +10956,7 @@
       </c>
       <c r="C49" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D49" s="90" t="inlineStr">
@@ -10399,7 +10993,7 @@
       </c>
       <c r="I49" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J49" s="90" t="n"/>
@@ -10420,7 +11014,7 @@
       </c>
       <c r="C50" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 13:30)</t>
+          <t>03:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D50" s="90" t="inlineStr">
@@ -10457,7 +11051,7 @@
       </c>
       <c r="I50" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J50" s="90" t="n"/>
@@ -10478,7 +11072,7 @@
       </c>
       <c r="C51" s="91" t="inlineStr">
         <is>
-          <t>07:30 (allí 12:30)</t>
+          <t>04:30 (09:30 allí)</t>
         </is>
       </c>
       <c r="D51" s="90" t="inlineStr">
@@ -10515,7 +11109,7 @@
       </c>
       <c r="I51" s="90" t="inlineStr">
         <is>
-          <t>Abre el correo original en Enviados &gt; Responder (así queda en el mismo hilo). Pega el texto. Sin adjuntos. Envíalo a las 07:30 de Nueva York. Antes, mira en el CRM que no haya contestado por otro canal.</t>
+          <t>Busca el correo original por destinatario (Outlook buscador &gt; All folders, o Mail &gt; Enviados) y pulsa Responder para que quede en el mismo hilo. Pega el texto. Sin adjuntos. Envíalo más tarde a la hora de la columna C. Antes, mira en el CRM que no haya contestado por otro canal.</t>
         </is>
       </c>
       <c r="J51" s="90" t="n"/>
@@ -12065,7 +12659,7 @@
       <c r="N10" s="10" t="n"/>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
@@ -12541,7 +13135,7 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
+          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Textos para copiar'!$A$4:$K$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Segmento A - Clubes'!$A$5:$P$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Segmento B - America'!$A$5:$O$13</definedName>
@@ -2076,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="50" min="1" max="1"/>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J16" s="70" t="n"/>
     </row>
-    <row r="17" ht="134.5" customHeight="1" s="50">
+    <row r="17" ht="163.5" customHeight="1" s="50">
       <c r="A17" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2679,57 +2679,10 @@
       </c>
       <c r="E17" s="62" t="inlineStr">
         <is>
-          <t>Programar en Apple Mail los envíos del miércoles 14/10</t>
+          <t>Programar en Apple Mail los envíos del jueves 15/10</t>
         </is>
       </c>
       <c r="F17" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 14/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
-• Holbeach United | Email 1 | programar para las 04:30 hora Nueva York (09:30 allí)
-• Søreide IL | Email 1 | programar para las 03:30 hora Nueva York (09:30 allí)
-Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
-        </is>
-      </c>
-      <c r="G17" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H17" s="70" t="n">
-        <v>25</v>
-      </c>
-      <c r="I17" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J17" s="70" t="n"/>
-    </row>
-    <row r="18" ht="163.5" customHeight="1" s="50">
-      <c r="A18" s="94" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B18" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C18" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D18" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E18" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del jueves 15/10</t>
-        </is>
-      </c>
-      <c r="F18" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 15/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Email 1 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -2738,14 +2691,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G17" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H17" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J17" s="70" t="n"/>
+    </row>
+    <row r="18" ht="47.5" customHeight="1" s="50">
+      <c r="A18" s="94" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D18" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E18" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR email 1 a Maidstone United</t>
+        </is>
+      </c>
+      <c r="F18" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G18" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H18" s="70" t="n">
-        <v>30</v>
-      </c>
+      <c r="H18" s="70" t="n"/>
       <c r="I18" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2774,7 +2769,7 @@
       </c>
       <c r="E19" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a Maidstone United</t>
+          <t>ENVIAR email 1 a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F19" s="70" t="inlineStr">
@@ -2806,7 +2801,7 @@
       </c>
       <c r="C20" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D20" s="74" t="inlineStr">
@@ -2816,12 +2811,12 @@
       </c>
       <c r="E20" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a Whitehaven AFC</t>
+          <t>ENVIAR email 1 a IA Akranes</t>
         </is>
       </c>
       <c r="F20" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G20" s="70" t="inlineStr">
@@ -2837,7 +2832,7 @@
       </c>
       <c r="J20" s="70" t="n"/>
     </row>
-    <row r="21" ht="47.5" customHeight="1" s="50">
+    <row r="21" ht="62" customHeight="1" s="50">
       <c r="A21" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2848,30 +2843,32 @@
       </c>
       <c r="C21" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D21" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D21" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E21" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a IA Akranes</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F21" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G21" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H21" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H21" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I21" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -2879,7 +2876,7 @@
       </c>
       <c r="J21" s="70" t="n"/>
     </row>
-    <row r="22" ht="62" customHeight="1" s="50">
+    <row r="22" ht="76.5" customHeight="1" s="50">
       <c r="A22" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2893,28 +2890,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D22" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D22" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E22" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F22" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G22" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H22" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I22" s="70" t="inlineStr">
         <is>
@@ -2923,7 +2920,7 @@
       </c>
       <c r="J22" s="70" t="n"/>
     </row>
-    <row r="23" ht="76.5" customHeight="1" s="50">
+    <row r="23" ht="33" customHeight="1" s="50">
       <c r="A23" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2934,31 +2931,31 @@
       </c>
       <c r="C23" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D23" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D23" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E23" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Darme tu feedback sobre la ficha de Becas EEUU</t>
         </is>
       </c>
       <c r="F23" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Ábrela (02-sales/assets/Always-Up-Becas-EEUU.pdf) y dime qué cambiarías. Antes de cambiar nada te digo si me parece buena idea.</t>
         </is>
       </c>
       <c r="G23" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>02-sales/assets</t>
         </is>
       </c>
       <c r="H23" s="70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I23" s="70" t="inlineStr">
         <is>
@@ -2981,24 +2978,24 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D24" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D24" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E24" s="62" t="inlineStr">
         <is>
-          <t>Darme tu feedback sobre la ficha de Becas EEUU</t>
+          <t>Pedir al club irlandés testimonio y presentaciones</t>
         </is>
       </c>
       <c r="F24" s="70" t="inlineStr">
         <is>
-          <t>Ábrela (02-sales/assets/Always-Up-Becas-EEUU.pdf) y dime qué cambiarías. Antes de cambiar nada te digo si me parece buena idea.</t>
+          <t>Es lo que más puede acelerar ventas: un club que ya compró habla mejor de nosotros que cualquier email. Texto en 'Respuestas tipo'. Puedes mandarlo tú o Enrique.</t>
         </is>
       </c>
       <c r="G24" s="70" t="inlineStr">
         <is>
-          <t>02-sales/assets</t>
+          <t>Textos para copiar (Respuestas tipo)</t>
         </is>
       </c>
       <c r="H24" s="70" t="n">
@@ -3011,7 +3008,7 @@
       </c>
       <c r="J24" s="70" t="n"/>
     </row>
-    <row r="25" ht="33" customHeight="1" s="50">
+    <row r="25" ht="76.5" customHeight="1" s="50">
       <c r="A25" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3025,28 +3022,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D25" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D25" s="72" t="inlineStr">
+        <is>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="E25" s="62" t="inlineStr">
         <is>
-          <t>Pedir al club irlandés testimonio y presentaciones</t>
+          <t>Ajustar Calendly por mercado (franjas distintas para clubes y familias)</t>
         </is>
       </c>
       <c r="F25" s="70" t="inlineStr">
         <is>
-          <t>Es lo que más puede acelerar ventas: un club que ya compró habla mejor de nosotros que cualquier email. Texto en 'Respuestas tipo'. Puedes mandarlo tú o Enrique.</t>
+          <t>Mira la tabla de franjas en LEEME. Resumen: para clubes de Europa solo sirven Martes 13:00 a 15:00 y Miércoles 11:00 a 12:30 (hora NY). Para familias de América sirven Lunes y Jueves por la tarde. Pasos: crea el evento 'Always Up Intro Call' (20 min, Zoom) con la agenda Europa, y deja 'USA Scholarship Assessment' con la agenda Américas. Luego pásame el enlace de cada uno.</t>
         </is>
       </c>
       <c r="G25" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (Respuestas tipo)</t>
+          <t>Calendly</t>
         </is>
       </c>
       <c r="H25" s="70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I25" s="70" t="inlineStr">
         <is>
@@ -3055,7 +3052,7 @@
       </c>
       <c r="J25" s="70" t="n"/>
     </row>
-    <row r="26" ht="76.5" customHeight="1" s="50">
+    <row r="26" ht="62" customHeight="1" s="50">
       <c r="A26" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3076,21 +3073,17 @@
       </c>
       <c r="E26" s="62" t="inlineStr">
         <is>
-          <t>Ajustar Calendly por mercado (franjas distintas para clubes y familias)</t>
+          <t>Calentar el dominio: 2 o 3 correos reales más a gente de confianza (ya hiciste 3)</t>
         </is>
       </c>
       <c r="F26" s="70" t="inlineStr">
         <is>
-          <t>Mira la tabla de franjas en LEEME. Resumen: para clubes de Europa solo sirven Martes 13:00 a 15:00 y Miércoles 11:00 a 12:30 (hora NY). Para familias de América sirven Lunes y Jueves por la tarde. Pasos: crea el evento 'Always Up Intro Call' (20 min, Zoom) con la agenda Europa, y deja 'USA Scholarship Assessment' con la agenda Américas. Luego pásame el enlace de cada uno.</t>
-        </is>
-      </c>
-      <c r="G26" s="70" t="inlineStr">
-        <is>
-          <t>Calendly</t>
-        </is>
-      </c>
+          <t>Escribe desde alwaysup.es a 2 o 3 personas más (familia, amigos, conocidos con Gmail, Outlook o iCloud) un correo normal con una pregunta, y pídeles que respondan. Si caen en spam, que lo marquen como 'No es spam'. Es la forma más rápida de mejorar la reputación de un dominio nuevo.</t>
+        </is>
+      </c>
+      <c r="G26" s="70" t="inlineStr"/>
       <c r="H26" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I26" s="70" t="inlineStr">
         <is>
@@ -3099,7 +3092,7 @@
       </c>
       <c r="J26" s="70" t="n"/>
     </row>
-    <row r="27" ht="62" customHeight="1" s="50">
+    <row r="27" ht="76.5" customHeight="1" s="50">
       <c r="A27" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3113,77 +3106,81 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
-        <is>
-          <t>Transversal</t>
+      <c r="D27" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E27" s="62" t="inlineStr">
         <is>
-          <t>Calentar el dominio: 2 o 3 correos reales más a gente de confianza (ya hiciste 3)</t>
+          <t>LinkedIn: conectar con Georgia Townsend (Hastings United)</t>
         </is>
       </c>
       <c r="F27" s="70" t="inlineStr">
         <is>
-          <t>Escribe desde alwaysup.es a 2 o 3 personas más (familia, amigos, conocidos con Gmail, Outlook o iCloud) un correo normal con una pregunta, y pídeles que respondan. Si caen en spam, que lo marquen como 'No es spam'. Es la forma más rápida de mejorar la reputación de un dominio nuevo.</t>
-        </is>
-      </c>
-      <c r="G27" s="70" t="inlineStr"/>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Georgia, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+        </is>
+      </c>
+      <c r="G27" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
       <c r="H27" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J27" s="70" t="n"/>
+    </row>
+    <row r="28" ht="62" customHeight="1" s="50">
+      <c r="A28" s="94" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B28" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C28" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D28" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E28" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F28" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G28" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H28" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I27" s="70" t="inlineStr">
+      <c r="I28" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J27" s="70" t="n"/>
-    </row>
-    <row r="28" ht="76.5" customHeight="1" s="50">
-      <c r="A28" s="94" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B28" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C28" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D28" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E28" s="62" t="inlineStr">
-        <is>
-          <t>LinkedIn: conectar con Georgia Townsend (Hastings United)</t>
-        </is>
-      </c>
-      <c r="F28" s="70" t="inlineStr">
-        <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Georgia, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
-        </is>
-      </c>
-      <c r="G28" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H28" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I28" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J28" s="70" t="n"/>
     </row>
-    <row r="29" ht="62" customHeight="1" s="50">
+    <row r="29" ht="33" customHeight="1" s="50">
       <c r="A29" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3194,7 +3191,7 @@
       </c>
       <c r="C29" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D29" s="72" t="inlineStr">
@@ -3204,21 +3201,21 @@
       </c>
       <c r="E29" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Revisión semanal 1: qué ha pasado esta semana</t>
         </is>
       </c>
       <c r="F29" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Mira la hoja Hoy y anota respuestas, rebotes y llamadas. Pásame un resumen de tres líneas: yo ajusto el plan.</t>
         </is>
       </c>
       <c r="G29" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="H29" s="70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I29" s="70" t="inlineStr">
         <is>
@@ -3227,7 +3224,7 @@
       </c>
       <c r="J29" s="70" t="n"/>
     </row>
-    <row r="30" ht="33" customHeight="1" s="50">
+    <row r="30" ht="76.5" customHeight="1" s="50">
       <c r="A30" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3241,28 +3238,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D30" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D30" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E30" s="62" t="inlineStr">
         <is>
-          <t>Revisión semanal 1: qué ha pasado esta semana</t>
+          <t>LinkedIn: conectar con Callum Lawe (Holbeach United)</t>
         </is>
       </c>
       <c r="F30" s="70" t="inlineStr">
         <is>
-          <t>Mira la hoja Hoy y anota respuestas, rebotes y llamadas. Pásame un resumen de tres líneas: yo ajusto el plan.</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Callum, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G30" s="70" t="inlineStr">
         <is>
-          <t>Hoy</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H30" s="70" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I30" s="70" t="inlineStr">
         <is>
@@ -3292,12 +3289,12 @@
       </c>
       <c r="E31" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Callum Lawe (Holbeach United)</t>
+          <t>LinkedIn: conectar con Marius Engen (Søreide IL)</t>
         </is>
       </c>
       <c r="F31" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Callum, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Marius, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G31" s="70" t="inlineStr">
@@ -3315,7 +3312,7 @@
       </c>
       <c r="J31" s="70" t="n"/>
     </row>
-    <row r="32" ht="76.5" customHeight="1" s="50">
+    <row r="32" ht="33" customHeight="1" s="50">
       <c r="A32" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3329,28 +3326,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D32" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D32" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E32" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Marius Engen (Søreide IL)</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F32" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Marius, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G32" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H32" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I32" s="70" t="inlineStr">
         <is>
@@ -3359,13 +3356,13 @@
       </c>
       <c r="J32" s="70" t="n"/>
     </row>
-    <row r="33" ht="33" customHeight="1" s="50">
+    <row r="33" ht="47.5" customHeight="1" s="50">
       <c r="A33" s="94" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B33" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="C33" s="71" t="inlineStr">
@@ -3373,88 +3370,88 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D33" s="72" t="inlineStr">
+      <c r="D33" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E33" s="62" t="inlineStr">
+        <is>
+          <t>Sesión de redes sociales y marca personal con Claude (30 a 60 min)</t>
+        </is>
+      </c>
+      <c r="F33" s="70" t="inlineStr">
+        <is>
+          <t>Objetivo: 10.000 seguidores antes de fin de 2026. Salir con un plan de contenido de 4 semanas. Hasta tener este plan no se publica nada. Sin fotos de menores identificables.</t>
+        </is>
+      </c>
+      <c r="G33" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
+      <c r="H33" s="70" t="n">
+        <v>60</v>
+      </c>
+      <c r="I33" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J33" s="70" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1" s="50">
+      <c r="A34" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  19/10 a 25/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="62" customHeight="1" s="50">
+      <c r="A35" s="94" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B35" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C35" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D35" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E33" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F33" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G33" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H33" s="70" t="n">
+      <c r="E35" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F35" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G35" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H35" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I33" s="70" t="inlineStr">
+      <c r="I35" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J33" s="70" t="n"/>
-    </row>
-    <row r="34" ht="47.5" customHeight="1" s="50">
-      <c r="A34" s="94" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B34" s="70" t="inlineStr">
-        <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="C34" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D34" s="75" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="E34" s="62" t="inlineStr">
-        <is>
-          <t>Sesión de redes sociales y marca personal con Claude (30 a 60 min)</t>
-        </is>
-      </c>
-      <c r="F34" s="70" t="inlineStr">
-        <is>
-          <t>Objetivo: 10.000 seguidores antes de fin de 2026. Salir con un plan de contenido de 4 semanas. Hasta tener este plan no se publica nada. Sin fotos de menores identificables.</t>
-        </is>
-      </c>
-      <c r="G34" s="70" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H34" s="70" t="n">
-        <v>60</v>
-      </c>
-      <c r="I34" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J34" s="70" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1" s="50">
-      <c r="A35" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  19/10 a 25/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="62" customHeight="1" s="50">
+      <c r="J35" s="70" t="n"/>
+    </row>
+    <row r="36" ht="33" customHeight="1" s="50">
       <c r="A36" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3465,31 +3462,31 @@
       </c>
       <c r="C36" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D36" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D36" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E36" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F36" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G36" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H36" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I36" s="70" t="inlineStr">
         <is>
@@ -3512,28 +3509,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D37" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D37" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E37" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F37" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G37" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H37" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I37" s="70" t="inlineStr">
         <is>
@@ -3542,7 +3539,7 @@
       </c>
       <c r="J37" s="70" t="n"/>
     </row>
-    <row r="38" ht="33" customHeight="1" s="50">
+    <row r="38" ht="76.5" customHeight="1" s="50">
       <c r="A38" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3556,28 +3553,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D38" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D38" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E38" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>LinkedIn: conectar con Luke Johnston (Whitehaven AFC)</t>
         </is>
       </c>
       <c r="F38" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Luke, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G38" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H38" s="70" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I38" s="70" t="inlineStr">
         <is>
@@ -3586,7 +3583,7 @@
       </c>
       <c r="J38" s="70" t="n"/>
     </row>
-    <row r="39" ht="76.5" customHeight="1" s="50">
+    <row r="39" ht="33" customHeight="1" s="50">
       <c r="A39" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3607,21 +3604,17 @@
       </c>
       <c r="E39" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Luke Johnston (Whitehaven AFC)</t>
+          <t>LinkedIn: 10 minutos de actividad</t>
         </is>
       </c>
       <c r="F39" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Luke, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
-        </is>
-      </c>
-      <c r="G39" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
+          <t>Acepta conexiones, comenta tres publicaciones de entrenadores o clubes con algo de valor (no publicidad). Eso hace que te vean antes de que llegue el email.</t>
+        </is>
+      </c>
+      <c r="G39" s="70" t="inlineStr"/>
       <c r="H39" s="70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I39" s="70" t="inlineStr">
         <is>
@@ -3630,7 +3623,7 @@
       </c>
       <c r="J39" s="70" t="n"/>
     </row>
-    <row r="40" ht="33" customHeight="1" s="50">
+    <row r="40" ht="192.5" customHeight="1" s="50">
       <c r="A40" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3641,7 +3634,7 @@
       </c>
       <c r="C40" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D40" s="74" t="inlineStr">
@@ -3651,50 +3644,10 @@
       </c>
       <c r="E40" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: 10 minutos de actividad</t>
+          <t>Programar en Apple Mail los envíos del martes 20/10</t>
         </is>
       </c>
       <c r="F40" s="70" t="inlineStr">
-        <is>
-          <t>Acepta conexiones, comenta tres publicaciones de entrenadores o clubes con algo de valor (no publicidad). Eso hace que te vean antes de que llegue el email.</t>
-        </is>
-      </c>
-      <c r="G40" s="70" t="inlineStr"/>
-      <c r="H40" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I40" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J40" s="70" t="n"/>
-    </row>
-    <row r="41" ht="192.5" customHeight="1" s="50">
-      <c r="A41" s="94" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B41" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C41" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D41" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E41" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del martes 20/10</t>
-        </is>
-      </c>
-      <c r="F41" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 20/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Email 1 | programar para las 03:30 hora Nueva York (09:30 allí)
@@ -3704,14 +3657,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G40" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H40" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I40" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J40" s="70" t="n"/>
+    </row>
+    <row r="41" ht="47.5" customHeight="1" s="50">
+      <c r="A41" s="94" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B41" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C41" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D41" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E41" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR email 1 a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F41" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G41" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H41" s="70" t="n">
-        <v>35</v>
-      </c>
+      <c r="H41" s="70" t="n"/>
       <c r="I41" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3730,7 +3725,7 @@
       </c>
       <c r="C42" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D42" s="74" t="inlineStr">
@@ -3740,12 +3735,12 @@
       </c>
       <c r="E42" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a FC Porte d'Aquitaine</t>
+          <t>ENVIAR follow-up 1 a Hastings United</t>
         </is>
       </c>
       <c r="F42" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G42" s="70" t="inlineStr">
@@ -3782,7 +3777,7 @@
       </c>
       <c r="E43" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Hastings United</t>
+          <t>ENVIAR follow-up 1 a Home Farm FC</t>
         </is>
       </c>
       <c r="F43" s="70" t="inlineStr">
@@ -3824,7 +3819,7 @@
       </c>
       <c r="E44" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Home Farm FC</t>
+          <t>ENVIAR email 1 a Virtu Academy</t>
         </is>
       </c>
       <c r="F44" s="70" t="inlineStr">
@@ -3845,7 +3840,7 @@
       </c>
       <c r="J44" s="70" t="n"/>
     </row>
-    <row r="45" ht="47.5" customHeight="1" s="50">
+    <row r="45" ht="62" customHeight="1" s="50">
       <c r="A45" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3856,30 +3851,32 @@
       </c>
       <c r="C45" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D45" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D45" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E45" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a Virtu Academy</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F45" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G45" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H45" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H45" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I45" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3887,7 +3884,7 @@
       </c>
       <c r="J45" s="70" t="n"/>
     </row>
-    <row r="46" ht="62" customHeight="1" s="50">
+    <row r="46" ht="76.5" customHeight="1" s="50">
       <c r="A46" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3901,28 +3898,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D46" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D46" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E46" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F46" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G46" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H46" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I46" s="70" t="inlineStr">
         <is>
@@ -3931,7 +3928,7 @@
       </c>
       <c r="J46" s="70" t="n"/>
     </row>
-    <row r="47" ht="76.5" customHeight="1" s="50">
+    <row r="47" ht="47.5" customHeight="1" s="50">
       <c r="A47" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3942,31 +3939,31 @@
       </c>
       <c r="C47" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D47" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D47" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E47" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Omar: último mensaje corto si sigue sin contestar</t>
         </is>
       </c>
       <c r="F47" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>«Hola Omar, no quiero atosigarte. Si en este momento no es prioridad, no pasa nada, lo dejamos aquí y lo retomamos cuando te venga bien. Si quieres seguir, mándame lo que tengas del vídeo y empezamos.» Después pásalo a 'Frío' en el CRM.</t>
         </is>
       </c>
       <c r="G47" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H47" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I47" s="70" t="inlineStr">
         <is>
@@ -3975,7 +3972,7 @@
       </c>
       <c r="J47" s="70" t="n"/>
     </row>
-    <row r="48" ht="47.5" customHeight="1" s="50">
+    <row r="48" ht="149" customHeight="1" s="50">
       <c r="A48" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3986,64 +3983,20 @@
       </c>
       <c r="C48" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D48" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D48" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E48" s="62" t="inlineStr">
         <is>
-          <t>Omar: último mensaje corto si sigue sin contestar</t>
+          <t>Programar en Apple Mail los envíos del miércoles 21/10</t>
         </is>
       </c>
       <c r="F48" s="70" t="inlineStr">
-        <is>
-          <t>«Hola Omar, no quiero atosigarte. Si en este momento no es prioridad, no pasa nada, lo dejamos aquí y lo retomamos cuando te venga bien. Si quieres seguir, mándame lo que tengas del vídeo y empezamos.» Después pásalo a 'Frío' en el CRM.</t>
-        </is>
-      </c>
-      <c r="G48" s="70" t="inlineStr">
-        <is>
-          <t>Segmento C - Becas</t>
-        </is>
-      </c>
-      <c r="H48" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I48" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J48" s="70" t="n"/>
-    </row>
-    <row r="49" ht="149" customHeight="1" s="50">
-      <c r="A49" s="94" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B49" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C49" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D49" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E49" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del miércoles 21/10</t>
-        </is>
-      </c>
-      <c r="F49" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 21/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • Holbeach United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -4051,14 +4004,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G48" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H48" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I48" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J48" s="70" t="n"/>
+    </row>
+    <row r="49" ht="47.5" customHeight="1" s="50">
+      <c r="A49" s="94" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B49" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C49" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D49" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E49" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a Søreide IL</t>
+        </is>
+      </c>
+      <c r="F49" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G49" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H49" s="70" t="n">
-        <v>25</v>
-      </c>
+      <c r="H49" s="70" t="n"/>
       <c r="I49" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4077,7 +4072,7 @@
       </c>
       <c r="C50" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D50" s="74" t="inlineStr">
@@ -4087,12 +4082,12 @@
       </c>
       <c r="E50" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Søreide IL</t>
+          <t>ENVIAR follow-up 1 a Holbeach United</t>
         </is>
       </c>
       <c r="F50" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G50" s="70" t="inlineStr">
@@ -4108,7 +4103,7 @@
       </c>
       <c r="J50" s="70" t="n"/>
     </row>
-    <row r="51" ht="47.5" customHeight="1" s="50">
+    <row r="51" ht="62" customHeight="1" s="50">
       <c r="A51" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4119,30 +4114,32 @@
       </c>
       <c r="C51" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D51" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D51" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E51" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Holbeach United</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F51" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G51" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H51" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H51" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I51" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4150,7 +4147,7 @@
       </c>
       <c r="J51" s="70" t="n"/>
     </row>
-    <row r="52" ht="62" customHeight="1" s="50">
+    <row r="52" ht="76.5" customHeight="1" s="50">
       <c r="A52" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4164,28 +4161,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D52" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D52" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E52" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F52" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G52" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H52" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I52" s="70" t="inlineStr">
         <is>
@@ -4194,7 +4191,7 @@
       </c>
       <c r="J52" s="70" t="n"/>
     </row>
-    <row r="53" ht="76.5" customHeight="1" s="50">
+    <row r="53" ht="178" customHeight="1" s="50">
       <c r="A53" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4205,7 +4202,7 @@
       </c>
       <c r="C53" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D53" s="74" t="inlineStr">
@@ -4215,54 +4212,10 @@
       </c>
       <c r="E53" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Programar en Apple Mail los envíos del jueves 22/10</t>
         </is>
       </c>
       <c r="F53" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G53" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H53" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I53" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J53" s="70" t="n"/>
-    </row>
-    <row r="54" ht="178" customHeight="1" s="50">
-      <c r="A54" s="94" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B54" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C54" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D54" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E54" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del jueves 22/10</t>
-        </is>
-      </c>
-      <c r="F54" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 22/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -4271,14 +4224,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G53" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H53" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J53" s="70" t="n"/>
+    </row>
+    <row r="54" ht="47.5" customHeight="1" s="50">
+      <c r="A54" s="94" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B54" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C54" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D54" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E54" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a Maidstone United</t>
+        </is>
+      </c>
+      <c r="F54" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G54" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H54" s="70" t="n">
-        <v>30</v>
-      </c>
+      <c r="H54" s="70" t="n"/>
       <c r="I54" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4307,7 +4302,7 @@
       </c>
       <c r="E55" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Maidstone United</t>
+          <t>ENVIAR follow-up 1 a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F55" s="70" t="inlineStr">
@@ -4339,7 +4334,7 @@
       </c>
       <c r="C56" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D56" s="74" t="inlineStr">
@@ -4349,12 +4344,12 @@
       </c>
       <c r="E56" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Whitehaven AFC</t>
+          <t>ENVIAR follow-up 1 a IA Akranes</t>
         </is>
       </c>
       <c r="F56" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G56" s="70" t="inlineStr">
@@ -4370,7 +4365,7 @@
       </c>
       <c r="J56" s="70" t="n"/>
     </row>
-    <row r="57" ht="47.5" customHeight="1" s="50">
+    <row r="57" ht="62" customHeight="1" s="50">
       <c r="A57" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4381,30 +4376,32 @@
       </c>
       <c r="C57" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D57" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D57" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E57" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a IA Akranes</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F57" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G57" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H57" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H57" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I57" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4412,7 +4409,7 @@
       </c>
       <c r="J57" s="70" t="n"/>
     </row>
-    <row r="58" ht="62" customHeight="1" s="50">
+    <row r="58" ht="76.5" customHeight="1" s="50">
       <c r="A58" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4426,28 +4423,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D58" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D58" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E58" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F58" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G58" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H58" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I58" s="70" t="inlineStr">
         <is>
@@ -4456,7 +4453,7 @@
       </c>
       <c r="J58" s="70" t="n"/>
     </row>
-    <row r="59" ht="76.5" customHeight="1" s="50">
+    <row r="59" ht="47.5" customHeight="1" s="50">
       <c r="A59" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4467,71 +4464,71 @@
       </c>
       <c r="C59" s="71" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D59" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E59" s="62" t="inlineStr">
+        <is>
+          <t>Preguntar a Atlético y Real Sociedad por las fechas reales de Semana Santa y verano 2027</t>
+        </is>
+      </c>
+      <c r="F59" s="70" t="inlineStr">
+        <is>
+          <t>Necesitamos saber qué semanas hay disponibles y hasta cuándo se pueden reservar. Con eso tendremos urgencia real y honesta para los follow-ups (hoy no la tenemos). Puede hacerlo Enrique.</t>
+        </is>
+      </c>
+      <c r="G59" s="70" t="inlineStr"/>
+      <c r="H59" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I59" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J59" s="70" t="n"/>
+    </row>
+    <row r="60" ht="62" customHeight="1" s="50">
+      <c r="A60" s="94" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B60" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C60" s="71" t="inlineStr">
+        <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D59" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E59" s="62" t="inlineStr">
-        <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
-        </is>
-      </c>
-      <c r="F59" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G59" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H59" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I59" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J59" s="70" t="n"/>
-    </row>
-    <row r="60" ht="47.5" customHeight="1" s="50">
-      <c r="A60" s="94" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B60" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C60" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D60" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D60" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E60" s="62" t="inlineStr">
         <is>
-          <t>Preguntar a Atlético y Real Sociedad por las fechas reales de Semana Santa y verano 2027</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F60" s="70" t="inlineStr">
         <is>
-          <t>Necesitamos saber qué semanas hay disponibles y hasta cuándo se pueden reservar. Con eso tendremos urgencia real y honesta para los follow-ups (hoy no la tenemos). Puede hacerlo Enrique.</t>
-        </is>
-      </c>
-      <c r="G60" s="70" t="inlineStr"/>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G60" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
       <c r="H60" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I60" s="70" t="inlineStr">
         <is>
@@ -4551,7 +4548,7 @@
       </c>
       <c r="C61" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D61" s="72" t="inlineStr">
@@ -4561,21 +4558,21 @@
       </c>
       <c r="E61" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
         </is>
       </c>
       <c r="F61" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
         </is>
       </c>
       <c r="G61" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>plan-outreach-30-dias.md sección 7</t>
         </is>
       </c>
       <c r="H61" s="70" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I61" s="70" t="inlineStr">
         <is>
@@ -4584,7 +4581,7 @@
       </c>
       <c r="J61" s="70" t="n"/>
     </row>
-    <row r="62" ht="62" customHeight="1" s="50">
+    <row r="62" ht="33" customHeight="1" s="50">
       <c r="A62" s="94" t="n">
         <v>46318</v>
       </c>
@@ -4598,28 +4595,24 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D62" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D62" s="76" t="inlineStr">
+        <is>
+          <t>International Program</t>
         </is>
       </c>
       <c r="E62" s="62" t="inlineStr">
         <is>
-          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
+          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
         </is>
       </c>
       <c r="F62" s="70" t="inlineStr">
         <is>
-          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
-        </is>
-      </c>
-      <c r="G62" s="70" t="inlineStr">
-        <is>
-          <t>plan-outreach-30-dias.md sección 7</t>
-        </is>
-      </c>
+          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
+        </is>
+      </c>
+      <c r="G62" s="70" t="inlineStr"/>
       <c r="H62" s="70" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="I62" s="70" t="inlineStr">
         <is>
@@ -4642,24 +4635,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D63" s="76" t="inlineStr">
-        <is>
-          <t>International Program</t>
+      <c r="D63" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E63" s="62" t="inlineStr">
         <is>
-          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F63" s="70" t="inlineStr">
         <is>
-          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
-        </is>
-      </c>
-      <c r="G63" s="70" t="inlineStr"/>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G63" s="70" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
       <c r="H63" s="70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I63" s="70" t="inlineStr">
         <is>
@@ -4670,11 +4667,11 @@
     </row>
     <row r="64" ht="33" customHeight="1" s="50">
       <c r="A64" s="94" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B64" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="C64" s="71" t="inlineStr">
@@ -4682,88 +4679,88 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D64" s="72" t="inlineStr">
+      <c r="D64" s="76" t="inlineStr">
+        <is>
+          <t>GEE / Fichas</t>
+        </is>
+      </c>
+      <c r="E64" s="62" t="inlineStr">
+        <is>
+          <t>Revisar las nuevas fichas (GEE, Campus Internacional, International Program)</t>
+        </is>
+      </c>
+      <c r="F64" s="70" t="inlineStr">
+        <is>
+          <t>Las preparo yo tras tu feedback de la ficha de Becas. Tú revisas y me dices qué cambiar.</t>
+        </is>
+      </c>
+      <c r="G64" s="70" t="inlineStr">
+        <is>
+          <t>02-sales/assets</t>
+        </is>
+      </c>
+      <c r="H64" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J64" s="70" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1" s="50">
+      <c r="A65" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  26/10 a 01/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="62" customHeight="1" s="50">
+      <c r="A66" s="94" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B66" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C66" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D66" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E64" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F64" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G64" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H64" s="70" t="n">
+      <c r="E66" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F66" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G66" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H66" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I64" s="70" t="inlineStr">
+      <c r="I66" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J64" s="70" t="n"/>
-    </row>
-    <row r="65" ht="33" customHeight="1" s="50">
-      <c r="A65" s="94" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B65" s="70" t="inlineStr">
-        <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="C65" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D65" s="76" t="inlineStr">
-        <is>
-          <t>GEE / Fichas</t>
-        </is>
-      </c>
-      <c r="E65" s="62" t="inlineStr">
-        <is>
-          <t>Revisar las nuevas fichas (GEE, Campus Internacional, International Program)</t>
-        </is>
-      </c>
-      <c r="F65" s="70" t="inlineStr">
-        <is>
-          <t>Las preparo yo tras tu feedback de la ficha de Becas. Tú revisas y me dices qué cambiar.</t>
-        </is>
-      </c>
-      <c r="G65" s="70" t="inlineStr">
-        <is>
-          <t>02-sales/assets</t>
-        </is>
-      </c>
-      <c r="H65" s="70" t="n">
-        <v>30</v>
-      </c>
-      <c r="I65" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J65" s="70" t="n"/>
-    </row>
-    <row r="66" ht="22" customHeight="1" s="50">
-      <c r="A66" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  26/10 a 01/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="62" customHeight="1" s="50">
+      <c r="J66" s="70" t="n"/>
+    </row>
+    <row r="67" ht="33" customHeight="1" s="50">
       <c r="A67" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4774,31 +4771,31 @@
       </c>
       <c r="C67" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D67" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D67" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E67" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F67" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G67" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H67" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I67" s="70" t="inlineStr">
         <is>
@@ -4821,28 +4818,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D68" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D68" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E68" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F68" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G68" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H68" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I68" s="70" t="inlineStr">
         <is>
@@ -4865,28 +4862,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D69" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D69" s="76" t="inlineStr">
+        <is>
+          <t>Campus Internacional</t>
         </is>
       </c>
       <c r="E69" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
         </is>
       </c>
       <c r="F69" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
         </is>
       </c>
       <c r="G69" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Oportunidades y notas</t>
         </is>
       </c>
       <c r="H69" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I69" s="70" t="inlineStr">
         <is>
@@ -4895,7 +4892,7 @@
       </c>
       <c r="J69" s="70" t="n"/>
     </row>
-    <row r="70" ht="33" customHeight="1" s="50">
+    <row r="70" ht="207" customHeight="1" s="50">
       <c r="A70" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4906,64 +4903,20 @@
       </c>
       <c r="C70" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D70" s="76" t="inlineStr">
-        <is>
-          <t>Campus Internacional</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D70" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E70" s="62" t="inlineStr">
         <is>
-          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
+          <t>Programar en Apple Mail los envíos del martes 27/10</t>
         </is>
       </c>
       <c r="F70" s="70" t="inlineStr">
-        <is>
-          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
-        </is>
-      </c>
-      <c r="G70" s="70" t="inlineStr">
-        <is>
-          <t>Oportunidades y notas</t>
-        </is>
-      </c>
-      <c r="H70" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I70" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J70" s="70" t="n"/>
-    </row>
-    <row r="71" ht="207" customHeight="1" s="50">
-      <c r="A71" s="94" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B71" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C71" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D71" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E71" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del martes 27/10</t>
-        </is>
-      </c>
-      <c r="F71" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 27/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -4973,14 +4926,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G70" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H70" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I70" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J70" s="70" t="n"/>
+    </row>
+    <row r="71" ht="47.5" customHeight="1" s="50">
+      <c r="A71" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B71" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C71" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D71" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E71" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F71" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G71" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H71" s="70" t="n">
-        <v>35</v>
-      </c>
+      <c r="H71" s="70" t="n"/>
       <c r="I71" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4999,7 +4994,7 @@
       </c>
       <c r="C72" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D72" s="74" t="inlineStr">
@@ -5009,12 +5004,12 @@
       </c>
       <c r="E72" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a FC Porte d'Aquitaine</t>
+          <t>ENVIAR follow-up 2 a Hastings United</t>
         </is>
       </c>
       <c r="F72" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G72" s="70" t="inlineStr">
@@ -5051,7 +5046,7 @@
       </c>
       <c r="E73" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Hastings United</t>
+          <t>ENVIAR follow-up 2 a Home Farm FC</t>
         </is>
       </c>
       <c r="F73" s="70" t="inlineStr">
@@ -5093,7 +5088,7 @@
       </c>
       <c r="E74" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Home Farm FC</t>
+          <t>ENVIAR follow-up 1 a Virtu Academy</t>
         </is>
       </c>
       <c r="F74" s="70" t="inlineStr">
@@ -5114,7 +5109,7 @@
       </c>
       <c r="J74" s="70" t="n"/>
     </row>
-    <row r="75" ht="47.5" customHeight="1" s="50">
+    <row r="75" ht="62" customHeight="1" s="50">
       <c r="A75" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5125,30 +5120,32 @@
       </c>
       <c r="C75" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D75" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D75" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E75" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Virtu Academy</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F75" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G75" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H75" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H75" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I75" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5156,7 +5153,7 @@
       </c>
       <c r="J75" s="70" t="n"/>
     </row>
-    <row r="76" ht="62" customHeight="1" s="50">
+    <row r="76" ht="76.5" customHeight="1" s="50">
       <c r="A76" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5170,28 +5167,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D76" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D76" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E76" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F76" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G76" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H76" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I76" s="70" t="inlineStr">
         <is>
@@ -5200,7 +5197,7 @@
       </c>
       <c r="J76" s="70" t="n"/>
     </row>
-    <row r="77" ht="76.5" customHeight="1" s="50">
+    <row r="77" ht="33" customHeight="1" s="50">
       <c r="A77" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5211,7 +5208,7 @@
       </c>
       <c r="C77" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D77" s="74" t="inlineStr">
@@ -5221,21 +5218,21 @@
       </c>
       <c r="E77" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
         </is>
       </c>
       <c r="F77" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
         </is>
       </c>
       <c r="G77" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H77" s="70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I77" s="70" t="inlineStr">
         <is>
@@ -5244,7 +5241,7 @@
       </c>
       <c r="J77" s="70" t="n"/>
     </row>
-    <row r="78" ht="33" customHeight="1" s="50">
+    <row r="78" ht="149" customHeight="1" s="50">
       <c r="A78" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5255,7 +5252,7 @@
       </c>
       <c r="C78" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D78" s="74" t="inlineStr">
@@ -5265,54 +5262,10 @@
       </c>
       <c r="E78" s="62" t="inlineStr">
         <is>
-          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
+          <t>Programar en Apple Mail los envíos del miércoles 28/10</t>
         </is>
       </c>
       <c r="F78" s="70" t="inlineStr">
-        <is>
-          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
-        </is>
-      </c>
-      <c r="G78" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H78" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I78" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J78" s="70" t="n"/>
-    </row>
-    <row r="79" ht="149" customHeight="1" s="50">
-      <c r="A79" s="94" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B79" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C79" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D79" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E79" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del miércoles 28/10</t>
-        </is>
-      </c>
-      <c r="F79" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 28/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • Holbeach United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -5320,14 +5273,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G78" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H78" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I78" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J78" s="70" t="n"/>
+    </row>
+    <row r="79" ht="47.5" customHeight="1" s="50">
+      <c r="A79" s="94" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B79" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C79" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D79" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E79" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Søreide IL</t>
+        </is>
+      </c>
+      <c r="F79" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G79" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H79" s="70" t="n">
-        <v>25</v>
-      </c>
+      <c r="H79" s="70" t="n"/>
       <c r="I79" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5346,7 +5341,7 @@
       </c>
       <c r="C80" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D80" s="74" t="inlineStr">
@@ -5356,12 +5351,12 @@
       </c>
       <c r="E80" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Søreide IL</t>
+          <t>ENVIAR follow-up 2 a Holbeach United</t>
         </is>
       </c>
       <c r="F80" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G80" s="70" t="inlineStr">
@@ -5377,7 +5372,7 @@
       </c>
       <c r="J80" s="70" t="n"/>
     </row>
-    <row r="81" ht="47.5" customHeight="1" s="50">
+    <row r="81" ht="62" customHeight="1" s="50">
       <c r="A81" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5388,30 +5383,32 @@
       </c>
       <c r="C81" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D81" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D81" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E81" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Holbeach United</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F81" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G81" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H81" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H81" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I81" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5419,7 +5416,7 @@
       </c>
       <c r="J81" s="70" t="n"/>
     </row>
-    <row r="82" ht="62" customHeight="1" s="50">
+    <row r="82" ht="76.5" customHeight="1" s="50">
       <c r="A82" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5433,28 +5430,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D82" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D82" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E82" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F82" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G82" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H82" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I82" s="70" t="inlineStr">
         <is>
@@ -5463,7 +5460,7 @@
       </c>
       <c r="J82" s="70" t="n"/>
     </row>
-    <row r="83" ht="76.5" customHeight="1" s="50">
+    <row r="83" ht="47.5" customHeight="1" s="50">
       <c r="A83" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5474,31 +5471,31 @@
       </c>
       <c r="C83" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D83" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D83" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E83" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
         </is>
       </c>
       <c r="F83" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
         </is>
       </c>
       <c r="G83" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H83" s="70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I83" s="70" t="inlineStr">
         <is>
@@ -5507,7 +5504,7 @@
       </c>
       <c r="J83" s="70" t="n"/>
     </row>
-    <row r="84" ht="47.5" customHeight="1" s="50">
+    <row r="84" ht="76.5" customHeight="1" s="50">
       <c r="A84" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5521,19 +5518,19 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D84" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D84" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E84" s="62" t="inlineStr">
         <is>
-          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
+          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
         </is>
       </c>
       <c r="F84" s="70" t="inlineStr">
         <is>
-          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G84" s="70" t="inlineStr">
@@ -5542,7 +5539,7 @@
         </is>
       </c>
       <c r="H84" s="70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I84" s="70" t="inlineStr">
         <is>
@@ -5572,7 +5569,7 @@
       </c>
       <c r="E85" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
+          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
         </is>
       </c>
       <c r="F85" s="70" t="inlineStr">
@@ -5595,7 +5592,7 @@
       </c>
       <c r="J85" s="70" t="n"/>
     </row>
-    <row r="86" ht="76.5" customHeight="1" s="50">
+    <row r="86" ht="178" customHeight="1" s="50">
       <c r="A86" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5606,7 +5603,7 @@
       </c>
       <c r="C86" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D86" s="74" t="inlineStr">
@@ -5616,54 +5613,10 @@
       </c>
       <c r="E86" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
+          <t>Programar en Apple Mail los envíos del jueves 29/10</t>
         </is>
       </c>
       <c r="F86" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G86" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H86" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I86" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J86" s="70" t="n"/>
-    </row>
-    <row r="87" ht="178" customHeight="1" s="50">
-      <c r="A87" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B87" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C87" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D87" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E87" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del jueves 29/10</t>
-        </is>
-      </c>
-      <c r="F87" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 29/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -5672,14 +5625,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G86" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H86" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J86" s="70" t="n"/>
+    </row>
+    <row r="87" ht="47.5" customHeight="1" s="50">
+      <c r="A87" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B87" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C87" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D87" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E87" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a IA Akranes</t>
+        </is>
+      </c>
+      <c r="F87" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G87" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H87" s="70" t="n">
-        <v>30</v>
-      </c>
+      <c r="H87" s="70" t="n"/>
       <c r="I87" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5708,7 +5703,7 @@
       </c>
       <c r="E88" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a IA Akranes</t>
+          <t>ENVIAR follow-up 2 a Maidstone United</t>
         </is>
       </c>
       <c r="F88" s="70" t="inlineStr">
@@ -5750,7 +5745,7 @@
       </c>
       <c r="E89" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Maidstone United</t>
+          <t>ENVIAR follow-up 2 a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F89" s="70" t="inlineStr">
@@ -5771,7 +5766,7 @@
       </c>
       <c r="J89" s="70" t="n"/>
     </row>
-    <row r="90" ht="47.5" customHeight="1" s="50">
+    <row r="90" ht="62" customHeight="1" s="50">
       <c r="A90" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5782,30 +5777,32 @@
       </c>
       <c r="C90" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D90" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D90" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E90" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Whitehaven AFC</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F90" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G90" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H90" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H90" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I90" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5813,7 +5810,7 @@
       </c>
       <c r="J90" s="70" t="n"/>
     </row>
-    <row r="91" ht="62" customHeight="1" s="50">
+    <row r="91" ht="76.5" customHeight="1" s="50">
       <c r="A91" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5827,28 +5824,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D91" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D91" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E91" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F91" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G91" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H91" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I91" s="70" t="inlineStr">
         <is>
@@ -5868,7 +5865,7 @@
       </c>
       <c r="C92" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D92" s="74" t="inlineStr">
@@ -5878,21 +5875,21 @@
       </c>
       <c r="E92" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
         </is>
       </c>
       <c r="F92" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G92" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H92" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I92" s="70" t="inlineStr">
         <is>
@@ -5922,7 +5919,7 @@
       </c>
       <c r="E93" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
+          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
         </is>
       </c>
       <c r="F93" s="70" t="inlineStr">
@@ -5945,42 +5942,42 @@
       </c>
       <c r="J93" s="70" t="n"/>
     </row>
-    <row r="94" ht="76.5" customHeight="1" s="50">
+    <row r="94" ht="62" customHeight="1" s="50">
       <c r="A94" s="94" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B94" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C94" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D94" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D94" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E94" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F94" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G94" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H94" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I94" s="70" t="inlineStr">
         <is>
@@ -5989,7 +5986,7 @@
       </c>
       <c r="J94" s="70" t="n"/>
     </row>
-    <row r="95" ht="62" customHeight="1" s="50">
+    <row r="95" ht="76.5" customHeight="1" s="50">
       <c r="A95" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6000,31 +5997,31 @@
       </c>
       <c r="C95" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D95" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D95" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E95" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
         </is>
       </c>
       <c r="F95" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G95" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H95" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I95" s="70" t="inlineStr">
         <is>
@@ -6054,7 +6051,7 @@
       </c>
       <c r="E96" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
+          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
         </is>
       </c>
       <c r="F96" s="70" t="inlineStr">
@@ -6098,7 +6095,7 @@
       </c>
       <c r="E97" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
+          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
         </is>
       </c>
       <c r="F97" s="70" t="inlineStr">
@@ -6121,7 +6118,7 @@
       </c>
       <c r="J97" s="70" t="n"/>
     </row>
-    <row r="98" ht="76.5" customHeight="1" s="50">
+    <row r="98" ht="33" customHeight="1" s="50">
       <c r="A98" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6135,28 +6132,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D98" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D98" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E98" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F98" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G98" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H98" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I98" s="70" t="inlineStr">
         <is>
@@ -6165,58 +6162,58 @@
       </c>
       <c r="J98" s="70" t="n"/>
     </row>
-    <row r="99" ht="33" customHeight="1" s="50">
-      <c r="A99" s="94" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B99" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C99" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D99" s="72" t="inlineStr">
+    <row r="99" ht="22" customHeight="1" s="50">
+      <c r="A99" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  02/11 a 08/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="62" customHeight="1" s="50">
+      <c r="A100" s="94" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B100" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C100" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D100" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E99" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F99" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G99" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H99" s="70" t="n">
+      <c r="E100" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F100" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G100" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H100" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I99" s="70" t="inlineStr">
+      <c r="I100" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J99" s="70" t="n"/>
-    </row>
-    <row r="100" ht="22" customHeight="1" s="50">
-      <c r="A100" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  02/11 a 08/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="62" customHeight="1" s="50">
+      <c r="J100" s="70" t="n"/>
+    </row>
+    <row r="101" ht="33" customHeight="1" s="50">
       <c r="A101" s="94" t="n">
         <v>46328</v>
       </c>
@@ -6227,31 +6224,31 @@
       </c>
       <c r="C101" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D101" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D101" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E101" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F101" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G101" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H101" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I101" s="70" t="inlineStr">
         <is>
@@ -6274,28 +6271,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D102" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D102" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E102" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F102" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G102" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H102" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I102" s="70" t="inlineStr">
         <is>
@@ -6304,7 +6301,7 @@
       </c>
       <c r="J102" s="70" t="n"/>
     </row>
-    <row r="103" ht="33" customHeight="1" s="50">
+    <row r="103" ht="192.5" customHeight="1" s="50">
       <c r="A103" s="94" t="n">
         <v>46328</v>
       </c>
@@ -6315,64 +6312,20 @@
       </c>
       <c r="C103" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D103" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D103" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E103" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Programar en Apple Mail los envíos del martes 03/11</t>
         </is>
       </c>
       <c r="F103" s="70" t="inlineStr">
-        <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
-        </is>
-      </c>
-      <c r="G103" s="70" t="inlineStr">
-        <is>
-          <t>Segmento C - Becas</t>
-        </is>
-      </c>
-      <c r="H103" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I103" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J103" s="70" t="n"/>
-    </row>
-    <row r="104" ht="192.5" customHeight="1" s="50">
-      <c r="A104" s="94" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B104" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C104" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D104" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E104" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del martes 03/11</t>
-        </is>
-      </c>
-      <c r="F104" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 03/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Follow-up 2 | programar para las 03:30 hora Nueva York (09:30 allí)
@@ -6382,14 +6335,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G103" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H103" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I103" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J103" s="70" t="n"/>
+    </row>
+    <row r="104" ht="47.5" customHeight="1" s="50">
+      <c r="A104" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B104" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C104" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D104" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E104" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F104" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G104" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H104" s="70" t="n">
-        <v>35</v>
-      </c>
+      <c r="H104" s="70" t="n"/>
       <c r="I104" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6408,7 +6403,7 @@
       </c>
       <c r="C105" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D105" s="74" t="inlineStr">
@@ -6418,12 +6413,12 @@
       </c>
       <c r="E105" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a FC Porte d'Aquitaine</t>
+          <t>ENVIAR cierre a Hastings United</t>
         </is>
       </c>
       <c r="F105" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G105" s="70" t="inlineStr">
@@ -6460,7 +6455,7 @@
       </c>
       <c r="E106" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Hastings United</t>
+          <t>ENVIAR cierre a Home Farm FC</t>
         </is>
       </c>
       <c r="F106" s="70" t="inlineStr">
@@ -6502,7 +6497,7 @@
       </c>
       <c r="E107" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Home Farm FC</t>
+          <t>ENVIAR follow-up 2 a Virtu Academy</t>
         </is>
       </c>
       <c r="F107" s="70" t="inlineStr">
@@ -6523,7 +6518,7 @@
       </c>
       <c r="J107" s="70" t="n"/>
     </row>
-    <row r="108" ht="47.5" customHeight="1" s="50">
+    <row r="108" ht="62" customHeight="1" s="50">
       <c r="A108" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6534,30 +6529,32 @@
       </c>
       <c r="C108" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D108" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D108" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E108" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Virtu Academy</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F108" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G108" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H108" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H108" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I108" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6565,7 +6562,7 @@
       </c>
       <c r="J108" s="70" t="n"/>
     </row>
-    <row r="109" ht="62" customHeight="1" s="50">
+    <row r="109" ht="76.5" customHeight="1" s="50">
       <c r="A109" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6579,28 +6576,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D109" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D109" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E109" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F109" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G109" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H109" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I109" s="70" t="inlineStr">
         <is>
@@ -6609,7 +6606,7 @@
       </c>
       <c r="J109" s="70" t="n"/>
     </row>
-    <row r="110" ht="76.5" customHeight="1" s="50">
+    <row r="110" ht="30" customHeight="1" s="50">
       <c r="A110" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6620,7 +6617,7 @@
       </c>
       <c r="C110" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D110" s="74" t="inlineStr">
@@ -6630,21 +6627,21 @@
       </c>
       <c r="E110" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Enviar la tanda 4 de emails</t>
         </is>
       </c>
       <c r="F110" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
         </is>
       </c>
       <c r="G110" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H110" s="70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I110" s="70" t="inlineStr">
         <is>
@@ -6653,7 +6650,7 @@
       </c>
       <c r="J110" s="70" t="n"/>
     </row>
-    <row r="111" ht="30" customHeight="1" s="50">
+    <row r="111" ht="134.5" customHeight="1" s="50">
       <c r="A111" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6664,7 +6661,7 @@
       </c>
       <c r="C111" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D111" s="74" t="inlineStr">
@@ -6674,54 +6671,10 @@
       </c>
       <c r="E111" s="62" t="inlineStr">
         <is>
-          <t>Enviar la tanda 4 de emails</t>
+          <t>Programar en Apple Mail los envíos del miércoles 04/11</t>
         </is>
       </c>
       <c r="F111" s="70" t="inlineStr">
-        <is>
-          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
-        </is>
-      </c>
-      <c r="G111" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H111" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I111" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J111" s="70" t="n"/>
-    </row>
-    <row r="112" ht="134.5" customHeight="1" s="50">
-      <c r="A112" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B112" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C112" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D112" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E112" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del miércoles 04/11</t>
-        </is>
-      </c>
-      <c r="F112" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 04/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • Holbeach United | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -6729,14 +6682,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G111" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H111" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I111" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J111" s="70" t="n"/>
+    </row>
+    <row r="112" ht="47.5" customHeight="1" s="50">
+      <c r="A112" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B112" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C112" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D112" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E112" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a Søreide IL</t>
+        </is>
+      </c>
+      <c r="F112" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G112" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H112" s="70" t="n">
-        <v>25</v>
-      </c>
+      <c r="H112" s="70" t="n"/>
       <c r="I112" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6755,7 +6750,7 @@
       </c>
       <c r="C113" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D113" s="74" t="inlineStr">
@@ -6765,12 +6760,12 @@
       </c>
       <c r="E113" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Søreide IL</t>
+          <t>ENVIAR cierre a Holbeach United</t>
         </is>
       </c>
       <c r="F113" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G113" s="70" t="inlineStr">
@@ -6786,7 +6781,7 @@
       </c>
       <c r="J113" s="70" t="n"/>
     </row>
-    <row r="114" ht="47.5" customHeight="1" s="50">
+    <row r="114" ht="62" customHeight="1" s="50">
       <c r="A114" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6797,30 +6792,32 @@
       </c>
       <c r="C114" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D114" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D114" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E114" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Holbeach United</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F114" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G114" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H114" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H114" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I114" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6828,7 +6825,7 @@
       </c>
       <c r="J114" s="70" t="n"/>
     </row>
-    <row r="115" ht="62" customHeight="1" s="50">
+    <row r="115" ht="76.5" customHeight="1" s="50">
       <c r="A115" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6842,28 +6839,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D115" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D115" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E115" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F115" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G115" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H115" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I115" s="70" t="inlineStr">
         <is>
@@ -6872,7 +6869,7 @@
       </c>
       <c r="J115" s="70" t="n"/>
     </row>
-    <row r="116" ht="76.5" customHeight="1" s="50">
+    <row r="116" ht="91" customHeight="1" s="50">
       <c r="A116" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6883,7 +6880,7 @@
       </c>
       <c r="C116" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D116" s="74" t="inlineStr">
@@ -6893,21 +6890,21 @@
       </c>
       <c r="E116" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
         </is>
       </c>
       <c r="F116" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
         </is>
       </c>
       <c r="G116" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H116" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I116" s="70" t="inlineStr">
         <is>
@@ -6916,7 +6913,7 @@
       </c>
       <c r="J116" s="70" t="n"/>
     </row>
-    <row r="117" ht="91" customHeight="1" s="50">
+    <row r="117" ht="76.5" customHeight="1" s="50">
       <c r="A117" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6937,12 +6934,12 @@
       </c>
       <c r="E117" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
+          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
         </is>
       </c>
       <c r="F117" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G117" s="70" t="inlineStr">
@@ -6960,7 +6957,7 @@
       </c>
       <c r="J117" s="70" t="n"/>
     </row>
-    <row r="118" ht="76.5" customHeight="1" s="50">
+    <row r="118" ht="149" customHeight="1" s="50">
       <c r="A118" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6971,7 +6968,7 @@
       </c>
       <c r="C118" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D118" s="74" t="inlineStr">
@@ -6981,54 +6978,10 @@
       </c>
       <c r="E118" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
+          <t>Programar en Apple Mail los envíos del jueves 05/11</t>
         </is>
       </c>
       <c r="F118" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G118" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H118" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I118" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J118" s="70" t="n"/>
-    </row>
-    <row r="119" ht="149" customHeight="1" s="50">
-      <c r="A119" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B119" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C119" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D119" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E119" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del jueves 05/11</t>
-        </is>
-      </c>
-      <c r="F119" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 05/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -7037,14 +6990,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G118" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H118" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J118" s="70" t="n"/>
+    </row>
+    <row r="119" ht="47.5" customHeight="1" s="50">
+      <c r="A119" s="94" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B119" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C119" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D119" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E119" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a IA Akranes</t>
+        </is>
+      </c>
+      <c r="F119" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G119" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H119" s="70" t="n">
-        <v>30</v>
-      </c>
+      <c r="H119" s="70" t="n"/>
       <c r="I119" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7073,7 +7068,7 @@
       </c>
       <c r="E120" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a IA Akranes</t>
+          <t>ENVIAR cierre a Maidstone United</t>
         </is>
       </c>
       <c r="F120" s="70" t="inlineStr">
@@ -7115,7 +7110,7 @@
       </c>
       <c r="E121" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Maidstone United</t>
+          <t>ENVIAR cierre a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F121" s="70" t="inlineStr">
@@ -7136,7 +7131,7 @@
       </c>
       <c r="J121" s="70" t="n"/>
     </row>
-    <row r="122" ht="47.5" customHeight="1" s="50">
+    <row r="122" ht="62" customHeight="1" s="50">
       <c r="A122" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7147,30 +7142,32 @@
       </c>
       <c r="C122" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D122" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D122" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E122" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Whitehaven AFC</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F122" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G122" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H122" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H122" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I122" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7178,7 +7175,7 @@
       </c>
       <c r="J122" s="70" t="n"/>
     </row>
-    <row r="123" ht="62" customHeight="1" s="50">
+    <row r="123" ht="76.5" customHeight="1" s="50">
       <c r="A123" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7192,81 +7189,81 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D123" s="72" t="inlineStr">
+      <c r="D123" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E123" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F123" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G123" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H123" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I123" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J123" s="70" t="n"/>
+    </row>
+    <row r="124" ht="62" customHeight="1" s="50">
+      <c r="A124" s="94" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B124" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C124" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D124" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E123" s="62" t="inlineStr">
+      <c r="E124" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F123" s="70" t="inlineStr">
+      <c r="F124" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G123" s="70" t="inlineStr">
+      <c r="G124" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H123" s="70" t="n">
+      <c r="H124" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I123" s="70" t="inlineStr">
+      <c r="I124" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J123" s="70" t="n"/>
-    </row>
-    <row r="124" ht="76.5" customHeight="1" s="50">
-      <c r="A124" s="94" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B124" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C124" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D124" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E124" s="62" t="inlineStr">
-        <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
-        </is>
-      </c>
-      <c r="F124" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G124" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H124" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I124" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J124" s="70" t="n"/>
     </row>
-    <row r="125" ht="62" customHeight="1" s="50">
+    <row r="125" ht="33" customHeight="1" s="50">
       <c r="A125" s="94" t="n">
         <v>46332</v>
       </c>
@@ -7277,7 +7274,7 @@
       </c>
       <c r="C125" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D125" s="72" t="inlineStr">
@@ -7287,21 +7284,21 @@
       </c>
       <c r="E125" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
         </is>
       </c>
       <c r="F125" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
         </is>
       </c>
       <c r="G125" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="H125" s="70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I125" s="70" t="inlineStr">
         <is>
@@ -7331,21 +7328,21 @@
       </c>
       <c r="E126" s="62" t="inlineStr">
         <is>
-          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F126" s="70" t="inlineStr">
         <is>
-          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G126" s="70" t="inlineStr">
         <is>
-          <t>Hoy</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H126" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I126" s="70" t="inlineStr">
         <is>
@@ -7354,58 +7351,58 @@
       </c>
       <c r="J126" s="70" t="n"/>
     </row>
-    <row r="127" ht="33" customHeight="1" s="50">
-      <c r="A127" s="94" t="n">
-        <v>46332</v>
-      </c>
-      <c r="B127" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C127" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D127" s="72" t="inlineStr">
+    <row r="127" ht="22" customHeight="1" s="50">
+      <c r="A127" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  09/11 a 15/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="62" customHeight="1" s="50">
+      <c r="A128" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B128" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C128" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D128" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E127" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F127" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G127" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H127" s="70" t="n">
+      <c r="E128" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F128" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G128" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H128" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I127" s="70" t="inlineStr">
+      <c r="I128" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J127" s="70" t="n"/>
-    </row>
-    <row r="128" ht="22" customHeight="1" s="50">
-      <c r="A128" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  09/11 a 15/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="62" customHeight="1" s="50">
+      <c r="J128" s="70" t="n"/>
+    </row>
+    <row r="129" ht="33" customHeight="1" s="50">
       <c r="A129" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7416,31 +7413,31 @@
       </c>
       <c r="C129" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D129" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D129" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E129" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F129" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G129" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H129" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I129" s="70" t="inlineStr">
         <is>
@@ -7463,28 +7460,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D130" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D130" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E130" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F130" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G130" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H130" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I130" s="70" t="inlineStr">
         <is>
@@ -7507,28 +7504,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D131" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D131" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E131" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Revisión del mes con Claude (45 min)</t>
         </is>
       </c>
       <c r="F131" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real.</t>
         </is>
       </c>
       <c r="G131" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H131" s="70" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I131" s="70" t="inlineStr">
         <is>
@@ -7537,7 +7534,7 @@
       </c>
       <c r="J131" s="70" t="n"/>
     </row>
-    <row r="132" ht="33" customHeight="1" s="50">
+    <row r="132" ht="134.5" customHeight="1" s="50">
       <c r="A132" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7548,64 +7545,20 @@
       </c>
       <c r="C132" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D132" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D132" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E132" s="62" t="inlineStr">
         <is>
-          <t>Revisión del mes con Claude (45 min)</t>
+          <t>Programar en Apple Mail los envíos del martes 10/11</t>
         </is>
       </c>
       <c r="F132" s="70" t="inlineStr">
-        <is>
-          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real.</t>
-        </is>
-      </c>
-      <c r="G132" s="70" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H132" s="70" t="n">
-        <v>45</v>
-      </c>
-      <c r="I132" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J132" s="70" t="n"/>
-    </row>
-    <row r="133" ht="134.5" customHeight="1" s="50">
-      <c r="A133" s="94" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B133" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C133" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D133" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E133" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del martes 10/11</t>
-        </is>
-      </c>
-      <c r="F133" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 10/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Cierre | programar para las 03:30 hora Nueva York (09:30 allí)
@@ -7613,14 +7566,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G132" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H132" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I132" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J132" s="70" t="n"/>
+    </row>
+    <row r="133" ht="47.5" customHeight="1" s="50">
+      <c r="A133" s="94" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B133" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C133" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D133" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E133" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F133" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G133" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H133" s="70" t="n">
-        <v>25</v>
-      </c>
+      <c r="H133" s="70" t="n"/>
       <c r="I133" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7639,7 +7634,7 @@
       </c>
       <c r="C134" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D134" s="74" t="inlineStr">
@@ -7649,12 +7644,12 @@
       </c>
       <c r="E134" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a FC Porte d'Aquitaine</t>
+          <t>ENVIAR cierre a Virtu Academy</t>
         </is>
       </c>
       <c r="F134" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G134" s="70" t="inlineStr">
@@ -7670,7 +7665,7 @@
       </c>
       <c r="J134" s="70" t="n"/>
     </row>
-    <row r="135" ht="47.5" customHeight="1" s="50">
+    <row r="135" ht="62" customHeight="1" s="50">
       <c r="A135" s="94" t="n">
         <v>46336</v>
       </c>
@@ -7681,30 +7676,32 @@
       </c>
       <c r="C135" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D135" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D135" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E135" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Virtu Academy</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F135" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G135" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H135" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H135" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I135" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7712,7 +7709,7 @@
       </c>
       <c r="J135" s="70" t="n"/>
     </row>
-    <row r="136" ht="62" customHeight="1" s="50">
+    <row r="136" ht="76.5" customHeight="1" s="50">
       <c r="A136" s="94" t="n">
         <v>46336</v>
       </c>
@@ -7726,72 +7723,72 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D136" s="72" t="inlineStr">
+      <c r="D136" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E136" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F136" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G136" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H136" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I136" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J136" s="70" t="n"/>
+    </row>
+    <row r="137" ht="62" customHeight="1" s="50">
+      <c r="A137" s="94" t="n">
+        <v>46337</v>
+      </c>
+      <c r="B137" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C137" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D137" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E136" s="62" t="inlineStr">
+      <c r="E137" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F136" s="70" t="inlineStr">
+      <c r="F137" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G136" s="70" t="inlineStr">
+      <c r="G137" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H136" s="70" t="n">
+      <c r="H137" s="70" t="n">
         <v>15</v>
-      </c>
-      <c r="I136" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J136" s="70" t="n"/>
-    </row>
-    <row r="137" ht="76.5" customHeight="1" s="50">
-      <c r="A137" s="94" t="n">
-        <v>46336</v>
-      </c>
-      <c r="B137" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C137" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D137" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E137" s="62" t="inlineStr">
-        <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
-        </is>
-      </c>
-      <c r="F137" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G137" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H137" s="70" t="n">
-        <v>10</v>
       </c>
       <c r="I137" s="70" t="inlineStr">
         <is>
@@ -7802,11 +7799,11 @@
     </row>
     <row r="138" ht="62" customHeight="1" s="50">
       <c r="A138" s="94" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="B138" s="70" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C138" s="71" t="inlineStr">
@@ -7846,11 +7843,11 @@
     </row>
     <row r="139" ht="62" customHeight="1" s="50">
       <c r="A139" s="94" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="B139" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C139" s="71" t="inlineStr">
@@ -7888,7 +7885,7 @@
       </c>
       <c r="J139" s="70" t="n"/>
     </row>
-    <row r="140" ht="62" customHeight="1" s="50">
+    <row r="140" ht="33" customHeight="1" s="50">
       <c r="A140" s="94" t="n">
         <v>46339</v>
       </c>
@@ -7899,7 +7896,7 @@
       </c>
       <c r="C140" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D140" s="72" t="inlineStr">
@@ -7909,17 +7906,17 @@
       </c>
       <c r="E140" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F140" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G140" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H140" s="70" t="n">
@@ -7932,61 +7929,17 @@
       </c>
       <c r="J140" s="70" t="n"/>
     </row>
-    <row r="141" ht="33" customHeight="1" s="50">
-      <c r="A141" s="94" t="n">
-        <v>46339</v>
-      </c>
-      <c r="B141" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C141" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D141" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E141" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F141" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G141" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H141" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I141" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J141" s="70" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:J141"/>
+  <autoFilter ref="A4:J140"/>
   <mergeCells count="6">
+    <mergeCell ref="A99:J99"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A100:J100"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A128:J128"/>
-    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A127:J127"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A65:J65"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J141">
+  <conditionalFormatting sqref="A5:J140">
     <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="1">
       <formula>$I5="Hecho"</formula>
     </cfRule>
@@ -7994,13 +7947,13 @@
       <formula>$A5=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I141">
+  <conditionalFormatting sqref="I5:I140">
     <cfRule type="expression" priority="3" dxfId="5">
       <formula>AND(ISNUMBER($A5),$A5&lt;TODAY(),$I5="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140 I141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Hecho,Saltado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12659,7 +12612,7 @@
       <c r="N10" s="10" t="n"/>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
@@ -13135,7 +13088,7 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
+          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -33,11 +33,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -128,61 +127,72 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF0B1F3A"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF444444"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
       <color rgb="FF777777"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF0B1F3A"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
       <color rgb="FF555555"/>
       <sz val="11"/>
@@ -395,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -523,6 +533,12 @@
     <xf numFmtId="0" fontId="21" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -535,12 +551,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -652,15 +662,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="31" fillId="21" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="31" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1074,8 +1075,8 @@
   <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="50" min="1" max="1"/>
-    <col width="110" customWidth="1" style="50" min="2" max="2"/>
+    <col width="24" customWidth="1" style="52" min="1" max="1"/>
+    <col width="110" customWidth="1" style="52" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1092,14 +1093,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" s="50">
+    <row r="4" ht="22" customHeight="1" s="52">
       <c r="A4" s="61" t="inlineStr">
         <is>
           <t>TU RUTINA</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" s="50">
+    <row r="5" ht="20" customHeight="1" s="52">
       <c r="A5" s="62" t="inlineStr">
         <is>
           <t>Cada mañana (15 min)</t>
@@ -1111,7 +1112,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" s="50">
+    <row r="6" ht="33" customHeight="1" s="52">
       <c r="A6" s="62" t="inlineStr">
         <is>
           <t>La víspera (20 min)</t>
@@ -1123,7 +1124,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" s="50">
+    <row r="7" ht="20" customHeight="1" s="52">
       <c r="A7" s="62" t="inlineStr">
         <is>
           <t>Cada viernes (20 min)</t>
@@ -1135,7 +1136,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1" s="50">
+    <row r="8" ht="20" customHeight="1" s="52">
       <c r="A8" s="62" t="inlineStr">
         <is>
           <t>Cada lunes (5 min)</t>
@@ -1147,14 +1148,14 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" s="50">
+    <row r="9" ht="22" customHeight="1" s="52">
       <c r="A9" s="61" t="inlineStr">
         <is>
           <t>PESTAÑAS</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1" s="50">
+    <row r="10" ht="20" customHeight="1" s="52">
       <c r="A10" s="62" t="inlineStr">
         <is>
           <t>Calendario diario</t>
@@ -1166,7 +1167,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" s="50">
+    <row r="11" ht="20" customHeight="1" s="52">
       <c r="A11" s="62" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
@@ -1178,7 +1179,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" s="50">
+    <row r="12" ht="20" customHeight="1" s="52">
       <c r="A12" s="62" t="inlineStr">
         <is>
           <t>Hoy</t>
@@ -1190,7 +1191,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1" s="50">
+    <row r="13" ht="20" customHeight="1" s="52">
       <c r="A13" s="62" t="inlineStr">
         <is>
           <t>Plan por servicio</t>
@@ -1202,7 +1203,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1" s="50">
+    <row r="14" ht="20" customHeight="1" s="52">
       <c r="A14" s="62" t="inlineStr">
         <is>
           <t>Verificación</t>
@@ -1214,7 +1215,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1" s="50">
+    <row r="15" ht="33" customHeight="1" s="52">
       <c r="A15" s="62" t="inlineStr">
         <is>
           <t>Segmento A / B / C</t>
@@ -1226,7 +1227,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1" s="50">
+    <row r="16" ht="20" customHeight="1" s="52">
       <c r="A16" s="62" t="inlineStr">
         <is>
           <t>Dashboard, LinkedIn, Oportunidades</t>
@@ -1238,14 +1239,14 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1" s="50">
+    <row r="17" ht="22" customHeight="1" s="52">
       <c r="A17" s="61" t="inlineStr">
         <is>
           <t>COMO Y CUANDO ENVIAR</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="33" customHeight="1" s="50">
+    <row r="18" ht="33" customHeight="1" s="52">
       <c r="A18" s="62" t="inlineStr">
         <is>
           <t>Qué se ha comprobado (14/10/2026)</t>
@@ -1257,7 +1258,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="47.5" customHeight="1" s="50">
+    <row r="19" ht="47.5" customHeight="1" s="52">
       <c r="A19" s="62" t="inlineStr">
         <is>
           <t>Por qué parecía que no salían</t>
@@ -1269,7 +1270,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1" s="50">
+    <row r="20" ht="33" customHeight="1" s="52">
       <c r="A20" s="62" t="inlineStr">
         <is>
           <t>Cómo se programa</t>
@@ -1281,7 +1282,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="33" customHeight="1" s="50">
+    <row r="21" ht="33" customHeight="1" s="52">
       <c r="A21" s="62" t="inlineStr">
         <is>
           <t>Regla para no duplicar</t>
@@ -1293,7 +1294,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="33" customHeight="1" s="50">
+    <row r="22" ht="33" customHeight="1" s="52">
       <c r="A22" s="62" t="inlineStr">
         <is>
           <t>Control</t>
@@ -1305,7 +1306,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="33" customHeight="1" s="50">
+    <row r="23" ht="33" customHeight="1" s="52">
       <c r="A23" s="62" t="inlineStr">
         <is>
           <t>Truco opcional</t>
@@ -1317,14 +1318,14 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1" s="50">
+    <row r="24" ht="22" customHeight="1" s="52">
       <c r="A24" s="61" t="inlineStr">
         <is>
           <t>TUS FRANJAS DE LLAMADA</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="33" customHeight="1" s="50">
+    <row r="25" ht="33" customHeight="1" s="52">
       <c r="A25" s="62" t="inlineStr">
         <is>
           <t>Lo que tienes en Calendly (hora Nueva York)</t>
@@ -1336,7 +1337,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="47.5" customHeight="1" s="50">
+    <row r="26" ht="47.5" customHeight="1" s="52">
       <c r="A26" s="62" t="inlineStr">
         <is>
           <t>Clubes de Europa (+5 h en UK e Irlanda, +6 h en Noruega, Francia y Países Bajos; +4 y +5 del 25 al 31/10)</t>
@@ -1348,7 +1349,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1" s="50">
+    <row r="27" ht="20" customHeight="1" s="52">
       <c r="A27" s="62" t="inlineStr">
         <is>
           <t>Familias de América (México, Latinoamérica, EEUU)</t>
@@ -1360,7 +1361,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="47.5" customHeight="1" s="50">
+    <row r="28" ht="47.5" customHeight="1" s="52">
       <c r="A28" s="62" t="inlineStr">
         <is>
           <t>Recomendación</t>
@@ -1372,14 +1373,14 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1" s="50">
+    <row r="29" ht="22" customHeight="1" s="52">
       <c r="A29" s="61" t="inlineStr">
         <is>
           <t>REGLAS QUE NO SE ROMPEN</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="33" customHeight="1" s="50">
+    <row r="30" ht="33" customHeight="1" s="52">
       <c r="A30" s="62" t="inlineStr">
         <is>
           <t>Nunca</t>
@@ -1391,7 +1392,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="33" customHeight="1" s="50">
+    <row r="31" ht="33" customHeight="1" s="52">
       <c r="A31" s="62" t="inlineStr">
         <is>
           <t>Si contestan</t>
@@ -1403,7 +1404,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1" s="50">
+    <row r="32" ht="20" customHeight="1" s="52">
       <c r="A32" s="62" t="inlineStr">
         <is>
           <t>Si un correo rebota</t>
@@ -1415,7 +1416,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="33" customHeight="1" s="50">
+    <row r="33" ht="33" customHeight="1" s="52">
       <c r="A33" s="62" t="inlineStr">
         <is>
           <t>Colores</t>
@@ -1448,31 +1449,31 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="50" min="1" max="1"/>
-    <col width="20" customWidth="1" style="50" min="2" max="2"/>
-    <col width="16" customWidth="1" style="50" min="3" max="4"/>
-    <col width="18" customWidth="1" style="50" min="5" max="5"/>
-    <col width="20" customWidth="1" style="50" min="6" max="6"/>
-    <col width="14" customWidth="1" style="50" min="7" max="7"/>
-    <col width="12" customWidth="1" style="50" min="8" max="8"/>
+    <col width="22" customWidth="1" style="52" min="1" max="1"/>
+    <col width="20" customWidth="1" style="52" min="2" max="2"/>
+    <col width="16" customWidth="1" style="52" min="3" max="4"/>
+    <col width="18" customWidth="1" style="52" min="5" max="5"/>
+    <col width="20" customWidth="1" style="52" min="6" max="6"/>
+    <col width="14" customWidth="1" style="52" min="7" max="7"/>
+    <col width="12" customWidth="1" style="52" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="50">
-      <c r="A1" s="53" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="52">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Dashboard — funnel por línea de negocio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>Estado actual de cada línea. Actualizar Estado/Etapa en las pestañas de segmento — esto se recalcula solo.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" s="50">
-      <c r="A3" s="56" t="inlineStr">
+    <row r="3" ht="60" customHeight="1" s="52">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Esto es una FOTO del estado ACTUAL de cada lead (cuántos están ahora mismo en cada estado), no un histórico acumulado de conversión — para eso haría falta guardar fecha de cada cambio de estado, cosa que no hacemos todavía. Sirve igual para ver dónde se acumulan los leads y detectar el cuello de botella real.</t>
         </is>
@@ -1569,7 +1570,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1" s="50">
+    <row r="11" ht="28" customHeight="1" s="52">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Nuevo</t>
@@ -1635,7 +1636,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>0 leads activos todavía — esta sección se activa con el primer lead real. Ver lineas-de-negocio.md línea 3. No crear pestaña de seguimiento hasta entonces.</t>
         </is>
@@ -1649,7 +1650,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="56" t="inlineStr">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>Sin funnel activo — decisión explícita de Joel de no priorizar hasta tener un cliente/jugador real interesado (lineas-de-negocio.md líneas 4 y 6). Si preguntan, ver manual-embudo-ventas.md para el guion de respuesta correcto (nunca prometer prueba/contrato garantizado).</t>
         </is>
@@ -1676,37 +1677,37 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="50" min="1" max="1"/>
-    <col width="20" customWidth="1" style="50" min="2" max="2"/>
-    <col width="26" customWidth="1" style="50" min="3" max="3"/>
-    <col width="30" customWidth="1" style="50" min="4" max="4"/>
-    <col width="18" customWidth="1" style="50" min="5" max="5"/>
-    <col width="40" customWidth="1" style="50" min="6" max="6"/>
+    <col width="14" customWidth="1" style="52" min="1" max="1"/>
+    <col width="20" customWidth="1" style="52" min="2" max="2"/>
+    <col width="26" customWidth="1" style="52" min="3" max="3"/>
+    <col width="30" customWidth="1" style="52" min="4" max="4"/>
+    <col width="18" customWidth="1" style="52" min="5" max="5"/>
+    <col width="40" customWidth="1" style="52" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="50">
-      <c r="A1" s="53" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="52">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>LinkedIn — plan diario</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>Rellenar cada día que trabajes outreach.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" s="50">
-      <c r="A3" s="56" t="inlineStr">
+    <row r="3" ht="60" customHeight="1" s="52">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>ACTIVA desde el 28/09/2026 — perfil de LinkedIn terminado (titular, experiencia, foto). Semana 1 (28/09-04/10): 5-10 conexiones/día con gente conocida (Mercy, Mount Aloysius, fútbol en España), sin vender nada, para construir base real antes de contactar decisores. Semana 2 en adelante: 5 conexiones/día a decisores reales de Segmento A/B (crm-ventas.xlsx), nota corta con señal real, ver plan-ventas-maestro.md sección 4.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5" ht="28" customHeight="1" s="50">
+    <row r="5" ht="28" customHeight="1" s="52">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -1837,30 +1838,30 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="50" min="1" max="1"/>
-    <col width="26" customWidth="1" style="50" min="2" max="2"/>
-    <col width="40" customWidth="1" style="50" min="3" max="3"/>
-    <col width="22" customWidth="1" style="50" min="4" max="4"/>
-    <col width="40" customWidth="1" style="50" min="5" max="5"/>
-    <col width="20" customWidth="1" style="50" min="6" max="6"/>
+    <col width="14" customWidth="1" style="52" min="1" max="1"/>
+    <col width="26" customWidth="1" style="52" min="2" max="2"/>
+    <col width="40" customWidth="1" style="52" min="3" max="3"/>
+    <col width="22" customWidth="1" style="52" min="4" max="4"/>
+    <col width="40" customWidth="1" style="52" min="5" max="5"/>
+    <col width="20" customWidth="1" style="52" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="50">
-      <c r="A1" s="53" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="52">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Oportunidades y notas sueltas</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>Ideas que surgen investigando, sin operativa de venta propia todavía.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="50">
-      <c r="A3" s="56" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="52">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Backlog ligero para líneas que aún no tienen operativa propia de venta — no crear pestañas dedicadas hasta que Joel las eleve de prioridad (ver roadmap-maestro.md).</t>
         </is>
@@ -1898,7 +1899,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" s="50">
+    <row r="5" ht="28" customHeight="1" s="52">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -1930,7 +1931,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" s="50">
+    <row r="6" ht="28" customHeight="1" s="52">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -1994,7 +1995,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" s="50">
+    <row r="8" ht="28" customHeight="1" s="52">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-07</t>
@@ -2026,7 +2027,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" s="50">
+    <row r="9" ht="42" customHeight="1" s="52">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-08-29</t>
@@ -2079,33 +2080,33 @@
   <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" style="50" min="1" max="1"/>
-    <col width="11" customWidth="1" style="50" min="2" max="2"/>
-    <col width="9" customWidth="1" style="50" min="3" max="3"/>
-    <col width="16" customWidth="1" style="50" min="4" max="4"/>
-    <col width="40" customWidth="1" style="50" min="5" max="5"/>
-    <col width="78" customWidth="1" style="50" min="6" max="6"/>
-    <col width="24" customWidth="1" style="50" min="7" max="7"/>
-    <col width="6" customWidth="1" style="50" min="8" max="8"/>
-    <col width="12" customWidth="1" style="50" min="9" max="9"/>
-    <col width="36" customWidth="1" style="50" min="10" max="10"/>
+    <col width="11" customWidth="1" style="52" min="1" max="1"/>
+    <col width="11" customWidth="1" style="52" min="2" max="2"/>
+    <col width="9" customWidth="1" style="52" min="3" max="3"/>
+    <col width="16" customWidth="1" style="52" min="4" max="4"/>
+    <col width="40" customWidth="1" style="52" min="5" max="5"/>
+    <col width="78" customWidth="1" style="52" min="6" max="6"/>
+    <col width="24" customWidth="1" style="52" min="7" max="7"/>
+    <col width="6" customWidth="1" style="52" min="8" max="8"/>
+    <col width="12" customWidth="1" style="52" min="9" max="9"/>
+    <col width="36" customWidth="1" style="52" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" s="50">
+    <row r="1" ht="26" customHeight="1" s="52">
       <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Calendario diario: 13 de octubre a 13 de noviembre de 2026</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1" s="50">
+    <row r="2" ht="46" customHeight="1" s="52">
       <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Qué haces tú cada día, a qué hora y cómo. Las horas son de Nueva York. Los correos se programan la víspera en Apple Mail (Enviar más tarde) para las 09:30 de cada club; a las 08:00 compruebas que salieron. Cambia la columna Estado a Hecho al terminar. Hoy se marca en amarillo. Si algo queda Pendiente de un día anterior, sale en rojo.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="50">
+    <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -2157,14 +2158,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" s="50">
+    <row r="5" ht="22" customHeight="1" s="52">
       <c r="A5" s="68" t="inlineStr">
         <is>
           <t>SEMANA  12/10 a 18/10</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="62" customHeight="1" s="50">
+    <row r="6" ht="62" customHeight="1" s="52">
       <c r="A6" s="94" t="n">
         <v>46308</v>
       </c>
@@ -2208,7 +2209,7 @@
       </c>
       <c r="J6" s="70" t="n"/>
     </row>
-    <row r="7" ht="33" customHeight="1" s="50">
+    <row r="7" ht="33" customHeight="1" s="52">
       <c r="A7" s="94" t="n">
         <v>46308</v>
       </c>
@@ -2250,7 +2251,7 @@
       </c>
       <c r="J7" s="70" t="n"/>
     </row>
-    <row r="8" ht="91" customHeight="1" s="50">
+    <row r="8" ht="91" customHeight="1" s="52">
       <c r="A8" s="94" t="n">
         <v>46308</v>
       </c>
@@ -2294,7 +2295,7 @@
       </c>
       <c r="J8" s="70" t="n"/>
     </row>
-    <row r="9" ht="47.5" customHeight="1" s="50">
+    <row r="9" ht="47.5" customHeight="1" s="52">
       <c r="A9" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2331,16 +2332,12 @@
       <c r="H9" s="70" t="n"/>
       <c r="I9" s="70" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="J9" s="70" t="inlineStr">
-        <is>
-          <t>Enviado a mano el 14/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="47.5" customHeight="1" s="50">
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J9" s="70" t="n"/>
+    </row>
+    <row r="10" ht="47.5" customHeight="1" s="52">
       <c r="A10" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2377,16 +2374,12 @@
       <c r="H10" s="70" t="n"/>
       <c r="I10" s="70" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="J10" s="70" t="inlineStr">
-        <is>
-          <t>Enviado a mano el 14/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="62" customHeight="1" s="50">
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J10" s="70" t="n"/>
+    </row>
+    <row r="11" ht="62" customHeight="1" s="52">
       <c r="A11" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2425,12 +2418,12 @@
       </c>
       <c r="I11" s="70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
       <c r="J11" s="70" t="n"/>
     </row>
-    <row r="12" ht="76.5" customHeight="1" s="50">
+    <row r="12" ht="76.5" customHeight="1" s="52">
       <c r="A12" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2474,7 +2467,7 @@
       </c>
       <c r="J12" s="70" t="n"/>
     </row>
-    <row r="13" ht="62" customHeight="1" s="50">
+    <row r="13" ht="62" customHeight="1" s="52">
       <c r="A13" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2513,12 +2506,16 @@
       </c>
       <c r="I13" s="70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J13" s="70" t="n"/>
-    </row>
-    <row r="14" ht="47.5" customHeight="1" s="50">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="J13" s="70" t="inlineStr">
+        <is>
+          <t>Søreide: 1 envío (14/10 8:34). Holbeach: 2 confirmados (13/10 18:50 y 14/10 4:41) y el de ~8:30 no localizado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="47.5" customHeight="1" s="52">
       <c r="A14" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2557,16 +2554,12 @@
       </c>
       <c r="I14" s="70" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="J14" s="70" t="inlineStr">
-        <is>
-          <t>Sale con Mail cerrado y Mac en reposo; no aparece en 'Sent' de Outlook (otra carpeta)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="76.5" customHeight="1" s="50">
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J14" s="70" t="n"/>
+    </row>
+    <row r="15" ht="76.5" customHeight="1" s="52">
       <c r="A15" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2605,16 +2598,12 @@
       </c>
       <c r="I15" s="70" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="J15" s="70" t="inlineStr">
-        <is>
-          <t>3 cuentas Outlook: todas en bandeja principal</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="47.5" customHeight="1" s="50">
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J15" s="70" t="n"/>
+    </row>
+    <row r="16" ht="62" customHeight="1" s="52">
       <c r="A16" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2625,7 +2614,7 @@
       </c>
       <c r="C16" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D16" s="73" t="inlineStr">
@@ -2635,17 +2624,17 @@
       </c>
       <c r="E16" s="62" t="inlineStr">
         <is>
-          <t>Daniel (MLS NEXT): apuntar su @usuario en el CRM</t>
+          <t>Daniel (MLS NEXT): enviar el follow-up por Instagram</t>
         </is>
       </c>
       <c r="F16" s="70" t="inlineStr">
         <is>
-          <t>Abre la conversación de Instagram con Daniel, copia su @usuario y pégalo en la fila 20 de Segmento C (columna del contacto). Solo sirve para tenerlo localizado: no bloquea nada. Si no le has contestado todavía, dímelo y preparamos la respuesta.</t>
+          <t>No contestó a tu mensaje del 21/09. Mi consejo: un único follow-up corto con salida fácil, y si no responde en 7 días, pasarlo a 'Frío'. Texto en 'Respuestas tipo' (Daniel). Mejor entre las 12:00 y las 14:00 de Nueva York (18:00 a 20:00 en España, cuando está libre de clase). Después apunta en el CRM la fecha de envío.</t>
         </is>
       </c>
       <c r="G16" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar (Respuestas tipo)</t>
         </is>
       </c>
       <c r="H16" s="70" t="n">
@@ -2658,7 +2647,7 @@
       </c>
       <c r="J16" s="70" t="n"/>
     </row>
-    <row r="17" ht="163.5" customHeight="1" s="50">
+    <row r="17" ht="163.5" customHeight="1" s="52">
       <c r="A17" s="94" t="n">
         <v>46309</v>
       </c>
@@ -2706,7 +2695,7 @@
       </c>
       <c r="J17" s="70" t="n"/>
     </row>
-    <row r="18" ht="47.5" customHeight="1" s="50">
+    <row r="18" ht="47.5" customHeight="1" s="52">
       <c r="A18" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2748,7 +2737,7 @@
       </c>
       <c r="J18" s="70" t="n"/>
     </row>
-    <row r="19" ht="47.5" customHeight="1" s="50">
+    <row r="19" ht="47.5" customHeight="1" s="52">
       <c r="A19" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2790,7 +2779,7 @@
       </c>
       <c r="J19" s="70" t="n"/>
     </row>
-    <row r="20" ht="47.5" customHeight="1" s="50">
+    <row r="20" ht="47.5" customHeight="1" s="52">
       <c r="A20" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2832,7 +2821,7 @@
       </c>
       <c r="J20" s="70" t="n"/>
     </row>
-    <row r="21" ht="62" customHeight="1" s="50">
+    <row r="21" ht="62" customHeight="1" s="52">
       <c r="A21" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2876,7 +2865,7 @@
       </c>
       <c r="J21" s="70" t="n"/>
     </row>
-    <row r="22" ht="76.5" customHeight="1" s="50">
+    <row r="22" ht="76.5" customHeight="1" s="52">
       <c r="A22" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2920,7 +2909,7 @@
       </c>
       <c r="J22" s="70" t="n"/>
     </row>
-    <row r="23" ht="33" customHeight="1" s="50">
+    <row r="23" ht="33" customHeight="1" s="52">
       <c r="A23" s="94" t="n">
         <v>46310</v>
       </c>
@@ -2964,7 +2953,7 @@
       </c>
       <c r="J23" s="70" t="n"/>
     </row>
-    <row r="24" ht="33" customHeight="1" s="50">
+    <row r="24" ht="33" customHeight="1" s="52">
       <c r="A24" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3008,7 +2997,7 @@
       </c>
       <c r="J24" s="70" t="n"/>
     </row>
-    <row r="25" ht="76.5" customHeight="1" s="50">
+    <row r="25" ht="76.5" customHeight="1" s="52">
       <c r="A25" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3052,7 +3041,7 @@
       </c>
       <c r="J25" s="70" t="n"/>
     </row>
-    <row r="26" ht="62" customHeight="1" s="50">
+    <row r="26" ht="62" customHeight="1" s="52">
       <c r="A26" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3092,7 +3081,7 @@
       </c>
       <c r="J26" s="70" t="n"/>
     </row>
-    <row r="27" ht="76.5" customHeight="1" s="50">
+    <row r="27" ht="76.5" customHeight="1" s="52">
       <c r="A27" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3136,7 +3125,7 @@
       </c>
       <c r="J27" s="70" t="n"/>
     </row>
-    <row r="28" ht="62" customHeight="1" s="50">
+    <row r="28" ht="62" customHeight="1" s="52">
       <c r="A28" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3180,7 +3169,7 @@
       </c>
       <c r="J28" s="70" t="n"/>
     </row>
-    <row r="29" ht="33" customHeight="1" s="50">
+    <row r="29" ht="33" customHeight="1" s="52">
       <c r="A29" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3224,7 +3213,7 @@
       </c>
       <c r="J29" s="70" t="n"/>
     </row>
-    <row r="30" ht="76.5" customHeight="1" s="50">
+    <row r="30" ht="76.5" customHeight="1" s="52">
       <c r="A30" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3268,7 +3257,7 @@
       </c>
       <c r="J30" s="70" t="n"/>
     </row>
-    <row r="31" ht="76.5" customHeight="1" s="50">
+    <row r="31" ht="76.5" customHeight="1" s="52">
       <c r="A31" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3312,7 +3301,7 @@
       </c>
       <c r="J31" s="70" t="n"/>
     </row>
-    <row r="32" ht="33" customHeight="1" s="50">
+    <row r="32" ht="33" customHeight="1" s="52">
       <c r="A32" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3356,7 +3345,7 @@
       </c>
       <c r="J32" s="70" t="n"/>
     </row>
-    <row r="33" ht="47.5" customHeight="1" s="50">
+    <row r="33" ht="47.5" customHeight="1" s="52">
       <c r="A33" s="94" t="n">
         <v>46312</v>
       </c>
@@ -3400,14 +3389,14 @@
       </c>
       <c r="J33" s="70" t="n"/>
     </row>
-    <row r="34" ht="22" customHeight="1" s="50">
+    <row r="34" ht="22" customHeight="1" s="52">
       <c r="A34" s="68" t="inlineStr">
         <is>
           <t>SEMANA  19/10 a 25/10</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="62" customHeight="1" s="50">
+    <row r="35" ht="62" customHeight="1" s="52">
       <c r="A35" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3451,7 +3440,7 @@
       </c>
       <c r="J35" s="70" t="n"/>
     </row>
-    <row r="36" ht="33" customHeight="1" s="50">
+    <row r="36" ht="33" customHeight="1" s="52">
       <c r="A36" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3495,7 +3484,7 @@
       </c>
       <c r="J36" s="70" t="n"/>
     </row>
-    <row r="37" ht="33" customHeight="1" s="50">
+    <row r="37" ht="33" customHeight="1" s="52">
       <c r="A37" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3539,7 +3528,7 @@
       </c>
       <c r="J37" s="70" t="n"/>
     </row>
-    <row r="38" ht="76.5" customHeight="1" s="50">
+    <row r="38" ht="76.5" customHeight="1" s="52">
       <c r="A38" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3583,7 +3572,7 @@
       </c>
       <c r="J38" s="70" t="n"/>
     </row>
-    <row r="39" ht="33" customHeight="1" s="50">
+    <row r="39" ht="33" customHeight="1" s="52">
       <c r="A39" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3623,7 +3612,7 @@
       </c>
       <c r="J39" s="70" t="n"/>
     </row>
-    <row r="40" ht="192.5" customHeight="1" s="50">
+    <row r="40" ht="192.5" customHeight="1" s="52">
       <c r="A40" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3672,7 +3661,7 @@
       </c>
       <c r="J40" s="70" t="n"/>
     </row>
-    <row r="41" ht="47.5" customHeight="1" s="50">
+    <row r="41" ht="47.5" customHeight="1" s="52">
       <c r="A41" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3714,7 +3703,7 @@
       </c>
       <c r="J41" s="70" t="n"/>
     </row>
-    <row r="42" ht="47.5" customHeight="1" s="50">
+    <row r="42" ht="47.5" customHeight="1" s="52">
       <c r="A42" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3756,7 +3745,7 @@
       </c>
       <c r="J42" s="70" t="n"/>
     </row>
-    <row r="43" ht="47.5" customHeight="1" s="50">
+    <row r="43" ht="47.5" customHeight="1" s="52">
       <c r="A43" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3798,7 +3787,7 @@
       </c>
       <c r="J43" s="70" t="n"/>
     </row>
-    <row r="44" ht="47.5" customHeight="1" s="50">
+    <row r="44" ht="47.5" customHeight="1" s="52">
       <c r="A44" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3840,7 +3829,7 @@
       </c>
       <c r="J44" s="70" t="n"/>
     </row>
-    <row r="45" ht="62" customHeight="1" s="50">
+    <row r="45" ht="62" customHeight="1" s="52">
       <c r="A45" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3884,7 +3873,7 @@
       </c>
       <c r="J45" s="70" t="n"/>
     </row>
-    <row r="46" ht="76.5" customHeight="1" s="50">
+    <row r="46" ht="76.5" customHeight="1" s="52">
       <c r="A46" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3928,7 +3917,7 @@
       </c>
       <c r="J46" s="70" t="n"/>
     </row>
-    <row r="47" ht="47.5" customHeight="1" s="50">
+    <row r="47" ht="47.5" customHeight="1" s="52">
       <c r="A47" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3972,7 +3961,7 @@
       </c>
       <c r="J47" s="70" t="n"/>
     </row>
-    <row r="48" ht="149" customHeight="1" s="50">
+    <row r="48" ht="149" customHeight="1" s="52">
       <c r="A48" s="94" t="n">
         <v>46315</v>
       </c>
@@ -4019,7 +4008,7 @@
       </c>
       <c r="J48" s="70" t="n"/>
     </row>
-    <row r="49" ht="47.5" customHeight="1" s="50">
+    <row r="49" ht="47.5" customHeight="1" s="52">
       <c r="A49" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4061,7 +4050,7 @@
       </c>
       <c r="J49" s="70" t="n"/>
     </row>
-    <row r="50" ht="47.5" customHeight="1" s="50">
+    <row r="50" ht="47.5" customHeight="1" s="52">
       <c r="A50" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4103,7 +4092,7 @@
       </c>
       <c r="J50" s="70" t="n"/>
     </row>
-    <row r="51" ht="62" customHeight="1" s="50">
+    <row r="51" ht="62" customHeight="1" s="52">
       <c r="A51" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4147,7 +4136,7 @@
       </c>
       <c r="J51" s="70" t="n"/>
     </row>
-    <row r="52" ht="76.5" customHeight="1" s="50">
+    <row r="52" ht="76.5" customHeight="1" s="52">
       <c r="A52" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4191,7 +4180,7 @@
       </c>
       <c r="J52" s="70" t="n"/>
     </row>
-    <row r="53" ht="178" customHeight="1" s="50">
+    <row r="53" ht="178" customHeight="1" s="52">
       <c r="A53" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4239,7 +4228,7 @@
       </c>
       <c r="J53" s="70" t="n"/>
     </row>
-    <row r="54" ht="47.5" customHeight="1" s="50">
+    <row r="54" ht="47.5" customHeight="1" s="52">
       <c r="A54" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4281,7 +4270,7 @@
       </c>
       <c r="J54" s="70" t="n"/>
     </row>
-    <row r="55" ht="47.5" customHeight="1" s="50">
+    <row r="55" ht="47.5" customHeight="1" s="52">
       <c r="A55" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4323,7 +4312,7 @@
       </c>
       <c r="J55" s="70" t="n"/>
     </row>
-    <row r="56" ht="47.5" customHeight="1" s="50">
+    <row r="56" ht="47.5" customHeight="1" s="52">
       <c r="A56" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4365,7 +4354,7 @@
       </c>
       <c r="J56" s="70" t="n"/>
     </row>
-    <row r="57" ht="62" customHeight="1" s="50">
+    <row r="57" ht="62" customHeight="1" s="52">
       <c r="A57" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4409,7 +4398,7 @@
       </c>
       <c r="J57" s="70" t="n"/>
     </row>
-    <row r="58" ht="76.5" customHeight="1" s="50">
+    <row r="58" ht="76.5" customHeight="1" s="52">
       <c r="A58" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4453,7 +4442,7 @@
       </c>
       <c r="J58" s="70" t="n"/>
     </row>
-    <row r="59" ht="47.5" customHeight="1" s="50">
+    <row r="59" ht="47.5" customHeight="1" s="52">
       <c r="A59" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4493,7 +4482,7 @@
       </c>
       <c r="J59" s="70" t="n"/>
     </row>
-    <row r="60" ht="62" customHeight="1" s="50">
+    <row r="60" ht="62" customHeight="1" s="52">
       <c r="A60" s="94" t="n">
         <v>46318</v>
       </c>
@@ -4537,7 +4526,7 @@
       </c>
       <c r="J60" s="70" t="n"/>
     </row>
-    <row r="61" ht="62" customHeight="1" s="50">
+    <row r="61" ht="62" customHeight="1" s="52">
       <c r="A61" s="94" t="n">
         <v>46318</v>
       </c>
@@ -4581,7 +4570,7 @@
       </c>
       <c r="J61" s="70" t="n"/>
     </row>
-    <row r="62" ht="33" customHeight="1" s="50">
+    <row r="62" ht="33" customHeight="1" s="52">
       <c r="A62" s="94" t="n">
         <v>46318</v>
       </c>
@@ -4621,7 +4610,7 @@
       </c>
       <c r="J62" s="70" t="n"/>
     </row>
-    <row r="63" ht="33" customHeight="1" s="50">
+    <row r="63" ht="33" customHeight="1" s="52">
       <c r="A63" s="94" t="n">
         <v>46318</v>
       </c>
@@ -4665,7 +4654,7 @@
       </c>
       <c r="J63" s="70" t="n"/>
     </row>
-    <row r="64" ht="33" customHeight="1" s="50">
+    <row r="64" ht="33" customHeight="1" s="52">
       <c r="A64" s="94" t="n">
         <v>46319</v>
       </c>
@@ -4709,14 +4698,14 @@
       </c>
       <c r="J64" s="70" t="n"/>
     </row>
-    <row r="65" ht="22" customHeight="1" s="50">
+    <row r="65" ht="22" customHeight="1" s="52">
       <c r="A65" s="68" t="inlineStr">
         <is>
           <t>SEMANA  26/10 a 01/11</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="62" customHeight="1" s="50">
+    <row r="66" ht="62" customHeight="1" s="52">
       <c r="A66" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4760,7 +4749,7 @@
       </c>
       <c r="J66" s="70" t="n"/>
     </row>
-    <row r="67" ht="33" customHeight="1" s="50">
+    <row r="67" ht="33" customHeight="1" s="52">
       <c r="A67" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4804,7 +4793,7 @@
       </c>
       <c r="J67" s="70" t="n"/>
     </row>
-    <row r="68" ht="33" customHeight="1" s="50">
+    <row r="68" ht="33" customHeight="1" s="52">
       <c r="A68" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4848,7 +4837,7 @@
       </c>
       <c r="J68" s="70" t="n"/>
     </row>
-    <row r="69" ht="33" customHeight="1" s="50">
+    <row r="69" ht="33" customHeight="1" s="52">
       <c r="A69" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4892,7 +4881,7 @@
       </c>
       <c r="J69" s="70" t="n"/>
     </row>
-    <row r="70" ht="207" customHeight="1" s="50">
+    <row r="70" ht="207" customHeight="1" s="52">
       <c r="A70" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4941,7 +4930,7 @@
       </c>
       <c r="J70" s="70" t="n"/>
     </row>
-    <row r="71" ht="47.5" customHeight="1" s="50">
+    <row r="71" ht="47.5" customHeight="1" s="52">
       <c r="A71" s="94" t="n">
         <v>46322</v>
       </c>
@@ -4983,7 +4972,7 @@
       </c>
       <c r="J71" s="70" t="n"/>
     </row>
-    <row r="72" ht="47.5" customHeight="1" s="50">
+    <row r="72" ht="47.5" customHeight="1" s="52">
       <c r="A72" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5025,7 +5014,7 @@
       </c>
       <c r="J72" s="70" t="n"/>
     </row>
-    <row r="73" ht="47.5" customHeight="1" s="50">
+    <row r="73" ht="47.5" customHeight="1" s="52">
       <c r="A73" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5067,7 +5056,7 @@
       </c>
       <c r="J73" s="70" t="n"/>
     </row>
-    <row r="74" ht="47.5" customHeight="1" s="50">
+    <row r="74" ht="47.5" customHeight="1" s="52">
       <c r="A74" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5109,7 +5098,7 @@
       </c>
       <c r="J74" s="70" t="n"/>
     </row>
-    <row r="75" ht="62" customHeight="1" s="50">
+    <row r="75" ht="62" customHeight="1" s="52">
       <c r="A75" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5153,7 +5142,7 @@
       </c>
       <c r="J75" s="70" t="n"/>
     </row>
-    <row r="76" ht="76.5" customHeight="1" s="50">
+    <row r="76" ht="76.5" customHeight="1" s="52">
       <c r="A76" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5197,7 +5186,7 @@
       </c>
       <c r="J76" s="70" t="n"/>
     </row>
-    <row r="77" ht="33" customHeight="1" s="50">
+    <row r="77" ht="33" customHeight="1" s="52">
       <c r="A77" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5241,7 +5230,7 @@
       </c>
       <c r="J77" s="70" t="n"/>
     </row>
-    <row r="78" ht="149" customHeight="1" s="50">
+    <row r="78" ht="149" customHeight="1" s="52">
       <c r="A78" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5288,7 +5277,7 @@
       </c>
       <c r="J78" s="70" t="n"/>
     </row>
-    <row r="79" ht="47.5" customHeight="1" s="50">
+    <row r="79" ht="47.5" customHeight="1" s="52">
       <c r="A79" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5330,7 +5319,7 @@
       </c>
       <c r="J79" s="70" t="n"/>
     </row>
-    <row r="80" ht="47.5" customHeight="1" s="50">
+    <row r="80" ht="47.5" customHeight="1" s="52">
       <c r="A80" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5372,7 +5361,7 @@
       </c>
       <c r="J80" s="70" t="n"/>
     </row>
-    <row r="81" ht="62" customHeight="1" s="50">
+    <row r="81" ht="62" customHeight="1" s="52">
       <c r="A81" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5416,7 +5405,7 @@
       </c>
       <c r="J81" s="70" t="n"/>
     </row>
-    <row r="82" ht="76.5" customHeight="1" s="50">
+    <row r="82" ht="76.5" customHeight="1" s="52">
       <c r="A82" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5460,7 +5449,7 @@
       </c>
       <c r="J82" s="70" t="n"/>
     </row>
-    <row r="83" ht="47.5" customHeight="1" s="50">
+    <row r="83" ht="47.5" customHeight="1" s="52">
       <c r="A83" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5504,7 +5493,7 @@
       </c>
       <c r="J83" s="70" t="n"/>
     </row>
-    <row r="84" ht="76.5" customHeight="1" s="50">
+    <row r="84" ht="76.5" customHeight="1" s="52">
       <c r="A84" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5548,7 +5537,7 @@
       </c>
       <c r="J84" s="70" t="n"/>
     </row>
-    <row r="85" ht="76.5" customHeight="1" s="50">
+    <row r="85" ht="76.5" customHeight="1" s="52">
       <c r="A85" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5592,7 +5581,7 @@
       </c>
       <c r="J85" s="70" t="n"/>
     </row>
-    <row r="86" ht="178" customHeight="1" s="50">
+    <row r="86" ht="178" customHeight="1" s="52">
       <c r="A86" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5640,7 +5629,7 @@
       </c>
       <c r="J86" s="70" t="n"/>
     </row>
-    <row r="87" ht="47.5" customHeight="1" s="50">
+    <row r="87" ht="47.5" customHeight="1" s="52">
       <c r="A87" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5682,7 +5671,7 @@
       </c>
       <c r="J87" s="70" t="n"/>
     </row>
-    <row r="88" ht="47.5" customHeight="1" s="50">
+    <row r="88" ht="47.5" customHeight="1" s="52">
       <c r="A88" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5724,7 +5713,7 @@
       </c>
       <c r="J88" s="70" t="n"/>
     </row>
-    <row r="89" ht="47.5" customHeight="1" s="50">
+    <row r="89" ht="47.5" customHeight="1" s="52">
       <c r="A89" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5766,7 +5755,7 @@
       </c>
       <c r="J89" s="70" t="n"/>
     </row>
-    <row r="90" ht="62" customHeight="1" s="50">
+    <row r="90" ht="62" customHeight="1" s="52">
       <c r="A90" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5810,7 +5799,7 @@
       </c>
       <c r="J90" s="70" t="n"/>
     </row>
-    <row r="91" ht="76.5" customHeight="1" s="50">
+    <row r="91" ht="76.5" customHeight="1" s="52">
       <c r="A91" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5854,7 +5843,7 @@
       </c>
       <c r="J91" s="70" t="n"/>
     </row>
-    <row r="92" ht="76.5" customHeight="1" s="50">
+    <row r="92" ht="76.5" customHeight="1" s="52">
       <c r="A92" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5898,7 +5887,7 @@
       </c>
       <c r="J92" s="70" t="n"/>
     </row>
-    <row r="93" ht="76.5" customHeight="1" s="50">
+    <row r="93" ht="76.5" customHeight="1" s="52">
       <c r="A93" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5942,7 +5931,7 @@
       </c>
       <c r="J93" s="70" t="n"/>
     </row>
-    <row r="94" ht="62" customHeight="1" s="50">
+    <row r="94" ht="62" customHeight="1" s="52">
       <c r="A94" s="94" t="n">
         <v>46325</v>
       </c>
@@ -5986,7 +5975,7 @@
       </c>
       <c r="J94" s="70" t="n"/>
     </row>
-    <row r="95" ht="76.5" customHeight="1" s="50">
+    <row r="95" ht="76.5" customHeight="1" s="52">
       <c r="A95" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6030,7 +6019,7 @@
       </c>
       <c r="J95" s="70" t="n"/>
     </row>
-    <row r="96" ht="76.5" customHeight="1" s="50">
+    <row r="96" ht="76.5" customHeight="1" s="52">
       <c r="A96" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6074,7 +6063,7 @@
       </c>
       <c r="J96" s="70" t="n"/>
     </row>
-    <row r="97" ht="76.5" customHeight="1" s="50">
+    <row r="97" ht="76.5" customHeight="1" s="52">
       <c r="A97" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6118,7 +6107,7 @@
       </c>
       <c r="J97" s="70" t="n"/>
     </row>
-    <row r="98" ht="33" customHeight="1" s="50">
+    <row r="98" ht="33" customHeight="1" s="52">
       <c r="A98" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6162,14 +6151,14 @@
       </c>
       <c r="J98" s="70" t="n"/>
     </row>
-    <row r="99" ht="22" customHeight="1" s="50">
+    <row r="99" ht="22" customHeight="1" s="52">
       <c r="A99" s="68" t="inlineStr">
         <is>
           <t>SEMANA  02/11 a 08/11</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="62" customHeight="1" s="50">
+    <row r="100" ht="62" customHeight="1" s="52">
       <c r="A100" s="94" t="n">
         <v>46328</v>
       </c>
@@ -6213,7 +6202,7 @@
       </c>
       <c r="J100" s="70" t="n"/>
     </row>
-    <row r="101" ht="33" customHeight="1" s="50">
+    <row r="101" ht="33" customHeight="1" s="52">
       <c r="A101" s="94" t="n">
         <v>46328</v>
       </c>
@@ -6257,7 +6246,7 @@
       </c>
       <c r="J101" s="70" t="n"/>
     </row>
-    <row r="102" ht="33" customHeight="1" s="50">
+    <row r="102" ht="33" customHeight="1" s="52">
       <c r="A102" s="94" t="n">
         <v>46328</v>
       </c>
@@ -6301,7 +6290,7 @@
       </c>
       <c r="J102" s="70" t="n"/>
     </row>
-    <row r="103" ht="192.5" customHeight="1" s="50">
+    <row r="103" ht="192.5" customHeight="1" s="52">
       <c r="A103" s="94" t="n">
         <v>46328</v>
       </c>
@@ -6350,7 +6339,7 @@
       </c>
       <c r="J103" s="70" t="n"/>
     </row>
-    <row r="104" ht="47.5" customHeight="1" s="50">
+    <row r="104" ht="47.5" customHeight="1" s="52">
       <c r="A104" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6392,7 +6381,7 @@
       </c>
       <c r="J104" s="70" t="n"/>
     </row>
-    <row r="105" ht="47.5" customHeight="1" s="50">
+    <row r="105" ht="47.5" customHeight="1" s="52">
       <c r="A105" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6434,7 +6423,7 @@
       </c>
       <c r="J105" s="70" t="n"/>
     </row>
-    <row r="106" ht="47.5" customHeight="1" s="50">
+    <row r="106" ht="47.5" customHeight="1" s="52">
       <c r="A106" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6476,7 +6465,7 @@
       </c>
       <c r="J106" s="70" t="n"/>
     </row>
-    <row r="107" ht="47.5" customHeight="1" s="50">
+    <row r="107" ht="47.5" customHeight="1" s="52">
       <c r="A107" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6518,7 +6507,7 @@
       </c>
       <c r="J107" s="70" t="n"/>
     </row>
-    <row r="108" ht="62" customHeight="1" s="50">
+    <row r="108" ht="62" customHeight="1" s="52">
       <c r="A108" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6562,7 +6551,7 @@
       </c>
       <c r="J108" s="70" t="n"/>
     </row>
-    <row r="109" ht="76.5" customHeight="1" s="50">
+    <row r="109" ht="76.5" customHeight="1" s="52">
       <c r="A109" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6606,7 +6595,7 @@
       </c>
       <c r="J109" s="70" t="n"/>
     </row>
-    <row r="110" ht="30" customHeight="1" s="50">
+    <row r="110" ht="30" customHeight="1" s="52">
       <c r="A110" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6650,7 +6639,7 @@
       </c>
       <c r="J110" s="70" t="n"/>
     </row>
-    <row r="111" ht="134.5" customHeight="1" s="50">
+    <row r="111" ht="134.5" customHeight="1" s="52">
       <c r="A111" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6697,7 +6686,7 @@
       </c>
       <c r="J111" s="70" t="n"/>
     </row>
-    <row r="112" ht="47.5" customHeight="1" s="50">
+    <row r="112" ht="47.5" customHeight="1" s="52">
       <c r="A112" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6739,7 +6728,7 @@
       </c>
       <c r="J112" s="70" t="n"/>
     </row>
-    <row r="113" ht="47.5" customHeight="1" s="50">
+    <row r="113" ht="47.5" customHeight="1" s="52">
       <c r="A113" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6781,7 +6770,7 @@
       </c>
       <c r="J113" s="70" t="n"/>
     </row>
-    <row r="114" ht="62" customHeight="1" s="50">
+    <row r="114" ht="62" customHeight="1" s="52">
       <c r="A114" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6825,7 +6814,7 @@
       </c>
       <c r="J114" s="70" t="n"/>
     </row>
-    <row r="115" ht="76.5" customHeight="1" s="50">
+    <row r="115" ht="76.5" customHeight="1" s="52">
       <c r="A115" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6869,7 +6858,7 @@
       </c>
       <c r="J115" s="70" t="n"/>
     </row>
-    <row r="116" ht="91" customHeight="1" s="50">
+    <row r="116" ht="91" customHeight="1" s="52">
       <c r="A116" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6913,7 +6902,7 @@
       </c>
       <c r="J116" s="70" t="n"/>
     </row>
-    <row r="117" ht="76.5" customHeight="1" s="50">
+    <row r="117" ht="76.5" customHeight="1" s="52">
       <c r="A117" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6957,7 +6946,7 @@
       </c>
       <c r="J117" s="70" t="n"/>
     </row>
-    <row r="118" ht="149" customHeight="1" s="50">
+    <row r="118" ht="149" customHeight="1" s="52">
       <c r="A118" s="94" t="n">
         <v>46330</v>
       </c>
@@ -7005,7 +6994,7 @@
       </c>
       <c r="J118" s="70" t="n"/>
     </row>
-    <row r="119" ht="47.5" customHeight="1" s="50">
+    <row r="119" ht="47.5" customHeight="1" s="52">
       <c r="A119" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7047,7 +7036,7 @@
       </c>
       <c r="J119" s="70" t="n"/>
     </row>
-    <row r="120" ht="47.5" customHeight="1" s="50">
+    <row r="120" ht="47.5" customHeight="1" s="52">
       <c r="A120" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7089,7 +7078,7 @@
       </c>
       <c r="J120" s="70" t="n"/>
     </row>
-    <row r="121" ht="47.5" customHeight="1" s="50">
+    <row r="121" ht="47.5" customHeight="1" s="52">
       <c r="A121" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7131,7 +7120,7 @@
       </c>
       <c r="J121" s="70" t="n"/>
     </row>
-    <row r="122" ht="62" customHeight="1" s="50">
+    <row r="122" ht="62" customHeight="1" s="52">
       <c r="A122" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7175,7 +7164,7 @@
       </c>
       <c r="J122" s="70" t="n"/>
     </row>
-    <row r="123" ht="76.5" customHeight="1" s="50">
+    <row r="123" ht="76.5" customHeight="1" s="52">
       <c r="A123" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7219,7 +7208,7 @@
       </c>
       <c r="J123" s="70" t="n"/>
     </row>
-    <row r="124" ht="62" customHeight="1" s="50">
+    <row r="124" ht="62" customHeight="1" s="52">
       <c r="A124" s="94" t="n">
         <v>46332</v>
       </c>
@@ -7263,7 +7252,7 @@
       </c>
       <c r="J124" s="70" t="n"/>
     </row>
-    <row r="125" ht="33" customHeight="1" s="50">
+    <row r="125" ht="33" customHeight="1" s="52">
       <c r="A125" s="94" t="n">
         <v>46332</v>
       </c>
@@ -7307,7 +7296,7 @@
       </c>
       <c r="J125" s="70" t="n"/>
     </row>
-    <row r="126" ht="33" customHeight="1" s="50">
+    <row r="126" ht="33" customHeight="1" s="52">
       <c r="A126" s="94" t="n">
         <v>46332</v>
       </c>
@@ -7351,14 +7340,14 @@
       </c>
       <c r="J126" s="70" t="n"/>
     </row>
-    <row r="127" ht="22" customHeight="1" s="50">
+    <row r="127" ht="22" customHeight="1" s="52">
       <c r="A127" s="68" t="inlineStr">
         <is>
           <t>SEMANA  09/11 a 15/11</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="62" customHeight="1" s="50">
+    <row r="128" ht="62" customHeight="1" s="52">
       <c r="A128" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7402,7 +7391,7 @@
       </c>
       <c r="J128" s="70" t="n"/>
     </row>
-    <row r="129" ht="33" customHeight="1" s="50">
+    <row r="129" ht="33" customHeight="1" s="52">
       <c r="A129" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7446,7 +7435,7 @@
       </c>
       <c r="J129" s="70" t="n"/>
     </row>
-    <row r="130" ht="33" customHeight="1" s="50">
+    <row r="130" ht="33" customHeight="1" s="52">
       <c r="A130" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7490,7 +7479,7 @@
       </c>
       <c r="J130" s="70" t="n"/>
     </row>
-    <row r="131" ht="33" customHeight="1" s="50">
+    <row r="131" ht="62" customHeight="1" s="52">
       <c r="A131" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7516,7 +7505,7 @@
       </c>
       <c r="F131" s="70" t="inlineStr">
         <is>
-          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real.</t>
+          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real. Valoramos también la automatización del envío (objetivo de Joel: cientos de correos a la semana): Google Workspace, herramienta de envíos con calentamiento y qué se puede delegar.</t>
         </is>
       </c>
       <c r="G131" s="70" t="inlineStr">
@@ -7534,7 +7523,7 @@
       </c>
       <c r="J131" s="70" t="n"/>
     </row>
-    <row r="132" ht="134.5" customHeight="1" s="50">
+    <row r="132" ht="134.5" customHeight="1" s="52">
       <c r="A132" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7581,7 +7570,7 @@
       </c>
       <c r="J132" s="70" t="n"/>
     </row>
-    <row r="133" ht="47.5" customHeight="1" s="50">
+    <row r="133" ht="47.5" customHeight="1" s="52">
       <c r="A133" s="94" t="n">
         <v>46336</v>
       </c>
@@ -7623,7 +7612,7 @@
       </c>
       <c r="J133" s="70" t="n"/>
     </row>
-    <row r="134" ht="47.5" customHeight="1" s="50">
+    <row r="134" ht="47.5" customHeight="1" s="52">
       <c r="A134" s="94" t="n">
         <v>46336</v>
       </c>
@@ -7665,7 +7654,7 @@
       </c>
       <c r="J134" s="70" t="n"/>
     </row>
-    <row r="135" ht="62" customHeight="1" s="50">
+    <row r="135" ht="62" customHeight="1" s="52">
       <c r="A135" s="94" t="n">
         <v>46336</v>
       </c>
@@ -7709,7 +7698,7 @@
       </c>
       <c r="J135" s="70" t="n"/>
     </row>
-    <row r="136" ht="76.5" customHeight="1" s="50">
+    <row r="136" ht="76.5" customHeight="1" s="52">
       <c r="A136" s="94" t="n">
         <v>46336</v>
       </c>
@@ -7753,7 +7742,7 @@
       </c>
       <c r="J136" s="70" t="n"/>
     </row>
-    <row r="137" ht="62" customHeight="1" s="50">
+    <row r="137" ht="62" customHeight="1" s="52">
       <c r="A137" s="94" t="n">
         <v>46337</v>
       </c>
@@ -7797,7 +7786,7 @@
       </c>
       <c r="J137" s="70" t="n"/>
     </row>
-    <row r="138" ht="62" customHeight="1" s="50">
+    <row r="138" ht="62" customHeight="1" s="52">
       <c r="A138" s="94" t="n">
         <v>46338</v>
       </c>
@@ -7841,7 +7830,7 @@
       </c>
       <c r="J138" s="70" t="n"/>
     </row>
-    <row r="139" ht="62" customHeight="1" s="50">
+    <row r="139" ht="62" customHeight="1" s="52">
       <c r="A139" s="94" t="n">
         <v>46339</v>
       </c>
@@ -7885,7 +7874,7 @@
       </c>
       <c r="J139" s="70" t="n"/>
     </row>
-    <row r="140" ht="33" customHeight="1" s="50">
+    <row r="140" ht="33" customHeight="1" s="52">
       <c r="A140" s="94" t="n">
         <v>46339</v>
       </c>
@@ -7970,22 +7959,22 @@
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" style="50" min="1" max="1"/>
-    <col width="18" customWidth="1" style="50" min="2" max="2"/>
-    <col width="16" customWidth="1" style="50" min="3" max="5"/>
-    <col width="18" customWidth="1" style="50" min="6" max="6"/>
-    <col width="12" customWidth="1" style="50" min="7" max="7"/>
+    <col width="50" customWidth="1" style="52" min="1" max="1"/>
+    <col width="18" customWidth="1" style="52" min="2" max="2"/>
+    <col width="16" customWidth="1" style="52" min="3" max="5"/>
+    <col width="18" customWidth="1" style="52" min="6" max="6"/>
+    <col width="12" customWidth="1" style="52" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="50">
-      <c r="A1" s="53" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="52">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Plan de ventas — panel diario Always Up</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>Actualizar cada día de trabajo. Fecha de última actualización:</t>
         </is>
@@ -7995,14 +7984,14 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="50">
+    <row r="4" ht="16" customHeight="1" s="52">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>🔴 URGENTE — mirar esto primero</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" s="50">
+    <row r="5" ht="28" customHeight="1" s="52">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Qué</t>
@@ -8047,14 +8036,14 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="50">
+    <row r="10" ht="16" customHeight="1" s="52">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>🟠 OUTBOUND — lo que generas tú hoy</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1" s="50">
+    <row r="11" ht="28" customHeight="1" s="52">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Métrica</t>
@@ -8110,14 +8099,14 @@
       </c>
       <c r="C14" s="6" t="n"/>
     </row>
-    <row r="17" ht="16" customHeight="1" s="50">
+    <row r="17" ht="16" customHeight="1" s="52">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>🟢 INBOUND — lo que te llega a ti</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1" s="50">
+    <row r="18" ht="28" customHeight="1" s="52">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Qué</t>
@@ -8140,7 +8129,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1" s="50">
+    <row r="21" ht="16" customHeight="1" s="52">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>📊 PIPELINE — resumen por segmento (detalle completo en pestaña Dashboard)</t>
@@ -8347,37 +8336,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" style="50" min="1" max="1"/>
-    <col width="9" customWidth="1" style="50" min="2" max="2"/>
-    <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="26" customWidth="1" style="50" min="4" max="4"/>
-    <col width="15" customWidth="1" style="50" min="5" max="5"/>
-    <col width="30" customWidth="1" style="50" min="6" max="6"/>
-    <col width="34" customWidth="1" style="50" min="7" max="7"/>
-    <col width="78" customWidth="1" style="50" min="8" max="8"/>
-    <col width="44" customWidth="1" style="50" min="9" max="9"/>
-    <col width="14" customWidth="1" style="50" min="10" max="10"/>
-    <col width="36" customWidth="1" style="50" min="11" max="11"/>
+    <col width="11" customWidth="1" style="52" min="1" max="1"/>
+    <col width="9" customWidth="1" style="52" min="2" max="2"/>
+    <col width="14" customWidth="1" style="52" min="3" max="3"/>
+    <col width="26" customWidth="1" style="52" min="4" max="4"/>
+    <col width="15" customWidth="1" style="52" min="5" max="5"/>
+    <col width="30" customWidth="1" style="52" min="6" max="6"/>
+    <col width="34" customWidth="1" style="52" min="7" max="7"/>
+    <col width="78" customWidth="1" style="52" min="8" max="8"/>
+    <col width="44" customWidth="1" style="52" min="9" max="9"/>
+    <col width="14" customWidth="1" style="52" min="10" max="10"/>
+    <col width="36" customWidth="1" style="52" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" s="50">
+    <row r="1" ht="26" customHeight="1" s="52">
       <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Textos para copiar y pegar</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1" s="50">
+    <row r="2" ht="46" customHeight="1" s="52">
       <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Una fila por envío, ordenada por fecha. Filtra la columna Fecha para ver solo el día que toca. Copia Para, Asunto y Texto sin cambiar nada: la firma ya va incluida. Hora = a qué hora de Nueva York programar el envío (son las 09:30 en el país del club). Los textos están revisados por Claude: sin guiones largos, sin placeholders, saludo a una sola persona.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="50">
+    <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -8434,7 +8423,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="279.5" customHeight="1" s="50">
+    <row r="5" ht="279.5" customHeight="1" s="52">
       <c r="A5" s="95" t="n">
         <v>46309</v>
       </c>
@@ -8486,16 +8475,14 @@
           <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
-      <c r="J5" s="102" t="n">
-        <v>46309</v>
-      </c>
+      <c r="J5" s="78" t="n"/>
       <c r="K5" s="78" t="inlineStr">
         <is>
           <t>Rebota: avísame y busco otra dirección. Contesta: para la cadencia y mira 'Respuestas tipo' abajo.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="294" customHeight="1" s="50">
+    <row r="6" ht="294" customHeight="1" s="52">
       <c r="A6" s="95" t="n">
         <v>46309</v>
       </c>
@@ -8547,16 +8534,14 @@
           <t>En Mail: correo nuevo desde joel.martinez@alwaysup.es. Pega Para, Asunto y Texto tal cual (la firma ya va dentro). Sin adjuntos. Flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y la hora de la columna C. Una vez programado, no lo envíes a mano.</t>
         </is>
       </c>
-      <c r="J6" s="102" t="n">
-        <v>46309</v>
-      </c>
+      <c r="J6" s="78" t="n"/>
       <c r="K6" s="78" t="inlineStr">
         <is>
           <t>Rebota: avísame y busco otra dirección. Contesta: para la cadencia y mira 'Respuestas tipo' abajo.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="62" customHeight="1" s="50">
+    <row r="7" ht="62" customHeight="1" s="52">
       <c r="A7" s="96" t="n">
         <v>46310</v>
       </c>
@@ -8607,7 +8592,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="236" customHeight="1" s="50">
+    <row r="8" ht="236" customHeight="1" s="52">
       <c r="A8" s="95" t="n">
         <v>46310</v>
       </c>
@@ -8665,7 +8650,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="250.5" customHeight="1" s="50">
+    <row r="9" ht="250.5" customHeight="1" s="52">
       <c r="A9" s="95" t="n">
         <v>46310</v>
       </c>
@@ -8723,7 +8708,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="265" customHeight="1" s="50">
+    <row r="10" ht="265" customHeight="1" s="52">
       <c r="A10" s="95" t="n">
         <v>46310</v>
       </c>
@@ -8781,7 +8766,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="62" customHeight="1" s="50">
+    <row r="11" ht="62" customHeight="1" s="52">
       <c r="A11" s="96" t="n">
         <v>46311</v>
       </c>
@@ -8832,7 +8817,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1" s="50">
+    <row r="12" ht="62" customHeight="1" s="52">
       <c r="A12" s="96" t="n">
         <v>46311</v>
       </c>
@@ -8883,7 +8868,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="62" customHeight="1" s="50">
+    <row r="13" ht="62" customHeight="1" s="52">
       <c r="A13" s="96" t="n">
         <v>46314</v>
       </c>
@@ -8934,7 +8919,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="279.5" customHeight="1" s="50">
+    <row r="14" ht="279.5" customHeight="1" s="52">
       <c r="A14" s="95" t="n">
         <v>46315</v>
       </c>
@@ -8992,7 +8977,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="250.5" customHeight="1" s="50">
+    <row r="15" ht="250.5" customHeight="1" s="52">
       <c r="A15" s="97" t="n">
         <v>46315</v>
       </c>
@@ -9051,7 +9036,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="250.5" customHeight="1" s="50">
+    <row r="16" ht="250.5" customHeight="1" s="52">
       <c r="A16" s="97" t="n">
         <v>46315</v>
       </c>
@@ -9110,7 +9095,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="236" customHeight="1" s="50">
+    <row r="17" ht="236" customHeight="1" s="52">
       <c r="A17" s="95" t="n">
         <v>46315</v>
       </c>
@@ -9168,7 +9153,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="250.5" customHeight="1" s="50">
+    <row r="18" ht="250.5" customHeight="1" s="52">
       <c r="A18" s="97" t="n">
         <v>46316</v>
       </c>
@@ -9227,7 +9212,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="250.5" customHeight="1" s="50">
+    <row r="19" ht="250.5" customHeight="1" s="52">
       <c r="A19" s="97" t="n">
         <v>46316</v>
       </c>
@@ -9286,7 +9271,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="221.5" customHeight="1" s="50">
+    <row r="20" ht="221.5" customHeight="1" s="52">
       <c r="A20" s="97" t="n">
         <v>46317</v>
       </c>
@@ -9344,7 +9329,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="221.5" customHeight="1" s="50">
+    <row r="21" ht="221.5" customHeight="1" s="52">
       <c r="A21" s="97" t="n">
         <v>46317</v>
       </c>
@@ -9402,7 +9387,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="250.5" customHeight="1" s="50">
+    <row r="22" ht="250.5" customHeight="1" s="52">
       <c r="A22" s="97" t="n">
         <v>46317</v>
       </c>
@@ -9461,7 +9446,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="279.5" customHeight="1" s="50">
+    <row r="23" ht="279.5" customHeight="1" s="52">
       <c r="A23" s="97" t="n">
         <v>46322</v>
       </c>
@@ -9520,7 +9505,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="178" customHeight="1" s="50">
+    <row r="24" ht="178" customHeight="1" s="52">
       <c r="A24" s="98" t="n">
         <v>46322</v>
       </c>
@@ -9577,7 +9562,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="178" customHeight="1" s="50">
+    <row r="25" ht="178" customHeight="1" s="52">
       <c r="A25" s="98" t="n">
         <v>46322</v>
       </c>
@@ -9634,7 +9619,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="221.5" customHeight="1" s="50">
+    <row r="26" ht="221.5" customHeight="1" s="52">
       <c r="A26" s="97" t="n">
         <v>46322</v>
       </c>
@@ -9692,7 +9677,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1" s="50">
+    <row r="27" ht="60" customHeight="1" s="52">
       <c r="A27" s="96" t="n">
         <v>46323</v>
       </c>
@@ -9743,7 +9728,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="178" customHeight="1" s="50">
+    <row r="28" ht="178" customHeight="1" s="52">
       <c r="A28" s="98" t="n">
         <v>46323</v>
       </c>
@@ -9800,7 +9785,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1" s="50">
+    <row r="29" ht="60" customHeight="1" s="52">
       <c r="A29" s="96" t="n">
         <v>46323</v>
       </c>
@@ -9851,7 +9836,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="178" customHeight="1" s="50">
+    <row r="30" ht="178" customHeight="1" s="52">
       <c r="A30" s="98" t="n">
         <v>46323</v>
       </c>
@@ -9908,7 +9893,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1" s="50">
+    <row r="31" ht="60" customHeight="1" s="52">
       <c r="A31" s="96" t="n">
         <v>46324</v>
       </c>
@@ -9959,7 +9944,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="178" customHeight="1" s="50">
+    <row r="32" ht="178" customHeight="1" s="52">
       <c r="A32" s="98" t="n">
         <v>46324</v>
       </c>
@@ -10016,7 +10001,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="178" customHeight="1" s="50">
+    <row r="33" ht="178" customHeight="1" s="52">
       <c r="A33" s="98" t="n">
         <v>46324</v>
       </c>
@@ -10073,7 +10058,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1" s="50">
+    <row r="34" ht="60" customHeight="1" s="52">
       <c r="A34" s="96" t="n">
         <v>46324</v>
       </c>
@@ -10124,7 +10109,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="178" customHeight="1" s="50">
+    <row r="35" ht="178" customHeight="1" s="52">
       <c r="A35" s="98" t="n">
         <v>46324</v>
       </c>
@@ -10181,7 +10166,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1" s="50">
+    <row r="36" ht="60" customHeight="1" s="52">
       <c r="A36" s="96" t="n">
         <v>46325</v>
       </c>
@@ -10232,7 +10217,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1" s="50">
+    <row r="37" ht="60" customHeight="1" s="52">
       <c r="A37" s="96" t="n">
         <v>46325</v>
       </c>
@@ -10283,7 +10268,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1" s="50">
+    <row r="38" ht="60" customHeight="1" s="52">
       <c r="A38" s="96" t="n">
         <v>46325</v>
       </c>
@@ -10334,7 +10319,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="207" customHeight="1" s="50">
+    <row r="39" ht="207" customHeight="1" s="52">
       <c r="A39" s="98" t="n">
         <v>46329</v>
       </c>
@@ -10391,7 +10376,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="192.5" customHeight="1" s="50">
+    <row r="40" ht="192.5" customHeight="1" s="52">
       <c r="A40" s="99" t="n">
         <v>46329</v>
       </c>
@@ -10449,7 +10434,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="192.5" customHeight="1" s="50">
+    <row r="41" ht="192.5" customHeight="1" s="52">
       <c r="A41" s="99" t="n">
         <v>46329</v>
       </c>
@@ -10507,7 +10492,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="178" customHeight="1" s="50">
+    <row r="42" ht="178" customHeight="1" s="52">
       <c r="A42" s="98" t="n">
         <v>46329</v>
       </c>
@@ -10564,7 +10549,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="62" customHeight="1" s="50">
+    <row r="43" ht="62" customHeight="1" s="52">
       <c r="A43" s="96" t="n">
         <v>46330</v>
       </c>
@@ -10615,7 +10600,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="192.5" customHeight="1" s="50">
+    <row r="44" ht="192.5" customHeight="1" s="52">
       <c r="A44" s="99" t="n">
         <v>46330</v>
       </c>
@@ -10673,7 +10658,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="192.5" customHeight="1" s="50">
+    <row r="45" ht="192.5" customHeight="1" s="52">
       <c r="A45" s="99" t="n">
         <v>46330</v>
       </c>
@@ -10731,7 +10716,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1" s="50">
+    <row r="46" ht="60" customHeight="1" s="52">
       <c r="A46" s="96" t="n">
         <v>46330</v>
       </c>
@@ -10782,7 +10767,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="192.5" customHeight="1" s="50">
+    <row r="47" ht="192.5" customHeight="1" s="52">
       <c r="A47" s="99" t="n">
         <v>46331</v>
       </c>
@@ -10840,7 +10825,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="192.5" customHeight="1" s="50">
+    <row r="48" ht="192.5" customHeight="1" s="52">
       <c r="A48" s="99" t="n">
         <v>46331</v>
       </c>
@@ -10898,7 +10883,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="192.5" customHeight="1" s="50">
+    <row r="49" ht="192.5" customHeight="1" s="52">
       <c r="A49" s="99" t="n">
         <v>46331</v>
       </c>
@@ -10956,7 +10941,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="207" customHeight="1" s="50">
+    <row r="50" ht="207" customHeight="1" s="52">
       <c r="A50" s="99" t="n">
         <v>46336</v>
       </c>
@@ -11014,7 +10999,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="192.5" customHeight="1" s="50">
+    <row r="51" ht="192.5" customHeight="1" s="52">
       <c r="A51" s="99" t="n">
         <v>46336</v>
       </c>
@@ -11079,7 +11064,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="120" customHeight="1" s="50">
+    <row r="55" ht="120" customHeight="1" s="52">
       <c r="D55" s="62" t="inlineStr">
         <is>
           <t>Responde: quiere hablar</t>
@@ -11100,7 +11085,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="120" customHeight="1" s="50">
+    <row r="56" ht="120" customHeight="1" s="52">
       <c r="D56" s="62" t="inlineStr">
         <is>
           <t>Responde: pide información</t>
@@ -11121,7 +11106,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="120" customHeight="1" s="50">
+    <row r="57" ht="120" customHeight="1" s="52">
       <c r="D57" s="62" t="inlineStr">
         <is>
           <t>Responde: pregunta el precio</t>
@@ -11142,7 +11127,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="105.5" customHeight="1" s="50">
+    <row r="58" ht="105.5" customHeight="1" s="52">
       <c r="D58" s="62" t="inlineStr">
         <is>
           <t>Responde: ahora no</t>
@@ -11163,7 +11148,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="105.5" customHeight="1" s="50">
+    <row r="59" ht="105.5" customHeight="1" s="52">
       <c r="D59" s="62" t="inlineStr">
         <is>
           <t>Responde: no soy la persona</t>
@@ -11184,19 +11169,38 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="120" customHeight="1" s="50">
+    <row r="60" ht="134.5" customHeight="1" s="52">
       <c r="D60" s="62" t="inlineStr">
         <is>
+          <t>Daniel (MLS NEXT): follow-up por Instagram</t>
+        </is>
+      </c>
+      <c r="H60" s="63" t="inlineStr">
+        <is>
+          <t>Hola Daniel, ¿qué tal? Hace unas semanas hablamos de tu duda entre 1º y 2º de Bachillerato y de cómo encajaría con el proceso universitario en EEUU. Te escribo solo para saber si sigues con ganas de explorarlo.
+Si es así, mándame tu posición y, si tienes, un vídeo o enlace de algún partido de la MLS NEXT, y te cuento con calma qué opciones reales habría en tu caso. Cuanto antes lo veamos, más margen hay para decidir bien lo del curso.
+Y si ahora no es el momento, no pasa nada, dímelo y lo dejamos aquí.</t>
+        </is>
+      </c>
+      <c r="I60" s="63" t="inlineStr">
+        <is>
+          <t>Instagram. Un solo follow-up. Si no contesta en 7 días, pasa a Frío en el CRM. No pidas más datos en este mensaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="120" customHeight="1" s="52">
+      <c r="D61" s="62" t="inlineStr">
+        <is>
           <t>Pedir testimonio y presentaciones al club irlandés</t>
         </is>
       </c>
-      <c r="H60" s="63" t="inlineStr">
+      <c r="H61" s="63" t="inlineStr">
         <is>
           <t>Hi [nombre], hope you and the squad are doing well. I have a small favour to ask. We're building up Always Up and your league title story means a lot to us. Would you be happy to share two or three lines about what the experience did for the players, or even a short video message? And if you know any other clubs who would enjoy a trip like yours, an introduction from you would help us enormously. Thank you so much.
 Joel</t>
         </is>
       </c>
-      <c r="I60" s="63" t="inlineStr">
+      <c r="I61" s="63" t="inlineStr">
         <is>
           <t>Mándalo tú o Enrique, por WhatsApp. El nombre del contacto lo pones tú. Si dice que sí, pídele una foto del trofeo con los jugadores (con permiso del club).</t>
         </is>
@@ -11222,32 +11226,32 @@
   <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="50" min="1" max="1"/>
-    <col width="11" customWidth="1" style="50" min="2" max="2"/>
-    <col width="28" customWidth="1" style="50" min="3" max="3"/>
-    <col width="46" customWidth="1" style="50" min="4" max="4"/>
-    <col width="40" customWidth="1" style="50" min="5" max="5"/>
-    <col width="44" customWidth="1" style="50" min="6" max="6"/>
-    <col width="30" customWidth="1" style="50" min="7" max="7"/>
-    <col width="26" customWidth="1" style="50" min="8" max="8"/>
-    <col width="40" customWidth="1" style="50" min="9" max="9"/>
+    <col width="24" customWidth="1" style="52" min="1" max="1"/>
+    <col width="11" customWidth="1" style="52" min="2" max="2"/>
+    <col width="28" customWidth="1" style="52" min="3" max="3"/>
+    <col width="46" customWidth="1" style="52" min="4" max="4"/>
+    <col width="40" customWidth="1" style="52" min="5" max="5"/>
+    <col width="44" customWidth="1" style="52" min="6" max="6"/>
+    <col width="30" customWidth="1" style="52" min="7" max="7"/>
+    <col width="26" customWidth="1" style="52" min="8" max="8"/>
+    <col width="40" customWidth="1" style="52" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" s="50">
+    <row r="1" ht="26" customHeight="1" s="52">
       <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Plan de captación por servicio</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1" s="50">
+    <row r="2" ht="46" customHeight="1" s="52">
       <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Un único plan para conseguir clientes en todos los servicios, con prioridades. Con 10 a 20 horas semanales no se pueden empujar siete líneas a la vez: se trabajan a fondo las dos primeras, se cuida el resto con contactos cálidos y se documenta lo demás. Detalle completo en 02-sales/plan-captacion-todos-los-servicios.md.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="50">
+    <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Servicio</t>
@@ -11294,7 +11298,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="91" customHeight="1" s="50">
+    <row r="5" ht="91" customHeight="1" s="52">
       <c r="A5" s="62" t="inlineStr">
         <is>
           <t>Team Experience</t>
@@ -11345,7 +11349,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" s="50">
+    <row r="6" ht="60" customHeight="1" s="52">
       <c r="A6" s="62" t="inlineStr">
         <is>
           <t>Coach Experience</t>
@@ -11392,7 +11396,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="91" customHeight="1" s="50">
+    <row r="7" ht="91" customHeight="1" s="52">
       <c r="A7" s="62" t="inlineStr">
         <is>
           <t>Becas EEUU (Study &amp; Play USA)</t>
@@ -11442,7 +11446,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="50">
+    <row r="8" ht="60" customHeight="1" s="52">
       <c r="A8" s="62" t="inlineStr">
         <is>
           <t>Campus Internacional (ATM y Real Sociedad fuera de España)</t>
@@ -11489,7 +11493,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="50">
+    <row r="9" ht="60" customHeight="1" s="52">
       <c r="A9" s="62" t="inlineStr">
         <is>
           <t>International Program (Real Sociedad)</t>
@@ -11536,7 +11540,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" s="50">
+    <row r="10" ht="60" customHeight="1" s="52">
       <c r="A10" s="62" t="inlineStr">
         <is>
           <t>GEE (colegios privados en EEUU)</t>
@@ -11583,7 +11587,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="50">
+    <row r="11" ht="60" customHeight="1" s="52">
       <c r="A11" s="62" t="inlineStr">
         <is>
           <t>Oportunidades profesionales (Alemania y España) y Player Development</t>
@@ -11630,7 +11634,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1" s="50">
+    <row r="12" ht="62" customHeight="1" s="52">
       <c r="A12" s="62" t="inlineStr">
         <is>
           <t>Transversal: marca y canales</t>
@@ -11695,30 +11699,30 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="50" min="1" max="1"/>
-    <col width="36" customWidth="1" style="50" min="2" max="2"/>
-    <col width="56" customWidth="1" style="50" min="3" max="3"/>
-    <col width="18" customWidth="1" style="50" min="4" max="4"/>
-    <col width="28" customWidth="1" style="50" min="5" max="5"/>
-    <col width="12" customWidth="1" style="50" min="6" max="6"/>
-    <col width="46" customWidth="1" style="50" min="7" max="7"/>
+    <col width="24" customWidth="1" style="52" min="1" max="1"/>
+    <col width="36" customWidth="1" style="52" min="2" max="2"/>
+    <col width="56" customWidth="1" style="52" min="3" max="3"/>
+    <col width="18" customWidth="1" style="52" min="4" max="4"/>
+    <col width="28" customWidth="1" style="52" min="5" max="5"/>
+    <col width="12" customWidth="1" style="52" min="6" max="6"/>
+    <col width="46" customWidth="1" style="52" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" s="50">
+    <row r="1" ht="26" customHeight="1" s="52">
       <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Verificación de contactos (control de calidad)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="46" customHeight="1" s="50">
+    <row r="2" ht="46" customHeight="1" s="52">
       <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Qué he comprobado de cada dirección y con qué fiabilidad. Importante: ningún método permite saber al 100 % que un buzón existe hasta enviar. Por eso, tras cada envío miras los rebotes a los pocos minutos (tarea diaria del calendario). «Dominio recibe correo» significa que el dominio tiene servidor de correo activo.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="50">
+    <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Club</t>
@@ -11755,7 +11759,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="50">
+    <row r="5" ht="30" customHeight="1" s="52">
       <c r="A5" s="63" t="inlineStr">
         <is>
           <t>Home Farm FC</t>
@@ -11792,7 +11796,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="50">
+    <row r="6" ht="30" customHeight="1" s="52">
       <c r="A6" s="63" t="inlineStr">
         <is>
           <t>Hastings United</t>
@@ -11829,7 +11833,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" s="50">
+    <row r="7" ht="33" customHeight="1" s="52">
       <c r="A7" s="63" t="inlineStr">
         <is>
           <t>Søreide IL</t>
@@ -11866,7 +11870,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" s="50">
+    <row r="8" ht="33" customHeight="1" s="52">
       <c r="A8" s="63" t="inlineStr">
         <is>
           <t>Holbeach United</t>
@@ -11903,7 +11907,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="47.5" customHeight="1" s="50">
+    <row r="9" ht="47.5" customHeight="1" s="52">
       <c r="A9" s="63" t="inlineStr">
         <is>
           <t>Whitehaven AFC</t>
@@ -11940,7 +11944,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="50">
+    <row r="10" ht="30" customHeight="1" s="52">
       <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Maidstone United</t>
@@ -11977,7 +11981,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="50">
+    <row r="11" ht="30" customHeight="1" s="52">
       <c r="A11" s="63" t="inlineStr">
         <is>
           <t>IA Akranes</t>
@@ -12014,7 +12018,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="50">
+    <row r="12" ht="30" customHeight="1" s="52">
       <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Virtu Academy</t>
@@ -12051,7 +12055,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1" s="50">
+    <row r="13" ht="33" customHeight="1" s="52">
       <c r="A13" s="63" t="inlineStr">
         <is>
           <t>FC Porte d'Aquitaine</t>
@@ -12088,15 +12092,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" s="50">
-      <c r="A15" s="55" t="inlineStr">
+    <row r="15" ht="32" customHeight="1" s="52">
+      <c r="A15" s="57" t="inlineStr">
         <is>
           <t>Descartados tras investigar (13/10): Morecambe Hawks United (equipo local pequeño, no encaja), Team ALTI (sin datos fiables), Lower Ormond (existe en la lista de Semana Santa pero no encuentro contacto).</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1" s="50">
-      <c r="A16" s="55" t="inlineStr">
+    <row r="16" ht="32" customHeight="1" s="52">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam: club profesional con academia (Joep Breimer, jefe de desarrollo de la cantera). Perfil distinto, prioridad baja.</t>
         </is>
@@ -12121,46 +12125,46 @@
   <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="50" min="1" max="1"/>
-    <col width="12" customWidth="1" style="50" min="2" max="2"/>
-    <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="30" customWidth="1" style="50" min="4" max="4"/>
-    <col width="16" customWidth="1" style="50" min="5" max="5"/>
-    <col width="22" customWidth="1" style="50" min="6" max="7"/>
-    <col width="20" customWidth="1" style="50" min="8" max="8"/>
-    <col width="18" customWidth="1" style="50" min="9" max="9"/>
-    <col width="28" customWidth="1" style="50" min="10" max="10"/>
-    <col width="30" customWidth="1" style="50" min="11" max="11"/>
-    <col width="45" customWidth="1" style="50" min="12" max="12"/>
-    <col width="12" customWidth="1" style="50" min="13" max="13"/>
-    <col width="14" customWidth="1" style="50" min="14" max="14"/>
-    <col width="30" customWidth="1" style="50" min="15" max="15"/>
-    <col width="55" customWidth="1" style="50" min="16" max="16"/>
+    <col width="26" customWidth="1" style="52" min="1" max="1"/>
+    <col width="12" customWidth="1" style="52" min="2" max="2"/>
+    <col width="14" customWidth="1" style="52" min="3" max="3"/>
+    <col width="30" customWidth="1" style="52" min="4" max="4"/>
+    <col width="16" customWidth="1" style="52" min="5" max="5"/>
+    <col width="22" customWidth="1" style="52" min="6" max="7"/>
+    <col width="20" customWidth="1" style="52" min="8" max="8"/>
+    <col width="18" customWidth="1" style="52" min="9" max="9"/>
+    <col width="28" customWidth="1" style="52" min="10" max="10"/>
+    <col width="30" customWidth="1" style="52" min="11" max="11"/>
+    <col width="45" customWidth="1" style="52" min="12" max="12"/>
+    <col width="12" customWidth="1" style="52" min="13" max="13"/>
+    <col width="14" customWidth="1" style="52" min="14" max="14"/>
+    <col width="30" customWidth="1" style="52" min="15" max="15"/>
+    <col width="55" customWidth="1" style="52" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="50">
-      <c r="A1" s="53" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="52">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Segmento A — Clubes juveniles internacionales</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>Perfil Greystones/Homefarm: decide un entrenador o comité de club, ciclo de venta corto.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" s="50">
-      <c r="A3" s="56" t="inlineStr">
+    <row r="3" ht="60" customHeight="1" s="52">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Prioridad principal (ver plan-ventas-maestro.md sección 3). Estado: usar exactamente estos valores para que las fórmulas de la pestaña Hoy funcionen — Pendiente investigar / Listo para enviar / Enviado / Respondido / Llamada agendada / Llamada realizada / Cerrado / Perdido / En negociación / Solo info.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5" ht="28" customHeight="1" s="50">
+    <row r="5" ht="28" customHeight="1" s="52">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Club/Academia</t>
@@ -12242,7 +12246,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" s="50">
+    <row r="6" ht="60" customHeight="1" s="52">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Home Farm FC (chicas U13-U15)</t>
@@ -12327,7 +12331,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" s="50">
+    <row r="7" ht="60" customHeight="1" s="52">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Søreide IL</t>
@@ -12366,12 +12370,12 @@
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Enviado</t>
+          <t>Listo para enviar</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Follow-up 1 el 21/10/2026 en el mismo hilo (enviar a las 07:30 hora Nueva York). Textos en la hoja 'Textos para copiar'.</t>
+          <t>Enviar el 14/10/2026 a las 07:30 hora Nueva York. Textos en la hoja 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
@@ -12392,11 +12396,11 @@
 joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
         </is>
       </c>
-      <c r="M7" s="100" t="n">
-        <v>46309</v>
-      </c>
-      <c r="N7" s="100" t="n">
-        <v>46309</v>
+      <c r="M7" s="10" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>46308</v>
       </c>
       <c r="O7" s="9" t="inlineStr">
         <is>
@@ -12409,7 +12413,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="50">
+    <row r="8" ht="18" customHeight="1" s="52">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Maidstone United (Girls Development Centre)</t>
@@ -12490,7 +12494,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" s="50">
+    <row r="9" ht="18" customHeight="1" s="52">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Whitehaven AFC (Juniors Girls U13-U15)</t>
@@ -12567,7 +12571,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" s="50">
+    <row r="10" ht="18" customHeight="1" s="52">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Lower Ormond</t>
@@ -12612,7 +12616,7 @@
       <c r="N10" s="10" t="n"/>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
@@ -12621,7 +12625,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" s="50">
+    <row r="11" ht="18" customHeight="1" s="52">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Holbeach United</t>
@@ -12664,12 +12668,12 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Enviado</t>
+          <t>Listo para enviar</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Follow-up 1 el 21/10/2026 en el mismo hilo (enviar a las 07:30 hora Nueva York). Textos en la hoja 'Textos para copiar'.</t>
+          <t>Enviar el 14/10/2026 a las 07:30 hora Nueva York. Textos en la hoja 'Textos para copiar'.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -12690,15 +12694,11 @@
 joel.martinez@alwaysup.es | +1 (814) 329 1929 | alwaysup.es</t>
         </is>
       </c>
-      <c r="M11" s="100" t="n">
-        <v>46309</v>
-      </c>
-      <c r="N11" s="100" t="n">
-        <v>46309</v>
-      </c>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: contacto general real, falta nombre de decisor | Enviado a mano el 14/10/2026 (el envío programado con Apple Mail no salió).</t>
+          <t>Investigado 2026-08-29: contacto general real, falta nombre de decisor | Posible duplicado: 13/10 18:50, 14/10 04:41 y 14/10 ~08:30 (el último no localizado). No pedir disculpas salvo que lo mencionen.</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
@@ -12707,7 +12707,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" s="50">
+    <row r="12" ht="60" customHeight="1" s="52">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Hastings United (Girls Academy)</t>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" s="50">
+    <row r="13" ht="18" customHeight="1" s="52">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Morecambe Hawks</t>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" s="50">
+    <row r="14" ht="18" customHeight="1" s="52">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>IA Akranes</t>
@@ -12914,7 +12914,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" s="50">
+    <row r="15" ht="18" customHeight="1" s="52">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam</t>
@@ -12968,7 +12968,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1" s="50">
+    <row r="16" ht="18" customHeight="1" s="52">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Deportivo de la Coruña</t>
@@ -13022,7 +13022,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="90" customHeight="1" s="50">
+    <row r="17" ht="90" customHeight="1" s="52">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Leonardo Uren / equipo (Brasil) — posible partner, no solo cliente</t>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
+          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
@@ -13097,7 +13097,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="293" customHeight="1" s="50">
+    <row r="18" ht="293" customHeight="1" s="52">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Virtu Academy</t>
@@ -13170,7 +13170,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="332" customHeight="1" s="50">
+    <row r="19" ht="332" customHeight="1" s="52">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>FC Porte d'Aquitaine</t>
@@ -13303,44 +13303,44 @@
   <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" style="50" min="1" max="1"/>
-    <col width="18" customWidth="1" style="50" min="2" max="3"/>
-    <col width="34" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="18" customWidth="1" style="50" min="6" max="7"/>
-    <col width="26" customWidth="1" style="50" min="8" max="8"/>
-    <col width="28" customWidth="1" style="50" min="9" max="9"/>
-    <col width="26" customWidth="1" style="50" min="10" max="10"/>
-    <col width="40" customWidth="1" style="50" min="11" max="11"/>
-    <col width="12" customWidth="1" style="50" min="12" max="12"/>
-    <col width="14" customWidth="1" style="50" min="13" max="13"/>
-    <col width="36" customWidth="1" style="50" min="14" max="14"/>
-    <col width="55" customWidth="1" style="50" min="15" max="15"/>
+    <col width="30" customWidth="1" style="52" min="1" max="1"/>
+    <col width="18" customWidth="1" style="52" min="2" max="3"/>
+    <col width="34" customWidth="1" style="52" min="4" max="4"/>
+    <col width="20" customWidth="1" style="52" min="5" max="5"/>
+    <col width="18" customWidth="1" style="52" min="6" max="7"/>
+    <col width="26" customWidth="1" style="52" min="8" max="8"/>
+    <col width="28" customWidth="1" style="52" min="9" max="9"/>
+    <col width="26" customWidth="1" style="52" min="10" max="10"/>
+    <col width="40" customWidth="1" style="52" min="11" max="11"/>
+    <col width="12" customWidth="1" style="52" min="12" max="12"/>
+    <col width="14" customWidth="1" style="52" min="13" max="13"/>
+    <col width="36" customWidth="1" style="52" min="14" max="14"/>
+    <col width="55" customWidth="1" style="52" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="50">
-      <c r="A1" s="53" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="52">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Segmento B — Universidades y clubes de América</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>NCAA + clubes/academias EEUU. Incluye fútbol femenino universitario (segmento en crecimiento, menos competido).</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" s="50">
-      <c r="A3" s="56" t="inlineStr">
+    <row r="3" ht="60" customHeight="1" s="52">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>PRIORIDAD SECUNDARIA — ver plan-ventas-maestro.md sección 3. Mercado ya servido por competidores establecidos (Alandis Travel + Sevilla FC, WorldStrides...) y con ciclos de decisión institucionales largos. No forzar volumen aquí hasta tener 2-3 conversaciones reales avanzando en Segmento A.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5" ht="28" customHeight="1" s="50">
+    <row r="5" ht="28" customHeight="1" s="52">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Programa/Club</t>
@@ -13417,7 +13417,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1" s="50">
+    <row r="6" ht="56" customHeight="1" s="52">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ODP Louisiana</t>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1" s="50">
+    <row r="7" ht="56" customHeight="1" s="52">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Dallas Texans</t>
@@ -13519,7 +13519,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1" s="50">
+    <row r="8" ht="56" customHeight="1" s="52">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Charlotte SA</t>
@@ -13572,7 +13572,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1" s="50">
+    <row r="9" ht="56" customHeight="1" s="52">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Philadelphia Union Academy</t>
@@ -13625,7 +13625,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1" s="50">
+    <row r="10" ht="56" customHeight="1" s="52">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Seattle United</t>
@@ -13678,7 +13678,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1" s="50">
+    <row r="11" ht="56" customHeight="1" s="52">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>San Diego Surf</t>
@@ -13731,7 +13731,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1" s="50">
+    <row r="12" ht="56" customHeight="1" s="52">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>UNC Women's Soccer</t>
@@ -13784,7 +13784,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1" s="50">
+    <row r="13" ht="56" customHeight="1" s="52">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Programas NCAA D2/D3 sin partnership visible (por identificar)</t>
@@ -13857,42 +13857,42 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" style="50" min="1" max="1"/>
-    <col width="8" customWidth="1" style="50" min="2" max="2"/>
-    <col width="18" customWidth="1" style="50" min="3" max="3"/>
-    <col width="30" customWidth="1" style="50" min="4" max="4"/>
-    <col width="18" customWidth="1" style="50" min="5" max="5"/>
-    <col width="16" customWidth="1" style="50" min="6" max="6"/>
-    <col width="28" customWidth="1" style="50" min="7" max="7"/>
-    <col width="34" customWidth="1" style="50" min="8" max="8"/>
-    <col width="16" customWidth="1" style="50" min="9" max="9"/>
-    <col width="40" customWidth="1" style="50" min="10" max="10"/>
-    <col width="55" customWidth="1" style="50" min="11" max="11"/>
+    <col width="30" customWidth="1" style="52" min="1" max="1"/>
+    <col width="8" customWidth="1" style="52" min="2" max="2"/>
+    <col width="18" customWidth="1" style="52" min="3" max="3"/>
+    <col width="30" customWidth="1" style="52" min="4" max="4"/>
+    <col width="18" customWidth="1" style="52" min="5" max="5"/>
+    <col width="16" customWidth="1" style="52" min="6" max="6"/>
+    <col width="28" customWidth="1" style="52" min="7" max="7"/>
+    <col width="34" customWidth="1" style="52" min="8" max="8"/>
+    <col width="16" customWidth="1" style="52" min="9" max="9"/>
+    <col width="40" customWidth="1" style="52" min="10" max="10"/>
+    <col width="55" customWidth="1" style="52" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="50">
-      <c r="A1" s="53" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="52">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Segmento C — Becas deportivas (inbound Instagram)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>No es outreach frío — es inbound que ya llega solo. El trabajo es cualificar y cerrar mejor.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" s="50">
-      <c r="A3" s="56" t="inlineStr">
+    <row r="3" ht="60" customHeight="1" s="52">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>MIGRADO desde 01-clients/pipeline.md (tabla 'Embudo — seguimiento de leads inbound') el 2026-08-29 — esta pestaña sustituye esa tabla como fuente única de verdad para leads de becas. Etapa: usar Nuevo / Cualificado / Llamada agendada / Llamada realizada / Cerrado / Perdido para que las fórmulas de Hoy funcionen.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5" ht="28" customHeight="1" s="50">
+    <row r="5" ht="28" customHeight="1" s="52">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Nombre / contacto (IG)</t>
@@ -13949,7 +13949,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" s="50">
+    <row r="6" ht="42" customHeight="1" s="52">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Francisco Ferreira / francisco_7ferreira</t>
@@ -14006,7 +14006,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1" s="50">
+    <row r="7" ht="42" customHeight="1" s="52">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Bauti / bautimoransalzano</t>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1" s="50">
+    <row r="8" ht="42" customHeight="1" s="52">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Pavel Gomez / paixvi.b</t>
@@ -14108,7 +14108,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" s="50">
+    <row r="9" ht="42" customHeight="1" s="52">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Gonzalo Caro / gonzalocarocontreras</t>
@@ -14149,7 +14149,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1" s="50">
+    <row r="10" ht="42" customHeight="1" s="52">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Tania Coeto / tania_coeto</t>
@@ -14190,7 +14190,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1" s="50">
+    <row r="11" ht="42" customHeight="1" s="52">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Barbara Cuellar / bcshisha</t>
@@ -14247,7 +14247,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="75" customHeight="1" s="50">
+    <row r="12" ht="75" customHeight="1" s="52">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Omar Escamilla / omare815 — CONFIRMADO mismo lead que WhatsApp +52 1 81 3408 2672 (Gabriel y Rafael)</t>
@@ -14304,7 +14304,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1" s="50">
+    <row r="13" ht="42" customHeight="1" s="52">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Angelica Suarez Rivera / angelicamiami</t>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1" s="50">
+    <row r="14" ht="42" customHeight="1" s="52">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Ana Aida Uribe / aauribe</t>
@@ -14406,7 +14406,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1" s="50">
+    <row r="15" ht="42" customHeight="1" s="52">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Jeinz Alzate / jeinzalzate</t>
@@ -14459,7 +14459,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1" s="50">
+    <row r="16" ht="42" customHeight="1" s="52">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Anita / ani_0487</t>
@@ -14508,7 +14508,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1" s="50">
+    <row r="17" ht="42" customHeight="1" s="52">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Margarita Vanegas / margaritavanegasoficial</t>
@@ -14561,7 +14561,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1" s="50">
+    <row r="18" ht="42" customHeight="1" s="52">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Edwin Serrato / edwinserrato84</t>
@@ -14618,7 +14618,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1" s="50">
+    <row r="19" ht="42" customHeight="1" s="52">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Juan Roberto / juan_roberto_16</t>
@@ -14659,10 +14659,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" s="50">
+    <row r="20" ht="60" customHeight="1" s="52">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Daniel (apellido/@ de Instagram pendiente de confirmar)</t>
+          <t>Daniel / Instagram: Danny (confirmar @usuario exacto)</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Esperar respuesta a las 3 preguntas (posición / ubicación en España / club actual) — probablemente avanza rápido a Calendly, es un lead fuerte</t>
+          <t>Enviar follow-up el 14/10 (texto en Textos para copiar). Si no responde en 7 días: pasar a Frío.</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>Pregunta genuina sobre 1º vs 2º de Bachillerato y elegibilidad NCAA — no se improvisó respuesta, se remitió a la evaluación completa con el equipo especializado. Edad+plazo+nivel ya fuertes antes incluso de pedir vídeo.</t>
+          <t>Pregunta genuina sobre 1º vs 2º de Bachillerato y elegibilidad NCAA — no se improvisó respuesta, se remitió a la evaluación completa con el equipo especializado. Edad+plazo+nivel ya fuertes antes incluso de pedir vídeo. | 14/10: sin respuesta desde el 21/09 (3 semanas). Un solo follow-up.</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -33,10 +33,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -405,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -663,6 +664,9 @@
     </xf>
     <xf numFmtId="165" fontId="31" fillId="21" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2642,10 +2646,14 @@
       </c>
       <c r="I16" s="70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J16" s="70" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="J16" s="70" t="inlineStr">
+        <is>
+          <t>Enviado el 14/10</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="163.5" customHeight="1" s="52">
       <c r="A17" s="94" t="n">
@@ -2690,10 +2698,14 @@
       </c>
       <c r="I17" s="70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J17" s="70" t="n"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="J17" s="70" t="inlineStr">
+        <is>
+          <t>Programados los 3 (confirmar mañana a las 08:00)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="47.5" customHeight="1" s="52">
       <c r="A18" s="94" t="n">
@@ -12122,7 +12134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="52" min="1" max="1"/>
@@ -13243,46 +13255,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
   </sheetData>
   <autoFilter ref="A5:P17"/>
   <mergeCells count="3">
@@ -14697,13 +14669,11 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Enviar follow-up el 14/10 (texto en Textos para copiar). Si no responde en 7 días: pasar a Frío.</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
+          <t>Follow-up enviado el 14/10. Si no responde el 21/10: pasar a Frío y no insistir.</t>
+        </is>
+      </c>
+      <c r="I20" s="100" t="n">
+        <v>46309</v>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Textos para copiar'!$A$4:$K$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Segmento A - Clubes'!$A$5:$P$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Segmento B - America'!$A$5:$O$13</definedName>
@@ -36,8 +36,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -406,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -665,7 +665,10 @@
     <xf numFmtId="165" fontId="31" fillId="21" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1368,12 +1371,12 @@
     <row r="28" ht="47.5" customHeight="1" s="52">
       <c r="A28" s="62" t="inlineStr">
         <is>
-          <t>Recomendación</t>
+          <t>Calendly: no hace falta tocarlo</t>
         </is>
       </c>
       <c r="B28" s="63" t="inlineStr">
         <is>
-          <t>Dos agendas en Calendly: 'Europa' (martes 13:00 a 15:00 y miércoles 11:00 a 12:30) para 'Always Up Intro Call', y 'Américas' (lunes y jueves tarde, martes 17:00 a 19:00) para 'USA Scholarship Assessment'. Así un club nunca ve una hora de madrugada. Cambia también el nombre 'Assessment Call' para clubes: 'Assessment' es un término de becas.</t>
+          <t>Calendly enseña a cada persona los huecos en SU hora, y elige ella. Para familias de becas sirve tal cual. Para clubes, lo normal es proponer tú dos horarios concretos de esta tabla en el email de respuesta (más cómodo para ellos y sin herramienta). El enlace queda como alternativa.</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="52" min="1" max="1"/>
@@ -3009,7 +3012,7 @@
       </c>
       <c r="J24" s="70" t="n"/>
     </row>
-    <row r="25" ht="76.5" customHeight="1" s="52">
+    <row r="25" ht="62" customHeight="1" s="52">
       <c r="A25" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3030,21 +3033,17 @@
       </c>
       <c r="E25" s="62" t="inlineStr">
         <is>
-          <t>Ajustar Calendly por mercado (franjas distintas para clubes y familias)</t>
+          <t>Calentar el dominio: 2 o 3 correos reales más a gente de confianza (ya hiciste 3)</t>
         </is>
       </c>
       <c r="F25" s="70" t="inlineStr">
         <is>
-          <t>Mira la tabla de franjas en LEEME. Resumen: para clubes de Europa solo sirven Martes 13:00 a 15:00 y Miércoles 11:00 a 12:30 (hora NY). Para familias de América sirven Lunes y Jueves por la tarde. Pasos: crea el evento 'Always Up Intro Call' (20 min, Zoom) con la agenda Europa, y deja 'USA Scholarship Assessment' con la agenda Américas. Luego pásame el enlace de cada uno.</t>
-        </is>
-      </c>
-      <c r="G25" s="70" t="inlineStr">
-        <is>
-          <t>Calendly</t>
-        </is>
-      </c>
+          <t>Escribe desde alwaysup.es a 2 o 3 personas más (familia, amigos, conocidos con Gmail, Outlook o iCloud) un correo normal con una pregunta, y pídeles que respondan. Si caen en spam, que lo marquen como 'No es spam'. Es la forma más rápida de mejorar la reputación de un dominio nuevo.</t>
+        </is>
+      </c>
+      <c r="G25" s="70" t="inlineStr"/>
       <c r="H25" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I25" s="70" t="inlineStr">
         <is>
@@ -3053,7 +3052,7 @@
       </c>
       <c r="J25" s="70" t="n"/>
     </row>
-    <row r="26" ht="62" customHeight="1" s="52">
+    <row r="26" ht="76.5" customHeight="1" s="52">
       <c r="A26" s="94" t="n">
         <v>46310</v>
       </c>
@@ -3067,77 +3066,81 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D26" s="72" t="inlineStr">
-        <is>
-          <t>Transversal</t>
+      <c r="D26" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E26" s="62" t="inlineStr">
         <is>
-          <t>Calentar el dominio: 2 o 3 correos reales más a gente de confianza (ya hiciste 3)</t>
+          <t>LinkedIn: conectar con Georgia Townsend (Hastings United)</t>
         </is>
       </c>
       <c r="F26" s="70" t="inlineStr">
         <is>
-          <t>Escribe desde alwaysup.es a 2 o 3 personas más (familia, amigos, conocidos con Gmail, Outlook o iCloud) un correo normal con una pregunta, y pídeles que respondan. Si caen en spam, que lo marquen como 'No es spam'. Es la forma más rápida de mejorar la reputación de un dominio nuevo.</t>
-        </is>
-      </c>
-      <c r="G26" s="70" t="inlineStr"/>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Georgia, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+        </is>
+      </c>
+      <c r="G26" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
       <c r="H26" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J26" s="70" t="n"/>
+    </row>
+    <row r="27" ht="62" customHeight="1" s="52">
+      <c r="A27" s="94" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C27" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D27" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E27" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F27" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G27" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H27" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I26" s="70" t="inlineStr">
+      <c r="I27" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J26" s="70" t="n"/>
-    </row>
-    <row r="27" ht="76.5" customHeight="1" s="52">
-      <c r="A27" s="94" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B27" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C27" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D27" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E27" s="62" t="inlineStr">
-        <is>
-          <t>LinkedIn: conectar con Georgia Townsend (Hastings United)</t>
-        </is>
-      </c>
-      <c r="F27" s="70" t="inlineStr">
-        <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Georgia, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
-        </is>
-      </c>
-      <c r="G27" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H27" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I27" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J27" s="70" t="n"/>
     </row>
-    <row r="28" ht="62" customHeight="1" s="52">
+    <row r="28" ht="33" customHeight="1" s="52">
       <c r="A28" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3148,7 +3151,7 @@
       </c>
       <c r="C28" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D28" s="72" t="inlineStr">
@@ -3158,21 +3161,21 @@
       </c>
       <c r="E28" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Revisión semanal 1: qué ha pasado esta semana</t>
         </is>
       </c>
       <c r="F28" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Mira la hoja Hoy y anota respuestas, rebotes y llamadas. Pásame un resumen de tres líneas: yo ajusto el plan.</t>
         </is>
       </c>
       <c r="G28" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="H28" s="70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I28" s="70" t="inlineStr">
         <is>
@@ -3181,7 +3184,7 @@
       </c>
       <c r="J28" s="70" t="n"/>
     </row>
-    <row r="29" ht="33" customHeight="1" s="52">
+    <row r="29" ht="76.5" customHeight="1" s="52">
       <c r="A29" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3195,28 +3198,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D29" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D29" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E29" s="62" t="inlineStr">
         <is>
-          <t>Revisión semanal 1: qué ha pasado esta semana</t>
+          <t>LinkedIn: conectar con Callum Lawe (Holbeach United)</t>
         </is>
       </c>
       <c r="F29" s="70" t="inlineStr">
         <is>
-          <t>Mira la hoja Hoy y anota respuestas, rebotes y llamadas. Pásame un resumen de tres líneas: yo ajusto el plan.</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Callum, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G29" s="70" t="inlineStr">
         <is>
-          <t>Hoy</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H29" s="70" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I29" s="70" t="inlineStr">
         <is>
@@ -3246,12 +3249,12 @@
       </c>
       <c r="E30" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Callum Lawe (Holbeach United)</t>
+          <t>LinkedIn: conectar con Marius Engen (Søreide IL)</t>
         </is>
       </c>
       <c r="F30" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Callum, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Marius, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G30" s="70" t="inlineStr">
@@ -3269,7 +3272,7 @@
       </c>
       <c r="J30" s="70" t="n"/>
     </row>
-    <row r="31" ht="76.5" customHeight="1" s="52">
+    <row r="31" ht="33" customHeight="1" s="52">
       <c r="A31" s="94" t="n">
         <v>46311</v>
       </c>
@@ -3283,28 +3286,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D31" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D31" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E31" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Marius Engen (Søreide IL)</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F31" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Marius, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G31" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H31" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I31" s="70" t="inlineStr">
         <is>
@@ -3313,13 +3316,13 @@
       </c>
       <c r="J31" s="70" t="n"/>
     </row>
-    <row r="32" ht="33" customHeight="1" s="52">
+    <row r="32" ht="47.5" customHeight="1" s="52">
       <c r="A32" s="94" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B32" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="C32" s="71" t="inlineStr">
@@ -3327,88 +3330,88 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D32" s="72" t="inlineStr">
+      <c r="D32" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E32" s="62" t="inlineStr">
+        <is>
+          <t>Sesión de redes sociales y marca personal con Claude (30 a 60 min)</t>
+        </is>
+      </c>
+      <c r="F32" s="70" t="inlineStr">
+        <is>
+          <t>Objetivo: 10.000 seguidores antes de fin de 2026. Salir con un plan de contenido de 4 semanas. Hasta tener este plan no se publica nada. Sin fotos de menores identificables.</t>
+        </is>
+      </c>
+      <c r="G32" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
+      <c r="H32" s="70" t="n">
+        <v>60</v>
+      </c>
+      <c r="I32" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J32" s="70" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1" s="52">
+      <c r="A33" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  19/10 a 25/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="62" customHeight="1" s="52">
+      <c r="A34" s="94" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B34" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C34" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D34" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E32" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F32" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G32" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H32" s="70" t="n">
+      <c r="E34" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F34" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G34" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H34" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I32" s="70" t="inlineStr">
+      <c r="I34" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J32" s="70" t="n"/>
-    </row>
-    <row r="33" ht="47.5" customHeight="1" s="52">
-      <c r="A33" s="94" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B33" s="70" t="inlineStr">
-        <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="C33" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D33" s="75" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="E33" s="62" t="inlineStr">
-        <is>
-          <t>Sesión de redes sociales y marca personal con Claude (30 a 60 min)</t>
-        </is>
-      </c>
-      <c r="F33" s="70" t="inlineStr">
-        <is>
-          <t>Objetivo: 10.000 seguidores antes de fin de 2026. Salir con un plan de contenido de 4 semanas. Hasta tener este plan no se publica nada. Sin fotos de menores identificables.</t>
-        </is>
-      </c>
-      <c r="G33" s="70" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H33" s="70" t="n">
-        <v>60</v>
-      </c>
-      <c r="I33" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J33" s="70" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1" s="52">
-      <c r="A34" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  19/10 a 25/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="62" customHeight="1" s="52">
+      <c r="J34" s="70" t="n"/>
+    </row>
+    <row r="35" ht="33" customHeight="1" s="52">
       <c r="A35" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3419,31 +3422,31 @@
       </c>
       <c r="C35" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D35" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D35" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E35" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F35" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G35" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H35" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I35" s="70" t="inlineStr">
         <is>
@@ -3466,28 +3469,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D36" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D36" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E36" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F36" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G36" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H36" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I36" s="70" t="inlineStr">
         <is>
@@ -3496,7 +3499,7 @@
       </c>
       <c r="J36" s="70" t="n"/>
     </row>
-    <row r="37" ht="33" customHeight="1" s="52">
+    <row r="37" ht="76.5" customHeight="1" s="52">
       <c r="A37" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3510,28 +3513,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D37" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D37" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E37" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>LinkedIn: conectar con Luke Johnston (Whitehaven AFC)</t>
         </is>
       </c>
       <c r="F37" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Luke, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
         </is>
       </c>
       <c r="G37" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H37" s="70" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I37" s="70" t="inlineStr">
         <is>
@@ -3540,7 +3543,7 @@
       </c>
       <c r="J37" s="70" t="n"/>
     </row>
-    <row r="38" ht="76.5" customHeight="1" s="52">
+    <row r="38" ht="33" customHeight="1" s="52">
       <c r="A38" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3561,21 +3564,17 @@
       </c>
       <c r="E38" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: conectar con Luke Johnston (Whitehaven AFC)</t>
+          <t>LinkedIn: 10 minutos de actividad</t>
         </is>
       </c>
       <c r="F38" s="70" t="inlineStr">
         <is>
-          <t>A mano en LinkedIn: perfil de la persona &gt; Conectar &gt; Añadir nota &gt; pegar el texto (máx. 300 caracteres). Si no deja añadir nota, conecta sin nota y manda el texto cuando acepte. Texto: «Hi Luke, I'm Joel, I run Always Up. We take youth teams to Spain to train with Atlético de Madrid and Real Sociedad. I emailed you this week and thought I'd connect here too. Joel»</t>
-        </is>
-      </c>
-      <c r="G38" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
+          <t>Acepta conexiones, comenta tres publicaciones de entrenadores o clubes con algo de valor (no publicidad). Eso hace que te vean antes de que llegue el email.</t>
+        </is>
+      </c>
+      <c r="G38" s="70" t="inlineStr"/>
       <c r="H38" s="70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I38" s="70" t="inlineStr">
         <is>
@@ -3584,7 +3583,7 @@
       </c>
       <c r="J38" s="70" t="n"/>
     </row>
-    <row r="39" ht="33" customHeight="1" s="52">
+    <row r="39" ht="192.5" customHeight="1" s="52">
       <c r="A39" s="94" t="n">
         <v>46314</v>
       </c>
@@ -3595,7 +3594,7 @@
       </c>
       <c r="C39" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D39" s="74" t="inlineStr">
@@ -3605,50 +3604,10 @@
       </c>
       <c r="E39" s="62" t="inlineStr">
         <is>
-          <t>LinkedIn: 10 minutos de actividad</t>
+          <t>Programar en Apple Mail los envíos del martes 20/10</t>
         </is>
       </c>
       <c r="F39" s="70" t="inlineStr">
-        <is>
-          <t>Acepta conexiones, comenta tres publicaciones de entrenadores o clubes con algo de valor (no publicidad). Eso hace que te vean antes de que llegue el email.</t>
-        </is>
-      </c>
-      <c r="G39" s="70" t="inlineStr"/>
-      <c r="H39" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I39" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J39" s="70" t="n"/>
-    </row>
-    <row r="40" ht="192.5" customHeight="1" s="52">
-      <c r="A40" s="94" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B40" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C40" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D40" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E40" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del martes 20/10</t>
-        </is>
-      </c>
-      <c r="F40" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 20/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Email 1 | programar para las 03:30 hora Nueva York (09:30 allí)
@@ -3658,14 +3617,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G39" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H39" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I39" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J39" s="70" t="n"/>
+    </row>
+    <row r="40" ht="47.5" customHeight="1" s="52">
+      <c r="A40" s="94" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B40" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C40" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D40" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E40" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR email 1 a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F40" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G40" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H40" s="70" t="n">
-        <v>35</v>
-      </c>
+      <c r="H40" s="70" t="n"/>
       <c r="I40" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3684,7 +3685,7 @@
       </c>
       <c r="C41" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D41" s="74" t="inlineStr">
@@ -3694,12 +3695,12 @@
       </c>
       <c r="E41" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a FC Porte d'Aquitaine</t>
+          <t>ENVIAR follow-up 1 a Hastings United</t>
         </is>
       </c>
       <c r="F41" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G41" s="70" t="inlineStr">
@@ -3736,7 +3737,7 @@
       </c>
       <c r="E42" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Hastings United</t>
+          <t>ENVIAR follow-up 1 a Home Farm FC</t>
         </is>
       </c>
       <c r="F42" s="70" t="inlineStr">
@@ -3778,7 +3779,7 @@
       </c>
       <c r="E43" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Home Farm FC</t>
+          <t>ENVIAR email 1 a Virtu Academy</t>
         </is>
       </c>
       <c r="F43" s="70" t="inlineStr">
@@ -3799,7 +3800,7 @@
       </c>
       <c r="J43" s="70" t="n"/>
     </row>
-    <row r="44" ht="47.5" customHeight="1" s="52">
+    <row r="44" ht="62" customHeight="1" s="52">
       <c r="A44" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3810,30 +3811,32 @@
       </c>
       <c r="C44" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D44" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D44" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E44" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR email 1 a Virtu Academy</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F44" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G44" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H44" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H44" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I44" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -3841,7 +3844,7 @@
       </c>
       <c r="J44" s="70" t="n"/>
     </row>
-    <row r="45" ht="62" customHeight="1" s="52">
+    <row r="45" ht="76.5" customHeight="1" s="52">
       <c r="A45" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3855,28 +3858,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D45" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D45" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E45" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F45" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G45" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H45" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I45" s="70" t="inlineStr">
         <is>
@@ -3885,7 +3888,7 @@
       </c>
       <c r="J45" s="70" t="n"/>
     </row>
-    <row r="46" ht="76.5" customHeight="1" s="52">
+    <row r="46" ht="47.5" customHeight="1" s="52">
       <c r="A46" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3896,31 +3899,31 @@
       </c>
       <c r="C46" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D46" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D46" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E46" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Omar: último mensaje corto si sigue sin contestar</t>
         </is>
       </c>
       <c r="F46" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>«Hola Omar, no quiero atosigarte. Si en este momento no es prioridad, no pasa nada, lo dejamos aquí y lo retomamos cuando te venga bien. Si quieres seguir, mándame lo que tengas del vídeo y empezamos.» Después pásalo a 'Frío' en el CRM.</t>
         </is>
       </c>
       <c r="G46" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H46" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I46" s="70" t="inlineStr">
         <is>
@@ -3929,7 +3932,7 @@
       </c>
       <c r="J46" s="70" t="n"/>
     </row>
-    <row r="47" ht="47.5" customHeight="1" s="52">
+    <row r="47" ht="149" customHeight="1" s="52">
       <c r="A47" s="94" t="n">
         <v>46315</v>
       </c>
@@ -3940,64 +3943,20 @@
       </c>
       <c r="C47" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D47" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D47" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E47" s="62" t="inlineStr">
         <is>
-          <t>Omar: último mensaje corto si sigue sin contestar</t>
+          <t>Programar en Apple Mail los envíos del miércoles 21/10</t>
         </is>
       </c>
       <c r="F47" s="70" t="inlineStr">
-        <is>
-          <t>«Hola Omar, no quiero atosigarte. Si en este momento no es prioridad, no pasa nada, lo dejamos aquí y lo retomamos cuando te venga bien. Si quieres seguir, mándame lo que tengas del vídeo y empezamos.» Después pásalo a 'Frío' en el CRM.</t>
-        </is>
-      </c>
-      <c r="G47" s="70" t="inlineStr">
-        <is>
-          <t>Segmento C - Becas</t>
-        </is>
-      </c>
-      <c r="H47" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I47" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J47" s="70" t="n"/>
-    </row>
-    <row r="48" ht="149" customHeight="1" s="52">
-      <c r="A48" s="94" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B48" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C48" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D48" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E48" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del miércoles 21/10</t>
-        </is>
-      </c>
-      <c r="F48" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 21/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • Holbeach United | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -4005,14 +3964,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G47" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H47" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I47" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J47" s="70" t="n"/>
+    </row>
+    <row r="48" ht="47.5" customHeight="1" s="52">
+      <c r="A48" s="94" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B48" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C48" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D48" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E48" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a Søreide IL</t>
+        </is>
+      </c>
+      <c r="F48" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G48" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H48" s="70" t="n">
-        <v>25</v>
-      </c>
+      <c r="H48" s="70" t="n"/>
       <c r="I48" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4031,7 +4032,7 @@
       </c>
       <c r="C49" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D49" s="74" t="inlineStr">
@@ -4041,12 +4042,12 @@
       </c>
       <c r="E49" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Søreide IL</t>
+          <t>ENVIAR follow-up 1 a Holbeach United</t>
         </is>
       </c>
       <c r="F49" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G49" s="70" t="inlineStr">
@@ -4062,7 +4063,7 @@
       </c>
       <c r="J49" s="70" t="n"/>
     </row>
-    <row r="50" ht="47.5" customHeight="1" s="52">
+    <row r="50" ht="62" customHeight="1" s="52">
       <c r="A50" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4073,30 +4074,32 @@
       </c>
       <c r="C50" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D50" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D50" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E50" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Holbeach United</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F50" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G50" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H50" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H50" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I50" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4104,7 +4107,7 @@
       </c>
       <c r="J50" s="70" t="n"/>
     </row>
-    <row r="51" ht="62" customHeight="1" s="52">
+    <row r="51" ht="76.5" customHeight="1" s="52">
       <c r="A51" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4118,28 +4121,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D51" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E51" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F51" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G51" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H51" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I51" s="70" t="inlineStr">
         <is>
@@ -4148,7 +4151,7 @@
       </c>
       <c r="J51" s="70" t="n"/>
     </row>
-    <row r="52" ht="76.5" customHeight="1" s="52">
+    <row r="52" ht="178" customHeight="1" s="52">
       <c r="A52" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4159,7 +4162,7 @@
       </c>
       <c r="C52" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D52" s="74" t="inlineStr">
@@ -4169,54 +4172,10 @@
       </c>
       <c r="E52" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Programar en Apple Mail los envíos del jueves 22/10</t>
         </is>
       </c>
       <c r="F52" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G52" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H52" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I52" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J52" s="70" t="n"/>
-    </row>
-    <row r="53" ht="178" customHeight="1" s="52">
-      <c r="A53" s="94" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B53" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C53" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D53" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E53" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del jueves 22/10</t>
-        </is>
-      </c>
-      <c r="F53" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 22/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -4225,14 +4184,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G52" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H52" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J52" s="70" t="n"/>
+    </row>
+    <row r="53" ht="47.5" customHeight="1" s="52">
+      <c r="A53" s="94" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B53" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C53" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D53" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E53" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a Maidstone United</t>
+        </is>
+      </c>
+      <c r="F53" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G53" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H53" s="70" t="n">
-        <v>30</v>
-      </c>
+      <c r="H53" s="70" t="n"/>
       <c r="I53" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4261,7 +4262,7 @@
       </c>
       <c r="E54" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Maidstone United</t>
+          <t>ENVIAR follow-up 1 a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F54" s="70" t="inlineStr">
@@ -4293,7 +4294,7 @@
       </c>
       <c r="C55" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D55" s="74" t="inlineStr">
@@ -4303,12 +4304,12 @@
       </c>
       <c r="E55" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Whitehaven AFC</t>
+          <t>ENVIAR follow-up 1 a IA Akranes</t>
         </is>
       </c>
       <c r="F55" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G55" s="70" t="inlineStr">
@@ -4324,7 +4325,7 @@
       </c>
       <c r="J55" s="70" t="n"/>
     </row>
-    <row r="56" ht="47.5" customHeight="1" s="52">
+    <row r="56" ht="62" customHeight="1" s="52">
       <c r="A56" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4335,30 +4336,32 @@
       </c>
       <c r="C56" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D56" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D56" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E56" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a IA Akranes</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F56" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G56" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H56" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H56" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I56" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4366,7 +4369,7 @@
       </c>
       <c r="J56" s="70" t="n"/>
     </row>
-    <row r="57" ht="62" customHeight="1" s="52">
+    <row r="57" ht="76.5" customHeight="1" s="52">
       <c r="A57" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4380,28 +4383,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D57" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D57" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E57" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F57" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G57" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H57" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I57" s="70" t="inlineStr">
         <is>
@@ -4410,7 +4413,7 @@
       </c>
       <c r="J57" s="70" t="n"/>
     </row>
-    <row r="58" ht="76.5" customHeight="1" s="52">
+    <row r="58" ht="47.5" customHeight="1" s="52">
       <c r="A58" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4421,71 +4424,71 @@
       </c>
       <c r="C58" s="71" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D58" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E58" s="62" t="inlineStr">
+        <is>
+          <t>Preguntar a Atlético y Real Sociedad por las fechas reales de Semana Santa y verano 2027</t>
+        </is>
+      </c>
+      <c r="F58" s="70" t="inlineStr">
+        <is>
+          <t>Necesitamos saber qué semanas hay disponibles y hasta cuándo se pueden reservar. Con eso tendremos urgencia real y honesta para los follow-ups (hoy no la tenemos). Puede hacerlo Enrique.</t>
+        </is>
+      </c>
+      <c r="G58" s="70" t="inlineStr"/>
+      <c r="H58" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I58" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J58" s="70" t="n"/>
+    </row>
+    <row r="59" ht="62" customHeight="1" s="52">
+      <c r="A59" s="94" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B59" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C59" s="71" t="inlineStr">
+        <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D58" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E58" s="62" t="inlineStr">
-        <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
-        </is>
-      </c>
-      <c r="F58" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G58" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H58" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I58" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J58" s="70" t="n"/>
-    </row>
-    <row r="59" ht="47.5" customHeight="1" s="52">
-      <c r="A59" s="94" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B59" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C59" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D59" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D59" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E59" s="62" t="inlineStr">
         <is>
-          <t>Preguntar a Atlético y Real Sociedad por las fechas reales de Semana Santa y verano 2027</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F59" s="70" t="inlineStr">
         <is>
-          <t>Necesitamos saber qué semanas hay disponibles y hasta cuándo se pueden reservar. Con eso tendremos urgencia real y honesta para los follow-ups (hoy no la tenemos). Puede hacerlo Enrique.</t>
-        </is>
-      </c>
-      <c r="G59" s="70" t="inlineStr"/>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G59" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
       <c r="H59" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I59" s="70" t="inlineStr">
         <is>
@@ -4505,7 +4508,7 @@
       </c>
       <c r="C60" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D60" s="72" t="inlineStr">
@@ -4515,21 +4518,21 @@
       </c>
       <c r="E60" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
         </is>
       </c>
       <c r="F60" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
         </is>
       </c>
       <c r="G60" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>plan-outreach-30-dias.md sección 7</t>
         </is>
       </c>
       <c r="H60" s="70" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I60" s="70" t="inlineStr">
         <is>
@@ -4538,7 +4541,7 @@
       </c>
       <c r="J60" s="70" t="n"/>
     </row>
-    <row r="61" ht="62" customHeight="1" s="52">
+    <row r="61" ht="33" customHeight="1" s="52">
       <c r="A61" s="94" t="n">
         <v>46318</v>
       </c>
@@ -4552,28 +4555,24 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D61" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D61" s="76" t="inlineStr">
+        <is>
+          <t>International Program</t>
         </is>
       </c>
       <c r="E61" s="62" t="inlineStr">
         <is>
-          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
+          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
         </is>
       </c>
       <c r="F61" s="70" t="inlineStr">
         <is>
-          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
-        </is>
-      </c>
-      <c r="G61" s="70" t="inlineStr">
-        <is>
-          <t>plan-outreach-30-dias.md sección 7</t>
-        </is>
-      </c>
+          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
+        </is>
+      </c>
+      <c r="G61" s="70" t="inlineStr"/>
       <c r="H61" s="70" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="I61" s="70" t="inlineStr">
         <is>
@@ -4596,24 +4595,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D62" s="76" t="inlineStr">
-        <is>
-          <t>International Program</t>
+      <c r="D62" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E62" s="62" t="inlineStr">
         <is>
-          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F62" s="70" t="inlineStr">
         <is>
-          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
-        </is>
-      </c>
-      <c r="G62" s="70" t="inlineStr"/>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G62" s="70" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
       <c r="H62" s="70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I62" s="70" t="inlineStr">
         <is>
@@ -4624,11 +4627,11 @@
     </row>
     <row r="63" ht="33" customHeight="1" s="52">
       <c r="A63" s="94" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B63" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Sábado</t>
         </is>
       </c>
       <c r="C63" s="71" t="inlineStr">
@@ -4636,88 +4639,88 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D63" s="72" t="inlineStr">
+      <c r="D63" s="76" t="inlineStr">
+        <is>
+          <t>GEE / Fichas</t>
+        </is>
+      </c>
+      <c r="E63" s="62" t="inlineStr">
+        <is>
+          <t>Revisar las nuevas fichas (GEE, Campus Internacional, International Program)</t>
+        </is>
+      </c>
+      <c r="F63" s="70" t="inlineStr">
+        <is>
+          <t>Las preparo yo tras tu feedback de la ficha de Becas. Tú revisas y me dices qué cambiar.</t>
+        </is>
+      </c>
+      <c r="G63" s="70" t="inlineStr">
+        <is>
+          <t>02-sales/assets</t>
+        </is>
+      </c>
+      <c r="H63" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J63" s="70" t="n"/>
+    </row>
+    <row r="64" ht="22" customHeight="1" s="52">
+      <c r="A64" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  26/10 a 01/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="62" customHeight="1" s="52">
+      <c r="A65" s="94" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B65" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C65" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D65" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E63" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F63" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G63" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H63" s="70" t="n">
+      <c r="E65" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F65" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G65" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H65" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I63" s="70" t="inlineStr">
+      <c r="I65" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J63" s="70" t="n"/>
-    </row>
-    <row r="64" ht="33" customHeight="1" s="52">
-      <c r="A64" s="94" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B64" s="70" t="inlineStr">
-        <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="C64" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D64" s="76" t="inlineStr">
-        <is>
-          <t>GEE / Fichas</t>
-        </is>
-      </c>
-      <c r="E64" s="62" t="inlineStr">
-        <is>
-          <t>Revisar las nuevas fichas (GEE, Campus Internacional, International Program)</t>
-        </is>
-      </c>
-      <c r="F64" s="70" t="inlineStr">
-        <is>
-          <t>Las preparo yo tras tu feedback de la ficha de Becas. Tú revisas y me dices qué cambiar.</t>
-        </is>
-      </c>
-      <c r="G64" s="70" t="inlineStr">
-        <is>
-          <t>02-sales/assets</t>
-        </is>
-      </c>
-      <c r="H64" s="70" t="n">
-        <v>30</v>
-      </c>
-      <c r="I64" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J64" s="70" t="n"/>
-    </row>
-    <row r="65" ht="22" customHeight="1" s="52">
-      <c r="A65" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  26/10 a 01/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="62" customHeight="1" s="52">
+      <c r="J65" s="70" t="n"/>
+    </row>
+    <row r="66" ht="33" customHeight="1" s="52">
       <c r="A66" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4728,31 +4731,31 @@
       </c>
       <c r="C66" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D66" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D66" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E66" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F66" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G66" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H66" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I66" s="70" t="inlineStr">
         <is>
@@ -4775,28 +4778,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D67" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D67" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E67" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F67" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G67" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H67" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I67" s="70" t="inlineStr">
         <is>
@@ -4819,28 +4822,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D68" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D68" s="76" t="inlineStr">
+        <is>
+          <t>Campus Internacional</t>
         </is>
       </c>
       <c r="E68" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
         </is>
       </c>
       <c r="F68" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
         </is>
       </c>
       <c r="G68" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Oportunidades y notas</t>
         </is>
       </c>
       <c r="H68" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I68" s="70" t="inlineStr">
         <is>
@@ -4849,7 +4852,7 @@
       </c>
       <c r="J68" s="70" t="n"/>
     </row>
-    <row r="69" ht="33" customHeight="1" s="52">
+    <row r="69" ht="207" customHeight="1" s="52">
       <c r="A69" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4860,64 +4863,20 @@
       </c>
       <c r="C69" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D69" s="76" t="inlineStr">
-        <is>
-          <t>Campus Internacional</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D69" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E69" s="62" t="inlineStr">
         <is>
-          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
+          <t>Programar en Apple Mail los envíos del martes 27/10</t>
         </is>
       </c>
       <c r="F69" s="70" t="inlineStr">
-        <is>
-          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
-        </is>
-      </c>
-      <c r="G69" s="70" t="inlineStr">
-        <is>
-          <t>Oportunidades y notas</t>
-        </is>
-      </c>
-      <c r="H69" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I69" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J69" s="70" t="n"/>
-    </row>
-    <row r="70" ht="207" customHeight="1" s="52">
-      <c r="A70" s="94" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B70" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C70" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D70" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E70" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del martes 27/10</t>
-        </is>
-      </c>
-      <c r="F70" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 27/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -4927,14 +4886,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G69" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H69" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I69" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J69" s="70" t="n"/>
+    </row>
+    <row r="70" ht="47.5" customHeight="1" s="52">
+      <c r="A70" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B70" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C70" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D70" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E70" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 1 a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F70" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G70" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H70" s="70" t="n">
-        <v>35</v>
-      </c>
+      <c r="H70" s="70" t="n"/>
       <c r="I70" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4953,7 +4954,7 @@
       </c>
       <c r="C71" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D71" s="74" t="inlineStr">
@@ -4963,12 +4964,12 @@
       </c>
       <c r="E71" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a FC Porte d'Aquitaine</t>
+          <t>ENVIAR follow-up 2 a Hastings United</t>
         </is>
       </c>
       <c r="F71" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G71" s="70" t="inlineStr">
@@ -5005,7 +5006,7 @@
       </c>
       <c r="E72" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Hastings United</t>
+          <t>ENVIAR follow-up 2 a Home Farm FC</t>
         </is>
       </c>
       <c r="F72" s="70" t="inlineStr">
@@ -5047,7 +5048,7 @@
       </c>
       <c r="E73" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Home Farm FC</t>
+          <t>ENVIAR follow-up 1 a Virtu Academy</t>
         </is>
       </c>
       <c r="F73" s="70" t="inlineStr">
@@ -5068,7 +5069,7 @@
       </c>
       <c r="J73" s="70" t="n"/>
     </row>
-    <row r="74" ht="47.5" customHeight="1" s="52">
+    <row r="74" ht="62" customHeight="1" s="52">
       <c r="A74" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5079,30 +5080,32 @@
       </c>
       <c r="C74" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D74" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D74" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E74" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Virtu Academy</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F74" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G74" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H74" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H74" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I74" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5110,7 +5113,7 @@
       </c>
       <c r="J74" s="70" t="n"/>
     </row>
-    <row r="75" ht="62" customHeight="1" s="52">
+    <row r="75" ht="76.5" customHeight="1" s="52">
       <c r="A75" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5124,28 +5127,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D75" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E75" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F75" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G75" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H75" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I75" s="70" t="inlineStr">
         <is>
@@ -5154,7 +5157,7 @@
       </c>
       <c r="J75" s="70" t="n"/>
     </row>
-    <row r="76" ht="76.5" customHeight="1" s="52">
+    <row r="76" ht="33" customHeight="1" s="52">
       <c r="A76" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5165,7 +5168,7 @@
       </c>
       <c r="C76" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D76" s="74" t="inlineStr">
@@ -5175,21 +5178,21 @@
       </c>
       <c r="E76" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
         </is>
       </c>
       <c r="F76" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
         </is>
       </c>
       <c r="G76" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H76" s="70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I76" s="70" t="inlineStr">
         <is>
@@ -5198,7 +5201,7 @@
       </c>
       <c r="J76" s="70" t="n"/>
     </row>
-    <row r="77" ht="33" customHeight="1" s="52">
+    <row r="77" ht="149" customHeight="1" s="52">
       <c r="A77" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5209,7 +5212,7 @@
       </c>
       <c r="C77" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D77" s="74" t="inlineStr">
@@ -5219,54 +5222,10 @@
       </c>
       <c r="E77" s="62" t="inlineStr">
         <is>
-          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
+          <t>Programar en Apple Mail los envíos del miércoles 28/10</t>
         </is>
       </c>
       <c r="F77" s="70" t="inlineStr">
-        <is>
-          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
-        </is>
-      </c>
-      <c r="G77" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H77" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I77" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J77" s="70" t="n"/>
-    </row>
-    <row r="78" ht="149" customHeight="1" s="52">
-      <c r="A78" s="94" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B78" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C78" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D78" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E78" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del miércoles 28/10</t>
-        </is>
-      </c>
-      <c r="F78" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 28/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • Holbeach United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -5274,14 +5233,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G77" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H77" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I77" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J77" s="70" t="n"/>
+    </row>
+    <row r="78" ht="47.5" customHeight="1" s="52">
+      <c r="A78" s="94" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C78" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D78" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E78" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Søreide IL</t>
+        </is>
+      </c>
+      <c r="F78" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G78" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H78" s="70" t="n">
-        <v>25</v>
-      </c>
+      <c r="H78" s="70" t="n"/>
       <c r="I78" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5300,7 +5301,7 @@
       </c>
       <c r="C79" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D79" s="74" t="inlineStr">
@@ -5310,12 +5311,12 @@
       </c>
       <c r="E79" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Søreide IL</t>
+          <t>ENVIAR follow-up 2 a Holbeach United</t>
         </is>
       </c>
       <c r="F79" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G79" s="70" t="inlineStr">
@@ -5331,7 +5332,7 @@
       </c>
       <c r="J79" s="70" t="n"/>
     </row>
-    <row r="80" ht="47.5" customHeight="1" s="52">
+    <row r="80" ht="62" customHeight="1" s="52">
       <c r="A80" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5342,30 +5343,32 @@
       </c>
       <c r="C80" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D80" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D80" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E80" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Holbeach United</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F80" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G80" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H80" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H80" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I80" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5373,7 +5376,7 @@
       </c>
       <c r="J80" s="70" t="n"/>
     </row>
-    <row r="81" ht="62" customHeight="1" s="52">
+    <row r="81" ht="76.5" customHeight="1" s="52">
       <c r="A81" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5387,28 +5390,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D81" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D81" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E81" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F81" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G81" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H81" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I81" s="70" t="inlineStr">
         <is>
@@ -5417,7 +5420,7 @@
       </c>
       <c r="J81" s="70" t="n"/>
     </row>
-    <row r="82" ht="76.5" customHeight="1" s="52">
+    <row r="82" ht="47.5" customHeight="1" s="52">
       <c r="A82" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5428,31 +5431,31 @@
       </c>
       <c r="C82" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D82" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D82" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E82" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
         </is>
       </c>
       <c r="F82" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
         </is>
       </c>
       <c r="G82" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H82" s="70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I82" s="70" t="inlineStr">
         <is>
@@ -5461,7 +5464,7 @@
       </c>
       <c r="J82" s="70" t="n"/>
     </row>
-    <row r="83" ht="47.5" customHeight="1" s="52">
+    <row r="83" ht="76.5" customHeight="1" s="52">
       <c r="A83" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5475,19 +5478,19 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D83" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D83" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E83" s="62" t="inlineStr">
         <is>
-          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
+          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
         </is>
       </c>
       <c r="F83" s="70" t="inlineStr">
         <is>
-          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G83" s="70" t="inlineStr">
@@ -5496,7 +5499,7 @@
         </is>
       </c>
       <c r="H83" s="70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I83" s="70" t="inlineStr">
         <is>
@@ -5526,7 +5529,7 @@
       </c>
       <c r="E84" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
+          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
         </is>
       </c>
       <c r="F84" s="70" t="inlineStr">
@@ -5549,7 +5552,7 @@
       </c>
       <c r="J84" s="70" t="n"/>
     </row>
-    <row r="85" ht="76.5" customHeight="1" s="52">
+    <row r="85" ht="178" customHeight="1" s="52">
       <c r="A85" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5560,7 +5563,7 @@
       </c>
       <c r="C85" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D85" s="74" t="inlineStr">
@@ -5570,54 +5573,10 @@
       </c>
       <c r="E85" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
+          <t>Programar en Apple Mail los envíos del jueves 29/10</t>
         </is>
       </c>
       <c r="F85" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G85" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H85" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I85" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J85" s="70" t="n"/>
-    </row>
-    <row r="86" ht="178" customHeight="1" s="52">
-      <c r="A86" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B86" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C86" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D86" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E86" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del jueves 29/10</t>
-        </is>
-      </c>
-      <c r="F86" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 29/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -5626,14 +5585,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G85" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H85" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J85" s="70" t="n"/>
+    </row>
+    <row r="86" ht="47.5" customHeight="1" s="52">
+      <c r="A86" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B86" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C86" s="71" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D86" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E86" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a IA Akranes</t>
+        </is>
+      </c>
+      <c r="F86" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G86" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H86" s="70" t="n">
-        <v>30</v>
-      </c>
+      <c r="H86" s="70" t="n"/>
       <c r="I86" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5662,7 +5663,7 @@
       </c>
       <c r="E87" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a IA Akranes</t>
+          <t>ENVIAR follow-up 2 a Maidstone United</t>
         </is>
       </c>
       <c r="F87" s="70" t="inlineStr">
@@ -5704,7 +5705,7 @@
       </c>
       <c r="E88" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Maidstone United</t>
+          <t>ENVIAR follow-up 2 a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F88" s="70" t="inlineStr">
@@ -5725,7 +5726,7 @@
       </c>
       <c r="J88" s="70" t="n"/>
     </row>
-    <row r="89" ht="47.5" customHeight="1" s="52">
+    <row r="89" ht="62" customHeight="1" s="52">
       <c r="A89" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5736,30 +5737,32 @@
       </c>
       <c r="C89" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D89" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D89" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E89" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Whitehaven AFC</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F89" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G89" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H89" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H89" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I89" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5767,7 +5770,7 @@
       </c>
       <c r="J89" s="70" t="n"/>
     </row>
-    <row r="90" ht="62" customHeight="1" s="52">
+    <row r="90" ht="76.5" customHeight="1" s="52">
       <c r="A90" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5781,28 +5784,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D90" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D90" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E90" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F90" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G90" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H90" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I90" s="70" t="inlineStr">
         <is>
@@ -5822,7 +5825,7 @@
       </c>
       <c r="C91" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D91" s="74" t="inlineStr">
@@ -5832,21 +5835,21 @@
       </c>
       <c r="E91" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
         </is>
       </c>
       <c r="F91" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G91" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H91" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I91" s="70" t="inlineStr">
         <is>
@@ -5876,7 +5879,7 @@
       </c>
       <c r="E92" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
+          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
         </is>
       </c>
       <c r="F92" s="70" t="inlineStr">
@@ -5899,42 +5902,42 @@
       </c>
       <c r="J92" s="70" t="n"/>
     </row>
-    <row r="93" ht="76.5" customHeight="1" s="52">
+    <row r="93" ht="62" customHeight="1" s="52">
       <c r="A93" s="94" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B93" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C93" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D93" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D93" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E93" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F93" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G93" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H93" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I93" s="70" t="inlineStr">
         <is>
@@ -5943,7 +5946,7 @@
       </c>
       <c r="J93" s="70" t="n"/>
     </row>
-    <row r="94" ht="62" customHeight="1" s="52">
+    <row r="94" ht="76.5" customHeight="1" s="52">
       <c r="A94" s="94" t="n">
         <v>46325</v>
       </c>
@@ -5954,31 +5957,31 @@
       </c>
       <c r="C94" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D94" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D94" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E94" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
         </is>
       </c>
       <c r="F94" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G94" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H94" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I94" s="70" t="inlineStr">
         <is>
@@ -6008,7 +6011,7 @@
       </c>
       <c r="E95" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
+          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
         </is>
       </c>
       <c r="F95" s="70" t="inlineStr">
@@ -6052,7 +6055,7 @@
       </c>
       <c r="E96" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
+          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
         </is>
       </c>
       <c r="F96" s="70" t="inlineStr">
@@ -6075,7 +6078,7 @@
       </c>
       <c r="J96" s="70" t="n"/>
     </row>
-    <row r="97" ht="76.5" customHeight="1" s="52">
+    <row r="97" ht="33" customHeight="1" s="52">
       <c r="A97" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6089,28 +6092,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D97" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D97" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E97" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F97" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G97" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H97" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I97" s="70" t="inlineStr">
         <is>
@@ -6119,58 +6122,58 @@
       </c>
       <c r="J97" s="70" t="n"/>
     </row>
-    <row r="98" ht="33" customHeight="1" s="52">
-      <c r="A98" s="94" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B98" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C98" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D98" s="72" t="inlineStr">
+    <row r="98" ht="22" customHeight="1" s="52">
+      <c r="A98" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  02/11 a 08/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="62" customHeight="1" s="52">
+      <c r="A99" s="94" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B99" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C99" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D99" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E98" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F98" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G98" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H98" s="70" t="n">
+      <c r="E99" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F99" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G99" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H99" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I98" s="70" t="inlineStr">
+      <c r="I99" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J98" s="70" t="n"/>
-    </row>
-    <row r="99" ht="22" customHeight="1" s="52">
-      <c r="A99" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  02/11 a 08/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="62" customHeight="1" s="52">
+      <c r="J99" s="70" t="n"/>
+    </row>
+    <row r="100" ht="33" customHeight="1" s="52">
       <c r="A100" s="94" t="n">
         <v>46328</v>
       </c>
@@ -6181,31 +6184,31 @@
       </c>
       <c r="C100" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D100" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D100" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E100" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F100" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G100" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H100" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I100" s="70" t="inlineStr">
         <is>
@@ -6228,28 +6231,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D101" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D101" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E101" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F101" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G101" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H101" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I101" s="70" t="inlineStr">
         <is>
@@ -6258,7 +6261,7 @@
       </c>
       <c r="J101" s="70" t="n"/>
     </row>
-    <row r="102" ht="33" customHeight="1" s="52">
+    <row r="102" ht="192.5" customHeight="1" s="52">
       <c r="A102" s="94" t="n">
         <v>46328</v>
       </c>
@@ -6269,64 +6272,20 @@
       </c>
       <c r="C102" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D102" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D102" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E102" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Programar en Apple Mail los envíos del martes 03/11</t>
         </is>
       </c>
       <c r="F102" s="70" t="inlineStr">
-        <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
-        </is>
-      </c>
-      <c r="G102" s="70" t="inlineStr">
-        <is>
-          <t>Segmento C - Becas</t>
-        </is>
-      </c>
-      <c r="H102" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I102" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J102" s="70" t="n"/>
-    </row>
-    <row r="103" ht="192.5" customHeight="1" s="52">
-      <c r="A103" s="94" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B103" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C103" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D103" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E103" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del martes 03/11</t>
-        </is>
-      </c>
-      <c r="F103" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 03/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Follow-up 2 | programar para las 03:30 hora Nueva York (09:30 allí)
@@ -6336,14 +6295,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G102" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H102" s="70" t="n">
+        <v>35</v>
+      </c>
+      <c r="I102" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J102" s="70" t="n"/>
+    </row>
+    <row r="103" ht="47.5" customHeight="1" s="52">
+      <c r="A103" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B103" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C103" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D103" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E103" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F103" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G103" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H103" s="70" t="n">
-        <v>35</v>
-      </c>
+      <c r="H103" s="70" t="n"/>
       <c r="I103" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6362,7 +6363,7 @@
       </c>
       <c r="C104" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D104" s="74" t="inlineStr">
@@ -6372,12 +6373,12 @@
       </c>
       <c r="E104" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a FC Porte d'Aquitaine</t>
+          <t>ENVIAR cierre a Hastings United</t>
         </is>
       </c>
       <c r="F104" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G104" s="70" t="inlineStr">
@@ -6414,7 +6415,7 @@
       </c>
       <c r="E105" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Hastings United</t>
+          <t>ENVIAR cierre a Home Farm FC</t>
         </is>
       </c>
       <c r="F105" s="70" t="inlineStr">
@@ -6456,7 +6457,7 @@
       </c>
       <c r="E106" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Home Farm FC</t>
+          <t>ENVIAR follow-up 2 a Virtu Academy</t>
         </is>
       </c>
       <c r="F106" s="70" t="inlineStr">
@@ -6477,7 +6478,7 @@
       </c>
       <c r="J106" s="70" t="n"/>
     </row>
-    <row r="107" ht="47.5" customHeight="1" s="52">
+    <row r="107" ht="62" customHeight="1" s="52">
       <c r="A107" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6488,30 +6489,32 @@
       </c>
       <c r="C107" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D107" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D107" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E107" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Virtu Academy</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F107" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G107" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H107" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H107" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I107" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6519,7 +6522,7 @@
       </c>
       <c r="J107" s="70" t="n"/>
     </row>
-    <row r="108" ht="62" customHeight="1" s="52">
+    <row r="108" ht="76.5" customHeight="1" s="52">
       <c r="A108" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6533,28 +6536,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D108" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D108" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E108" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F108" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G108" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H108" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I108" s="70" t="inlineStr">
         <is>
@@ -6563,7 +6566,7 @@
       </c>
       <c r="J108" s="70" t="n"/>
     </row>
-    <row r="109" ht="76.5" customHeight="1" s="52">
+    <row r="109" ht="30" customHeight="1" s="52">
       <c r="A109" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6574,7 +6577,7 @@
       </c>
       <c r="C109" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D109" s="74" t="inlineStr">
@@ -6584,21 +6587,21 @@
       </c>
       <c r="E109" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Enviar la tanda 4 de emails</t>
         </is>
       </c>
       <c r="F109" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
         </is>
       </c>
       <c r="G109" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H109" s="70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I109" s="70" t="inlineStr">
         <is>
@@ -6607,7 +6610,7 @@
       </c>
       <c r="J109" s="70" t="n"/>
     </row>
-    <row r="110" ht="30" customHeight="1" s="52">
+    <row r="110" ht="134.5" customHeight="1" s="52">
       <c r="A110" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6618,7 +6621,7 @@
       </c>
       <c r="C110" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D110" s="74" t="inlineStr">
@@ -6628,54 +6631,10 @@
       </c>
       <c r="E110" s="62" t="inlineStr">
         <is>
-          <t>Enviar la tanda 4 de emails</t>
+          <t>Programar en Apple Mail los envíos del miércoles 04/11</t>
         </is>
       </c>
       <c r="F110" s="70" t="inlineStr">
-        <is>
-          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
-        </is>
-      </c>
-      <c r="G110" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H110" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I110" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J110" s="70" t="n"/>
-    </row>
-    <row r="111" ht="134.5" customHeight="1" s="52">
-      <c r="A111" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B111" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C111" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D111" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E111" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del miércoles 04/11</t>
-        </is>
-      </c>
-      <c r="F111" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 04/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • Holbeach United | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -6683,14 +6642,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G110" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H110" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I110" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J110" s="70" t="n"/>
+    </row>
+    <row r="111" ht="47.5" customHeight="1" s="52">
+      <c r="A111" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B111" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C111" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D111" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E111" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a Søreide IL</t>
+        </is>
+      </c>
+      <c r="F111" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G111" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H111" s="70" t="n">
-        <v>25</v>
-      </c>
+      <c r="H111" s="70" t="n"/>
       <c r="I111" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6709,7 +6710,7 @@
       </c>
       <c r="C112" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D112" s="74" t="inlineStr">
@@ -6719,12 +6720,12 @@
       </c>
       <c r="E112" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Søreide IL</t>
+          <t>ENVIAR cierre a Holbeach United</t>
         </is>
       </c>
       <c r="F112" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G112" s="70" t="inlineStr">
@@ -6740,7 +6741,7 @@
       </c>
       <c r="J112" s="70" t="n"/>
     </row>
-    <row r="113" ht="47.5" customHeight="1" s="52">
+    <row r="113" ht="62" customHeight="1" s="52">
       <c r="A113" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6751,30 +6752,32 @@
       </c>
       <c r="C113" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D113" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D113" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E113" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Holbeach United</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F113" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G113" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H113" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H113" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I113" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6782,7 +6785,7 @@
       </c>
       <c r="J113" s="70" t="n"/>
     </row>
-    <row r="114" ht="62" customHeight="1" s="52">
+    <row r="114" ht="76.5" customHeight="1" s="52">
       <c r="A114" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6796,28 +6799,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D114" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D114" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E114" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F114" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G114" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H114" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I114" s="70" t="inlineStr">
         <is>
@@ -6826,7 +6829,7 @@
       </c>
       <c r="J114" s="70" t="n"/>
     </row>
-    <row r="115" ht="76.5" customHeight="1" s="52">
+    <row r="115" ht="91" customHeight="1" s="52">
       <c r="A115" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6837,7 +6840,7 @@
       </c>
       <c r="C115" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D115" s="74" t="inlineStr">
@@ -6847,21 +6850,21 @@
       </c>
       <c r="E115" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
         </is>
       </c>
       <c r="F115" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
         </is>
       </c>
       <c r="G115" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H115" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I115" s="70" t="inlineStr">
         <is>
@@ -6870,7 +6873,7 @@
       </c>
       <c r="J115" s="70" t="n"/>
     </row>
-    <row r="116" ht="91" customHeight="1" s="52">
+    <row r="116" ht="76.5" customHeight="1" s="52">
       <c r="A116" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6891,12 +6894,12 @@
       </c>
       <c r="E116" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
+          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
         </is>
       </c>
       <c r="F116" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G116" s="70" t="inlineStr">
@@ -6914,7 +6917,7 @@
       </c>
       <c r="J116" s="70" t="n"/>
     </row>
-    <row r="117" ht="76.5" customHeight="1" s="52">
+    <row r="117" ht="149" customHeight="1" s="52">
       <c r="A117" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6925,7 +6928,7 @@
       </c>
       <c r="C117" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="D117" s="74" t="inlineStr">
@@ -6935,54 +6938,10 @@
       </c>
       <c r="E117" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
+          <t>Programar en Apple Mail los envíos del jueves 05/11</t>
         </is>
       </c>
       <c r="F117" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G117" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H117" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I117" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J117" s="70" t="n"/>
-    </row>
-    <row r="118" ht="149" customHeight="1" s="52">
-      <c r="A118" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B118" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C118" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D118" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E118" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del jueves 05/11</t>
-        </is>
-      </c>
-      <c r="F118" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 05/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -6991,14 +6950,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G117" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H117" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J117" s="70" t="n"/>
+    </row>
+    <row r="118" ht="47.5" customHeight="1" s="52">
+      <c r="A118" s="94" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B118" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C118" s="71" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D118" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E118" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a IA Akranes</t>
+        </is>
+      </c>
+      <c r="F118" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G118" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H118" s="70" t="n">
-        <v>30</v>
-      </c>
+      <c r="H118" s="70" t="n"/>
       <c r="I118" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7027,7 +7028,7 @@
       </c>
       <c r="E119" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a IA Akranes</t>
+          <t>ENVIAR cierre a Maidstone United</t>
         </is>
       </c>
       <c r="F119" s="70" t="inlineStr">
@@ -7069,7 +7070,7 @@
       </c>
       <c r="E120" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Maidstone United</t>
+          <t>ENVIAR cierre a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F120" s="70" t="inlineStr">
@@ -7090,7 +7091,7 @@
       </c>
       <c r="J120" s="70" t="n"/>
     </row>
-    <row r="121" ht="47.5" customHeight="1" s="52">
+    <row r="121" ht="62" customHeight="1" s="52">
       <c r="A121" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7101,30 +7102,32 @@
       </c>
       <c r="C121" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D121" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D121" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E121" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Whitehaven AFC</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F121" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G121" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H121" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H121" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I121" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7132,7 +7135,7 @@
       </c>
       <c r="J121" s="70" t="n"/>
     </row>
-    <row r="122" ht="62" customHeight="1" s="52">
+    <row r="122" ht="76.5" customHeight="1" s="52">
       <c r="A122" s="94" t="n">
         <v>46331</v>
       </c>
@@ -7146,81 +7149,81 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D122" s="72" t="inlineStr">
+      <c r="D122" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E122" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F122" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G122" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H122" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I122" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J122" s="70" t="n"/>
+    </row>
+    <row r="123" ht="62" customHeight="1" s="52">
+      <c r="A123" s="94" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B123" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C123" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D123" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E122" s="62" t="inlineStr">
+      <c r="E123" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F122" s="70" t="inlineStr">
+      <c r="F123" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G122" s="70" t="inlineStr">
+      <c r="G123" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H122" s="70" t="n">
+      <c r="H123" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I122" s="70" t="inlineStr">
+      <c r="I123" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J122" s="70" t="n"/>
-    </row>
-    <row r="123" ht="76.5" customHeight="1" s="52">
-      <c r="A123" s="94" t="n">
-        <v>46331</v>
-      </c>
-      <c r="B123" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C123" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D123" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E123" s="62" t="inlineStr">
-        <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
-        </is>
-      </c>
-      <c r="F123" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G123" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H123" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I123" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J123" s="70" t="n"/>
     </row>
-    <row r="124" ht="62" customHeight="1" s="52">
+    <row r="124" ht="33" customHeight="1" s="52">
       <c r="A124" s="94" t="n">
         <v>46332</v>
       </c>
@@ -7231,7 +7234,7 @@
       </c>
       <c r="C124" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D124" s="72" t="inlineStr">
@@ -7241,21 +7244,21 @@
       </c>
       <c r="E124" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
         </is>
       </c>
       <c r="F124" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
         </is>
       </c>
       <c r="G124" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="H124" s="70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I124" s="70" t="inlineStr">
         <is>
@@ -7285,21 +7288,21 @@
       </c>
       <c r="E125" s="62" t="inlineStr">
         <is>
-          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F125" s="70" t="inlineStr">
         <is>
-          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G125" s="70" t="inlineStr">
         <is>
-          <t>Hoy</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H125" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I125" s="70" t="inlineStr">
         <is>
@@ -7308,58 +7311,58 @@
       </c>
       <c r="J125" s="70" t="n"/>
     </row>
-    <row r="126" ht="33" customHeight="1" s="52">
-      <c r="A126" s="94" t="n">
-        <v>46332</v>
-      </c>
-      <c r="B126" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C126" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D126" s="72" t="inlineStr">
+    <row r="126" ht="22" customHeight="1" s="52">
+      <c r="A126" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  09/11 a 15/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="62" customHeight="1" s="52">
+      <c r="A127" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B127" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C127" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D127" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E126" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F126" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G126" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H126" s="70" t="n">
+      <c r="E127" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F127" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G127" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H127" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I126" s="70" t="inlineStr">
+      <c r="I127" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J126" s="70" t="n"/>
-    </row>
-    <row r="127" ht="22" customHeight="1" s="52">
-      <c r="A127" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  09/11 a 15/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="62" customHeight="1" s="52">
+      <c r="J127" s="70" t="n"/>
+    </row>
+    <row r="128" ht="33" customHeight="1" s="52">
       <c r="A128" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7370,31 +7373,31 @@
       </c>
       <c r="C128" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D128" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D128" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E128" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
         </is>
       </c>
       <c r="F128" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G128" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H128" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I128" s="70" t="inlineStr">
         <is>
@@ -7417,28 +7420,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D129" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D129" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
         </is>
       </c>
       <c r="E129" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
       <c r="F129" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
       <c r="G129" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Segmento C - Becas</t>
         </is>
       </c>
       <c r="H129" s="70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I129" s="70" t="inlineStr">
         <is>
@@ -7447,7 +7450,7 @@
       </c>
       <c r="J129" s="70" t="n"/>
     </row>
-    <row r="130" ht="33" customHeight="1" s="52">
+    <row r="130" ht="62" customHeight="1" s="52">
       <c r="A130" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7461,28 +7464,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D130" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D130" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E130" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Revisión del mes con Claude (45 min)</t>
         </is>
       </c>
       <c r="F130" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real. Valoramos también la automatización del envío (objetivo de Joel: cientos de correos a la semana): Google Workspace, herramienta de envíos con calentamiento y qué se puede delegar.</t>
         </is>
       </c>
       <c r="G130" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H130" s="70" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I130" s="70" t="inlineStr">
         <is>
@@ -7491,7 +7494,7 @@
       </c>
       <c r="J130" s="70" t="n"/>
     </row>
-    <row r="131" ht="62" customHeight="1" s="52">
+    <row r="131" ht="134.5" customHeight="1" s="52">
       <c r="A131" s="94" t="n">
         <v>46335</v>
       </c>
@@ -7502,64 +7505,20 @@
       </c>
       <c r="C131" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D131" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="D131" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E131" s="62" t="inlineStr">
         <is>
-          <t>Revisión del mes con Claude (45 min)</t>
+          <t>Programar en Apple Mail los envíos del martes 10/11</t>
         </is>
       </c>
       <c r="F131" s="70" t="inlineStr">
-        <is>
-          <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real. Valoramos también la automatización del envío (objetivo de Joel: cientos de correos a la semana): Google Workspace, herramienta de envíos con calentamiento y qué se puede delegar.</t>
-        </is>
-      </c>
-      <c r="G131" s="70" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H131" s="70" t="n">
-        <v>45</v>
-      </c>
-      <c r="I131" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J131" s="70" t="n"/>
-    </row>
-    <row r="132" ht="134.5" customHeight="1" s="52">
-      <c r="A132" s="94" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B132" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C132" s="71" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="D132" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E132" s="62" t="inlineStr">
-        <is>
-          <t>Programar en Apple Mail los envíos del martes 10/11</t>
-        </is>
-      </c>
-      <c r="F132" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 10/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Cierre | programar para las 03:30 hora Nueva York (09:30 allí)
@@ -7567,14 +7526,56 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
+      <c r="G131" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H131" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I131" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J131" s="70" t="n"/>
+    </row>
+    <row r="132" ht="47.5" customHeight="1" s="52">
+      <c r="A132" s="94" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B132" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C132" s="71" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D132" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E132" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR cierre a FC Porte d'Aquitaine</t>
+        </is>
+      </c>
+      <c r="F132" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
       <c r="G132" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H132" s="70" t="n">
-        <v>25</v>
-      </c>
+      <c r="H132" s="70" t="n"/>
       <c r="I132" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7593,7 +7594,7 @@
       </c>
       <c r="C133" s="71" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D133" s="74" t="inlineStr">
@@ -7603,12 +7604,12 @@
       </c>
       <c r="E133" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a FC Porte d'Aquitaine</t>
+          <t>ENVIAR cierre a Virtu Academy</t>
         </is>
       </c>
       <c r="F133" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G133" s="70" t="inlineStr">
@@ -7624,7 +7625,7 @@
       </c>
       <c r="J133" s="70" t="n"/>
     </row>
-    <row r="134" ht="47.5" customHeight="1" s="52">
+    <row r="134" ht="62" customHeight="1" s="52">
       <c r="A134" s="94" t="n">
         <v>46336</v>
       </c>
@@ -7635,30 +7636,32 @@
       </c>
       <c r="C134" s="71" t="inlineStr">
         <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D134" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D134" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E134" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR cierre a Virtu Academy</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F134" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G134" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H134" s="70" t="n"/>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H134" s="70" t="n">
+        <v>15</v>
+      </c>
       <c r="I134" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -7666,7 +7669,7 @@
       </c>
       <c r="J134" s="70" t="n"/>
     </row>
-    <row r="135" ht="62" customHeight="1" s="52">
+    <row r="135" ht="76.5" customHeight="1" s="52">
       <c r="A135" s="94" t="n">
         <v>46336</v>
       </c>
@@ -7680,72 +7683,72 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D135" s="72" t="inlineStr">
+      <c r="D135" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E135" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F135" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G135" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H135" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I135" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J135" s="70" t="n"/>
+    </row>
+    <row r="136" ht="62" customHeight="1" s="52">
+      <c r="A136" s="94" t="n">
+        <v>46337</v>
+      </c>
+      <c r="B136" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C136" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D136" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E135" s="62" t="inlineStr">
+      <c r="E136" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F135" s="70" t="inlineStr">
+      <c r="F136" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G135" s="70" t="inlineStr">
+      <c r="G136" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H135" s="70" t="n">
+      <c r="H136" s="70" t="n">
         <v>15</v>
-      </c>
-      <c r="I135" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J135" s="70" t="n"/>
-    </row>
-    <row r="136" ht="76.5" customHeight="1" s="52">
-      <c r="A136" s="94" t="n">
-        <v>46336</v>
-      </c>
-      <c r="B136" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C136" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D136" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E136" s="62" t="inlineStr">
-        <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
-        </is>
-      </c>
-      <c r="F136" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G136" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H136" s="70" t="n">
-        <v>10</v>
       </c>
       <c r="I136" s="70" t="inlineStr">
         <is>
@@ -7756,11 +7759,11 @@
     </row>
     <row r="137" ht="62" customHeight="1" s="52">
       <c r="A137" s="94" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="B137" s="70" t="inlineStr">
         <is>
-          <t>Miércoles</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C137" s="71" t="inlineStr">
@@ -7800,11 +7803,11 @@
     </row>
     <row r="138" ht="62" customHeight="1" s="52">
       <c r="A138" s="94" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="B138" s="70" t="inlineStr">
         <is>
-          <t>Jueves</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C138" s="71" t="inlineStr">
@@ -7842,7 +7845,7 @@
       </c>
       <c r="J138" s="70" t="n"/>
     </row>
-    <row r="139" ht="62" customHeight="1" s="52">
+    <row r="139" ht="33" customHeight="1" s="52">
       <c r="A139" s="94" t="n">
         <v>46339</v>
       </c>
@@ -7853,7 +7856,7 @@
       </c>
       <c r="C139" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>Libre</t>
         </is>
       </c>
       <c r="D139" s="72" t="inlineStr">
@@ -7863,17 +7866,17 @@
       </c>
       <c r="E139" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
       <c r="F139" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
       <c r="G139" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Segmento A, B, C</t>
         </is>
       </c>
       <c r="H139" s="70" t="n">
@@ -7886,61 +7889,17 @@
       </c>
       <c r="J139" s="70" t="n"/>
     </row>
-    <row r="140" ht="33" customHeight="1" s="52">
-      <c r="A140" s="94" t="n">
-        <v>46339</v>
-      </c>
-      <c r="B140" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C140" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D140" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E140" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F140" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G140" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H140" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I140" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J140" s="70" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:J140"/>
+  <autoFilter ref="A4:J139"/>
   <mergeCells count="6">
-    <mergeCell ref="A99:J99"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A127:J127"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="A64:J64"/>
+    <mergeCell ref="A98:J98"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J140">
+  <conditionalFormatting sqref="A5:J139">
     <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="1">
       <formula>$I5="Hecho"</formula>
     </cfRule>
@@ -7948,13 +7907,13 @@
       <formula>$A5=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I140">
+  <conditionalFormatting sqref="I5:I139">
     <cfRule type="expression" priority="3" dxfId="5">
       <formula>AND(ISNUMBER($A5),$A5&lt;TODAY(),$I5="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I127 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Hecho,Saltado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11084,7 +11043,7 @@
       </c>
       <c r="H55" s="63" t="inlineStr">
         <is>
-          <t>Great, thanks for getting back to me. Here is a link to my calendar where you can pick a time that suits you (it shows your local time): {Calendly}. If you'd rather, tell me a couple of times that work and I'll adapt.
+          <t>Great, thanks for getting back to me. Would {A} or {B} work for a call? Those are your local times. If neither suits, tell me what does and I'll adapt. I'll send an invite as soon as we pick one.
 Best,
 Joel Martinez
 Founder, Always Up
@@ -11093,7 +11052,7 @@
       </c>
       <c r="I55" s="63" t="inlineStr">
         <is>
-          <t>Menos de 4 horas. Sustituye {Calendly} por el enlace del evento 'Always Up Intro Call' (cuando lo tengas). Mientras tanto, ofrece dos horarios de la tabla de LEEME convertidos a su hora.</t>
+          <t>Menos de 4 horas. Sustituye {A} y {B} por dos horarios de la tabla de LEEME convertidos a su hora. Si prefiere elegir él: ofrece el enlace de Calendly.</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="52" min="1" max="1"/>
@@ -12628,7 +12587,7 @@
       <c r="N10" s="10" t="n"/>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
@@ -13100,7 +13059,7 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
+          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
@@ -13255,6 +13214,46 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <autoFilter ref="A5:P17"/>
   <mergeCells count="3">
@@ -14672,7 +14671,7 @@
           <t>Follow-up enviado el 14/10. Si no responde el 21/10: pasar a Frío y no insistir.</t>
         </is>
       </c>
-      <c r="I20" s="100" t="n">
+      <c r="I20" s="101" t="n">
         <v>46309</v>
       </c>
       <c r="J20" s="9" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oportunidades y notas" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendario diario'!$A$4:$J$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Textos para copiar'!$A$4:$K$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Segmento A - Clubes'!$A$5:$P$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Segmento B - America'!$A$5:$O$13</definedName>
@@ -2084,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="52" min="1" max="1"/>
@@ -3337,17 +3337,17 @@
       </c>
       <c r="E32" s="62" t="inlineStr">
         <is>
-          <t>Sesión de redes sociales y marca personal con Claude (30 a 60 min)</t>
+          <t>Bloque de redes sociales (60 min)</t>
         </is>
       </c>
       <c r="F32" s="70" t="inlineStr">
         <is>
-          <t>Objetivo: 10.000 seguidores antes de fin de 2026. Salir con un plan de contenido de 4 semanas. Hasta tener este plan no se publica nada. Sin fotos de menores identificables.</t>
+          <t>Definir la estrategia y los pilares de contenido (sesión de agentes). Objetivo: plan v1 listo el 24/10. La meta sigue siendo 10.000 seguidores a fin de año; partimos de 2.150. Mide cada semana seguidores nuevos y mensajes de familias o clubes.</t>
         </is>
       </c>
       <c r="G32" s="70" t="inlineStr">
         <is>
-          <t>Chat con Claude</t>
+          <t>Chat con Claude / sesión de agentes</t>
         </is>
       </c>
       <c r="H32" s="70" t="n">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="E35" s="62" t="inlineStr">
         <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
+          <t>Pedirme: «investiga 10 clubes más» (Europa, EEUU o los dos) para la siguiente tanda</t>
         </is>
       </c>
       <c r="F35" s="70" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="J51" s="70" t="n"/>
     </row>
-    <row r="52" ht="178" customHeight="1" s="52">
+    <row r="52" ht="47.5" customHeight="1" s="52">
       <c r="A52" s="94" t="n">
         <v>46316</v>
       </c>
@@ -4162,20 +4162,64 @@
       </c>
       <c r="C52" s="71" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D52" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E52" s="62" t="inlineStr">
+        <is>
+          <t>Bloque de redes sociales (30 min)</t>
+        </is>
+      </c>
+      <c r="F52" s="70" t="inlineStr">
+        <is>
+          <t>Revisar lo que haya salido de la sesión de agentes y decidir qué se publica primero. La meta sigue siendo 10.000 seguidores a fin de año; partimos de 2.150. Mide cada semana seguidores nuevos y mensajes de familias o clubes.</t>
+        </is>
+      </c>
+      <c r="G52" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude / sesión de agentes</t>
+        </is>
+      </c>
+      <c r="H52" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J52" s="70" t="n"/>
+    </row>
+    <row r="53" ht="178" customHeight="1" s="52">
+      <c r="A53" s="94" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B53" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C53" s="71" t="inlineStr">
+        <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="D52" s="74" t="inlineStr">
+      <c r="D53" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E52" s="62" t="inlineStr">
+      <c r="E53" s="62" t="inlineStr">
         <is>
           <t>Programar en Apple Mail los envíos del jueves 22/10</t>
         </is>
       </c>
-      <c r="F52" s="70" t="inlineStr">
+      <c r="F53" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 22/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Follow-up 1 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -4184,56 +4228,14 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
-      <c r="G52" s="70" t="inlineStr">
+      <c r="G53" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H52" s="70" t="n">
+      <c r="H53" s="70" t="n">
         <v>30</v>
       </c>
-      <c r="I52" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J52" s="70" t="n"/>
-    </row>
-    <row r="53" ht="47.5" customHeight="1" s="52">
-      <c r="A53" s="94" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B53" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C53" s="71" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D53" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E53" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 1 a Maidstone United</t>
-        </is>
-      </c>
-      <c r="F53" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G53" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H53" s="70" t="n"/>
       <c r="I53" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4262,7 +4264,7 @@
       </c>
       <c r="E54" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Whitehaven AFC</t>
+          <t>ENVIAR follow-up 1 a Maidstone United</t>
         </is>
       </c>
       <c r="F54" s="70" t="inlineStr">
@@ -4294,7 +4296,7 @@
       </c>
       <c r="C55" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D55" s="74" t="inlineStr">
@@ -4304,12 +4306,12 @@
       </c>
       <c r="E55" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a IA Akranes</t>
+          <t>ENVIAR follow-up 1 a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F55" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G55" s="70" t="inlineStr">
@@ -4325,7 +4327,7 @@
       </c>
       <c r="J55" s="70" t="n"/>
     </row>
-    <row r="56" ht="62" customHeight="1" s="52">
+    <row r="56" ht="47.5" customHeight="1" s="52">
       <c r="A56" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4336,32 +4338,30 @@
       </c>
       <c r="C56" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D56" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D56" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E56" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>ENVIAR follow-up 1 a IA Akranes</t>
         </is>
       </c>
       <c r="F56" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G56" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H56" s="70" t="n">
-        <v>15</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H56" s="70" t="n"/>
       <c r="I56" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="J56" s="70" t="n"/>
     </row>
-    <row r="57" ht="76.5" customHeight="1" s="52">
+    <row r="57" ht="62" customHeight="1" s="52">
       <c r="A57" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4383,28 +4383,28 @@
           <t>8:00</t>
         </is>
       </c>
-      <c r="D57" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D57" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E57" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F57" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G57" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H57" s="70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I57" s="70" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="J57" s="70" t="n"/>
     </row>
-    <row r="58" ht="47.5" customHeight="1" s="52">
+    <row r="58" ht="76.5" customHeight="1" s="52">
       <c r="A58" s="94" t="n">
         <v>46317</v>
       </c>
@@ -4424,71 +4424,71 @@
       </c>
       <c r="C58" s="71" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D58" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E58" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F58" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G58" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H58" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I58" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J58" s="70" t="n"/>
+    </row>
+    <row r="59" ht="47.5" customHeight="1" s="52">
+      <c r="A59" s="94" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B59" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C59" s="71" t="inlineStr">
+        <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D58" s="74" t="inlineStr">
+      <c r="D59" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E58" s="62" t="inlineStr">
+      <c r="E59" s="62" t="inlineStr">
         <is>
           <t>Preguntar a Atlético y Real Sociedad por las fechas reales de Semana Santa y verano 2027</t>
         </is>
       </c>
-      <c r="F58" s="70" t="inlineStr">
+      <c r="F59" s="70" t="inlineStr">
         <is>
           <t>Necesitamos saber qué semanas hay disponibles y hasta cuándo se pueden reservar. Con eso tendremos urgencia real y honesta para los follow-ups (hoy no la tenemos). Puede hacerlo Enrique.</t>
         </is>
       </c>
-      <c r="G58" s="70" t="inlineStr"/>
-      <c r="H58" s="70" t="n">
+      <c r="G59" s="70" t="inlineStr"/>
+      <c r="H59" s="70" t="n">
         <v>20</v>
-      </c>
-      <c r="I58" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J58" s="70" t="n"/>
-    </row>
-    <row r="59" ht="62" customHeight="1" s="52">
-      <c r="A59" s="94" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B59" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C59" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D59" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E59" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F59" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G59" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H59" s="70" t="n">
-        <v>15</v>
       </c>
       <c r="I59" s="70" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="C60" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>8:00</t>
         </is>
       </c>
       <c r="D60" s="72" t="inlineStr">
@@ -4518,21 +4518,21 @@
       </c>
       <c r="E60" s="62" t="inlineStr">
         <is>
-          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F60" s="70" t="inlineStr">
         <is>
-          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G60" s="70" t="inlineStr">
         <is>
-          <t>plan-outreach-30-dias.md sección 7</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H60" s="70" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I60" s="70" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="J60" s="70" t="n"/>
     </row>
-    <row r="61" ht="33" customHeight="1" s="52">
+    <row r="61" ht="62" customHeight="1" s="52">
       <c r="A61" s="94" t="n">
         <v>46318</v>
       </c>
@@ -4555,24 +4555,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D61" s="76" t="inlineStr">
-        <is>
-          <t>International Program</t>
+      <c r="D61" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E61" s="62" t="inlineStr">
         <is>
-          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
+          <t>Sesión con Enrique: política de anticipo y Campus Internacional</t>
         </is>
       </c>
       <c r="F61" s="70" t="inlineStr">
         <is>
-          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
-        </is>
-      </c>
-      <c r="G61" s="70" t="inlineStr"/>
+          <t>Dos decisiones: (1) qué anticipo pedimos para reservar fechas (sugiero 20 a 30 % con condiciones de cancelación escritas) y qué dice el contrato sobre menores y seguros; (2) estructura A o B del Campus Internacional con ATM y RS y quién asume el riesgo de plazas. Sin esto, las llamadas acaban en «lo pensamos».</t>
+        </is>
+      </c>
+      <c r="G61" s="70" t="inlineStr">
+        <is>
+          <t>plan-outreach-30-dias.md sección 7</t>
+        </is>
+      </c>
       <c r="H61" s="70" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="I61" s="70" t="inlineStr">
         <is>
@@ -4595,28 +4599,24 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D62" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D62" s="76" t="inlineStr">
+        <is>
+          <t>International Program</t>
         </is>
       </c>
       <c r="E62" s="62" t="inlineStr">
         <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+          <t>Preguntar a Real Sociedad por plazas y plazos del International Program 2027</t>
         </is>
       </c>
       <c r="F62" s="70" t="inlineStr">
         <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G62" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
+          <t>Para poder vender con fechas límite reales. Lo puede preguntar Enrique en la misma conversación.</t>
+        </is>
+      </c>
+      <c r="G62" s="70" t="inlineStr"/>
       <c r="H62" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I62" s="70" t="inlineStr">
         <is>
@@ -4627,144 +4627,144 @@
     </row>
     <row r="63" ht="33" customHeight="1" s="52">
       <c r="A63" s="94" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B63" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C63" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D63" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E63" s="62" t="inlineStr">
+        <is>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+        </is>
+      </c>
+      <c r="F63" s="70" t="inlineStr">
+        <is>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G63" s="70" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
+      <c r="H63" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I63" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J63" s="70" t="n"/>
+    </row>
+    <row r="64" ht="62" customHeight="1" s="52">
+      <c r="A64" s="94" t="n">
         <v>46319</v>
       </c>
-      <c r="B63" s="70" t="inlineStr">
+      <c r="B64" s="70" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="C63" s="71" t="inlineStr">
+      <c r="C64" s="71" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D63" s="76" t="inlineStr">
+      <c r="D64" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E64" s="62" t="inlineStr">
+        <is>
+          <t>Bloque de redes sociales (60 min)</t>
+        </is>
+      </c>
+      <c r="F64" s="70" t="inlineStr">
+        <is>
+          <t>Cerrar el plan v1 y montar el calendario de contenido de las 2 primeras semanas (con los vídeos de 'Joel Content/03_Final'). La meta sigue siendo 10.000 seguidores a fin de año; partimos de 2.150. Mide cada semana seguidores nuevos y mensajes de familias o clubes.</t>
+        </is>
+      </c>
+      <c r="G64" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude / sesión de agentes</t>
+        </is>
+      </c>
+      <c r="H64" s="70" t="n">
+        <v>60</v>
+      </c>
+      <c r="I64" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J64" s="70" t="n"/>
+    </row>
+    <row r="65" ht="33" customHeight="1" s="52">
+      <c r="A65" s="94" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B65" s="70" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="C65" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D65" s="76" t="inlineStr">
         <is>
           <t>GEE / Fichas</t>
         </is>
       </c>
-      <c r="E63" s="62" t="inlineStr">
+      <c r="E65" s="62" t="inlineStr">
         <is>
           <t>Revisar las nuevas fichas (GEE, Campus Internacional, International Program)</t>
         </is>
       </c>
-      <c r="F63" s="70" t="inlineStr">
+      <c r="F65" s="70" t="inlineStr">
         <is>
           <t>Las preparo yo tras tu feedback de la ficha de Becas. Tú revisas y me dices qué cambiar.</t>
         </is>
       </c>
-      <c r="G63" s="70" t="inlineStr">
+      <c r="G65" s="70" t="inlineStr">
         <is>
           <t>02-sales/assets</t>
         </is>
       </c>
-      <c r="H63" s="70" t="n">
+      <c r="H65" s="70" t="n">
         <v>30</v>
       </c>
-      <c r="I63" s="70" t="inlineStr">
+      <c r="I65" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J63" s="70" t="n"/>
-    </row>
-    <row r="64" ht="22" customHeight="1" s="52">
-      <c r="A64" s="68" t="inlineStr">
+      <c r="J65" s="70" t="n"/>
+    </row>
+    <row r="66" ht="22" customHeight="1" s="52">
+      <c r="A66" s="68" t="inlineStr">
         <is>
           <t>SEMANA  26/10 a 01/11</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="62" customHeight="1" s="52">
-      <c r="A65" s="94" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B65" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C65" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D65" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E65" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F65" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G65" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H65" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I65" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J65" s="70" t="n"/>
-    </row>
-    <row r="66" ht="33" customHeight="1" s="52">
-      <c r="A66" s="94" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B66" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C66" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D66" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E66" s="62" t="inlineStr">
-        <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
-        </is>
-      </c>
-      <c r="F66" s="70" t="inlineStr">
-        <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
-        </is>
-      </c>
-      <c r="G66" s="70" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H66" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I66" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J66" s="70" t="n"/>
-    </row>
-    <row r="67" ht="33" customHeight="1" s="52">
+    <row r="67" ht="62" customHeight="1" s="52">
       <c r="A67" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4775,31 +4775,31 @@
       </c>
       <c r="C67" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D67" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D67" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E67" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F67" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G67" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H67" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I67" s="70" t="inlineStr">
         <is>
@@ -4822,28 +4822,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D68" s="76" t="inlineStr">
-        <is>
-          <t>Campus Internacional</t>
+      <c r="D68" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E68" s="62" t="inlineStr">
         <is>
-          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
+          <t>Pedirme: «investiga 10 clubes más» (Europa, EEUU o los dos) para la siguiente tanda</t>
         </is>
       </c>
       <c r="F68" s="70" t="inlineStr">
         <is>
-          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
       <c r="G68" s="70" t="inlineStr">
         <is>
-          <t>Oportunidades y notas</t>
+          <t>Chat con Claude</t>
         </is>
       </c>
       <c r="H68" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I68" s="70" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="J68" s="70" t="n"/>
     </row>
-    <row r="69" ht="207" customHeight="1" s="52">
+    <row r="69" ht="33" customHeight="1" s="52">
       <c r="A69" s="94" t="n">
         <v>46321</v>
       </c>
@@ -4863,20 +4863,108 @@
       </c>
       <c r="C69" s="71" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D69" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E69" s="62" t="inlineStr">
+        <is>
+          <t>Revisar leads de becas con acción vencida</t>
+        </is>
+      </c>
+      <c r="F69" s="70" t="inlineStr">
+        <is>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G69" s="70" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
+      <c r="H69" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I69" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J69" s="70" t="n"/>
+    </row>
+    <row r="70" ht="33" customHeight="1" s="52">
+      <c r="A70" s="94" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B70" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C70" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D70" s="76" t="inlineStr">
+        <is>
+          <t>Campus Internacional</t>
+        </is>
+      </c>
+      <c r="E70" s="62" t="inlineStr">
+        <is>
+          <t>Retomar los contactos cálidos del Campus Internacional (Bélgica y Puerto Rico/SADE)</t>
+        </is>
+      </c>
+      <c r="F70" s="70" t="inlineStr">
+        <is>
+          <t>Escríbeme cómo está cada uno. Con la decisión de la sesión del 23/10 les contestamos con una propuesta clara. No hacemos outreach frío de este servicio todavía.</t>
+        </is>
+      </c>
+      <c r="G70" s="70" t="inlineStr">
+        <is>
+          <t>Oportunidades y notas</t>
+        </is>
+      </c>
+      <c r="H70" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I70" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J70" s="70" t="n"/>
+    </row>
+    <row r="71" ht="207" customHeight="1" s="52">
+      <c r="A71" s="94" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C71" s="71" t="inlineStr">
+        <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="D69" s="74" t="inlineStr">
+      <c r="D71" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E69" s="62" t="inlineStr">
+      <c r="E71" s="62" t="inlineStr">
         <is>
           <t>Programar en Apple Mail los envíos del martes 27/10</t>
         </is>
       </c>
-      <c r="F69" s="70" t="inlineStr">
+      <c r="F71" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 27/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Follow-up 1 | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -4886,98 +4974,14 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
-      <c r="G69" s="70" t="inlineStr">
+      <c r="G71" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H69" s="70" t="n">
+      <c r="H71" s="70" t="n">
         <v>35</v>
       </c>
-      <c r="I69" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J69" s="70" t="n"/>
-    </row>
-    <row r="70" ht="47.5" customHeight="1" s="52">
-      <c r="A70" s="94" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B70" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C70" s="71" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D70" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E70" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 1 a FC Porte d'Aquitaine</t>
-        </is>
-      </c>
-      <c r="F70" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G70" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H70" s="70" t="n"/>
-      <c r="I70" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J70" s="70" t="n"/>
-    </row>
-    <row r="71" ht="47.5" customHeight="1" s="52">
-      <c r="A71" s="94" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B71" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C71" s="71" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D71" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E71" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Hastings United</t>
-        </is>
-      </c>
-      <c r="F71" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G71" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H71" s="70" t="n"/>
       <c r="I71" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -4996,7 +5000,7 @@
       </c>
       <c r="C72" s="71" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D72" s="74" t="inlineStr">
@@ -5006,12 +5010,12 @@
       </c>
       <c r="E72" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 2 a Home Farm FC</t>
+          <t>ENVIAR follow-up 1 a FC Porte d'Aquitaine</t>
         </is>
       </c>
       <c r="F72" s="70" t="inlineStr">
         <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G72" s="70" t="inlineStr">
@@ -5048,7 +5052,7 @@
       </c>
       <c r="E73" s="62" t="inlineStr">
         <is>
-          <t>ENVIAR follow-up 1 a Virtu Academy</t>
+          <t>ENVIAR follow-up 2 a Hastings United</t>
         </is>
       </c>
       <c r="F73" s="70" t="inlineStr">
@@ -5069,7 +5073,7 @@
       </c>
       <c r="J73" s="70" t="n"/>
     </row>
-    <row r="74" ht="62" customHeight="1" s="52">
+    <row r="74" ht="47.5" customHeight="1" s="52">
       <c r="A74" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5080,32 +5084,30 @@
       </c>
       <c r="C74" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D74" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D74" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E74" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>ENVIAR follow-up 2 a Home Farm FC</t>
         </is>
       </c>
       <c r="F74" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G74" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H74" s="70" t="n">
-        <v>15</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H74" s="70" t="n"/>
       <c r="I74" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5113,7 +5115,7 @@
       </c>
       <c r="J74" s="70" t="n"/>
     </row>
-    <row r="75" ht="76.5" customHeight="1" s="52">
+    <row r="75" ht="47.5" customHeight="1" s="52">
       <c r="A75" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5124,7 +5126,7 @@
       </c>
       <c r="C75" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D75" s="74" t="inlineStr">
@@ -5134,22 +5136,20 @@
       </c>
       <c r="E75" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>ENVIAR follow-up 1 a Virtu Academy</t>
         </is>
       </c>
       <c r="F75" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G75" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H75" s="70" t="n">
-        <v>10</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H75" s="70" t="n"/>
       <c r="I75" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="J75" s="70" t="n"/>
     </row>
-    <row r="76" ht="33" customHeight="1" s="52">
+    <row r="76" ht="62" customHeight="1" s="52">
       <c r="A76" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5168,31 +5168,31 @@
       </c>
       <c r="C76" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D76" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D76" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E76" s="62" t="inlineStr">
         <is>
-          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F76" s="70" t="inlineStr">
         <is>
-          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G76" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H76" s="70" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I76" s="70" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="J76" s="70" t="n"/>
     </row>
-    <row r="77" ht="149" customHeight="1" s="52">
+    <row r="77" ht="76.5" customHeight="1" s="52">
       <c r="A77" s="94" t="n">
         <v>46322</v>
       </c>
@@ -5212,20 +5212,108 @@
       </c>
       <c r="C77" s="71" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D77" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E77" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F77" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G77" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H77" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I77" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J77" s="70" t="n"/>
+    </row>
+    <row r="78" ht="33" customHeight="1" s="52">
+      <c r="A78" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B78" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C78" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D78" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E78" s="62" t="inlineStr">
+        <is>
+          <t>Enviar la tanda 3 de emails (los textos los tengo listos tras tu petición del 19/10)</t>
+        </is>
+      </c>
+      <c r="F78" s="70" t="inlineStr">
+        <is>
+          <t>Aparecerán en la hoja Textos para copiar con su hora de programación.</t>
+        </is>
+      </c>
+      <c r="G78" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H78" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I78" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J78" s="70" t="n"/>
+    </row>
+    <row r="79" ht="149" customHeight="1" s="52">
+      <c r="A79" s="94" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B79" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C79" s="71" t="inlineStr">
+        <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="D77" s="74" t="inlineStr">
+      <c r="D79" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E77" s="62" t="inlineStr">
+      <c r="E79" s="62" t="inlineStr">
         <is>
           <t>Programar en Apple Mail los envíos del miércoles 28/10</t>
         </is>
       </c>
-      <c r="F77" s="70" t="inlineStr">
+      <c r="F79" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 28/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • Holbeach United | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -5233,106 +5321,22 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
-      <c r="G77" s="70" t="inlineStr">
+      <c r="G79" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H77" s="70" t="n">
+      <c r="H79" s="70" t="n">
         <v>25</v>
       </c>
-      <c r="I77" s="70" t="inlineStr">
+      <c r="I79" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J77" s="70" t="n"/>
-    </row>
-    <row r="78" ht="47.5" customHeight="1" s="52">
-      <c r="A78" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B78" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C78" s="71" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D78" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E78" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Søreide IL</t>
-        </is>
-      </c>
-      <c r="F78" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G78" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H78" s="70" t="n"/>
-      <c r="I78" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J78" s="70" t="n"/>
-    </row>
-    <row r="79" ht="47.5" customHeight="1" s="52">
-      <c r="A79" s="94" t="n">
-        <v>46323</v>
-      </c>
-      <c r="B79" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C79" s="71" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D79" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E79" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Holbeach United</t>
-        </is>
-      </c>
-      <c r="F79" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G79" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H79" s="70" t="n"/>
-      <c r="I79" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J79" s="70" t="n"/>
     </row>
-    <row r="80" ht="62" customHeight="1" s="52">
+    <row r="80" ht="47.5" customHeight="1" s="52">
       <c r="A80" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5343,32 +5347,30 @@
       </c>
       <c r="C80" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D80" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D80" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E80" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>ENVIAR follow-up 2 a Søreide IL</t>
         </is>
       </c>
       <c r="F80" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G80" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H80" s="70" t="n">
-        <v>15</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H80" s="70" t="n"/>
       <c r="I80" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5376,7 +5378,7 @@
       </c>
       <c r="J80" s="70" t="n"/>
     </row>
-    <row r="81" ht="76.5" customHeight="1" s="52">
+    <row r="81" ht="47.5" customHeight="1" s="52">
       <c r="A81" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5387,7 +5389,7 @@
       </c>
       <c r="C81" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D81" s="74" t="inlineStr">
@@ -5397,22 +5399,20 @@
       </c>
       <c r="E81" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>ENVIAR follow-up 2 a Holbeach United</t>
         </is>
       </c>
       <c r="F81" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G81" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H81" s="70" t="n">
-        <v>10</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H81" s="70" t="n"/>
       <c r="I81" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="J81" s="70" t="n"/>
     </row>
-    <row r="82" ht="47.5" customHeight="1" s="52">
+    <row r="82" ht="62" customHeight="1" s="52">
       <c r="A82" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5431,31 +5431,31 @@
       </c>
       <c r="C82" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D82" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D82" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E82" s="62" t="inlineStr">
         <is>
-          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F82" s="70" t="inlineStr">
         <is>
-          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G82" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H82" s="70" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I82" s="70" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C83" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>8:00</t>
         </is>
       </c>
       <c r="D83" s="74" t="inlineStr">
@@ -5485,21 +5485,21 @@
       </c>
       <c r="E83" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F83" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G83" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H83" s="70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I83" s="70" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="J83" s="70" t="n"/>
     </row>
-    <row r="84" ht="76.5" customHeight="1" s="52">
+    <row r="84" ht="47.5" customHeight="1" s="52">
       <c r="A84" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5522,28 +5522,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D84" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+      <c r="D84" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E84" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
+          <t>Bloque de redes sociales (30 min)</t>
         </is>
       </c>
       <c r="F84" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Preparar o programar las 2 publicaciones de la semana. La meta sigue siendo 10.000 seguidores a fin de año; partimos de 2.150. Mide cada semana seguidores nuevos y mensajes de familias o clubes.</t>
         </is>
       </c>
       <c r="G84" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Chat con Claude / sesión de agentes</t>
         </is>
       </c>
       <c r="H84" s="70" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I84" s="70" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="J84" s="70" t="n"/>
     </row>
-    <row r="85" ht="178" customHeight="1" s="52">
+    <row r="85" ht="47.5" customHeight="1" s="52">
       <c r="A85" s="94" t="n">
         <v>46323</v>
       </c>
@@ -5563,20 +5563,152 @@
       </c>
       <c r="C85" s="71" t="inlineStr">
         <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D85" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E85" s="62" t="inlineStr">
+        <is>
+          <t>Piloto: 5 mensajes a entrenadores de club o instituto que tengan jugadores de 15 a 18 años</t>
+        </is>
+      </c>
+      <c r="F85" s="70" t="inlineStr">
+        <is>
+          <t>Yo investigo la lista y los textos (se entregan el 26/10). La idea: un entrenador que recomienda la ficha de Becas trae varias familias a la vez. Los textos nunca nombran al partner ni prometen becas.</t>
+        </is>
+      </c>
+      <c r="G85" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H85" s="70" t="n">
+        <v>25</v>
+      </c>
+      <c r="I85" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J85" s="70" t="n"/>
+    </row>
+    <row r="86" ht="76.5" customHeight="1" s="52">
+      <c r="A86" s="94" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B86" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C86" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D86" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E86" s="62" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Instagram de Hastings United (Hastings United)</t>
+        </is>
+      </c>
+      <c r="F86" s="70" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G86" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H86" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I86" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J86" s="70" t="n"/>
+    </row>
+    <row r="87" ht="76.5" customHeight="1" s="52">
+      <c r="A87" s="94" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B87" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C87" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D87" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E87" s="62" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Facebook o Instagram de Home Farm FC (Home Farm FC)</t>
+        </is>
+      </c>
+      <c r="F87" s="70" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G87" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H87" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I87" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J87" s="70" t="n"/>
+    </row>
+    <row r="88" ht="178" customHeight="1" s="52">
+      <c r="A88" s="94" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B88" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C88" s="71" t="inlineStr">
+        <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="D85" s="74" t="inlineStr">
+      <c r="D88" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E85" s="62" t="inlineStr">
+      <c r="E88" s="62" t="inlineStr">
         <is>
           <t>Programar en Apple Mail los envíos del jueves 29/10</t>
         </is>
       </c>
-      <c r="F85" s="70" t="inlineStr">
+      <c r="F88" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 29/10). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Follow-up 2 | programar para las 05:30 hora Nueva York (09:30 allí)
@@ -5585,148 +5717,22 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
-      <c r="G85" s="70" t="inlineStr">
+      <c r="G88" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H85" s="70" t="n">
+      <c r="H88" s="70" t="n">
         <v>30</v>
       </c>
-      <c r="I85" s="70" t="inlineStr">
+      <c r="I88" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J85" s="70" t="n"/>
-    </row>
-    <row r="86" ht="47.5" customHeight="1" s="52">
-      <c r="A86" s="94" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B86" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C86" s="71" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D86" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E86" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a IA Akranes</t>
-        </is>
-      </c>
-      <c r="F86" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G86" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H86" s="70" t="n"/>
-      <c r="I86" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J86" s="70" t="n"/>
-    </row>
-    <row r="87" ht="47.5" customHeight="1" s="52">
-      <c r="A87" s="94" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B87" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C87" s="71" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D87" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E87" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Maidstone United</t>
-        </is>
-      </c>
-      <c r="F87" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G87" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H87" s="70" t="n"/>
-      <c r="I87" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J87" s="70" t="n"/>
-    </row>
-    <row r="88" ht="47.5" customHeight="1" s="52">
-      <c r="A88" s="94" t="n">
-        <v>46324</v>
-      </c>
-      <c r="B88" s="70" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="C88" s="71" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="D88" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E88" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Whitehaven AFC</t>
-        </is>
-      </c>
-      <c r="F88" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G88" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H88" s="70" t="n"/>
-      <c r="I88" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J88" s="70" t="n"/>
     </row>
-    <row r="89" ht="62" customHeight="1" s="52">
+    <row r="89" ht="47.5" customHeight="1" s="52">
       <c r="A89" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5737,32 +5743,30 @@
       </c>
       <c r="C89" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D89" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="D89" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E89" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>ENVIAR follow-up 2 a IA Akranes</t>
         </is>
       </c>
       <c r="F89" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G89" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H89" s="70" t="n">
-        <v>15</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H89" s="70" t="n"/>
       <c r="I89" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="J89" s="70" t="n"/>
     </row>
-    <row r="90" ht="76.5" customHeight="1" s="52">
+    <row r="90" ht="47.5" customHeight="1" s="52">
       <c r="A90" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5781,7 +5785,7 @@
       </c>
       <c r="C90" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D90" s="74" t="inlineStr">
@@ -5791,22 +5795,20 @@
       </c>
       <c r="E90" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>ENVIAR follow-up 2 a Maidstone United</t>
         </is>
       </c>
       <c r="F90" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G90" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H90" s="70" t="n">
-        <v>10</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H90" s="70" t="n"/>
       <c r="I90" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5814,7 +5816,7 @@
       </c>
       <c r="J90" s="70" t="n"/>
     </row>
-    <row r="91" ht="76.5" customHeight="1" s="52">
+    <row r="91" ht="47.5" customHeight="1" s="52">
       <c r="A91" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5825,7 +5827,7 @@
       </c>
       <c r="C91" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="D91" s="74" t="inlineStr">
@@ -5835,12 +5837,12 @@
       </c>
       <c r="E91" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
+          <t>ENVIAR follow-up 2 a Whitehaven AFC</t>
         </is>
       </c>
       <c r="F91" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Sale a las 05:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G91" s="70" t="inlineStr">
@@ -5848,9 +5850,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H91" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H91" s="70" t="n"/>
       <c r="I91" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="J91" s="70" t="n"/>
     </row>
-    <row r="92" ht="76.5" customHeight="1" s="52">
+    <row r="92" ht="62" customHeight="1" s="52">
       <c r="A92" s="94" t="n">
         <v>46324</v>
       </c>
@@ -5869,75 +5869,75 @@
       </c>
       <c r="C92" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D92" s="74" t="inlineStr">
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D92" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E92" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F92" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G92" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H92" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I92" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J92" s="70" t="n"/>
+    </row>
+    <row r="93" ht="76.5" customHeight="1" s="52">
+      <c r="A93" s="94" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B93" s="70" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="C93" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D93" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E92" s="62" t="inlineStr">
-        <is>
-          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
-        </is>
-      </c>
-      <c r="F92" s="70" t="inlineStr">
-        <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
-        </is>
-      </c>
-      <c r="G92" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H92" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="I92" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J92" s="70" t="n"/>
-    </row>
-    <row r="93" ht="62" customHeight="1" s="52">
-      <c r="A93" s="94" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B93" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C93" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D93" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
       <c r="E93" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
       <c r="F93" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
       <c r="G93" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
       <c r="H93" s="70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I93" s="70" t="inlineStr">
         <is>
@@ -5948,11 +5948,11 @@
     </row>
     <row r="94" ht="76.5" customHeight="1" s="52">
       <c r="A94" s="94" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B94" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C94" s="71" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="E94" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
+          <t>Opcional: DM a Instagram @holbeachunitedcsa (Holbeach United)</t>
         </is>
       </c>
       <c r="F94" s="70" t="inlineStr">
@@ -5992,11 +5992,11 @@
     </row>
     <row r="95" ht="76.5" customHeight="1" s="52">
       <c r="A95" s="94" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B95" s="70" t="inlineStr">
         <is>
-          <t>Viernes</t>
+          <t>Jueves</t>
         </is>
       </c>
       <c r="C95" s="71" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="E95" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
+          <t>Opcional: DM a Facebook o Instagram de Søreide IL (Søreide IL)</t>
         </is>
       </c>
       <c r="F95" s="70" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="J95" s="70" t="n"/>
     </row>
-    <row r="96" ht="76.5" customHeight="1" s="52">
+    <row r="96" ht="62" customHeight="1" s="52">
       <c r="A96" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6045,31 +6045,31 @@
       </c>
       <c r="C96" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D96" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D96" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E96" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
       <c r="F96" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
       <c r="G96" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar</t>
+          <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
       <c r="H96" s="70" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I96" s="70" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J96" s="70" t="n"/>
     </row>
-    <row r="97" ht="33" customHeight="1" s="52">
+    <row r="97" ht="76.5" customHeight="1" s="52">
       <c r="A97" s="94" t="n">
         <v>46325</v>
       </c>
@@ -6092,28 +6092,28 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D97" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+      <c r="D97" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E97" s="62" t="inlineStr">
         <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+          <t>Opcional: DM a Facebook o Instagram de ÍA Akranes (IA Akranes)</t>
         </is>
       </c>
       <c r="F97" s="70" t="inlineStr">
         <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G97" s="70" t="inlineStr">
         <is>
-          <t>Segmento A, B, C</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H97" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I97" s="70" t="inlineStr">
         <is>
@@ -6122,49 +6122,86 @@
       </c>
       <c r="J97" s="70" t="n"/>
     </row>
-    <row r="98" ht="22" customHeight="1" s="52">
-      <c r="A98" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  02/11 a 08/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="62" customHeight="1" s="52">
+    <row r="98" ht="76.5" customHeight="1" s="52">
+      <c r="A98" s="94" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B98" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C98" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D98" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E98" s="62" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Facebook o Instagram de Maidstone United (Maidstone United)</t>
+        </is>
+      </c>
+      <c r="F98" s="70" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G98" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H98" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I98" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J98" s="70" t="n"/>
+    </row>
+    <row r="99" ht="76.5" customHeight="1" s="52">
       <c r="A99" s="94" t="n">
-        <v>46328</v>
+        <v>46325</v>
       </c>
       <c r="B99" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C99" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D99" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D99" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E99" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>Opcional: DM a Facebook de Whitehaven AFC (plan B si el email rebota) (Whitehaven AFC)</t>
         </is>
       </c>
       <c r="F99" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
         </is>
       </c>
       <c r="G99" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
+          <t>Textos para copiar</t>
         </is>
       </c>
       <c r="H99" s="70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I99" s="70" t="inlineStr">
         <is>
@@ -6175,117 +6212,256 @@
     </row>
     <row r="100" ht="33" customHeight="1" s="52">
       <c r="A100" s="94" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B100" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C100" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D100" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E100" s="62" t="inlineStr">
+        <is>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+        </is>
+      </c>
+      <c r="F100" s="70" t="inlineStr">
+        <is>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G100" s="70" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
+      <c r="H100" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I100" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J100" s="70" t="n"/>
+    </row>
+    <row r="101" ht="47.5" customHeight="1" s="52">
+      <c r="A101" s="94" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B101" s="70" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="C101" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D101" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E101" s="62" t="inlineStr">
+        <is>
+          <t>Bloque de redes sociales (60 min)</t>
+        </is>
+      </c>
+      <c r="F101" s="70" t="inlineStr">
+        <is>
+          <t>Grabar o editar el contenido nuevo de la semana siguiente. La meta sigue siendo 10.000 seguidores a fin de año; partimos de 2.150. Mide cada semana seguidores nuevos y mensajes de familias o clubes.</t>
+        </is>
+      </c>
+      <c r="G101" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude / sesión de agentes</t>
+        </is>
+      </c>
+      <c r="H101" s="70" t="n">
+        <v>60</v>
+      </c>
+      <c r="I101" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J101" s="70" t="n"/>
+    </row>
+    <row r="102" ht="22" customHeight="1" s="52">
+      <c r="A102" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  02/11 a 08/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="62" customHeight="1" s="52">
+      <c r="A103" s="94" t="n">
         <v>46328</v>
       </c>
-      <c r="B100" s="70" t="inlineStr">
+      <c r="B103" s="70" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C100" s="71" t="inlineStr">
+      <c r="C103" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D103" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E103" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F103" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G103" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H103" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I103" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J103" s="70" t="n"/>
+    </row>
+    <row r="104" ht="33" customHeight="1" s="52">
+      <c r="A104" s="94" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B104" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C104" s="71" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D100" s="74" t="inlineStr">
+      <c r="D104" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E100" s="62" t="inlineStr">
-        <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
-        </is>
-      </c>
-      <c r="F100" s="70" t="inlineStr">
+      <c r="E104" s="62" t="inlineStr">
+        <is>
+          <t>Pedirme: «investiga 10 clubes más» (Europa, EEUU o los dos) para la siguiente tanda</t>
+        </is>
+      </c>
+      <c r="F104" s="70" t="inlineStr">
         <is>
           <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
         </is>
       </c>
-      <c r="G100" s="70" t="inlineStr">
+      <c r="G104" s="70" t="inlineStr">
         <is>
           <t>Chat con Claude</t>
         </is>
       </c>
-      <c r="H100" s="70" t="n">
+      <c r="H104" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="I100" s="70" t="inlineStr">
+      <c r="I104" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J100" s="70" t="n"/>
-    </row>
-    <row r="101" ht="33" customHeight="1" s="52">
-      <c r="A101" s="94" t="n">
+      <c r="J104" s="70" t="n"/>
+    </row>
+    <row r="105" ht="33" customHeight="1" s="52">
+      <c r="A105" s="94" t="n">
         <v>46328</v>
       </c>
-      <c r="B101" s="70" t="inlineStr">
+      <c r="B105" s="70" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C101" s="71" t="inlineStr">
+      <c r="C105" s="71" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D101" s="73" t="inlineStr">
+      <c r="D105" s="73" t="inlineStr">
         <is>
           <t>Becas</t>
         </is>
       </c>
-      <c r="E101" s="62" t="inlineStr">
+      <c r="E105" s="62" t="inlineStr">
         <is>
           <t>Revisar leads de becas con acción vencida</t>
         </is>
       </c>
-      <c r="F101" s="70" t="inlineStr">
+      <c r="F105" s="70" t="inlineStr">
         <is>
           <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
         </is>
       </c>
-      <c r="G101" s="70" t="inlineStr">
+      <c r="G105" s="70" t="inlineStr">
         <is>
           <t>Segmento C - Becas</t>
         </is>
       </c>
-      <c r="H101" s="70" t="n">
+      <c r="H105" s="70" t="n">
         <v>20</v>
       </c>
-      <c r="I101" s="70" t="inlineStr">
+      <c r="I105" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J101" s="70" t="n"/>
-    </row>
-    <row r="102" ht="192.5" customHeight="1" s="52">
-      <c r="A102" s="94" t="n">
+      <c r="J105" s="70" t="n"/>
+    </row>
+    <row r="106" ht="192.5" customHeight="1" s="52">
+      <c r="A106" s="94" t="n">
         <v>46328</v>
       </c>
-      <c r="B102" s="70" t="inlineStr">
+      <c r="B106" s="70" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C102" s="71" t="inlineStr">
+      <c r="C106" s="71" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="D102" s="74" t="inlineStr">
+      <c r="D106" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E102" s="62" t="inlineStr">
+      <c r="E106" s="62" t="inlineStr">
         <is>
           <t>Programar en Apple Mail los envíos del martes 03/11</t>
         </is>
       </c>
-      <c r="F102" s="70" t="inlineStr">
+      <c r="F106" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 03/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Follow-up 2 | programar para las 03:30 hora Nueva York (09:30 allí)
@@ -6295,190 +6471,22 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
-      <c r="G102" s="70" t="inlineStr">
+      <c r="G106" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H102" s="70" t="n">
+      <c r="H106" s="70" t="n">
         <v>35</v>
       </c>
-      <c r="I102" s="70" t="inlineStr">
+      <c r="I106" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J102" s="70" t="n"/>
-    </row>
-    <row r="103" ht="47.5" customHeight="1" s="52">
-      <c r="A103" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B103" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C103" s="71" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="D103" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E103" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a FC Porte d'Aquitaine</t>
-        </is>
-      </c>
-      <c r="F103" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G103" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H103" s="70" t="n"/>
-      <c r="I103" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J103" s="70" t="n"/>
-    </row>
-    <row r="104" ht="47.5" customHeight="1" s="52">
-      <c r="A104" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B104" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C104" s="71" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D104" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E104" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR cierre a Hastings United</t>
-        </is>
-      </c>
-      <c r="F104" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G104" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H104" s="70" t="n"/>
-      <c r="I104" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J104" s="70" t="n"/>
-    </row>
-    <row r="105" ht="47.5" customHeight="1" s="52">
-      <c r="A105" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B105" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C105" s="71" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D105" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E105" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR cierre a Home Farm FC</t>
-        </is>
-      </c>
-      <c r="F105" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G105" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H105" s="70" t="n"/>
-      <c r="I105" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J105" s="70" t="n"/>
-    </row>
-    <row r="106" ht="47.5" customHeight="1" s="52">
-      <c r="A106" s="94" t="n">
-        <v>46329</v>
-      </c>
-      <c r="B106" s="70" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="C106" s="71" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D106" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E106" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR follow-up 2 a Virtu Academy</t>
-        </is>
-      </c>
-      <c r="F106" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G106" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H106" s="70" t="n"/>
-      <c r="I106" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J106" s="70" t="n"/>
     </row>
-    <row r="107" ht="62" customHeight="1" s="52">
+    <row r="107" ht="47.5" customHeight="1" s="52">
       <c r="A107" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6489,32 +6497,30 @@
       </c>
       <c r="C107" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D107" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="D107" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
         </is>
       </c>
       <c r="E107" s="62" t="inlineStr">
         <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+          <t>ENVIAR follow-up 2 a FC Porte d'Aquitaine</t>
         </is>
       </c>
       <c r="F107" s="70" t="inlineStr">
         <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G107" s="70" t="inlineStr">
         <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H107" s="70" t="n">
-        <v>15</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H107" s="70" t="n"/>
       <c r="I107" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6522,7 +6528,7 @@
       </c>
       <c r="J107" s="70" t="n"/>
     </row>
-    <row r="108" ht="76.5" customHeight="1" s="52">
+    <row r="108" ht="47.5" customHeight="1" s="52">
       <c r="A108" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6533,7 +6539,7 @@
       </c>
       <c r="C108" s="71" t="inlineStr">
         <is>
-          <t>8:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D108" s="74" t="inlineStr">
@@ -6543,22 +6549,20 @@
       </c>
       <c r="E108" s="62" t="inlineStr">
         <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+          <t>ENVIAR cierre a Hastings United</t>
         </is>
       </c>
       <c r="F108" s="70" t="inlineStr">
         <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G108" s="70" t="inlineStr">
         <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H108" s="70" t="n">
-        <v>10</v>
-      </c>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H108" s="70" t="n"/>
       <c r="I108" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6566,7 +6570,7 @@
       </c>
       <c r="J108" s="70" t="n"/>
     </row>
-    <row r="109" ht="30" customHeight="1" s="52">
+    <row r="109" ht="47.5" customHeight="1" s="52">
       <c r="A109" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6577,7 +6581,7 @@
       </c>
       <c r="C109" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D109" s="74" t="inlineStr">
@@ -6587,12 +6591,12 @@
       </c>
       <c r="E109" s="62" t="inlineStr">
         <is>
-          <t>Enviar la tanda 4 de emails</t>
+          <t>ENVIAR cierre a Home Farm FC</t>
         </is>
       </c>
       <c r="F109" s="70" t="inlineStr">
         <is>
-          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G109" s="70" t="inlineStr">
@@ -6600,9 +6604,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H109" s="70" t="n">
-        <v>20</v>
-      </c>
+      <c r="H109" s="70" t="n"/>
       <c r="I109" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6610,7 +6612,7 @@
       </c>
       <c r="J109" s="70" t="n"/>
     </row>
-    <row r="110" ht="134.5" customHeight="1" s="52">
+    <row r="110" ht="47.5" customHeight="1" s="52">
       <c r="A110" s="94" t="n">
         <v>46329</v>
       </c>
@@ -6621,20 +6623,194 @@
       </c>
       <c r="C110" s="71" t="inlineStr">
         <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="D110" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E110" s="62" t="inlineStr">
+        <is>
+          <t>ENVIAR follow-up 2 a Virtu Academy</t>
+        </is>
+      </c>
+      <c r="F110" s="70" t="inlineStr">
+        <is>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
+        </is>
+      </c>
+      <c r="G110" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H110" s="70" t="n"/>
+      <c r="I110" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J110" s="70" t="n"/>
+    </row>
+    <row r="111" ht="62" customHeight="1" s="52">
+      <c r="A111" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B111" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C111" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D111" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E111" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F111" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G111" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H111" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I111" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J111" s="70" t="n"/>
+    </row>
+    <row r="112" ht="76.5" customHeight="1" s="52">
+      <c r="A112" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B112" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C112" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D112" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E112" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F112" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G112" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H112" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I112" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J112" s="70" t="n"/>
+    </row>
+    <row r="113" ht="30" customHeight="1" s="52">
+      <c r="A113" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B113" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C113" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D113" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E113" s="62" t="inlineStr">
+        <is>
+          <t>Enviar la tanda 4 de emails</t>
+        </is>
+      </c>
+      <c r="F113" s="70" t="inlineStr">
+        <is>
+          <t>Mismo proceso. Los textos estarán en la hoja tras tu petición del 26/10.</t>
+        </is>
+      </c>
+      <c r="G113" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H113" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I113" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J113" s="70" t="n"/>
+    </row>
+    <row r="114" ht="134.5" customHeight="1" s="52">
+      <c r="A114" s="94" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B114" s="70" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="C114" s="71" t="inlineStr">
+        <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="D110" s="74" t="inlineStr">
+      <c r="D114" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E110" s="62" t="inlineStr">
+      <c r="E114" s="62" t="inlineStr">
         <is>
           <t>Programar en Apple Mail los envíos del miércoles 04/11</t>
         </is>
       </c>
-      <c r="F110" s="70" t="inlineStr">
+      <c r="F114" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 04/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • Holbeach United | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -6642,194 +6818,22 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
-      <c r="G110" s="70" t="inlineStr">
+      <c r="G114" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H110" s="70" t="n">
+      <c r="H114" s="70" t="n">
         <v>25</v>
       </c>
-      <c r="I110" s="70" t="inlineStr">
+      <c r="I114" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J110" s="70" t="n"/>
-    </row>
-    <row r="111" ht="47.5" customHeight="1" s="52">
-      <c r="A111" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B111" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C111" s="71" t="inlineStr">
-        <is>
-          <t>03:30</t>
-        </is>
-      </c>
-      <c r="D111" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E111" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR cierre a Søreide IL</t>
-        </is>
-      </c>
-      <c r="F111" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G111" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H111" s="70" t="n"/>
-      <c r="I111" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J111" s="70" t="n"/>
-    </row>
-    <row r="112" ht="47.5" customHeight="1" s="52">
-      <c r="A112" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B112" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C112" s="71" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="D112" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E112" s="62" t="inlineStr">
-        <is>
-          <t>ENVIAR cierre a Holbeach United</t>
-        </is>
-      </c>
-      <c r="F112" s="70" t="inlineStr">
-        <is>
-          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
-        </is>
-      </c>
-      <c r="G112" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar</t>
-        </is>
-      </c>
-      <c r="H112" s="70" t="n"/>
-      <c r="I112" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J112" s="70" t="n"/>
-    </row>
-    <row r="113" ht="62" customHeight="1" s="52">
-      <c r="A113" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B113" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C113" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D113" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E113" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F113" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G113" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H113" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I113" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J113" s="70" t="n"/>
-    </row>
-    <row r="114" ht="76.5" customHeight="1" s="52">
-      <c r="A114" s="94" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B114" s="70" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="C114" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D114" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E114" s="62" t="inlineStr">
-        <is>
-          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
-        </is>
-      </c>
-      <c r="F114" s="70" t="inlineStr">
-        <is>
-          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
-        </is>
-      </c>
-      <c r="G114" s="70" t="inlineStr">
-        <is>
-          <t>Outlook buscador / Mail Enviados</t>
-        </is>
-      </c>
-      <c r="H114" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="I114" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
       <c r="J114" s="70" t="n"/>
     </row>
-    <row r="115" ht="91" customHeight="1" s="52">
+    <row r="115" ht="47.5" customHeight="1" s="52">
       <c r="A115" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6840,7 +6844,7 @@
       </c>
       <c r="C115" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="D115" s="74" t="inlineStr">
@@ -6850,12 +6854,12 @@
       </c>
       <c r="E115" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
+          <t>ENVIAR cierre a Søreide IL</t>
         </is>
       </c>
       <c r="F115" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
+          <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G115" s="70" t="inlineStr">
@@ -6863,9 +6867,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H115" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H115" s="70" t="n"/>
       <c r="I115" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6873,7 +6875,7 @@
       </c>
       <c r="J115" s="70" t="n"/>
     </row>
-    <row r="116" ht="76.5" customHeight="1" s="52">
+    <row r="116" ht="47.5" customHeight="1" s="52">
       <c r="A116" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6884,7 +6886,7 @@
       </c>
       <c r="C116" s="71" t="inlineStr">
         <is>
-          <t>Libre</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="D116" s="74" t="inlineStr">
@@ -6894,12 +6896,12 @@
       </c>
       <c r="E116" s="62" t="inlineStr">
         <is>
-          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
+          <t>ENVIAR cierre a Holbeach United</t>
         </is>
       </c>
       <c r="F116" s="70" t="inlineStr">
         <is>
-          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+          <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
       <c r="G116" s="70" t="inlineStr">
@@ -6907,9 +6909,7 @@
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H116" s="70" t="n">
-        <v>5</v>
-      </c>
+      <c r="H116" s="70" t="n"/>
       <c r="I116" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="J116" s="70" t="n"/>
     </row>
-    <row r="117" ht="149" customHeight="1" s="52">
+    <row r="117" ht="62" customHeight="1" s="52">
       <c r="A117" s="94" t="n">
         <v>46330</v>
       </c>
@@ -6928,20 +6928,240 @@
       </c>
       <c r="C117" s="71" t="inlineStr">
         <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D117" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E117" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F117" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G117" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H117" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I117" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J117" s="70" t="n"/>
+    </row>
+    <row r="118" ht="76.5" customHeight="1" s="52">
+      <c r="A118" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B118" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C118" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D118" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E118" s="62" t="inlineStr">
+        <is>
+          <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
+        </is>
+      </c>
+      <c r="F118" s="70" t="inlineStr">
+        <is>
+          <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
+        </is>
+      </c>
+      <c r="G118" s="70" t="inlineStr">
+        <is>
+          <t>Outlook buscador / Mail Enviados</t>
+        </is>
+      </c>
+      <c r="H118" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I118" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J118" s="70" t="n"/>
+    </row>
+    <row r="119" ht="47.5" customHeight="1" s="52">
+      <c r="A119" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B119" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C119" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D119" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E119" s="62" t="inlineStr">
+        <is>
+          <t>Bloque de redes sociales (30 min)</t>
+        </is>
+      </c>
+      <c r="F119" s="70" t="inlineStr">
+        <is>
+          <t>Preparar o programar las publicaciones de la semana. La meta sigue siendo 10.000 seguidores a fin de año; partimos de 2.150. Mide cada semana seguidores nuevos y mensajes de familias o clubes.</t>
+        </is>
+      </c>
+      <c r="G119" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude / sesión de agentes</t>
+        </is>
+      </c>
+      <c r="H119" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J119" s="70" t="n"/>
+    </row>
+    <row r="120" ht="91" customHeight="1" s="52">
+      <c r="A120" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B120" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C120" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D120" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E120" s="62" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Facebook du FC Porte d'Aquitaine (FC Porte d'Aquitaine)</t>
+        </is>
+      </c>
+      <c r="F120" s="70" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Bonjour ! Je suis Joel d'Always Up. Nous emmenons des équipes de jeunes en Espagne pour des semaines d'entraînement (Atlético de Madrid, Real Sociedad). J'ai écrit au club récemment. Qui serait la bonne personne pour parler des déplacements des équipes de jeunes ?»</t>
+        </is>
+      </c>
+      <c r="G120" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H120" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I120" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J120" s="70" t="n"/>
+    </row>
+    <row r="121" ht="76.5" customHeight="1" s="52">
+      <c r="A121" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B121" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C121" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D121" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E121" s="62" t="inlineStr">
+        <is>
+          <t>Opcional: DM a Instagram de Virtu Academy (Virtu Academy)</t>
+        </is>
+      </c>
+      <c r="F121" s="70" t="inlineStr">
+        <is>
+          <t>Solo si el club no ha respondido a nada. A mano desde la cuenta de la red indicada. Solo si no ha contestado al follow-up 2. Sin enlaces. Texto: «Hi! I'm Joel from Always Up. We take youth teams to Spain for training weeks (Atlético de Madrid, Real Sociedad). I emailed the club recently. Who would be the best person to speak to about trips for your youth teams?»</t>
+        </is>
+      </c>
+      <c r="G121" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar</t>
+        </is>
+      </c>
+      <c r="H121" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I121" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J121" s="70" t="n"/>
+    </row>
+    <row r="122" ht="149" customHeight="1" s="52">
+      <c r="A122" s="94" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B122" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C122" s="71" t="inlineStr">
+        <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="D117" s="74" t="inlineStr">
+      <c r="D122" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E117" s="62" t="inlineStr">
+      <c r="E122" s="62" t="inlineStr">
         <is>
           <t>Programar en Apple Mail los envíos del jueves 05/11</t>
         </is>
       </c>
-      <c r="F117" s="70" t="inlineStr">
+      <c r="F122" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 05/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • IA Akranes | Cierre | programar para las 04:30 hora Nueva York (09:30 allí)
@@ -6950,454 +7170,271 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
-      <c r="G117" s="70" t="inlineStr">
+      <c r="G122" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H117" s="70" t="n">
+      <c r="H122" s="70" t="n">
         <v>30</v>
       </c>
-      <c r="I117" s="70" t="inlineStr">
+      <c r="I122" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J117" s="70" t="n"/>
-    </row>
-    <row r="118" ht="47.5" customHeight="1" s="52">
-      <c r="A118" s="94" t="n">
+      <c r="J122" s="70" t="n"/>
+    </row>
+    <row r="123" ht="47.5" customHeight="1" s="52">
+      <c r="A123" s="94" t="n">
         <v>46331</v>
       </c>
-      <c r="B118" s="70" t="inlineStr">
+      <c r="B123" s="70" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C118" s="71" t="inlineStr">
+      <c r="C123" s="71" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="D118" s="74" t="inlineStr">
+      <c r="D123" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E118" s="62" t="inlineStr">
+      <c r="E123" s="62" t="inlineStr">
         <is>
           <t>ENVIAR cierre a IA Akranes</t>
         </is>
       </c>
-      <c r="F118" s="70" t="inlineStr">
+      <c r="F123" s="70" t="inlineStr">
         <is>
           <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
-      <c r="G118" s="70" t="inlineStr">
+      <c r="G123" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H118" s="70" t="n"/>
-      <c r="I118" s="70" t="inlineStr">
+      <c r="H123" s="70" t="n"/>
+      <c r="I123" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J118" s="70" t="n"/>
-    </row>
-    <row r="119" ht="47.5" customHeight="1" s="52">
-      <c r="A119" s="94" t="n">
+      <c r="J123" s="70" t="n"/>
+    </row>
+    <row r="124" ht="47.5" customHeight="1" s="52">
+      <c r="A124" s="94" t="n">
         <v>46331</v>
       </c>
-      <c r="B119" s="70" t="inlineStr">
+      <c r="B124" s="70" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C119" s="71" t="inlineStr">
+      <c r="C124" s="71" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="D119" s="74" t="inlineStr">
+      <c r="D124" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E119" s="62" t="inlineStr">
+      <c r="E124" s="62" t="inlineStr">
         <is>
           <t>ENVIAR cierre a Maidstone United</t>
         </is>
       </c>
-      <c r="F119" s="70" t="inlineStr">
+      <c r="F124" s="70" t="inlineStr">
         <is>
           <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
-      <c r="G119" s="70" t="inlineStr">
+      <c r="G124" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H119" s="70" t="n"/>
-      <c r="I119" s="70" t="inlineStr">
+      <c r="H124" s="70" t="n"/>
+      <c r="I124" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J119" s="70" t="n"/>
-    </row>
-    <row r="120" ht="47.5" customHeight="1" s="52">
-      <c r="A120" s="94" t="n">
+      <c r="J124" s="70" t="n"/>
+    </row>
+    <row r="125" ht="47.5" customHeight="1" s="52">
+      <c r="A125" s="94" t="n">
         <v>46331</v>
       </c>
-      <c r="B120" s="70" t="inlineStr">
+      <c r="B125" s="70" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C120" s="71" t="inlineStr">
+      <c r="C125" s="71" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="D120" s="74" t="inlineStr">
+      <c r="D125" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E120" s="62" t="inlineStr">
+      <c r="E125" s="62" t="inlineStr">
         <is>
           <t>ENVIAR cierre a Whitehaven AFC</t>
         </is>
       </c>
-      <c r="F120" s="70" t="inlineStr">
+      <c r="F125" s="70" t="inlineStr">
         <is>
           <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
-      <c r="G120" s="70" t="inlineStr">
+      <c r="G125" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H120" s="70" t="n"/>
-      <c r="I120" s="70" t="inlineStr">
+      <c r="H125" s="70" t="n"/>
+      <c r="I125" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J120" s="70" t="n"/>
-    </row>
-    <row r="121" ht="62" customHeight="1" s="52">
-      <c r="A121" s="94" t="n">
+      <c r="J125" s="70" t="n"/>
+    </row>
+    <row r="126" ht="62" customHeight="1" s="52">
+      <c r="A126" s="94" t="n">
         <v>46331</v>
       </c>
-      <c r="B121" s="70" t="inlineStr">
+      <c r="B126" s="70" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C121" s="71" t="inlineStr">
+      <c r="C126" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D121" s="72" t="inlineStr">
+      <c r="D126" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E121" s="62" t="inlineStr">
+      <c r="E126" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F121" s="70" t="inlineStr">
+      <c r="F126" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G121" s="70" t="inlineStr">
+      <c r="G126" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H121" s="70" t="n">
+      <c r="H126" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I121" s="70" t="inlineStr">
+      <c r="I126" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J121" s="70" t="n"/>
-    </row>
-    <row r="122" ht="76.5" customHeight="1" s="52">
-      <c r="A122" s="94" t="n">
+      <c r="J126" s="70" t="n"/>
+    </row>
+    <row r="127" ht="76.5" customHeight="1" s="52">
+      <c r="A127" s="94" t="n">
         <v>46331</v>
       </c>
-      <c r="B122" s="70" t="inlineStr">
+      <c r="B127" s="70" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C122" s="71" t="inlineStr">
+      <c r="C127" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D122" s="74" t="inlineStr">
+      <c r="D127" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E122" s="62" t="inlineStr">
+      <c r="E127" s="62" t="inlineStr">
         <is>
           <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
-      <c r="F122" s="70" t="inlineStr">
+      <c r="F127" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
-      <c r="G122" s="70" t="inlineStr">
+      <c r="G127" s="70" t="inlineStr">
         <is>
           <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
-      <c r="H122" s="70" t="n">
+      <c r="H127" s="70" t="n">
         <v>10</v>
       </c>
-      <c r="I122" s="70" t="inlineStr">
+      <c r="I127" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J122" s="70" t="n"/>
-    </row>
-    <row r="123" ht="62" customHeight="1" s="52">
-      <c r="A123" s="94" t="n">
+      <c r="J127" s="70" t="n"/>
+    </row>
+    <row r="128" ht="62" customHeight="1" s="52">
+      <c r="A128" s="94" t="n">
         <v>46332</v>
       </c>
-      <c r="B123" s="70" t="inlineStr">
+      <c r="B128" s="70" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="C123" s="71" t="inlineStr">
+      <c r="C128" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D123" s="72" t="inlineStr">
+      <c r="D128" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E123" s="62" t="inlineStr">
+      <c r="E128" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F123" s="70" t="inlineStr">
+      <c r="F128" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G123" s="70" t="inlineStr">
+      <c r="G128" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H123" s="70" t="n">
+      <c r="H128" s="70" t="n">
         <v>15</v>
-      </c>
-      <c r="I123" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J123" s="70" t="n"/>
-    </row>
-    <row r="124" ht="33" customHeight="1" s="52">
-      <c r="A124" s="94" t="n">
-        <v>46332</v>
-      </c>
-      <c r="B124" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C124" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D124" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E124" s="62" t="inlineStr">
-        <is>
-          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
-        </is>
-      </c>
-      <c r="F124" s="70" t="inlineStr">
-        <is>
-          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
-        </is>
-      </c>
-      <c r="G124" s="70" t="inlineStr">
-        <is>
-          <t>Hoy</t>
-        </is>
-      </c>
-      <c r="H124" s="70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I124" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J124" s="70" t="n"/>
-    </row>
-    <row r="125" ht="33" customHeight="1" s="52">
-      <c r="A125" s="94" t="n">
-        <v>46332</v>
-      </c>
-      <c r="B125" s="70" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="C125" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D125" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E125" s="62" t="inlineStr">
-        <is>
-          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
-        </is>
-      </c>
-      <c r="F125" s="70" t="inlineStr">
-        <is>
-          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
-        </is>
-      </c>
-      <c r="G125" s="70" t="inlineStr">
-        <is>
-          <t>Segmento A, B, C</t>
-        </is>
-      </c>
-      <c r="H125" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I125" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J125" s="70" t="n"/>
-    </row>
-    <row r="126" ht="22" customHeight="1" s="52">
-      <c r="A126" s="68" t="inlineStr">
-        <is>
-          <t>SEMANA  09/11 a 15/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="62" customHeight="1" s="52">
-      <c r="A127" s="94" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B127" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C127" s="71" t="inlineStr">
-        <is>
-          <t>8:00</t>
-        </is>
-      </c>
-      <c r="D127" s="72" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="E127" s="62" t="inlineStr">
-        <is>
-          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
-        </is>
-      </c>
-      <c r="F127" s="70" t="inlineStr">
-        <is>
-          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
-        </is>
-      </c>
-      <c r="G127" s="70" t="inlineStr">
-        <is>
-          <t>Textos para copiar (final de la hoja)</t>
-        </is>
-      </c>
-      <c r="H127" s="70" t="n">
-        <v>15</v>
-      </c>
-      <c r="I127" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="J127" s="70" t="n"/>
-    </row>
-    <row r="128" ht="33" customHeight="1" s="52">
-      <c r="A128" s="94" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B128" s="70" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="C128" s="71" t="inlineStr">
-        <is>
-          <t>Libre</t>
-        </is>
-      </c>
-      <c r="D128" s="74" t="inlineStr">
-        <is>
-          <t>Team/Coach</t>
-        </is>
-      </c>
-      <c r="E128" s="62" t="inlineStr">
-        <is>
-          <t>Pedirme: «investiga 10 clubes más» para la siguiente tanda</t>
-        </is>
-      </c>
-      <c r="F128" s="70" t="inlineStr">
-        <is>
-          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
-        </is>
-      </c>
-      <c r="G128" s="70" t="inlineStr">
-        <is>
-          <t>Chat con Claude</t>
-        </is>
-      </c>
-      <c r="H128" s="70" t="n">
-        <v>5</v>
       </c>
       <c r="I128" s="70" t="inlineStr">
         <is>
@@ -7408,11 +7445,11 @@
     </row>
     <row r="129" ht="33" customHeight="1" s="52">
       <c r="A129" s="94" t="n">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="B129" s="70" t="inlineStr">
         <is>
-          <t>Lunes</t>
+          <t>Viernes</t>
         </is>
       </c>
       <c r="C129" s="71" t="inlineStr">
@@ -7420,24 +7457,24 @@
           <t>Libre</t>
         </is>
       </c>
-      <c r="D129" s="73" t="inlineStr">
-        <is>
-          <t>Becas</t>
+      <c r="D129" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E129" s="62" t="inlineStr">
         <is>
-          <t>Revisar leads de becas con acción vencida</t>
+          <t>Revisión semanal 4: qué asunto y qué mensaje funcionan mejor</t>
         </is>
       </c>
       <c r="F129" s="70" t="inlineStr">
         <is>
-          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+          <t>Con ya 20 o 30 emails enviados se puede empezar a comparar. Pásame respuestas por email para ajustar.</t>
         </is>
       </c>
       <c r="G129" s="70" t="inlineStr">
         <is>
-          <t>Segmento C - Becas</t>
+          <t>Hoy</t>
         </is>
       </c>
       <c r="H129" s="70" t="n">
@@ -7450,75 +7487,302 @@
       </c>
       <c r="J129" s="70" t="n"/>
     </row>
-    <row r="130" ht="62" customHeight="1" s="52">
+    <row r="130" ht="33" customHeight="1" s="52">
       <c r="A130" s="94" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B130" s="70" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="C130" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D130" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E130" s="62" t="inlineStr">
+        <is>
+          <t>Actualizar el CRM con lo que ha pasado esta semana</t>
+        </is>
+      </c>
+      <c r="F130" s="70" t="inlineStr">
+        <is>
+          <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
+        </is>
+      </c>
+      <c r="G130" s="70" t="inlineStr">
+        <is>
+          <t>Segmento A, B, C</t>
+        </is>
+      </c>
+      <c r="H130" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I130" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J130" s="70" t="n"/>
+    </row>
+    <row r="131" ht="47.5" customHeight="1" s="52">
+      <c r="A131" s="94" t="n">
+        <v>46333</v>
+      </c>
+      <c r="B131" s="70" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="C131" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D131" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E131" s="62" t="inlineStr">
+        <is>
+          <t>Bloque de redes sociales (60 min)</t>
+        </is>
+      </c>
+      <c r="F131" s="70" t="inlineStr">
+        <is>
+          <t>Grabar o editar contenido y revisar métricas de las 2 primeras semanas (qué funciona). La meta sigue siendo 10.000 seguidores a fin de año; partimos de 2.150. Mide cada semana seguidores nuevos y mensajes de familias o clubes.</t>
+        </is>
+      </c>
+      <c r="G131" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude / sesión de agentes</t>
+        </is>
+      </c>
+      <c r="H131" s="70" t="n">
+        <v>60</v>
+      </c>
+      <c r="I131" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J131" s="70" t="n"/>
+    </row>
+    <row r="132" ht="22" customHeight="1" s="52">
+      <c r="A132" s="68" t="inlineStr">
+        <is>
+          <t>SEMANA  09/11 a 15/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="62" customHeight="1" s="52">
+      <c r="A133" s="94" t="n">
         <v>46335</v>
       </c>
-      <c r="B130" s="70" t="inlineStr">
+      <c r="B133" s="70" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C130" s="71" t="inlineStr">
+      <c r="C133" s="71" t="inlineStr">
+        <is>
+          <t>8:00</t>
+        </is>
+      </c>
+      <c r="D133" s="72" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E133" s="62" t="inlineStr">
+        <is>
+          <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
+        </is>
+      </c>
+      <c r="F133" s="70" t="inlineStr">
+        <is>
+          <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
+        </is>
+      </c>
+      <c r="G133" s="70" t="inlineStr">
+        <is>
+          <t>Textos para copiar (final de la hoja)</t>
+        </is>
+      </c>
+      <c r="H133" s="70" t="n">
+        <v>15</v>
+      </c>
+      <c r="I133" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J133" s="70" t="n"/>
+    </row>
+    <row r="134" ht="33" customHeight="1" s="52">
+      <c r="A134" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B134" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C134" s="71" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D130" s="72" t="inlineStr">
+      <c r="D134" s="74" t="inlineStr">
+        <is>
+          <t>Team/Coach</t>
+        </is>
+      </c>
+      <c r="E134" s="62" t="inlineStr">
+        <is>
+          <t>Pedirme: «investiga 10 clubes más» (Europa, EEUU o los dos) para la siguiente tanda</t>
+        </is>
+      </c>
+      <c r="F134" s="70" t="inlineStr">
+        <is>
+          <t>Escríbeme esa frase. Yo verifico decisor y email en la web del club y te dejo los correos listos en esta hoja antes del jueves.</t>
+        </is>
+      </c>
+      <c r="G134" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude</t>
+        </is>
+      </c>
+      <c r="H134" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="I134" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J134" s="70" t="n"/>
+    </row>
+    <row r="135" ht="33" customHeight="1" s="52">
+      <c r="A135" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B135" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C135" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D135" s="73" t="inlineStr">
+        <is>
+          <t>Becas</t>
+        </is>
+      </c>
+      <c r="E135" s="62" t="inlineStr">
+        <is>
+          <t>Revisar leads de becas con acción vencida</t>
+        </is>
+      </c>
+      <c r="F135" s="70" t="inlineStr">
+        <is>
+          <t>Pestaña Segmento C - Becas: ordena por 'Próxima acción'. Contesta o actualiza todo lo atrasado. Aplica las 4 preguntas de cualificación.</t>
+        </is>
+      </c>
+      <c r="G135" s="70" t="inlineStr">
+        <is>
+          <t>Segmento C - Becas</t>
+        </is>
+      </c>
+      <c r="H135" s="70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I135" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J135" s="70" t="n"/>
+    </row>
+    <row r="136" ht="62" customHeight="1" s="52">
+      <c r="A136" s="94" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B136" s="70" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="C136" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D136" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E130" s="62" t="inlineStr">
+      <c r="E136" s="62" t="inlineStr">
         <is>
           <t>Revisión del mes con Claude (45 min)</t>
         </is>
       </c>
-      <c r="F130" s="70" t="inlineStr">
+      <c r="F136" s="70" t="inlineStr">
         <is>
           <t>Resultados, qué cambiamos, qué dejamos y plan del segundo mes. Comprobamos si llegamos a la primera venta real. Valoramos también la automatización del envío (objetivo de Joel: cientos de correos a la semana): Google Workspace, herramienta de envíos con calentamiento y qué se puede delegar.</t>
         </is>
       </c>
-      <c r="G130" s="70" t="inlineStr">
+      <c r="G136" s="70" t="inlineStr">
         <is>
           <t>Chat con Claude</t>
         </is>
       </c>
-      <c r="H130" s="70" t="n">
+      <c r="H136" s="70" t="n">
         <v>45</v>
       </c>
-      <c r="I130" s="70" t="inlineStr">
+      <c r="I136" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J130" s="70" t="n"/>
-    </row>
-    <row r="131" ht="134.5" customHeight="1" s="52">
-      <c r="A131" s="94" t="n">
+      <c r="J136" s="70" t="n"/>
+    </row>
+    <row r="137" ht="134.5" customHeight="1" s="52">
+      <c r="A137" s="94" t="n">
         <v>46335</v>
       </c>
-      <c r="B131" s="70" t="inlineStr">
+      <c r="B137" s="70" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C131" s="71" t="inlineStr">
+      <c r="C137" s="71" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="D131" s="74" t="inlineStr">
+      <c r="D137" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E131" s="62" t="inlineStr">
+      <c r="E137" s="62" t="inlineStr">
         <is>
           <t>Programar en Apple Mail los envíos del martes 10/11</t>
         </is>
       </c>
-      <c r="F131" s="70" t="inlineStr">
+      <c r="F137" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: copia Para, Asunto y Texto de la hoja 'Textos para copiar' (filtra por la fecha 10/11). Revisa en 30 segundos: saludo, nombre del club, firma, sin adjuntos. En Mail: flecha junto a Enviar &gt; Enviar más tarde &gt; fecha y hora indicadas.
 • FC Porte d'Aquitaine | Cierre | programar para las 03:30 hora Nueva York (09:30 allí)
@@ -7526,380 +7790,424 @@
 Regla: una vez programado, NO lo envíes a mano (se duplicaría). Si a las 08:00 no aparece enviado, entonces sí.</t>
         </is>
       </c>
-      <c r="G131" s="70" t="inlineStr">
+      <c r="G137" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H131" s="70" t="n">
+      <c r="H137" s="70" t="n">
         <v>25</v>
       </c>
-      <c r="I131" s="70" t="inlineStr">
+      <c r="I137" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J131" s="70" t="n"/>
-    </row>
-    <row r="132" ht="47.5" customHeight="1" s="52">
-      <c r="A132" s="94" t="n">
+      <c r="J137" s="70" t="n"/>
+    </row>
+    <row r="138" ht="47.5" customHeight="1" s="52">
+      <c r="A138" s="94" t="n">
         <v>46336</v>
       </c>
-      <c r="B132" s="70" t="inlineStr">
+      <c r="B138" s="70" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C132" s="71" t="inlineStr">
+      <c r="C138" s="71" t="inlineStr">
         <is>
           <t>03:30</t>
         </is>
       </c>
-      <c r="D132" s="74" t="inlineStr">
+      <c r="D138" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E132" s="62" t="inlineStr">
+      <c r="E138" s="62" t="inlineStr">
         <is>
           <t>ENVIAR cierre a FC Porte d'Aquitaine</t>
         </is>
       </c>
-      <c r="F132" s="70" t="inlineStr">
+      <c r="F138" s="70" t="inlineStr">
         <is>
           <t>Sale a las 03:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
-      <c r="G132" s="70" t="inlineStr">
+      <c r="G138" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H132" s="70" t="n"/>
-      <c r="I132" s="70" t="inlineStr">
+      <c r="H138" s="70" t="n"/>
+      <c r="I138" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J132" s="70" t="n"/>
-    </row>
-    <row r="133" ht="47.5" customHeight="1" s="52">
-      <c r="A133" s="94" t="n">
+      <c r="J138" s="70" t="n"/>
+    </row>
+    <row r="139" ht="47.5" customHeight="1" s="52">
+      <c r="A139" s="94" t="n">
         <v>46336</v>
       </c>
-      <c r="B133" s="70" t="inlineStr">
+      <c r="B139" s="70" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C133" s="71" t="inlineStr">
+      <c r="C139" s="71" t="inlineStr">
         <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="D133" s="74" t="inlineStr">
+      <c r="D139" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E133" s="62" t="inlineStr">
+      <c r="E139" s="62" t="inlineStr">
         <is>
           <t>ENVIAR cierre a Virtu Academy</t>
         </is>
       </c>
-      <c r="F133" s="70" t="inlineStr">
+      <c r="F139" s="70" t="inlineStr">
         <is>
           <t>Sale a las 04:30 hora Nueva York (09:30 allí) si lo programaste la víspera. No hace falta hacer nada a esta hora. Si es follow-up, se envía respondiendo al correo original (búscalo por destinatario en Outlook o Mail y pulsa Responder).</t>
         </is>
       </c>
-      <c r="G133" s="70" t="inlineStr">
+      <c r="G139" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar</t>
         </is>
       </c>
-      <c r="H133" s="70" t="n"/>
-      <c r="I133" s="70" t="inlineStr">
+      <c r="H139" s="70" t="n"/>
+      <c r="I139" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J133" s="70" t="n"/>
-    </row>
-    <row r="134" ht="62" customHeight="1" s="52">
-      <c r="A134" s="94" t="n">
+      <c r="J139" s="70" t="n"/>
+    </row>
+    <row r="140" ht="62" customHeight="1" s="52">
+      <c r="A140" s="94" t="n">
         <v>46336</v>
       </c>
-      <c r="B134" s="70" t="inlineStr">
+      <c r="B140" s="70" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C134" s="71" t="inlineStr">
+      <c r="C140" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D134" s="72" t="inlineStr">
+      <c r="D140" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E134" s="62" t="inlineStr">
+      <c r="E140" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F134" s="70" t="inlineStr">
+      <c r="F140" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G134" s="70" t="inlineStr">
+      <c r="G140" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H134" s="70" t="n">
+      <c r="H140" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I134" s="70" t="inlineStr">
+      <c r="I140" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J134" s="70" t="n"/>
-    </row>
-    <row r="135" ht="76.5" customHeight="1" s="52">
-      <c r="A135" s="94" t="n">
+      <c r="J140" s="70" t="n"/>
+    </row>
+    <row r="141" ht="76.5" customHeight="1" s="52">
+      <c r="A141" s="94" t="n">
         <v>46336</v>
       </c>
-      <c r="B135" s="70" t="inlineStr">
+      <c r="B141" s="70" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="C135" s="71" t="inlineStr">
+      <c r="C141" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D135" s="74" t="inlineStr">
+      <c r="D141" s="74" t="inlineStr">
         <is>
           <t>Team/Coach</t>
         </is>
       </c>
-      <c r="E135" s="62" t="inlineStr">
+      <c r="E141" s="62" t="inlineStr">
         <is>
           <t>Confirmar que salieron los correos de hoy y mirar rebotes</t>
         </is>
       </c>
-      <c r="F135" s="70" t="inlineStr">
+      <c r="F141" s="70" t="inlineStr">
         <is>
           <t>Para cada correo: en Outlook, buscador &gt; escribe el destinatario &gt; 'All folders' (el correo puede estar en 'INBOX.Sent' o 'Sent Messages', no solo en 'Sent'); o en Mail, mira el buzón Enviados. Si aparece: marca Hecho en 'Textos para copiar'. Si NO aparece: envíalo ya a mano. Después mira Recibidos por si hay rebote ('Undeliverable' o 'permanent fatal errors'); si lo hay, anótalo y avísame.</t>
         </is>
       </c>
-      <c r="G135" s="70" t="inlineStr">
+      <c r="G141" s="70" t="inlineStr">
         <is>
           <t>Outlook buscador / Mail Enviados</t>
         </is>
       </c>
-      <c r="H135" s="70" t="n">
+      <c r="H141" s="70" t="n">
         <v>10</v>
       </c>
-      <c r="I135" s="70" t="inlineStr">
+      <c r="I141" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J135" s="70" t="n"/>
-    </row>
-    <row r="136" ht="62" customHeight="1" s="52">
-      <c r="A136" s="94" t="n">
+      <c r="J141" s="70" t="n"/>
+    </row>
+    <row r="142" ht="62" customHeight="1" s="52">
+      <c r="A142" s="94" t="n">
         <v>46337</v>
       </c>
-      <c r="B136" s="70" t="inlineStr">
+      <c r="B142" s="70" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="C136" s="71" t="inlineStr">
+      <c r="C142" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D136" s="72" t="inlineStr">
+      <c r="D142" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E136" s="62" t="inlineStr">
+      <c r="E142" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F136" s="70" t="inlineStr">
+      <c r="F142" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G136" s="70" t="inlineStr">
+      <c r="G142" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H136" s="70" t="n">
+      <c r="H142" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I136" s="70" t="inlineStr">
+      <c r="I142" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J136" s="70" t="n"/>
-    </row>
-    <row r="137" ht="62" customHeight="1" s="52">
-      <c r="A137" s="94" t="n">
+      <c r="J142" s="70" t="n"/>
+    </row>
+    <row r="143" ht="47.5" customHeight="1" s="52">
+      <c r="A143" s="94" t="n">
+        <v>46337</v>
+      </c>
+      <c r="B143" s="70" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="C143" s="71" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="D143" s="75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E143" s="62" t="inlineStr">
+        <is>
+          <t>Bloque de redes sociales (30 min)</t>
+        </is>
+      </c>
+      <c r="F143" s="70" t="inlineStr">
+        <is>
+          <t>Preparar o programar las publicaciones y ajustar el plan según métricas. La meta sigue siendo 10.000 seguidores a fin de año; partimos de 2.150. Mide cada semana seguidores nuevos y mensajes de familias o clubes.</t>
+        </is>
+      </c>
+      <c r="G143" s="70" t="inlineStr">
+        <is>
+          <t>Chat con Claude / sesión de agentes</t>
+        </is>
+      </c>
+      <c r="H143" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="70" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="J143" s="70" t="n"/>
+    </row>
+    <row r="144" ht="62" customHeight="1" s="52">
+      <c r="A144" s="94" t="n">
         <v>46338</v>
       </c>
-      <c r="B137" s="70" t="inlineStr">
+      <c r="B144" s="70" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="C137" s="71" t="inlineStr">
+      <c r="C144" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D137" s="72" t="inlineStr">
+      <c r="D144" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E137" s="62" t="inlineStr">
+      <c r="E144" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F137" s="70" t="inlineStr">
+      <c r="F144" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G137" s="70" t="inlineStr">
+      <c r="G144" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H137" s="70" t="n">
+      <c r="H144" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I137" s="70" t="inlineStr">
+      <c r="I144" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J137" s="70" t="n"/>
-    </row>
-    <row r="138" ht="62" customHeight="1" s="52">
-      <c r="A138" s="94" t="n">
+      <c r="J144" s="70" t="n"/>
+    </row>
+    <row r="145" ht="62" customHeight="1" s="52">
+      <c r="A145" s="94" t="n">
         <v>46339</v>
       </c>
-      <c r="B138" s="70" t="inlineStr">
+      <c r="B145" s="70" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="C138" s="71" t="inlineStr">
+      <c r="C145" s="71" t="inlineStr">
         <is>
           <t>8:00</t>
         </is>
       </c>
-      <c r="D138" s="72" t="inlineStr">
+      <c r="D145" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E138" s="62" t="inlineStr">
+      <c r="E145" s="62" t="inlineStr">
         <is>
           <t>Revisión diaria: bandeja, Instagram, WhatsApp</t>
         </is>
       </c>
-      <c r="F138" s="70" t="inlineStr">
+      <c r="F145" s="70" t="inlineStr">
         <is>
           <t>1) Outlook: mira Recibidos y busca rebotes (correos del sistema que dicen 'Undeliverable' o 'permanent fatal errors'). 2) Instagram y WhatsApp: responde a todo lo que haya entrado, máximo 12 h de espera. 3) Si un club ha contestado: para su cadencia y usa 'Respuestas tipo' en la hoja Textos para copiar.</t>
         </is>
       </c>
-      <c r="G138" s="70" t="inlineStr">
+      <c r="G145" s="70" t="inlineStr">
         <is>
           <t>Textos para copiar (final de la hoja)</t>
         </is>
       </c>
-      <c r="H138" s="70" t="n">
+      <c r="H145" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I138" s="70" t="inlineStr">
+      <c r="I145" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J138" s="70" t="n"/>
-    </row>
-    <row r="139" ht="33" customHeight="1" s="52">
-      <c r="A139" s="94" t="n">
+      <c r="J145" s="70" t="n"/>
+    </row>
+    <row r="146" ht="33" customHeight="1" s="52">
+      <c r="A146" s="94" t="n">
         <v>46339</v>
       </c>
-      <c r="B139" s="70" t="inlineStr">
+      <c r="B146" s="70" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="C139" s="71" t="inlineStr">
+      <c r="C146" s="71" t="inlineStr">
         <is>
           <t>Libre</t>
         </is>
       </c>
-      <c r="D139" s="72" t="inlineStr">
+      <c r="D146" s="72" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E139" s="62" t="inlineStr">
+      <c r="E146" s="62" t="inlineStr">
         <is>
           <t>Actualizar el CRM con lo que ha pasado esta semana</t>
         </is>
       </c>
-      <c r="F139" s="70" t="inlineStr">
+      <c r="F146" s="70" t="inlineStr">
         <is>
           <t>Estado y fecha de último contacto de cada club o lead. Así la hoja Hoy cuenta bien.</t>
         </is>
       </c>
-      <c r="G139" s="70" t="inlineStr">
+      <c r="G146" s="70" t="inlineStr">
         <is>
           <t>Segmento A, B, C</t>
         </is>
       </c>
-      <c r="H139" s="70" t="n">
+      <c r="H146" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="I139" s="70" t="inlineStr">
+      <c r="I146" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="J139" s="70" t="n"/>
+      <c r="J146" s="70" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J139"/>
+  <autoFilter ref="A4:J146"/>
   <mergeCells count="6">
+    <mergeCell ref="A102:J102"/>
     <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A132:J132"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="A64:J64"/>
-    <mergeCell ref="A98:J98"/>
     <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A66:J66"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J139">
+  <conditionalFormatting sqref="A5:J146">
     <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="1">
       <formula>$I5="Hecho"</formula>
     </cfRule>
@@ -7907,13 +8215,13 @@
       <formula>$A5=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I139">
+  <conditionalFormatting sqref="I5:I146">
     <cfRule type="expression" priority="3" dxfId="5">
       <formula>AND(ISNUMBER($A5),$A5&lt;TODAY(),$I5="Pendiente")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I127 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I128 I129 I130 I131 I133 I134 I135 I136 I137 I138 I139 I140 I141 I142 I143 I144 I145 I146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Hecho,Saltado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11667,7 +11975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="52" min="1" max="1"/>
@@ -12029,49 +12337,271 @@
     <row r="13" ht="33" customHeight="1" s="52">
       <c r="A13" s="63" t="inlineStr">
         <is>
+          <t>Seacoast United (EEUU)</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>iscott@seacoastunited.com</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>Director de coaching según directorios de terceros (búsqueda); la web no lo publica en texto</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E13" s="63" t="inlineStr">
+        <is>
+          <t>Pendiente: falta dirección postal de la empresa</t>
+        </is>
+      </c>
+      <c r="F13" s="84" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G13" s="63" t="inlineStr">
+        <is>
+          <t>questions@seacoastunited.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="33" customHeight="1" s="52">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>Cedar Stars Academy (EEUU)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>phil.swenda@cedarstars.com</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>Página de staff de Monmouth (cedarstars.com/monmouth-staff)</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E14" s="63" t="inlineStr">
+        <is>
+          <t>Pendiente: falta dirección postal de la empresa</t>
+        </is>
+      </c>
+      <c r="F14" s="84" t="inlineStr">
+        <is>
+          <t>Media-alta</t>
+        </is>
+      </c>
+      <c r="G14" s="63" t="inlineStr">
+        <is>
+          <t>contactus@cedarstars.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="52">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>IFA New England (EEUU)</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>mhardiman@ifanewengland.com</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>Contacto publicado por el club para consultas de chicos</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E15" s="63" t="inlineStr">
+        <is>
+          <t>Pendiente: falta dirección postal de la empresa</t>
+        </is>
+      </c>
+      <c r="F15" s="84" t="inlineStr">
+        <is>
+          <t>Media-alta</t>
+        </is>
+      </c>
+      <c r="G15" s="63" t="inlineStr">
+        <is>
+          <t>Formulario de ifanewengland.com/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="52">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>Ballistic United (EEUU)</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>jerrylosson@busc.org</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>Página de staff MLS NEXT (busc.org/mls-next/staff)</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E16" s="63" t="inlineStr">
+        <is>
+          <t>Pendiente: falta dirección postal de la empresa</t>
+        </is>
+      </c>
+      <c r="F16" s="84" t="inlineStr">
+        <is>
+          <t>Media-alta</t>
+        </is>
+      </c>
+      <c r="G16" s="63" t="inlineStr">
+        <is>
+          <t>Directorio busc.org/about/directory</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33" customHeight="1" s="52">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>FC Delco (EEUU)</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>info@fcdelco.org</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>Contacto general publicado; Jeff Zaun es Director de MLS NEXT, email personal no encontrado</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E17" s="63" t="inlineStr">
+        <is>
+          <t>Pendiente: falta dirección postal de la empresa</t>
+        </is>
+      </c>
+      <c r="F17" s="84" t="inlineStr">
+        <is>
+          <t>Alta (general)</t>
+        </is>
+      </c>
+      <c r="G17" s="63" t="inlineStr">
+        <is>
+          <t>Formulario de fcdelco.org/administration/contact-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="33" customHeight="1" s="52">
+      <c r="A18" s="63" t="inlineStr">
+        <is>
+          <t>Michigan Jaguars (EEUU)</t>
+        </is>
+      </c>
+      <c r="B18" s="63" t="inlineStr">
+        <is>
+          <t>mo.hijazi@michiganjaguarsfc.com</t>
+        </is>
+      </c>
+      <c r="C18" s="63" t="inlineStr">
+        <is>
+          <t>Página de staff de la sede de Dearborn; el club tiene varias sedes</t>
+        </is>
+      </c>
+      <c r="D18" s="63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E18" s="63" t="inlineStr">
+        <is>
+          <t>Pendiente: falta dirección postal de la empresa</t>
+        </is>
+      </c>
+      <c r="F18" s="84" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G18" s="63" t="inlineStr">
+        <is>
+          <t>michiganjaguarsfc.com/club/staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33" customHeight="1" s="52">
+      <c r="A19" s="63" t="inlineStr">
+        <is>
           <t>FC Porte d'Aquitaine</t>
         </is>
       </c>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t>math.bachowski.mb@gmail.com</t>
         </is>
       </c>
-      <c r="C13" s="63" t="inlineStr">
+      <c r="C19" s="63" t="inlineStr">
         <is>
           <t>Responsable técnico de jóvenes según directorio (búsqueda). Gmail personal.</t>
         </is>
       </c>
-      <c r="D13" s="63" t="inlineStr">
+      <c r="D19" s="63" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="E13" s="63" t="inlineStr">
+      <c r="E19" s="63" t="inlineStr">
         <is>
           <t>Pendiente de enviar</t>
         </is>
       </c>
-      <c r="F13" s="84" t="inlineStr">
+      <c r="F19" s="84" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="G13" s="63" t="inlineStr">
+      <c r="G19" s="63" t="inlineStr">
         <is>
           <t>Email oficial del club en la FFF: 560792@lfna.fr</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" s="52">
-      <c r="A15" s="57" t="inlineStr">
+    <row r="21" ht="32" customHeight="1" s="52">
+      <c r="A21" s="57" t="inlineStr">
         <is>
           <t>Descartados tras investigar (13/10): Morecambe Hawks United (equipo local pequeño, no encaja), Team ALTI (sin datos fiables), Lower Ormond (existe en la lista de Semana Santa pero no encuentro contacto).</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1" s="52">
-      <c r="A16" s="57" t="inlineStr">
+    <row r="22" ht="32" customHeight="1" s="52">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>Excelsior Rotterdam: club profesional con academia (Joep Breimer, jefe de desarrollo de la cantera). Perfil distinto, prioridad baja.</t>
         </is>
@@ -12079,9 +12609,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12587,7 +13117,7 @@
       <c r="N10" s="10" t="n"/>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
+          <t>Investigado 2026-08-29: posible error de nombre en el research original — no gastar más tiempo hasta verificar en la fuente original | 13/10/2026: costadauradacup.com lo lista como club de Inglaterra en la edición de Semana Santa 2026. Existe: falta encontrar su contacto. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable. | 13/10/2026: aparece como club de Inglaterra en la edición de Semana Santa de la Costa Daurada Cup. No encuentro contacto fiable.</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
@@ -13059,7 +13589,7 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
+          <t>Historial real: llamada en abril 2026, Leonardo mandó una presentación (enfocada en becas EEUU, poco encaje con lo que ya cubre el partner de becas), Joel propuso el ángulo real (intercambio Brasil-España de jugadores/equipos), propuso llamada con el padre para junio, luego siguió el 03/07 proponiendo martes — sin respuesta desde entonces (2+ meses). No confundir con un club prospecto normal de Segmento A — esto es más una posible relación de partner/distribución que una venta directa. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta. | 13/10/2026: Joel decide no reactivar: varios intentos y las dos últimas sin respuesta.</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
@@ -13271,7 +13801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="52" min="1" max="1"/>
@@ -13808,6 +14338,408 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Seacoast United</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>EEUU (New Hampshire)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Club MLS NEXT</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Miembro del directorio oficial de MLS NEXT; club independiente (no academia de franquicia MLS)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>mlssoccer.com/mlsnext (lista de Joel) + web del club</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Iain Scott (Director of Coaching)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>iscott@seacoastunited.com</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente investigar</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Falta la dirección postal de Quality Servix Premium SL para poder enviar a EEUU (ley CAN-SPAM). Fecha prevista: 27/10/2026.</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>1er email: nada adjunto, solo texto. Si pide información: deck de empresa + ficha Team Experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Cedar Stars Academy</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>EEUU (Nueva Jersey)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Club MLS NEXT</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Miembro del directorio oficial de MLS NEXT; club independiente (no academia de franquicia MLS)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>mlssoccer.com/mlsnext (lista de Joel) + web del club</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Phil Swenda (Academy Director, Monmouth)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>phil.swenda@cedarstars.com</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente investigar</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Falta la dirección postal de Quality Servix Premium SL para poder enviar a EEUU (ley CAN-SPAM). Fecha prevista: 27/10/2026.</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>1er email: nada adjunto, solo texto. Si pide información: deck de empresa + ficha Team Experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Intercontinental Football Academy of New England</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>EEUU (Massachusetts)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Club MLS NEXT</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Miembro del directorio oficial de MLS NEXT; club independiente (no academia de franquicia MLS)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>mlssoccer.com/mlsnext (lista de Joel) + web del club</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Matt Hardiman (consultas de chicos)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>mhardiman@ifanewengland.com</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente investigar</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Falta la dirección postal de Quality Servix Premium SL para poder enviar a EEUU (ley CAN-SPAM). Fecha prevista: 27/10/2026.</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>1er email: nada adjunto, solo texto. Si pide información: deck de empresa + ficha Team Experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Ballistic United</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>EEUU (California)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Club MLS NEXT</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Miembro del directorio oficial de MLS NEXT; club independiente (no academia de franquicia MLS)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>mlssoccer.com/mlsnext (lista de Joel) + web del club</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Jerry Losson (MLS NEXT Director of Coaching)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>jerrylosson@busc.org</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente investigar</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Falta la dirección postal de Quality Servix Premium SL para poder enviar a EEUU (ley CAN-SPAM). Fecha prevista: 28/10/2026.</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>1er email: nada adjunto, solo texto. Si pide información: deck de empresa + ficha Team Experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>FC Delco</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>EEUU (Pensilvania)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Club MLS NEXT</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Miembro del directorio oficial de MLS NEXT; club independiente (no academia de franquicia MLS)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>mlssoccer.com/mlsnext (lista de Joel) + web del club</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Jeff Zaun (Director de MLS NEXT; email personal sin confirmar)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>info@fcdelco.org</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente investigar</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Falta la dirección postal de Quality Servix Premium SL para poder enviar a EEUU (ley CAN-SPAM). Fecha prevista: 28/10/2026.</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>1er email: nada adjunto, solo texto. Si pide información: deck de empresa + ficha Team Experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Michigan Jaguars FC</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>EEUU (Míchigan)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Club MLS NEXT</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Miembro del directorio oficial de MLS NEXT; club independiente (no academia de franquicia MLS)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>mlssoccer.com/mlsnext (lista de Joel) + web del club</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Mo Hijazi (Director of Coaching, Dearborn; hay varias sedes)</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>mo.hijazi@michiganjaguarsfc.com</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Pendiente investigar</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Falta la dirección postal de Quality Servix Premium SL para poder enviar a EEUU (ley CAN-SPAM). Fecha prevista: 28/10/2026.</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>1er email: nada adjunto, solo texto. Si pide información: deck de empresa + ficha Team Experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <autoFilter ref="A5:O13"/>
   <mergeCells count="3">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -34,12 +34,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="168" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -379,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -629,7 +628,10 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1860,7 +1862,7 @@
           <t>Frío: sin respuesta al follow-up del 13/10 ni al último mensaje del 20/10. Retomar en enero 2027 con el gancho de los plazos de la temporada siguiente. No insistir.</t>
         </is>
       </c>
-      <c r="I12" s="97" t="n">
+      <c r="I12" s="98" t="n">
         <v>46322</v>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -2270,7 +2272,7 @@
           <t>Frío: sin respuesta al mensaje del 21/09 ni al follow-up del 14/10. Retomar en enero 2027 si él escribe. No insistir.</t>
         </is>
       </c>
-      <c r="I20" s="97" t="n">
+      <c r="I20" s="98" t="n">
         <v>46322</v>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -2690,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="47" min="1" max="1"/>
@@ -2911,6 +2913,38 @@
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Pendiente investigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Socio / canal Argentina</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Gonzalo (Argentina): mueve unas 1.000 personas a España en 2027 (jugadores y acompañantes) con red de familias, niños y clubes. Quiere ver opciones y cómo trabajar juntos para 2028.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Reunión con Joel (semana del 19/10/2026)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Propuesta enviada el 27/10 (01-clients/propuestas/Always-Up-Propuesta-Gonzalo-Argentina.pdf). Siguiente: llamada de 30 min esta semana o la próxima y preguntas de descubrimiento (grupos, volumen 2028, presupuesto, cómo viajan hoy). Modelo de colaboración y condiciones: decisión de Joel y Enrique antes de dar números.</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Propuesta preparada</t>
         </is>
       </c>
     </row>

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -2692,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="47" min="1" max="1"/>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Propuesta enviada el 27/10 (01-clients/propuestas/Always-Up-Propuesta-Gonzalo-Argentina.pdf). Siguiente: llamada de 30 min esta semana o la próxima y preguntas de descubrimiento (grupos, volumen 2028, presupuesto, cómo viajan hoy). Modelo de colaboración y condiciones: decisión de Joel y Enrique antes de dar números.</t>
+          <t>Propuesta definitiva (mezcla de Joel y Enrique) lista el 27/10 (01-clients/propuestas/Always-Up-Propuesta-Gonzalo-Argentina-2028.pdf). Siguiente: llamada de 30 min esta semana o la próxima y preguntas de descubrimiento (grupos, volumen 2028, presupuesto, cómo viajan hoy). Modelo de colaboración y condiciones: decisión de Joel y Enrique antes de dar números.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">

--- a/01-clients/crm-ventas.xlsx
+++ b/01-clients/crm-ventas.xlsx
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Gonzalo (Argentina): mueve unas 1.000 personas a España en 2027 (jugadores y acompañantes) con red de familias, niños y clubes. Quiere ver opciones y cómo trabajar juntos para 2028.</t>
+          <t>Gonzalo Lamas (Argentina): mueve unas 1.000 personas a España en 2027 (jugadores y acompañantes) con red de familias, niños y clubes. Quiere ver opciones y cómo trabajar juntos para 2028.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Propuesta definitiva (mezcla de Joel y Enrique) lista el 27/10 (01-clients/propuestas/Always-Up-Propuesta-Gonzalo-Argentina-2028.pdf). Siguiente: llamada de 30 min esta semana o la próxima y preguntas de descubrimiento (grupos, volumen 2028, presupuesto, cómo viajan hoy). Modelo de colaboración y condiciones: decisión de Joel y Enrique antes de dar números.</t>
+          <t>Propuesta definitiva (mezcla de Joel y Enrique) lista el 27/10 (01-clients/propuestas/Always-Up-Propuesta-Gonzalo-Lamas-Argentina-2028.pdf). Siguiente: llamada de 30 min esta semana o la próxima y preguntas de descubrimiento (grupos, volumen 2028, presupuesto, cómo viajan hoy). Modelo de colaboración y condiciones: decisión de Joel y Enrique antes de dar números.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
